--- a/บันทึกผลการดำเนินงาน_RM_2569.xlsx
+++ b/บันทึกผลการดำเนินงาน_RM_2569.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devill/1_กฟน./2569/Dashborad_RM/rm-dashboard-2569/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F21ACC-A5A7-AF43-A99D-87C785DF65BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAA1681-3CAA-354F-8073-00EF01FA4BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="14720" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="บันทึกผล" sheetId="1" r:id="rId1"/>
@@ -2024,13 +2024,13 @@
         <v>100</v>
       </c>
       <c r="S2" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T2" s="7">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U2" s="7">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="V2" s="7">
         <v>33</v>
@@ -2041,12 +2041,24 @@
       <c r="X2" s="7">
         <v>50</v>
       </c>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="7"/>
-      <c r="AC2" s="7"/>
-      <c r="AD2" s="7"/>
+      <c r="Y2" s="7">
+        <v>58</v>
+      </c>
+      <c r="Z2" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA2" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB2" s="7">
+        <v>83</v>
+      </c>
+      <c r="AC2" s="7">
+        <v>92</v>
+      </c>
+      <c r="AD2" s="7">
+        <v>100</v>
+      </c>
       <c r="AE2" s="8" t="s">
         <v>38</v>
       </c>
@@ -2109,13 +2121,13 @@
         <v>100</v>
       </c>
       <c r="S3" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T3" s="7">
         <v>17</v>
       </c>
       <c r="U3" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V3" s="7">
         <v>33</v>
@@ -2124,14 +2136,26 @@
         <v>42</v>
       </c>
       <c r="X3" s="7">
-        <v>47</v>
-      </c>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
-      <c r="AD3" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y3" s="7">
+        <v>58</v>
+      </c>
+      <c r="Z3" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA3" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB3" s="7">
+        <v>83</v>
+      </c>
+      <c r="AC3" s="7">
+        <v>92</v>
+      </c>
+      <c r="AD3" s="7">
+        <v>100</v>
+      </c>
       <c r="AE3" s="8" t="s">
         <v>44</v>
       </c>
@@ -2194,29 +2218,41 @@
         <v>100</v>
       </c>
       <c r="S4" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T4" s="7">
         <v>17</v>
       </c>
       <c r="U4" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V4" s="7">
         <v>33</v>
       </c>
       <c r="W4" s="7">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="X4" s="7">
         <v>50</v>
       </c>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7"/>
-      <c r="AB4" s="7"/>
-      <c r="AC4" s="7"/>
-      <c r="AD4" s="7"/>
+      <c r="Y4" s="7">
+        <v>58</v>
+      </c>
+      <c r="Z4" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA4" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB4" s="7">
+        <v>83</v>
+      </c>
+      <c r="AC4" s="7">
+        <v>92</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>100</v>
+      </c>
       <c r="AE4" s="8" t="s">
         <v>49</v>
       </c>
@@ -2279,17 +2315,29 @@
         <v>33</v>
       </c>
       <c r="W5" s="7">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="X5" s="7">
         <v>100</v>
       </c>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
-      <c r="AC5" s="7"/>
-      <c r="AD5" s="7"/>
+      <c r="Y5" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z5" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA5" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB5" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC5" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD5" s="7">
+        <v>100</v>
+      </c>
       <c r="AE5" s="8" t="s">
         <v>54</v>
       </c>
@@ -2345,12 +2393,24 @@
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
-      <c r="AA6" s="7"/>
-      <c r="AB6" s="7"/>
-      <c r="AC6" s="7"/>
-      <c r="AD6" s="7"/>
+      <c r="Y6" s="7">
+        <v>33</v>
+      </c>
+      <c r="Z6" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA6" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB6" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC6" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD6" s="7">
+        <v>100</v>
+      </c>
       <c r="AE6" s="8"/>
       <c r="AF6" s="8"/>
       <c r="AG6" s="9" t="s">
@@ -2401,9 +2461,15 @@
       <c r="Y7" s="7"/>
       <c r="Z7" s="7"/>
       <c r="AA7" s="7"/>
-      <c r="AB7" s="7"/>
-      <c r="AC7" s="7"/>
-      <c r="AD7" s="7"/>
+      <c r="AB7" s="7">
+        <v>50</v>
+      </c>
+      <c r="AC7" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD7" s="7">
+        <v>100</v>
+      </c>
       <c r="AE7" s="8"/>
       <c r="AF7" s="8"/>
       <c r="AG7" s="9" t="s">
@@ -2454,9 +2520,15 @@
       <c r="Y8" s="7"/>
       <c r="Z8" s="7"/>
       <c r="AA8" s="7"/>
-      <c r="AB8" s="7"/>
-      <c r="AC8" s="7"/>
-      <c r="AD8" s="7"/>
+      <c r="AB8" s="7">
+        <v>33</v>
+      </c>
+      <c r="AC8" s="7">
+        <v>67</v>
+      </c>
+      <c r="AD8" s="7">
+        <v>100</v>
+      </c>
       <c r="AE8" s="8"/>
       <c r="AF8" s="8"/>
       <c r="AG8" s="9" t="s">
@@ -2507,9 +2579,15 @@
       <c r="Y9" s="7"/>
       <c r="Z9" s="7"/>
       <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
-      <c r="AC9" s="7"/>
-      <c r="AD9" s="7"/>
+      <c r="AB9" s="7">
+        <v>33</v>
+      </c>
+      <c r="AC9" s="7">
+        <v>67</v>
+      </c>
+      <c r="AD9" s="7">
+        <v>100</v>
+      </c>
       <c r="AE9" s="8"/>
       <c r="AF9" s="8"/>
       <c r="AG9" s="9" t="s">
@@ -2560,9 +2638,15 @@
       <c r="Y10" s="7"/>
       <c r="Z10" s="7"/>
       <c r="AA10" s="7"/>
-      <c r="AB10" s="7"/>
-      <c r="AC10" s="7"/>
-      <c r="AD10" s="7"/>
+      <c r="AB10" s="7">
+        <v>33</v>
+      </c>
+      <c r="AC10" s="7">
+        <v>67</v>
+      </c>
+      <c r="AD10" s="7">
+        <v>100</v>
+      </c>
       <c r="AE10" s="8"/>
       <c r="AF10" s="8"/>
       <c r="AG10" s="9" t="s">
@@ -2623,29 +2707,41 @@
         <v>100</v>
       </c>
       <c r="S11" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" s="7">
         <v>17</v>
       </c>
       <c r="U11" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V11" s="7">
         <v>33</v>
       </c>
       <c r="W11" s="7">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="X11" s="7">
-        <v>47</v>
-      </c>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
-      <c r="AB11" s="7"/>
-      <c r="AC11" s="7"/>
-      <c r="AD11" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y11" s="7">
+        <v>58</v>
+      </c>
+      <c r="Z11" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA11" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB11" s="7">
+        <v>83</v>
+      </c>
+      <c r="AC11" s="7">
+        <v>92</v>
+      </c>
+      <c r="AD11" s="7">
+        <v>100</v>
+      </c>
       <c r="AE11" s="8" t="s">
         <v>77</v>
       </c>
@@ -2705,20 +2801,32 @@
       <c r="T12" s="7"/>
       <c r="U12" s="7"/>
       <c r="V12" s="7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W12" s="7">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="X12" s="7">
         <v>50</v>
       </c>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
-      <c r="AB12" s="7"/>
-      <c r="AC12" s="7"/>
-      <c r="AD12" s="7"/>
+      <c r="Y12" s="7">
+        <v>67</v>
+      </c>
+      <c r="Z12" s="7">
+        <v>83</v>
+      </c>
+      <c r="AA12" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB12" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC12" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD12" s="7">
+        <v>100</v>
+      </c>
       <c r="AE12" s="8" t="s">
         <v>82</v>
       </c>
@@ -2774,12 +2882,24 @@
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="7"/>
-      <c r="AB13" s="7"/>
-      <c r="AC13" s="7"/>
-      <c r="AD13" s="7"/>
+      <c r="Y13" s="7">
+        <v>33</v>
+      </c>
+      <c r="Z13" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA13" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB13" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC13" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD13" s="7">
+        <v>100</v>
+      </c>
       <c r="AE13" s="8"/>
       <c r="AF13" s="8"/>
       <c r="AG13" s="9" t="s">
@@ -2840,29 +2960,41 @@
         <v>100</v>
       </c>
       <c r="S14" s="7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T14" s="7">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U14" s="7">
         <v>25</v>
       </c>
       <c r="V14" s="7">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="W14" s="7">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X14" s="7">
         <v>50</v>
       </c>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
-      <c r="AA14" s="7"/>
-      <c r="AB14" s="7"/>
-      <c r="AC14" s="7"/>
-      <c r="AD14" s="7"/>
+      <c r="Y14" s="7">
+        <v>58</v>
+      </c>
+      <c r="Z14" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA14" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB14" s="7">
+        <v>83</v>
+      </c>
+      <c r="AC14" s="7">
+        <v>92</v>
+      </c>
+      <c r="AD14" s="7">
+        <v>100</v>
+      </c>
       <c r="AE14" s="8" t="s">
         <v>91</v>
       </c>
@@ -2931,23 +3063,35 @@
         <v>17</v>
       </c>
       <c r="U15" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V15" s="7">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="W15" s="7">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="X15" s="7">
-        <v>54</v>
-      </c>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="7"/>
-      <c r="AC15" s="7"/>
-      <c r="AD15" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y15" s="7">
+        <v>58</v>
+      </c>
+      <c r="Z15" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA15" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB15" s="7">
+        <v>83</v>
+      </c>
+      <c r="AC15" s="7">
+        <v>92</v>
+      </c>
+      <c r="AD15" s="7">
+        <v>100</v>
+      </c>
       <c r="AE15" s="8" t="s">
         <v>96</v>
       </c>
@@ -3010,29 +3154,41 @@
         <v>100</v>
       </c>
       <c r="S16" s="7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T16" s="7">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="U16" s="7">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="V16" s="7">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="W16" s="7">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="X16" s="7">
         <v>100</v>
       </c>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
-      <c r="AA16" s="7"/>
-      <c r="AB16" s="7"/>
-      <c r="AC16" s="7"/>
-      <c r="AD16" s="7"/>
+      <c r="Y16" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z16" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA16" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB16" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC16" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD16" s="7">
+        <v>100</v>
+      </c>
       <c r="AE16" s="8" t="s">
         <v>101</v>
       </c>
@@ -3088,12 +3244,24 @@
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="7"/>
-      <c r="AA17" s="7"/>
-      <c r="AB17" s="7"/>
-      <c r="AC17" s="7"/>
-      <c r="AD17" s="7"/>
+      <c r="Y17" s="7">
+        <v>17</v>
+      </c>
+      <c r="Z17" s="7">
+        <v>33</v>
+      </c>
+      <c r="AA17" s="7">
+        <v>50</v>
+      </c>
+      <c r="AB17" s="7">
+        <v>67</v>
+      </c>
+      <c r="AC17" s="7">
+        <v>83</v>
+      </c>
+      <c r="AD17" s="7">
+        <v>100</v>
+      </c>
       <c r="AE17" s="8"/>
       <c r="AF17" s="8"/>
       <c r="AG17" s="9" t="s">
@@ -3149,12 +3317,24 @@
       <c r="V18" s="7"/>
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="7"/>
-      <c r="AD18" s="7"/>
+      <c r="Y18" s="7">
+        <v>50</v>
+      </c>
+      <c r="Z18" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA18" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB18" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC18" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD18" s="7">
+        <v>100</v>
+      </c>
       <c r="AE18" s="8"/>
       <c r="AF18" s="8"/>
       <c r="AG18" s="9" t="s">
@@ -3209,11 +3389,21 @@
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
-      <c r="Z19" s="7"/>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="7"/>
-      <c r="AC19" s="7"/>
-      <c r="AD19" s="7"/>
+      <c r="Z19" s="7">
+        <v>50</v>
+      </c>
+      <c r="AA19" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB19" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC19" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD19" s="7">
+        <v>100</v>
+      </c>
       <c r="AE19" s="8"/>
       <c r="AF19" s="8"/>
       <c r="AG19" s="9" t="s">
@@ -3266,9 +3456,15 @@
       <c r="Y20" s="7"/>
       <c r="Z20" s="7"/>
       <c r="AA20" s="7"/>
-      <c r="AB20" s="7"/>
-      <c r="AC20" s="7"/>
-      <c r="AD20" s="7"/>
+      <c r="AB20" s="7">
+        <v>33</v>
+      </c>
+      <c r="AC20" s="7">
+        <v>67</v>
+      </c>
+      <c r="AD20" s="7">
+        <v>100</v>
+      </c>
       <c r="AE20" s="8"/>
       <c r="AF20" s="8"/>
       <c r="AG20" s="9" t="s">
@@ -3320,8 +3516,12 @@
       <c r="Z21" s="7"/>
       <c r="AA21" s="7"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="7"/>
-      <c r="AD21" s="7"/>
+      <c r="AC21" s="7">
+        <v>50</v>
+      </c>
+      <c r="AD21" s="7">
+        <v>100</v>
+      </c>
       <c r="AE21" s="8"/>
       <c r="AF21" s="8"/>
       <c r="AG21" s="9" t="s">
@@ -3372,7 +3572,9 @@
       <c r="AA22" s="7"/>
       <c r="AB22" s="7"/>
       <c r="AC22" s="7"/>
-      <c r="AD22" s="7"/>
+      <c r="AD22" s="7">
+        <v>100</v>
+      </c>
       <c r="AE22" s="8"/>
       <c r="AF22" s="8"/>
       <c r="AG22" s="9" t="s">
@@ -3431,17 +3633,29 @@
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
       <c r="W23" s="7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="X23" s="7">
         <v>40</v>
       </c>
-      <c r="Y23" s="7"/>
-      <c r="Z23" s="7"/>
-      <c r="AA23" s="7"/>
-      <c r="AB23" s="7"/>
-      <c r="AC23" s="7"/>
-      <c r="AD23" s="7"/>
+      <c r="Y23" s="7">
+        <v>60</v>
+      </c>
+      <c r="Z23" s="7">
+        <v>80</v>
+      </c>
+      <c r="AA23" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB23" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC23" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD23" s="7">
+        <v>100</v>
+      </c>
       <c r="AE23" s="8" t="s">
         <v>122</v>
       </c>
@@ -3496,9 +3710,15 @@
       <c r="Y24" s="7"/>
       <c r="Z24" s="7"/>
       <c r="AA24" s="7"/>
-      <c r="AB24" s="7"/>
-      <c r="AC24" s="7"/>
-      <c r="AD24" s="7"/>
+      <c r="AB24" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC24" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD24" s="7">
+        <v>100</v>
+      </c>
       <c r="AE24" s="8"/>
       <c r="AF24" s="8"/>
       <c r="AG24" s="9" t="s">
@@ -3550,8 +3770,12 @@
       <c r="Z25" s="7"/>
       <c r="AA25" s="7"/>
       <c r="AB25" s="7"/>
-      <c r="AC25" s="7"/>
-      <c r="AD25" s="7"/>
+      <c r="AC25" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD25" s="7">
+        <v>100</v>
+      </c>
       <c r="AE25" s="8"/>
       <c r="AF25" s="8"/>
       <c r="AG25" s="9" t="s">
@@ -3602,7 +3826,9 @@
       <c r="AA26" s="7"/>
       <c r="AB26" s="7"/>
       <c r="AC26" s="7"/>
-      <c r="AD26" s="7"/>
+      <c r="AD26" s="7">
+        <v>100</v>
+      </c>
       <c r="AE26" s="8"/>
       <c r="AF26" s="8"/>
       <c r="AG26" s="9" t="s">
@@ -3660,14 +3886,26 @@
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7">
-        <v>18</v>
-      </c>
-      <c r="Y27" s="7"/>
-      <c r="Z27" s="7"/>
-      <c r="AA27" s="7"/>
-      <c r="AB27" s="7"/>
-      <c r="AC27" s="7"/>
-      <c r="AD27" s="7"/>
+        <v>33</v>
+      </c>
+      <c r="Y27" s="7">
+        <v>67</v>
+      </c>
+      <c r="Z27" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA27" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB27" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC27" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD27" s="7">
+        <v>100</v>
+      </c>
       <c r="AE27" s="8" t="s">
         <v>130</v>
       </c>
@@ -3726,11 +3964,21 @@
       <c r="W28" s="7"/>
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
-      <c r="Z28" s="7"/>
-      <c r="AA28" s="7"/>
-      <c r="AB28" s="7"/>
-      <c r="AC28" s="7"/>
-      <c r="AD28" s="7"/>
+      <c r="Z28" s="7">
+        <v>50</v>
+      </c>
+      <c r="AA28" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB28" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC28" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD28" s="7">
+        <v>100</v>
+      </c>
       <c r="AE28" s="8"/>
       <c r="AF28" s="8"/>
       <c r="AG28" s="9" t="s">
@@ -3783,9 +4031,15 @@
       <c r="Y29" s="7"/>
       <c r="Z29" s="7"/>
       <c r="AA29" s="7"/>
-      <c r="AB29" s="7"/>
-      <c r="AC29" s="7"/>
-      <c r="AD29" s="7"/>
+      <c r="AB29" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC29" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD29" s="7">
+        <v>100</v>
+      </c>
       <c r="AE29" s="8"/>
       <c r="AF29" s="8"/>
       <c r="AG29" s="9" t="s">
@@ -3837,8 +4091,12 @@
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
       <c r="AB30" s="7"/>
-      <c r="AC30" s="7"/>
-      <c r="AD30" s="7"/>
+      <c r="AC30" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD30" s="7">
+        <v>100</v>
+      </c>
       <c r="AE30" s="8"/>
       <c r="AF30" s="8"/>
       <c r="AG30" s="9" t="s">
@@ -3889,7 +4147,9 @@
       <c r="AA31" s="7"/>
       <c r="AB31" s="7"/>
       <c r="AC31" s="7"/>
-      <c r="AD31" s="7"/>
+      <c r="AD31" s="7">
+        <v>100</v>
+      </c>
       <c r="AE31" s="8"/>
       <c r="AF31" s="8"/>
       <c r="AG31" s="9" t="s">
@@ -3952,16 +4212,16 @@
         <v>100</v>
       </c>
       <c r="S32" s="7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T32" s="7">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="U32" s="7">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="V32" s="7">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="W32" s="7">
         <v>83</v>
@@ -3969,12 +4229,24 @@
       <c r="X32" s="7">
         <v>100</v>
       </c>
-      <c r="Y32" s="7"/>
-      <c r="Z32" s="7"/>
-      <c r="AA32" s="7"/>
-      <c r="AB32" s="7"/>
-      <c r="AC32" s="7"/>
-      <c r="AD32" s="7"/>
+      <c r="Y32" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z32" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA32" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB32" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC32" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD32" s="7">
+        <v>100</v>
+      </c>
       <c r="AE32" s="8" t="s">
         <v>142</v>
       </c>
@@ -4039,10 +4311,10 @@
         <v>100</v>
       </c>
       <c r="S33" s="7">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="T33" s="7">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="U33" s="7">
         <v>100</v>
@@ -4056,12 +4328,24 @@
       <c r="X33" s="7">
         <v>100</v>
       </c>
-      <c r="Y33" s="7"/>
-      <c r="Z33" s="7"/>
-      <c r="AA33" s="7"/>
-      <c r="AB33" s="7"/>
-      <c r="AC33" s="7"/>
-      <c r="AD33" s="7"/>
+      <c r="Y33" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z33" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA33" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB33" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC33" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD33" s="7">
+        <v>100</v>
+      </c>
       <c r="AE33" s="8" t="s">
         <v>146</v>
       </c>
@@ -4131,12 +4415,24 @@
       <c r="X34" s="7">
         <v>100</v>
       </c>
-      <c r="Y34" s="7"/>
-      <c r="Z34" s="7"/>
-      <c r="AA34" s="7"/>
-      <c r="AB34" s="7"/>
-      <c r="AC34" s="7"/>
-      <c r="AD34" s="7"/>
+      <c r="Y34" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z34" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA34" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB34" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC34" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD34" s="7">
+        <v>100</v>
+      </c>
       <c r="AE34" s="8" t="s">
         <v>149</v>
       </c>
@@ -4201,16 +4497,16 @@
         <v>100</v>
       </c>
       <c r="S35" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T35" s="7">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="U35" s="7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="V35" s="7">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="W35" s="7">
         <v>42</v>
@@ -4218,12 +4514,24 @@
       <c r="X35" s="7">
         <v>50</v>
       </c>
-      <c r="Y35" s="7"/>
-      <c r="Z35" s="7"/>
-      <c r="AA35" s="7"/>
-      <c r="AB35" s="7"/>
-      <c r="AC35" s="7"/>
-      <c r="AD35" s="7"/>
+      <c r="Y35" s="7">
+        <v>58</v>
+      </c>
+      <c r="Z35" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA35" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB35" s="7">
+        <v>83</v>
+      </c>
+      <c r="AC35" s="7">
+        <v>92</v>
+      </c>
+      <c r="AD35" s="7">
+        <v>100</v>
+      </c>
       <c r="AE35" s="8" t="s">
         <v>153</v>
       </c>
@@ -4279,10 +4587,18 @@
       <c r="X36" s="7"/>
       <c r="Y36" s="7"/>
       <c r="Z36" s="7"/>
-      <c r="AA36" s="7"/>
-      <c r="AB36" s="7"/>
-      <c r="AC36" s="7"/>
-      <c r="AD36" s="7"/>
+      <c r="AA36" s="7">
+        <v>50</v>
+      </c>
+      <c r="AB36" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC36" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD36" s="7">
+        <v>100</v>
+      </c>
       <c r="AE36" s="8"/>
       <c r="AF36" s="8"/>
       <c r="AG36" s="9" t="s">
@@ -4335,9 +4651,15 @@
       <c r="Y37" s="7"/>
       <c r="Z37" s="7"/>
       <c r="AA37" s="7"/>
-      <c r="AB37" s="7"/>
-      <c r="AC37" s="7"/>
-      <c r="AD37" s="7"/>
+      <c r="AB37" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC37" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD37" s="7">
+        <v>100</v>
+      </c>
       <c r="AE37" s="8"/>
       <c r="AF37" s="8"/>
       <c r="AG37" s="9" t="s">
@@ -4397,20 +4719,32 @@
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
       <c r="V38" s="7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W38" s="7">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="X38" s="7">
         <v>43</v>
       </c>
-      <c r="Y38" s="7"/>
-      <c r="Z38" s="7"/>
-      <c r="AA38" s="7"/>
-      <c r="AB38" s="7"/>
-      <c r="AC38" s="7"/>
-      <c r="AD38" s="7"/>
+      <c r="Y38" s="7">
+        <v>57</v>
+      </c>
+      <c r="Z38" s="7">
+        <v>71</v>
+      </c>
+      <c r="AA38" s="7">
+        <v>86</v>
+      </c>
+      <c r="AB38" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC38" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD38" s="7">
+        <v>100</v>
+      </c>
       <c r="AE38" s="8" t="s">
         <v>160</v>
       </c>
@@ -4464,8 +4798,12 @@
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
       <c r="AB39" s="7"/>
-      <c r="AC39" s="7"/>
-      <c r="AD39" s="7"/>
+      <c r="AC39" s="7">
+        <v>50</v>
+      </c>
+      <c r="AD39" s="7">
+        <v>100</v>
+      </c>
       <c r="AE39" s="8"/>
       <c r="AF39" s="8"/>
       <c r="AG39" s="9" t="s">
@@ -4517,8 +4855,12 @@
       <c r="Z40" s="7"/>
       <c r="AA40" s="7"/>
       <c r="AB40" s="7"/>
-      <c r="AC40" s="7"/>
-      <c r="AD40" s="7"/>
+      <c r="AC40" s="7">
+        <v>50</v>
+      </c>
+      <c r="AD40" s="7">
+        <v>100</v>
+      </c>
       <c r="AE40" s="8"/>
       <c r="AF40" s="8"/>
       <c r="AG40" s="9" t="s">
@@ -4583,23 +4925,35 @@
         <v>33</v>
       </c>
       <c r="U41" s="7">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="V41" s="7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="W41" s="7">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="X41" s="7">
-        <v>97</v>
-      </c>
-      <c r="Y41" s="7"/>
-      <c r="Z41" s="7"/>
-      <c r="AA41" s="7"/>
-      <c r="AB41" s="7"/>
-      <c r="AC41" s="7"/>
-      <c r="AD41" s="7"/>
+        <v>100</v>
+      </c>
+      <c r="Y41" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z41" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA41" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB41" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC41" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD41" s="7">
+        <v>100</v>
+      </c>
       <c r="AE41" s="8" t="s">
         <v>168</v>
       </c>
@@ -4664,7 +5018,7 @@
         <v>100</v>
       </c>
       <c r="S42" s="7">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="T42" s="7">
         <v>100</v>
@@ -4681,12 +5035,24 @@
       <c r="X42" s="7">
         <v>100</v>
       </c>
-      <c r="Y42" s="7"/>
-      <c r="Z42" s="7"/>
-      <c r="AA42" s="7"/>
-      <c r="AB42" s="7"/>
-      <c r="AC42" s="7"/>
-      <c r="AD42" s="7"/>
+      <c r="Y42" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z42" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA42" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB42" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC42" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD42" s="7">
+        <v>100</v>
+      </c>
       <c r="AE42" s="8" t="s">
         <v>171</v>
       </c>
@@ -4751,7 +5117,7 @@
         <v>100</v>
       </c>
       <c r="S43" s="7">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T43" s="7">
         <v>100</v>
@@ -4768,12 +5134,24 @@
       <c r="X43" s="7">
         <v>100</v>
       </c>
-      <c r="Y43" s="7"/>
-      <c r="Z43" s="7"/>
-      <c r="AA43" s="7"/>
-      <c r="AB43" s="7"/>
-      <c r="AC43" s="7"/>
-      <c r="AD43" s="7"/>
+      <c r="Y43" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z43" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA43" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB43" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC43" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD43" s="7">
+        <v>100</v>
+      </c>
       <c r="AE43" s="8" t="s">
         <v>174</v>
       </c>
@@ -4837,26 +5215,38 @@
       </c>
       <c r="S44" s="7"/>
       <c r="T44" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U44" s="7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V44" s="7">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="W44" s="7">
         <v>36</v>
       </c>
       <c r="X44" s="7">
-        <v>50</v>
-      </c>
-      <c r="Y44" s="7"/>
-      <c r="Z44" s="7"/>
-      <c r="AA44" s="7"/>
-      <c r="AB44" s="7"/>
-      <c r="AC44" s="7"/>
-      <c r="AD44" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="Y44" s="7">
+        <v>55</v>
+      </c>
+      <c r="Z44" s="7">
+        <v>64</v>
+      </c>
+      <c r="AA44" s="7">
+        <v>73</v>
+      </c>
+      <c r="AB44" s="7">
+        <v>82</v>
+      </c>
+      <c r="AC44" s="7">
+        <v>91</v>
+      </c>
+      <c r="AD44" s="7">
+        <v>100</v>
+      </c>
       <c r="AE44" s="8" t="s">
         <v>177</v>
       </c>
@@ -4914,12 +5304,24 @@
       <c r="V45" s="7"/>
       <c r="W45" s="7"/>
       <c r="X45" s="7"/>
-      <c r="Y45" s="7"/>
-      <c r="Z45" s="7"/>
-      <c r="AA45" s="7"/>
-      <c r="AB45" s="7"/>
-      <c r="AC45" s="7"/>
-      <c r="AD45" s="7"/>
+      <c r="Y45" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z45" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA45" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB45" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC45" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD45" s="7">
+        <v>100</v>
+      </c>
       <c r="AE45" s="8"/>
       <c r="AF45" s="8"/>
       <c r="AG45" s="9" t="s">
@@ -4974,11 +5376,21 @@
       <c r="W46" s="7"/>
       <c r="X46" s="7"/>
       <c r="Y46" s="7"/>
-      <c r="Z46" s="7"/>
-      <c r="AA46" s="7"/>
-      <c r="AB46" s="7"/>
-      <c r="AC46" s="7"/>
-      <c r="AD46" s="7"/>
+      <c r="Z46" s="7">
+        <v>50</v>
+      </c>
+      <c r="AA46" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB46" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC46" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD46" s="7">
+        <v>100</v>
+      </c>
       <c r="AE46" s="8"/>
       <c r="AF46" s="8"/>
       <c r="AG46" s="9" t="s">
@@ -5032,10 +5444,18 @@
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="7"/>
-      <c r="AA47" s="7"/>
-      <c r="AB47" s="7"/>
-      <c r="AC47" s="7"/>
-      <c r="AD47" s="7"/>
+      <c r="AA47" s="7">
+        <v>50</v>
+      </c>
+      <c r="AB47" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC47" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD47" s="7">
+        <v>100</v>
+      </c>
       <c r="AE47" s="8"/>
       <c r="AF47" s="8"/>
       <c r="AG47" s="9" t="s">
@@ -5087,8 +5507,12 @@
       <c r="Z48" s="7"/>
       <c r="AA48" s="7"/>
       <c r="AB48" s="7"/>
-      <c r="AC48" s="7"/>
-      <c r="AD48" s="7"/>
+      <c r="AC48" s="7">
+        <v>50</v>
+      </c>
+      <c r="AD48" s="7">
+        <v>100</v>
+      </c>
       <c r="AE48" s="8"/>
       <c r="AF48" s="8"/>
       <c r="AG48" s="9" t="s">
@@ -5151,13 +5575,13 @@
         <v>100</v>
       </c>
       <c r="S49" s="7">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T49" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="U49" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="V49" s="7">
         <v>100</v>
@@ -5168,12 +5592,24 @@
       <c r="X49" s="7">
         <v>100</v>
       </c>
-      <c r="Y49" s="7"/>
-      <c r="Z49" s="7"/>
-      <c r="AA49" s="7"/>
-      <c r="AB49" s="7"/>
-      <c r="AC49" s="7"/>
-      <c r="AD49" s="7"/>
+      <c r="Y49" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z49" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA49" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB49" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC49" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD49" s="7">
+        <v>100</v>
+      </c>
       <c r="AE49" s="8" t="s">
         <v>190</v>
       </c>
@@ -5237,26 +5673,38 @@
       </c>
       <c r="S50" s="7"/>
       <c r="T50" s="7">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="U50" s="7">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V50" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="W50" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="X50" s="7">
         <v>100</v>
       </c>
-      <c r="Y50" s="7"/>
-      <c r="Z50" s="7"/>
-      <c r="AA50" s="7"/>
-      <c r="AB50" s="7"/>
-      <c r="AC50" s="7"/>
-      <c r="AD50" s="7"/>
+      <c r="Y50" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z50" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA50" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB50" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC50" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD50" s="7">
+        <v>100</v>
+      </c>
       <c r="AE50" s="8" t="s">
         <v>193</v>
       </c>
@@ -5326,12 +5774,24 @@
       <c r="X51" s="7">
         <v>100</v>
       </c>
-      <c r="Y51" s="7"/>
-      <c r="Z51" s="7"/>
-      <c r="AA51" s="7"/>
-      <c r="AB51" s="7"/>
-      <c r="AC51" s="7"/>
-      <c r="AD51" s="7"/>
+      <c r="Y51" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z51" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA51" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB51" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC51" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD51" s="7">
+        <v>100</v>
+      </c>
       <c r="AE51" s="8" t="s">
         <v>196</v>
       </c>
@@ -5392,17 +5852,29 @@
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
       <c r="W52" s="7">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="X52" s="7">
-        <v>94</v>
-      </c>
-      <c r="Y52" s="7"/>
-      <c r="Z52" s="7"/>
-      <c r="AA52" s="7"/>
-      <c r="AB52" s="7"/>
-      <c r="AC52" s="7"/>
-      <c r="AD52" s="7"/>
+        <v>100</v>
+      </c>
+      <c r="Y52" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z52" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA52" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB52" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC52" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD52" s="7">
+        <v>100</v>
+      </c>
       <c r="AE52" s="8" t="s">
         <v>198</v>
       </c>
@@ -5470,7 +5942,7 @@
         <v>33</v>
       </c>
       <c r="T53" s="7">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="U53" s="7">
         <v>100</v>
@@ -5484,12 +5956,24 @@
       <c r="X53" s="7">
         <v>100</v>
       </c>
-      <c r="Y53" s="7"/>
-      <c r="Z53" s="7"/>
-      <c r="AA53" s="7"/>
-      <c r="AB53" s="7"/>
-      <c r="AC53" s="7"/>
-      <c r="AD53" s="7"/>
+      <c r="Y53" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z53" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA53" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB53" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC53" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD53" s="7">
+        <v>100</v>
+      </c>
       <c r="AE53" s="8" t="s">
         <v>203</v>
       </c>
@@ -5552,10 +6036,10 @@
       <c r="S54" s="7"/>
       <c r="T54" s="7"/>
       <c r="U54" s="7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="V54" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="W54" s="7">
         <v>100</v>
@@ -5563,12 +6047,24 @@
       <c r="X54" s="7">
         <v>100</v>
       </c>
-      <c r="Y54" s="7"/>
-      <c r="Z54" s="7"/>
-      <c r="AA54" s="7"/>
-      <c r="AB54" s="7"/>
-      <c r="AC54" s="7"/>
-      <c r="AD54" s="7"/>
+      <c r="Y54" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z54" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA54" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB54" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC54" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD54" s="7">
+        <v>100</v>
+      </c>
       <c r="AE54" s="8" t="s">
         <v>206</v>
       </c>
@@ -5630,20 +6126,32 @@
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
       <c r="V55" s="7">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="W55" s="7">
         <v>29</v>
       </c>
       <c r="X55" s="7">
-        <v>29</v>
-      </c>
-      <c r="Y55" s="7"/>
-      <c r="Z55" s="7"/>
-      <c r="AA55" s="7"/>
-      <c r="AB55" s="7"/>
-      <c r="AC55" s="7"/>
-      <c r="AD55" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="Y55" s="7">
+        <v>57</v>
+      </c>
+      <c r="Z55" s="7">
+        <v>71</v>
+      </c>
+      <c r="AA55" s="7">
+        <v>86</v>
+      </c>
+      <c r="AB55" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC55" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD55" s="7">
+        <v>100</v>
+      </c>
       <c r="AE55" s="8" t="s">
         <v>209</v>
       </c>
@@ -5698,9 +6206,15 @@
       <c r="Y56" s="7"/>
       <c r="Z56" s="7"/>
       <c r="AA56" s="7"/>
-      <c r="AB56" s="7"/>
-      <c r="AC56" s="7"/>
-      <c r="AD56" s="7"/>
+      <c r="AB56" s="7">
+        <v>50</v>
+      </c>
+      <c r="AC56" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD56" s="7">
+        <v>100</v>
+      </c>
       <c r="AE56" s="8"/>
       <c r="AF56" s="8"/>
       <c r="AG56" s="9" t="s">
@@ -5752,8 +6266,12 @@
       <c r="Z57" s="7"/>
       <c r="AA57" s="7"/>
       <c r="AB57" s="7"/>
-      <c r="AC57" s="7"/>
-      <c r="AD57" s="7"/>
+      <c r="AC57" s="7">
+        <v>50</v>
+      </c>
+      <c r="AD57" s="7">
+        <v>100</v>
+      </c>
       <c r="AE57" s="8"/>
       <c r="AF57" s="8"/>
       <c r="AG57" s="9" t="s">
@@ -5804,7 +6322,9 @@
       <c r="AA58" s="7"/>
       <c r="AB58" s="7"/>
       <c r="AC58" s="7"/>
-      <c r="AD58" s="7"/>
+      <c r="AD58" s="7">
+        <v>100</v>
+      </c>
       <c r="AE58" s="8"/>
       <c r="AF58" s="8"/>
       <c r="AG58" s="9" t="s">
@@ -5865,23 +6385,35 @@
       <c r="S59" s="7"/>
       <c r="T59" s="7"/>
       <c r="U59" s="7">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="V59" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="W59" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="X59" s="7">
-        <v>97</v>
-      </c>
-      <c r="Y59" s="7"/>
-      <c r="Z59" s="7"/>
-      <c r="AA59" s="7"/>
-      <c r="AB59" s="7"/>
-      <c r="AC59" s="7"/>
-      <c r="AD59" s="7"/>
+        <v>100</v>
+      </c>
+      <c r="Y59" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z59" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA59" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB59" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC59" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD59" s="7">
+        <v>100</v>
+      </c>
       <c r="AE59" s="8" t="s">
         <v>220</v>
       </c>
@@ -5946,17 +6478,29 @@
         <v>33</v>
       </c>
       <c r="W60" s="7">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="X60" s="7">
-        <v>97</v>
-      </c>
-      <c r="Y60" s="7"/>
-      <c r="Z60" s="7"/>
-      <c r="AA60" s="7"/>
-      <c r="AB60" s="7"/>
-      <c r="AC60" s="7"/>
-      <c r="AD60" s="7"/>
+        <v>100</v>
+      </c>
+      <c r="Y60" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z60" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA60" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB60" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC60" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD60" s="7">
+        <v>100</v>
+      </c>
       <c r="AE60" s="8" t="s">
         <v>224</v>
       </c>
@@ -6020,14 +6564,26 @@
         <v>50</v>
       </c>
       <c r="X61" s="7">
-        <v>94</v>
-      </c>
-      <c r="Y61" s="7"/>
-      <c r="Z61" s="7"/>
-      <c r="AA61" s="7"/>
-      <c r="AB61" s="7"/>
-      <c r="AC61" s="7"/>
-      <c r="AD61" s="7"/>
+        <v>100</v>
+      </c>
+      <c r="Y61" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z61" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA61" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB61" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC61" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD61" s="7">
+        <v>100</v>
+      </c>
       <c r="AE61" s="8" t="s">
         <v>227</v>
       </c>
@@ -6095,26 +6651,38 @@
         <v>14</v>
       </c>
       <c r="T62" s="7">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="U62" s="7">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="V62" s="7">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="W62" s="7">
         <v>71</v>
       </c>
       <c r="X62" s="7">
-        <v>90</v>
-      </c>
-      <c r="Y62" s="7"/>
-      <c r="Z62" s="7"/>
-      <c r="AA62" s="7"/>
-      <c r="AB62" s="7"/>
-      <c r="AC62" s="7"/>
-      <c r="AD62" s="7"/>
+        <v>86</v>
+      </c>
+      <c r="Y62" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z62" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA62" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB62" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC62" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD62" s="7">
+        <v>100</v>
+      </c>
       <c r="AE62" s="8" t="s">
         <v>230</v>
       </c>
@@ -6172,12 +6740,24 @@
       <c r="V63" s="7"/>
       <c r="W63" s="7"/>
       <c r="X63" s="7"/>
-      <c r="Y63" s="7"/>
-      <c r="Z63" s="7"/>
-      <c r="AA63" s="7"/>
-      <c r="AB63" s="7"/>
-      <c r="AC63" s="7"/>
-      <c r="AD63" s="7"/>
+      <c r="Y63" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z63" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA63" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB63" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC63" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD63" s="7">
+        <v>100</v>
+      </c>
       <c r="AE63" s="8"/>
       <c r="AF63" s="8"/>
       <c r="AG63" s="9" t="s">
@@ -6257,12 +6837,24 @@
       <c r="X64" s="7">
         <v>100</v>
       </c>
-      <c r="Y64" s="7"/>
-      <c r="Z64" s="7"/>
-      <c r="AA64" s="7"/>
-      <c r="AB64" s="7"/>
-      <c r="AC64" s="7"/>
-      <c r="AD64" s="7"/>
+      <c r="Y64" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z64" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA64" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB64" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC64" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD64" s="7">
+        <v>100</v>
+      </c>
       <c r="AE64" s="8" t="s">
         <v>235</v>
       </c>
@@ -6332,20 +6924,32 @@
         <v>18</v>
       </c>
       <c r="V65" s="7">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="W65" s="7">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X65" s="7">
-        <v>50</v>
-      </c>
-      <c r="Y65" s="7"/>
-      <c r="Z65" s="7"/>
-      <c r="AA65" s="7"/>
-      <c r="AB65" s="7"/>
-      <c r="AC65" s="7"/>
-      <c r="AD65" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="Y65" s="7">
+        <v>55</v>
+      </c>
+      <c r="Z65" s="7">
+        <v>64</v>
+      </c>
+      <c r="AA65" s="7">
+        <v>73</v>
+      </c>
+      <c r="AB65" s="7">
+        <v>82</v>
+      </c>
+      <c r="AC65" s="7">
+        <v>91</v>
+      </c>
+      <c r="AD65" s="7">
+        <v>100</v>
+      </c>
       <c r="AE65" s="8" t="s">
         <v>238</v>
       </c>
@@ -6408,7 +7012,7 @@
       <c r="S66" s="7"/>
       <c r="T66" s="7"/>
       <c r="U66" s="7">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="V66" s="7">
         <v>100</v>
@@ -6419,12 +7023,24 @@
       <c r="X66" s="7">
         <v>100</v>
       </c>
-      <c r="Y66" s="7"/>
-      <c r="Z66" s="7"/>
-      <c r="AA66" s="7"/>
-      <c r="AB66" s="7"/>
-      <c r="AC66" s="7"/>
-      <c r="AD66" s="7"/>
+      <c r="Y66" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z66" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA66" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB66" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC66" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD66" s="7">
+        <v>100</v>
+      </c>
       <c r="AE66" s="8" t="s">
         <v>241</v>
       </c>
@@ -6494,12 +7110,24 @@
       <c r="X67" s="7">
         <v>100</v>
       </c>
-      <c r="Y67" s="7"/>
-      <c r="Z67" s="7"/>
-      <c r="AA67" s="7"/>
-      <c r="AB67" s="7"/>
-      <c r="AC67" s="7"/>
-      <c r="AD67" s="7"/>
+      <c r="Y67" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z67" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA67" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB67" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC67" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD67" s="7">
+        <v>100</v>
+      </c>
       <c r="AE67" s="8" t="s">
         <v>245</v>
       </c>
@@ -6559,14 +7187,26 @@
       <c r="V68" s="7"/>
       <c r="W68" s="7"/>
       <c r="X68" s="7">
-        <v>30</v>
-      </c>
-      <c r="Y68" s="7"/>
-      <c r="Z68" s="7"/>
-      <c r="AA68" s="7"/>
-      <c r="AB68" s="7"/>
-      <c r="AC68" s="7"/>
-      <c r="AD68" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y68" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z68" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA68" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB68" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC68" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD68" s="7">
+        <v>100</v>
+      </c>
       <c r="AE68" s="8" t="s">
         <v>248</v>
       </c>
@@ -6630,20 +7270,32 @@
       <c r="T69" s="7"/>
       <c r="U69" s="7"/>
       <c r="V69" s="7">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="W69" s="7">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="X69" s="7">
-        <v>85</v>
-      </c>
-      <c r="Y69" s="7"/>
-      <c r="Z69" s="7"/>
-      <c r="AA69" s="7"/>
-      <c r="AB69" s="7"/>
-      <c r="AC69" s="7"/>
-      <c r="AD69" s="7"/>
+        <v>100</v>
+      </c>
+      <c r="Y69" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z69" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA69" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB69" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC69" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD69" s="7">
+        <v>100</v>
+      </c>
       <c r="AE69" s="8" t="s">
         <v>252</v>
       </c>
@@ -6703,12 +7355,24 @@
       <c r="V70" s="7"/>
       <c r="W70" s="7"/>
       <c r="X70" s="7"/>
-      <c r="Y70" s="7"/>
-      <c r="Z70" s="7"/>
-      <c r="AA70" s="7"/>
-      <c r="AB70" s="7"/>
-      <c r="AC70" s="7"/>
-      <c r="AD70" s="7"/>
+      <c r="Y70" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z70" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA70" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB70" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC70" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD70" s="7">
+        <v>100</v>
+      </c>
       <c r="AE70" s="8"/>
       <c r="AF70" s="8"/>
       <c r="AG70" s="9" t="s">
@@ -6770,14 +7434,26 @@
         <v>33</v>
       </c>
       <c r="X71" s="7">
-        <v>72</v>
-      </c>
-      <c r="Y71" s="7"/>
-      <c r="Z71" s="7"/>
-      <c r="AA71" s="7"/>
-      <c r="AB71" s="7"/>
-      <c r="AC71" s="7"/>
-      <c r="AD71" s="7"/>
+        <v>67</v>
+      </c>
+      <c r="Y71" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z71" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA71" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB71" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC71" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD71" s="7">
+        <v>100</v>
+      </c>
       <c r="AE71" s="8" t="s">
         <v>258</v>
       </c>
@@ -6839,12 +7515,24 @@
       <c r="X72" s="7">
         <v>100</v>
       </c>
-      <c r="Y72" s="7"/>
-      <c r="Z72" s="7"/>
-      <c r="AA72" s="7"/>
-      <c r="AB72" s="7"/>
-      <c r="AC72" s="7"/>
-      <c r="AD72" s="7"/>
+      <c r="Y72" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z72" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA72" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB72" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC72" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD72" s="7">
+        <v>100</v>
+      </c>
       <c r="AE72" s="8" t="s">
         <v>262</v>
       </c>
@@ -6904,14 +7592,26 @@
       <c r="V73" s="7"/>
       <c r="W73" s="7"/>
       <c r="X73" s="7">
-        <v>54</v>
-      </c>
-      <c r="Y73" s="7"/>
-      <c r="Z73" s="7"/>
-      <c r="AA73" s="7"/>
-      <c r="AB73" s="7"/>
-      <c r="AC73" s="7"/>
-      <c r="AD73" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y73" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z73" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA73" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB73" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC73" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD73" s="7">
+        <v>100</v>
+      </c>
       <c r="AE73" s="8" t="s">
         <v>265</v>
       </c>
@@ -6969,12 +7669,24 @@
       <c r="V74" s="7"/>
       <c r="W74" s="7"/>
       <c r="X74" s="7"/>
-      <c r="Y74" s="7"/>
-      <c r="Z74" s="7"/>
-      <c r="AA74" s="7"/>
-      <c r="AB74" s="7"/>
-      <c r="AC74" s="7"/>
-      <c r="AD74" s="7"/>
+      <c r="Y74" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z74" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA74" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB74" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC74" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD74" s="7">
+        <v>100</v>
+      </c>
       <c r="AE74" s="8"/>
       <c r="AF74" s="8"/>
       <c r="AG74" s="9" t="s">
@@ -7032,14 +7744,26 @@
       <c r="V75" s="7"/>
       <c r="W75" s="7"/>
       <c r="X75" s="7">
-        <v>85</v>
-      </c>
-      <c r="Y75" s="7"/>
-      <c r="Z75" s="7"/>
-      <c r="AA75" s="7"/>
-      <c r="AB75" s="7"/>
-      <c r="AC75" s="7"/>
-      <c r="AD75" s="7"/>
+        <v>100</v>
+      </c>
+      <c r="Y75" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z75" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA75" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB75" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC75" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD75" s="7">
+        <v>100</v>
+      </c>
       <c r="AE75" s="8" t="s">
         <v>271</v>
       </c>
@@ -7101,14 +7825,26 @@
       <c r="V76" s="7"/>
       <c r="W76" s="7"/>
       <c r="X76" s="7">
-        <v>13</v>
-      </c>
-      <c r="Y76" s="7"/>
-      <c r="Z76" s="7"/>
-      <c r="AA76" s="7"/>
-      <c r="AB76" s="7"/>
-      <c r="AC76" s="7"/>
-      <c r="AD76" s="7"/>
+        <v>33</v>
+      </c>
+      <c r="Y76" s="7">
+        <v>67</v>
+      </c>
+      <c r="Z76" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA76" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB76" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC76" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD76" s="7">
+        <v>100</v>
+      </c>
       <c r="AE76" s="8" t="s">
         <v>274</v>
       </c>
@@ -7166,10 +7902,18 @@
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
       <c r="Z77" s="7"/>
-      <c r="AA77" s="7"/>
-      <c r="AB77" s="7"/>
-      <c r="AC77" s="7"/>
-      <c r="AD77" s="7"/>
+      <c r="AA77" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB77" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC77" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD77" s="7">
+        <v>100</v>
+      </c>
       <c r="AE77" s="8"/>
       <c r="AF77" s="8"/>
       <c r="AG77" s="9" t="s">
@@ -7232,29 +7976,41 @@
         <v>100</v>
       </c>
       <c r="S78" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T78" s="7">
         <v>17</v>
       </c>
       <c r="U78" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V78" s="7">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="W78" s="7">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="X78" s="7">
         <v>50</v>
       </c>
-      <c r="Y78" s="7"/>
-      <c r="Z78" s="7"/>
-      <c r="AA78" s="7"/>
-      <c r="AB78" s="7"/>
-      <c r="AC78" s="7"/>
-      <c r="AD78" s="7"/>
+      <c r="Y78" s="7">
+        <v>58</v>
+      </c>
+      <c r="Z78" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA78" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB78" s="7">
+        <v>83</v>
+      </c>
+      <c r="AC78" s="7">
+        <v>92</v>
+      </c>
+      <c r="AD78" s="7">
+        <v>100</v>
+      </c>
       <c r="AE78" s="8" t="s">
         <v>282</v>
       </c>
@@ -7314,14 +8070,26 @@
       <c r="V79" s="7"/>
       <c r="W79" s="7"/>
       <c r="X79" s="7">
-        <v>10</v>
-      </c>
-      <c r="Y79" s="7"/>
-      <c r="Z79" s="7"/>
-      <c r="AA79" s="7"/>
-      <c r="AB79" s="7"/>
-      <c r="AC79" s="7"/>
-      <c r="AD79" s="7"/>
+        <v>25</v>
+      </c>
+      <c r="Y79" s="7">
+        <v>50</v>
+      </c>
+      <c r="Z79" s="7">
+        <v>50</v>
+      </c>
+      <c r="AA79" s="7">
+        <v>50</v>
+      </c>
+      <c r="AB79" s="7">
+        <v>50</v>
+      </c>
+      <c r="AC79" s="7">
+        <v>75</v>
+      </c>
+      <c r="AD79" s="7">
+        <v>100</v>
+      </c>
       <c r="AE79" s="8" t="s">
         <v>284</v>
       </c>
@@ -7387,14 +8155,26 @@
         <v>33</v>
       </c>
       <c r="X80" s="7">
-        <v>52</v>
-      </c>
-      <c r="Y80" s="7"/>
-      <c r="Z80" s="7"/>
-      <c r="AA80" s="7"/>
-      <c r="AB80" s="7"/>
-      <c r="AC80" s="7"/>
-      <c r="AD80" s="7"/>
+        <v>67</v>
+      </c>
+      <c r="Y80" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z80" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA80" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB80" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC80" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD80" s="7">
+        <v>100</v>
+      </c>
       <c r="AE80" s="8" t="s">
         <v>287</v>
       </c>
@@ -7456,14 +8236,26 @@
       <c r="V81" s="7"/>
       <c r="W81" s="7"/>
       <c r="X81" s="7">
-        <v>37</v>
-      </c>
-      <c r="Y81" s="7"/>
-      <c r="Z81" s="7"/>
-      <c r="AA81" s="7"/>
-      <c r="AB81" s="7"/>
-      <c r="AC81" s="7"/>
-      <c r="AD81" s="7"/>
+        <v>33</v>
+      </c>
+      <c r="Y81" s="7">
+        <v>67</v>
+      </c>
+      <c r="Z81" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA81" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB81" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC81" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD81" s="7">
+        <v>100</v>
+      </c>
       <c r="AE81" s="8" t="s">
         <v>291</v>
       </c>
@@ -7523,14 +8315,26 @@
       <c r="V82" s="7"/>
       <c r="W82" s="7"/>
       <c r="X82" s="7">
-        <v>38</v>
-      </c>
-      <c r="Y82" s="7"/>
-      <c r="Z82" s="7"/>
-      <c r="AA82" s="7"/>
-      <c r="AB82" s="7"/>
-      <c r="AC82" s="7"/>
-      <c r="AD82" s="7"/>
+        <v>33</v>
+      </c>
+      <c r="Y82" s="7">
+        <v>67</v>
+      </c>
+      <c r="Z82" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA82" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB82" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC82" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD82" s="7">
+        <v>100</v>
+      </c>
       <c r="AE82" s="8" t="s">
         <v>294</v>
       </c>
@@ -7588,12 +8392,24 @@
       <c r="V83" s="7"/>
       <c r="W83" s="7"/>
       <c r="X83" s="7"/>
-      <c r="Y83" s="7"/>
-      <c r="Z83" s="7"/>
-      <c r="AA83" s="7"/>
-      <c r="AB83" s="7"/>
-      <c r="AC83" s="7"/>
-      <c r="AD83" s="7"/>
+      <c r="Y83" s="7">
+        <v>33</v>
+      </c>
+      <c r="Z83" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA83" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB83" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC83" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD83" s="7">
+        <v>100</v>
+      </c>
       <c r="AE83" s="8"/>
       <c r="AF83" s="8"/>
       <c r="AG83" s="9" t="s">
@@ -7647,10 +8463,18 @@
       <c r="X84" s="7"/>
       <c r="Y84" s="7"/>
       <c r="Z84" s="7"/>
-      <c r="AA84" s="7"/>
-      <c r="AB84" s="7"/>
-      <c r="AC84" s="7"/>
-      <c r="AD84" s="7"/>
+      <c r="AA84" s="7">
+        <v>50</v>
+      </c>
+      <c r="AB84" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC84" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD84" s="7">
+        <v>100</v>
+      </c>
       <c r="AE84" s="8"/>
       <c r="AF84" s="8"/>
       <c r="AG84" s="9" t="s">
@@ -7704,10 +8528,18 @@
       <c r="X85" s="7"/>
       <c r="Y85" s="7"/>
       <c r="Z85" s="7"/>
-      <c r="AA85" s="7"/>
-      <c r="AB85" s="7"/>
-      <c r="AC85" s="7"/>
-      <c r="AD85" s="7"/>
+      <c r="AA85" s="7">
+        <v>33</v>
+      </c>
+      <c r="AB85" s="7">
+        <v>67</v>
+      </c>
+      <c r="AC85" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD85" s="7">
+        <v>100</v>
+      </c>
       <c r="AE85" s="8"/>
       <c r="AF85" s="8"/>
       <c r="AG85" s="9" t="s">
@@ -7762,11 +8594,21 @@
       <c r="W86" s="7"/>
       <c r="X86" s="7"/>
       <c r="Y86" s="7"/>
-      <c r="Z86" s="7"/>
-      <c r="AA86" s="7"/>
-      <c r="AB86" s="7"/>
-      <c r="AC86" s="7"/>
-      <c r="AD86" s="7"/>
+      <c r="Z86" s="7">
+        <v>25</v>
+      </c>
+      <c r="AA86" s="7">
+        <v>50</v>
+      </c>
+      <c r="AB86" s="7">
+        <v>75</v>
+      </c>
+      <c r="AC86" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD86" s="7">
+        <v>100</v>
+      </c>
       <c r="AE86" s="8"/>
       <c r="AF86" s="8"/>
       <c r="AG86" s="9" t="s">
@@ -7821,11 +8663,21 @@
       <c r="W87" s="7"/>
       <c r="X87" s="7"/>
       <c r="Y87" s="7"/>
-      <c r="Z87" s="7"/>
-      <c r="AA87" s="7"/>
-      <c r="AB87" s="7"/>
-      <c r="AC87" s="7"/>
-      <c r="AD87" s="7"/>
+      <c r="Z87" s="7">
+        <v>25</v>
+      </c>
+      <c r="AA87" s="7">
+        <v>50</v>
+      </c>
+      <c r="AB87" s="7">
+        <v>75</v>
+      </c>
+      <c r="AC87" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD87" s="7">
+        <v>100</v>
+      </c>
       <c r="AE87" s="8"/>
       <c r="AF87" s="8"/>
       <c r="AG87" s="9" t="s">
@@ -7888,29 +8740,41 @@
         <v>100</v>
       </c>
       <c r="S88" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T88" s="7">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="U88" s="7">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="V88" s="7">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="W88" s="7">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="X88" s="7">
-        <v>44</v>
-      </c>
-      <c r="Y88" s="7"/>
-      <c r="Z88" s="7"/>
-      <c r="AA88" s="7"/>
-      <c r="AB88" s="7"/>
-      <c r="AC88" s="7"/>
-      <c r="AD88" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y88" s="7">
+        <v>58</v>
+      </c>
+      <c r="Z88" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA88" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB88" s="7">
+        <v>83</v>
+      </c>
+      <c r="AC88" s="7">
+        <v>92</v>
+      </c>
+      <c r="AD88" s="7">
+        <v>100</v>
+      </c>
       <c r="AE88" s="8" t="s">
         <v>311</v>
       </c>
@@ -7975,29 +8839,41 @@
         <v>100</v>
       </c>
       <c r="S89" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T89" s="7">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="U89" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V89" s="7">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="W89" s="7">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X89" s="7">
         <v>50</v>
       </c>
-      <c r="Y89" s="7"/>
-      <c r="Z89" s="7"/>
-      <c r="AA89" s="7"/>
-      <c r="AB89" s="7"/>
-      <c r="AC89" s="7"/>
-      <c r="AD89" s="7"/>
+      <c r="Y89" s="7">
+        <v>58</v>
+      </c>
+      <c r="Z89" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA89" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB89" s="7">
+        <v>83</v>
+      </c>
+      <c r="AC89" s="7">
+        <v>92</v>
+      </c>
+      <c r="AD89" s="7">
+        <v>100</v>
+      </c>
       <c r="AE89" s="8" t="s">
         <v>314</v>
       </c>
@@ -8067,12 +8943,24 @@
       <c r="X90" s="7">
         <v>25</v>
       </c>
-      <c r="Y90" s="7"/>
-      <c r="Z90" s="7"/>
-      <c r="AA90" s="7"/>
-      <c r="AB90" s="7"/>
-      <c r="AC90" s="7"/>
-      <c r="AD90" s="7"/>
+      <c r="Y90" s="7">
+        <v>50</v>
+      </c>
+      <c r="Z90" s="7">
+        <v>50</v>
+      </c>
+      <c r="AA90" s="7">
+        <v>50</v>
+      </c>
+      <c r="AB90" s="7">
+        <v>75</v>
+      </c>
+      <c r="AC90" s="7">
+        <v>75</v>
+      </c>
+      <c r="AD90" s="7">
+        <v>100</v>
+      </c>
       <c r="AE90" s="8" t="s">
         <v>317</v>
       </c>
@@ -8137,29 +9025,41 @@
         <v>100</v>
       </c>
       <c r="S91" s="7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T91" s="7">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="U91" s="7">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="V91" s="7">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="W91" s="7">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X91" s="7">
-        <v>54</v>
-      </c>
-      <c r="Y91" s="7"/>
-      <c r="Z91" s="7"/>
-      <c r="AA91" s="7"/>
-      <c r="AB91" s="7"/>
-      <c r="AC91" s="7"/>
-      <c r="AD91" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y91" s="7">
+        <v>58</v>
+      </c>
+      <c r="Z91" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA91" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB91" s="7">
+        <v>83</v>
+      </c>
+      <c r="AC91" s="7">
+        <v>92</v>
+      </c>
+      <c r="AD91" s="7">
+        <v>100</v>
+      </c>
       <c r="AE91" s="8" t="s">
         <v>321</v>
       </c>
@@ -8214,9 +9114,15 @@
       <c r="Y92" s="7"/>
       <c r="Z92" s="7"/>
       <c r="AA92" s="7"/>
-      <c r="AB92" s="7"/>
-      <c r="AC92" s="7"/>
-      <c r="AD92" s="7"/>
+      <c r="AB92" s="7">
+        <v>33</v>
+      </c>
+      <c r="AC92" s="7">
+        <v>67</v>
+      </c>
+      <c r="AD92" s="7">
+        <v>100</v>
+      </c>
       <c r="AE92" s="8"/>
       <c r="AF92" s="8"/>
       <c r="AG92" s="9" t="s">
@@ -8269,9 +9175,15 @@
       <c r="Y93" s="7"/>
       <c r="Z93" s="7"/>
       <c r="AA93" s="7"/>
-      <c r="AB93" s="7"/>
-      <c r="AC93" s="7"/>
-      <c r="AD93" s="7"/>
+      <c r="AB93" s="7">
+        <v>33</v>
+      </c>
+      <c r="AC93" s="7">
+        <v>67</v>
+      </c>
+      <c r="AD93" s="7">
+        <v>100</v>
+      </c>
       <c r="AE93" s="8"/>
       <c r="AF93" s="8"/>
       <c r="AG93" s="9" t="s">
@@ -8324,9 +9236,15 @@
       <c r="Y94" s="7"/>
       <c r="Z94" s="7"/>
       <c r="AA94" s="7"/>
-      <c r="AB94" s="7"/>
-      <c r="AC94" s="7"/>
-      <c r="AD94" s="7"/>
+      <c r="AB94" s="7">
+        <v>33</v>
+      </c>
+      <c r="AC94" s="7">
+        <v>67</v>
+      </c>
+      <c r="AD94" s="7">
+        <v>100</v>
+      </c>
       <c r="AE94" s="8"/>
       <c r="AF94" s="8"/>
       <c r="AG94" s="9" t="s">
@@ -8377,7 +9295,9 @@
       <c r="AA95" s="7"/>
       <c r="AB95" s="7"/>
       <c r="AC95" s="7"/>
-      <c r="AD95" s="7"/>
+      <c r="AD95" s="7">
+        <v>100</v>
+      </c>
       <c r="AE95" s="8"/>
       <c r="AF95" s="8"/>
       <c r="AG95" s="9" t="s">
@@ -8443,7 +9363,7 @@
         <v>33</v>
       </c>
       <c r="T96" s="7">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="U96" s="7">
         <v>100</v>
@@ -8457,12 +9377,24 @@
       <c r="X96" s="7">
         <v>100</v>
       </c>
-      <c r="Y96" s="7"/>
-      <c r="Z96" s="7"/>
-      <c r="AA96" s="7"/>
-      <c r="AB96" s="7"/>
-      <c r="AC96" s="7"/>
-      <c r="AD96" s="7"/>
+      <c r="Y96" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z96" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA96" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB96" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC96" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD96" s="7">
+        <v>100</v>
+      </c>
       <c r="AE96" s="8" t="s">
         <v>335</v>
       </c>
@@ -8525,23 +9457,35 @@
       <c r="S97" s="7"/>
       <c r="T97" s="7"/>
       <c r="U97" s="7">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="V97" s="7">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="W97" s="7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="X97" s="7">
         <v>100</v>
       </c>
-      <c r="Y97" s="7"/>
-      <c r="Z97" s="7"/>
-      <c r="AA97" s="7"/>
-      <c r="AB97" s="7"/>
-      <c r="AC97" s="7"/>
-      <c r="AD97" s="7"/>
+      <c r="Y97" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z97" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA97" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB97" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC97" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD97" s="7">
+        <v>100</v>
+      </c>
       <c r="AE97" s="8" t="s">
         <v>338</v>
       </c>
@@ -8602,17 +9546,29 @@
       <c r="U98" s="7"/>
       <c r="V98" s="7"/>
       <c r="W98" s="7">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="X98" s="7">
-        <v>71</v>
-      </c>
-      <c r="Y98" s="7"/>
-      <c r="Z98" s="7"/>
-      <c r="AA98" s="7"/>
-      <c r="AB98" s="7"/>
-      <c r="AC98" s="7"/>
-      <c r="AD98" s="7"/>
+        <v>67</v>
+      </c>
+      <c r="Y98" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z98" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA98" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB98" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC98" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD98" s="7">
+        <v>100</v>
+      </c>
       <c r="AE98" s="8" t="s">
         <v>341</v>
       </c>
@@ -8670,12 +9626,24 @@
       <c r="V99" s="7"/>
       <c r="W99" s="7"/>
       <c r="X99" s="7"/>
-      <c r="Y99" s="7"/>
-      <c r="Z99" s="7"/>
-      <c r="AA99" s="7"/>
-      <c r="AB99" s="7"/>
-      <c r="AC99" s="7"/>
-      <c r="AD99" s="7"/>
+      <c r="Y99" s="7">
+        <v>33</v>
+      </c>
+      <c r="Z99" s="7">
+        <v>67</v>
+      </c>
+      <c r="AA99" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB99" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC99" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD99" s="7">
+        <v>100</v>
+      </c>
       <c r="AE99" s="8"/>
       <c r="AF99" s="8"/>
       <c r="AG99" s="9" t="s">
@@ -8728,9 +9696,15 @@
       <c r="Y100" s="7"/>
       <c r="Z100" s="7"/>
       <c r="AA100" s="7"/>
-      <c r="AB100" s="7"/>
-      <c r="AC100" s="7"/>
-      <c r="AD100" s="7"/>
+      <c r="AB100" s="7">
+        <v>33</v>
+      </c>
+      <c r="AC100" s="7">
+        <v>67</v>
+      </c>
+      <c r="AD100" s="7">
+        <v>100</v>
+      </c>
       <c r="AE100" s="8"/>
       <c r="AF100" s="8"/>
       <c r="AG100" s="9" t="s">
@@ -8802,12 +9776,24 @@
       <c r="X101" s="7">
         <v>100</v>
       </c>
-      <c r="Y101" s="7"/>
-      <c r="Z101" s="7"/>
-      <c r="AA101" s="7"/>
-      <c r="AB101" s="7"/>
-      <c r="AC101" s="7"/>
-      <c r="AD101" s="7"/>
+      <c r="Y101" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z101" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA101" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB101" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC101" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD101" s="7">
+        <v>100</v>
+      </c>
       <c r="AE101" s="8" t="s">
         <v>349</v>
       </c>
@@ -8869,7 +9855,7 @@
       <c r="T102" s="7"/>
       <c r="U102" s="7"/>
       <c r="V102" s="7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="W102" s="7">
         <v>100</v>
@@ -8877,12 +9863,24 @@
       <c r="X102" s="7">
         <v>100</v>
       </c>
-      <c r="Y102" s="7"/>
-      <c r="Z102" s="7"/>
-      <c r="AA102" s="7"/>
-      <c r="AB102" s="7"/>
-      <c r="AC102" s="7"/>
-      <c r="AD102" s="7"/>
+      <c r="Y102" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z102" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA102" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB102" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC102" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD102" s="7">
+        <v>100</v>
+      </c>
       <c r="AE102" s="8" t="s">
         <v>352</v>
       </c>
@@ -8944,20 +9942,32 @@
       <c r="T103" s="7"/>
       <c r="U103" s="7"/>
       <c r="V103" s="7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W103" s="7">
         <v>22</v>
       </c>
       <c r="X103" s="7">
-        <v>30</v>
-      </c>
-      <c r="Y103" s="7"/>
-      <c r="Z103" s="7"/>
-      <c r="AA103" s="7"/>
-      <c r="AB103" s="7"/>
-      <c r="AC103" s="7"/>
-      <c r="AD103" s="7"/>
+        <v>33</v>
+      </c>
+      <c r="Y103" s="7">
+        <v>44</v>
+      </c>
+      <c r="Z103" s="7">
+        <v>56</v>
+      </c>
+      <c r="AA103" s="7">
+        <v>67</v>
+      </c>
+      <c r="AB103" s="7">
+        <v>78</v>
+      </c>
+      <c r="AC103" s="7">
+        <v>89</v>
+      </c>
+      <c r="AD103" s="7">
+        <v>100</v>
+      </c>
       <c r="AE103" s="8" t="s">
         <v>355</v>
       </c>
@@ -9019,20 +10029,32 @@
       <c r="T104" s="7"/>
       <c r="U104" s="7"/>
       <c r="V104" s="7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W104" s="7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X104" s="7">
         <v>33</v>
       </c>
-      <c r="Y104" s="7"/>
-      <c r="Z104" s="7"/>
-      <c r="AA104" s="7"/>
-      <c r="AB104" s="7"/>
-      <c r="AC104" s="7"/>
-      <c r="AD104" s="7"/>
+      <c r="Y104" s="7">
+        <v>44</v>
+      </c>
+      <c r="Z104" s="7">
+        <v>56</v>
+      </c>
+      <c r="AA104" s="7">
+        <v>67</v>
+      </c>
+      <c r="AB104" s="7">
+        <v>78</v>
+      </c>
+      <c r="AC104" s="7">
+        <v>89</v>
+      </c>
+      <c r="AD104" s="7">
+        <v>100</v>
+      </c>
       <c r="AE104" s="8" t="s">
         <v>358</v>
       </c>
@@ -9106,12 +10128,24 @@
       <c r="X105" s="7">
         <v>100</v>
       </c>
-      <c r="Y105" s="7"/>
-      <c r="Z105" s="7"/>
-      <c r="AA105" s="7"/>
-      <c r="AB105" s="7"/>
-      <c r="AC105" s="7"/>
-      <c r="AD105" s="7"/>
+      <c r="Y105" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z105" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA105" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB105" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC105" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD105" s="7">
+        <v>100</v>
+      </c>
       <c r="AE105" s="8" t="s">
         <v>362</v>
       </c>
@@ -9174,10 +10208,10 @@
       <c r="S106" s="7"/>
       <c r="T106" s="7"/>
       <c r="U106" s="7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="V106" s="7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="W106" s="7">
         <v>100</v>
@@ -9185,12 +10219,24 @@
       <c r="X106" s="7">
         <v>100</v>
       </c>
-      <c r="Y106" s="7"/>
-      <c r="Z106" s="7"/>
-      <c r="AA106" s="7"/>
-      <c r="AB106" s="7"/>
-      <c r="AC106" s="7"/>
-      <c r="AD106" s="7"/>
+      <c r="Y106" s="7">
+        <v>100</v>
+      </c>
+      <c r="Z106" s="7">
+        <v>100</v>
+      </c>
+      <c r="AA106" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB106" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC106" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD106" s="7">
+        <v>100</v>
+      </c>
       <c r="AE106" s="8" t="s">
         <v>365</v>
       </c>
@@ -9252,20 +10298,32 @@
       <c r="T107" s="7"/>
       <c r="U107" s="7"/>
       <c r="V107" s="7">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="W107" s="7">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="X107" s="7">
-        <v>55</v>
-      </c>
-      <c r="Y107" s="7"/>
-      <c r="Z107" s="7"/>
-      <c r="AA107" s="7"/>
-      <c r="AB107" s="7"/>
-      <c r="AC107" s="7"/>
-      <c r="AD107" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y107" s="7">
+        <v>67</v>
+      </c>
+      <c r="Z107" s="7">
+        <v>83</v>
+      </c>
+      <c r="AA107" s="7">
+        <v>100</v>
+      </c>
+      <c r="AB107" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC107" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD107" s="7">
+        <v>100</v>
+      </c>
       <c r="AE107" s="8" t="s">
         <v>368</v>
       </c>
@@ -9320,9 +10378,15 @@
       <c r="Y108" s="7"/>
       <c r="Z108" s="7"/>
       <c r="AA108" s="7"/>
-      <c r="AB108" s="7"/>
-      <c r="AC108" s="7"/>
-      <c r="AD108" s="7"/>
+      <c r="AB108" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC108" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD108" s="7">
+        <v>100</v>
+      </c>
       <c r="AE108" s="8"/>
       <c r="AF108" s="8"/>
       <c r="AG108" s="9" t="s">
@@ -9374,8 +10438,12 @@
       <c r="Z109" s="7"/>
       <c r="AA109" s="7"/>
       <c r="AB109" s="7"/>
-      <c r="AC109" s="7"/>
-      <c r="AD109" s="7"/>
+      <c r="AC109" s="7">
+        <v>50</v>
+      </c>
+      <c r="AD109" s="7">
+        <v>100</v>
+      </c>
       <c r="AE109" s="8"/>
       <c r="AF109" s="8"/>
       <c r="AG109" s="9" t="s">
@@ -9447,20 +10515,32 @@
         <v>30</v>
       </c>
       <c r="V110" s="7">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="W110" s="7">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="X110" s="7">
-        <v>54</v>
-      </c>
-      <c r="Y110" s="7"/>
-      <c r="Z110" s="7"/>
-      <c r="AA110" s="7"/>
-      <c r="AB110" s="7"/>
-      <c r="AC110" s="7"/>
-      <c r="AD110" s="7"/>
+        <v>60</v>
+      </c>
+      <c r="Y110" s="7">
+        <v>70</v>
+      </c>
+      <c r="Z110" s="7">
+        <v>80</v>
+      </c>
+      <c r="AA110" s="7">
+        <v>90</v>
+      </c>
+      <c r="AB110" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC110" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD110" s="7">
+        <v>100</v>
+      </c>
       <c r="AE110" s="8" t="s">
         <v>376</v>
       </c>
@@ -9524,26 +10604,38 @@
       </c>
       <c r="S111" s="7"/>
       <c r="T111" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U111" s="7">
         <v>20</v>
       </c>
       <c r="V111" s="7">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="W111" s="7">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="X111" s="7">
-        <v>35</v>
-      </c>
-      <c r="Y111" s="7"/>
-      <c r="Z111" s="7"/>
-      <c r="AA111" s="7"/>
-      <c r="AB111" s="7"/>
-      <c r="AC111" s="7"/>
-      <c r="AD111" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y111" s="7">
+        <v>60</v>
+      </c>
+      <c r="Z111" s="7">
+        <v>70</v>
+      </c>
+      <c r="AA111" s="7">
+        <v>80</v>
+      </c>
+      <c r="AB111" s="7">
+        <v>90</v>
+      </c>
+      <c r="AC111" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD111" s="7">
+        <v>100</v>
+      </c>
       <c r="AE111" s="8" t="s">
         <v>379</v>
       </c>
@@ -9609,26 +10701,38 @@
       </c>
       <c r="S112" s="7"/>
       <c r="T112" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U112" s="7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V112" s="7">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="W112" s="7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="X112" s="7">
-        <v>55</v>
-      </c>
-      <c r="Y112" s="7"/>
-      <c r="Z112" s="7"/>
-      <c r="AA112" s="7"/>
-      <c r="AB112" s="7"/>
-      <c r="AC112" s="7"/>
-      <c r="AD112" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y112" s="7">
+        <v>60</v>
+      </c>
+      <c r="Z112" s="7">
+        <v>70</v>
+      </c>
+      <c r="AA112" s="7">
+        <v>80</v>
+      </c>
+      <c r="AB112" s="7">
+        <v>90</v>
+      </c>
+      <c r="AC112" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD112" s="7">
+        <v>100</v>
+      </c>
       <c r="AE112" s="8" t="s">
         <v>382</v>
       </c>
@@ -9682,8 +10786,12 @@
       <c r="Z113" s="7"/>
       <c r="AA113" s="7"/>
       <c r="AB113" s="7"/>
-      <c r="AC113" s="7"/>
-      <c r="AD113" s="7"/>
+      <c r="AC113" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD113" s="7">
+        <v>100</v>
+      </c>
       <c r="AE113" s="8"/>
       <c r="AF113" s="8"/>
       <c r="AG113" s="9" t="s">
@@ -9736,9 +10844,15 @@
       <c r="Y114" s="7"/>
       <c r="Z114" s="7"/>
       <c r="AA114" s="7"/>
-      <c r="AB114" s="7"/>
-      <c r="AC114" s="7"/>
-      <c r="AD114" s="7"/>
+      <c r="AB114" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC114" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD114" s="7">
+        <v>100</v>
+      </c>
       <c r="AE114" s="8"/>
       <c r="AF114" s="8"/>
       <c r="AG114" s="9" t="s">
@@ -9791,9 +10905,15 @@
       <c r="Y115" s="7"/>
       <c r="Z115" s="7"/>
       <c r="AA115" s="7"/>
-      <c r="AB115" s="7"/>
-      <c r="AC115" s="7"/>
-      <c r="AD115" s="7"/>
+      <c r="AB115" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC115" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD115" s="7">
+        <v>100</v>
+      </c>
       <c r="AE115" s="8"/>
       <c r="AF115" s="8"/>
       <c r="AG115" s="9" t="s">
@@ -9846,9 +10966,15 @@
       <c r="Y116" s="7"/>
       <c r="Z116" s="7"/>
       <c r="AA116" s="7"/>
-      <c r="AB116" s="7"/>
-      <c r="AC116" s="7"/>
-      <c r="AD116" s="7"/>
+      <c r="AB116" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC116" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD116" s="7">
+        <v>100</v>
+      </c>
       <c r="AE116" s="8"/>
       <c r="AF116" s="8"/>
       <c r="AG116" s="9" t="s">
@@ -9901,9 +11027,15 @@
       <c r="Y117" s="7"/>
       <c r="Z117" s="7"/>
       <c r="AA117" s="7"/>
-      <c r="AB117" s="7"/>
-      <c r="AC117" s="7"/>
-      <c r="AD117" s="7"/>
+      <c r="AB117" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC117" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD117" s="7">
+        <v>100</v>
+      </c>
       <c r="AE117" s="8"/>
       <c r="AF117" s="8"/>
       <c r="AG117" s="9" t="s">
@@ -9956,9 +11088,15 @@
       <c r="Y118" s="7"/>
       <c r="Z118" s="7"/>
       <c r="AA118" s="7"/>
-      <c r="AB118" s="7"/>
-      <c r="AC118" s="7"/>
-      <c r="AD118" s="7"/>
+      <c r="AB118" s="7">
+        <v>50</v>
+      </c>
+      <c r="AC118" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD118" s="7">
+        <v>100</v>
+      </c>
       <c r="AE118" s="8"/>
       <c r="AF118" s="8"/>
       <c r="AG118" s="9" t="s">
@@ -10010,8 +11148,12 @@
       <c r="Z119" s="7"/>
       <c r="AA119" s="7"/>
       <c r="AB119" s="7"/>
-      <c r="AC119" s="7"/>
-      <c r="AD119" s="7"/>
+      <c r="AC119" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD119" s="7">
+        <v>100</v>
+      </c>
       <c r="AE119" s="8"/>
       <c r="AF119" s="8"/>
       <c r="AG119" s="9" t="s">
@@ -10063,8 +11205,12 @@
       <c r="Z120" s="7"/>
       <c r="AA120" s="7"/>
       <c r="AB120" s="7"/>
-      <c r="AC120" s="7"/>
-      <c r="AD120" s="7"/>
+      <c r="AC120" s="7">
+        <v>100</v>
+      </c>
+      <c r="AD120" s="7">
+        <v>100</v>
+      </c>
       <c r="AE120" s="8"/>
       <c r="AF120" s="8"/>
       <c r="AG120" s="9" t="s">
@@ -10115,7 +11261,9 @@
       <c r="AA121" s="7"/>
       <c r="AB121" s="7"/>
       <c r="AC121" s="7"/>
-      <c r="AD121" s="7"/>
+      <c r="AD121" s="7">
+        <v>100</v>
+      </c>
       <c r="AE121" s="8"/>
       <c r="AF121" s="8"/>
       <c r="AG121" s="9" t="s">
@@ -10166,7 +11314,9 @@
       <c r="AA122" s="7"/>
       <c r="AB122" s="7"/>
       <c r="AC122" s="7"/>
-      <c r="AD122" s="7"/>
+      <c r="AD122" s="7">
+        <v>100</v>
+      </c>
       <c r="AE122" s="8"/>
       <c r="AF122" s="8"/>
       <c r="AG122" s="9" t="s">
@@ -10227,29 +11377,41 @@
         <v>100</v>
       </c>
       <c r="S123" s="7">
-        <v>8</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="T123" s="7">
-        <v>21</v>
+        <v>16.7</v>
       </c>
       <c r="U123" s="7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="V123" s="7">
-        <v>30</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="W123" s="7">
-        <v>47</v>
+        <v>41.7</v>
       </c>
       <c r="X123" s="7">
-        <v>55</v>
-      </c>
-      <c r="Y123" s="7"/>
-      <c r="Z123" s="7"/>
-      <c r="AA123" s="7"/>
-      <c r="AB123" s="7"/>
-      <c r="AC123" s="7"/>
-      <c r="AD123" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y123" s="7">
+        <v>58.3</v>
+      </c>
+      <c r="Z123" s="7">
+        <v>66.7</v>
+      </c>
+      <c r="AA123" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB123" s="7">
+        <v>83.3</v>
+      </c>
+      <c r="AC123" s="7">
+        <v>91.7</v>
+      </c>
+      <c r="AD123" s="7">
+        <v>100</v>
+      </c>
       <c r="AE123" s="8" t="s">
         <v>409</v>
       </c>
@@ -10312,29 +11474,41 @@
         <v>100</v>
       </c>
       <c r="S124" s="7">
-        <v>8</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="T124" s="7">
-        <v>8</v>
+        <v>16.7</v>
       </c>
       <c r="U124" s="7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="V124" s="7">
-        <v>33</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="W124" s="7">
-        <v>47</v>
+        <v>41.7</v>
       </c>
       <c r="X124" s="7">
-        <v>55</v>
-      </c>
-      <c r="Y124" s="7"/>
-      <c r="Z124" s="7"/>
-      <c r="AA124" s="7"/>
-      <c r="AB124" s="7"/>
-      <c r="AC124" s="7"/>
-      <c r="AD124" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y124" s="7">
+        <v>58.3</v>
+      </c>
+      <c r="Z124" s="7">
+        <v>66.7</v>
+      </c>
+      <c r="AA124" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB124" s="7">
+        <v>83.3</v>
+      </c>
+      <c r="AC124" s="7">
+        <v>91.7</v>
+      </c>
+      <c r="AD124" s="7">
+        <v>100</v>
+      </c>
       <c r="AE124" s="8" t="s">
         <v>414</v>
       </c>
@@ -10397,29 +11571,41 @@
         <v>100</v>
       </c>
       <c r="S125" s="7">
-        <v>13</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="T125" s="7">
-        <v>13</v>
+        <v>16.7</v>
       </c>
       <c r="U125" s="7">
         <v>25</v>
       </c>
       <c r="V125" s="7">
-        <v>33</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="W125" s="7">
-        <v>46</v>
+        <v>41.7</v>
       </c>
       <c r="X125" s="7">
-        <v>46</v>
-      </c>
-      <c r="Y125" s="7"/>
-      <c r="Z125" s="7"/>
-      <c r="AA125" s="7"/>
-      <c r="AB125" s="7"/>
-      <c r="AC125" s="7"/>
-      <c r="AD125" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y125" s="7">
+        <v>58.3</v>
+      </c>
+      <c r="Z125" s="7">
+        <v>66.7</v>
+      </c>
+      <c r="AA125" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB125" s="7">
+        <v>83.3</v>
+      </c>
+      <c r="AC125" s="7">
+        <v>91.7</v>
+      </c>
+      <c r="AD125" s="7">
+        <v>100</v>
+      </c>
       <c r="AE125" s="8" t="s">
         <v>419</v>
       </c>
@@ -10482,29 +11668,41 @@
         <v>100</v>
       </c>
       <c r="S126" s="7">
-        <v>8</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="T126" s="7">
-        <v>17</v>
+        <v>16.7</v>
       </c>
       <c r="U126" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V126" s="7">
-        <v>27</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="W126" s="7">
-        <v>27</v>
+        <v>41.7</v>
       </c>
       <c r="X126" s="7">
         <v>50</v>
       </c>
-      <c r="Y126" s="7"/>
-      <c r="Z126" s="7"/>
-      <c r="AA126" s="7"/>
-      <c r="AB126" s="7"/>
-      <c r="AC126" s="7"/>
-      <c r="AD126" s="7"/>
+      <c r="Y126" s="7">
+        <v>58.3</v>
+      </c>
+      <c r="Z126" s="7">
+        <v>66.7</v>
+      </c>
+      <c r="AA126" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB126" s="7">
+        <v>83.3</v>
+      </c>
+      <c r="AC126" s="7">
+        <v>91.7</v>
+      </c>
+      <c r="AD126" s="7">
+        <v>100</v>
+      </c>
       <c r="AE126" s="8" t="s">
         <v>424</v>
       </c>
@@ -10567,29 +11765,41 @@
         <v>100</v>
       </c>
       <c r="S127" s="7">
-        <v>8</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="T127" s="7">
-        <v>8</v>
+        <v>16.7</v>
       </c>
       <c r="U127" s="7">
         <v>25</v>
       </c>
       <c r="V127" s="7">
-        <v>33</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="W127" s="7">
-        <v>33</v>
+        <v>41.7</v>
       </c>
       <c r="X127" s="7">
-        <v>54</v>
-      </c>
-      <c r="Y127" s="7"/>
-      <c r="Z127" s="7"/>
-      <c r="AA127" s="7"/>
-      <c r="AB127" s="7"/>
-      <c r="AC127" s="7"/>
-      <c r="AD127" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="Y127" s="7">
+        <v>58.3</v>
+      </c>
+      <c r="Z127" s="7">
+        <v>66.7</v>
+      </c>
+      <c r="AA127" s="7">
+        <v>75</v>
+      </c>
+      <c r="AB127" s="7">
+        <v>83.3</v>
+      </c>
+      <c r="AC127" s="7">
+        <v>91.7</v>
+      </c>
+      <c r="AD127" s="7">
+        <v>100</v>
+      </c>
       <c r="AE127" s="8" t="s">
         <v>429</v>
       </c>

--- a/บันทึกผลการดำเนินงาน_RM_2569.xlsx
+++ b/บันทึกผลการดำเนินงาน_RM_2569.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devill/1_กฟน./2569/Dashborad_RM/rm-dashboard-2569/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAA1681-3CAA-354F-8073-00EF01FA4BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C614761-147F-DE46-BBA3-18EB24F4809D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="บันทึกผล" sheetId="1" r:id="rId1"/>
@@ -2041,24 +2041,12 @@
       <c r="X2" s="7">
         <v>50</v>
       </c>
-      <c r="Y2" s="7">
-        <v>58</v>
-      </c>
-      <c r="Z2" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA2" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB2" s="7">
-        <v>83</v>
-      </c>
-      <c r="AC2" s="7">
-        <v>92</v>
-      </c>
-      <c r="AD2" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="7"/>
+      <c r="AB2" s="7"/>
+      <c r="AC2" s="7"/>
+      <c r="AD2" s="7"/>
       <c r="AE2" s="8" t="s">
         <v>38</v>
       </c>
@@ -2138,24 +2126,12 @@
       <c r="X3" s="7">
         <v>50</v>
       </c>
-      <c r="Y3" s="7">
-        <v>58</v>
-      </c>
-      <c r="Z3" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA3" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB3" s="7">
-        <v>83</v>
-      </c>
-      <c r="AC3" s="7">
-        <v>92</v>
-      </c>
-      <c r="AD3" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="7"/>
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="7"/>
+      <c r="AD3" s="7"/>
       <c r="AE3" s="8" t="s">
         <v>44</v>
       </c>
@@ -2235,24 +2211,12 @@
       <c r="X4" s="7">
         <v>50</v>
       </c>
-      <c r="Y4" s="7">
-        <v>58</v>
-      </c>
-      <c r="Z4" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA4" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB4" s="7">
-        <v>83</v>
-      </c>
-      <c r="AC4" s="7">
-        <v>92</v>
-      </c>
-      <c r="AD4" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7"/>
+      <c r="AB4" s="7"/>
+      <c r="AC4" s="7"/>
+      <c r="AD4" s="7"/>
       <c r="AE4" s="8" t="s">
         <v>49</v>
       </c>
@@ -2320,24 +2284,12 @@
       <c r="X5" s="7">
         <v>100</v>
       </c>
-      <c r="Y5" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z5" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA5" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB5" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC5" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD5" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="7"/>
       <c r="AE5" s="8" t="s">
         <v>54</v>
       </c>
@@ -2393,24 +2345,12 @@
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7"/>
-      <c r="Y6" s="7">
-        <v>33</v>
-      </c>
-      <c r="Z6" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA6" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB6" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC6" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD6" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
+      <c r="AC6" s="7"/>
+      <c r="AD6" s="7"/>
       <c r="AE6" s="8"/>
       <c r="AF6" s="8"/>
       <c r="AG6" s="9" t="s">
@@ -2461,15 +2401,9 @@
       <c r="Y7" s="7"/>
       <c r="Z7" s="7"/>
       <c r="AA7" s="7"/>
-      <c r="AB7" s="7">
-        <v>50</v>
-      </c>
-      <c r="AC7" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD7" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB7" s="7"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="7"/>
       <c r="AE7" s="8"/>
       <c r="AF7" s="8"/>
       <c r="AG7" s="9" t="s">
@@ -2520,15 +2454,9 @@
       <c r="Y8" s="7"/>
       <c r="Z8" s="7"/>
       <c r="AA8" s="7"/>
-      <c r="AB8" s="7">
-        <v>33</v>
-      </c>
-      <c r="AC8" s="7">
-        <v>67</v>
-      </c>
-      <c r="AD8" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7"/>
       <c r="AE8" s="8"/>
       <c r="AF8" s="8"/>
       <c r="AG8" s="9" t="s">
@@ -2579,15 +2507,9 @@
       <c r="Y9" s="7"/>
       <c r="Z9" s="7"/>
       <c r="AA9" s="7"/>
-      <c r="AB9" s="7">
-        <v>33</v>
-      </c>
-      <c r="AC9" s="7">
-        <v>67</v>
-      </c>
-      <c r="AD9" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB9" s="7"/>
+      <c r="AC9" s="7"/>
+      <c r="AD9" s="7"/>
       <c r="AE9" s="8"/>
       <c r="AF9" s="8"/>
       <c r="AG9" s="9" t="s">
@@ -2638,15 +2560,9 @@
       <c r="Y10" s="7"/>
       <c r="Z10" s="7"/>
       <c r="AA10" s="7"/>
-      <c r="AB10" s="7">
-        <v>33</v>
-      </c>
-      <c r="AC10" s="7">
-        <v>67</v>
-      </c>
-      <c r="AD10" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB10" s="7"/>
+      <c r="AC10" s="7"/>
+      <c r="AD10" s="7"/>
       <c r="AE10" s="8"/>
       <c r="AF10" s="8"/>
       <c r="AG10" s="9" t="s">
@@ -2724,24 +2640,12 @@
       <c r="X11" s="7">
         <v>50</v>
       </c>
-      <c r="Y11" s="7">
-        <v>58</v>
-      </c>
-      <c r="Z11" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA11" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB11" s="7">
-        <v>83</v>
-      </c>
-      <c r="AC11" s="7">
-        <v>92</v>
-      </c>
-      <c r="AD11" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="7"/>
       <c r="AE11" s="8" t="s">
         <v>77</v>
       </c>
@@ -2809,24 +2713,12 @@
       <c r="X12" s="7">
         <v>50</v>
       </c>
-      <c r="Y12" s="7">
-        <v>67</v>
-      </c>
-      <c r="Z12" s="7">
-        <v>83</v>
-      </c>
-      <c r="AA12" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB12" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC12" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD12" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="7"/>
+      <c r="AD12" s="7"/>
       <c r="AE12" s="8" t="s">
         <v>82</v>
       </c>
@@ -2882,24 +2774,12 @@
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-      <c r="Y13" s="7">
-        <v>33</v>
-      </c>
-      <c r="Z13" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA13" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB13" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC13" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD13" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="7"/>
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="7"/>
       <c r="AE13" s="8"/>
       <c r="AF13" s="8"/>
       <c r="AG13" s="9" t="s">
@@ -2977,24 +2857,12 @@
       <c r="X14" s="7">
         <v>50</v>
       </c>
-      <c r="Y14" s="7">
-        <v>58</v>
-      </c>
-      <c r="Z14" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA14" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB14" s="7">
-        <v>83</v>
-      </c>
-      <c r="AC14" s="7">
-        <v>92</v>
-      </c>
-      <c r="AD14" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="7"/>
+      <c r="AC14" s="7"/>
+      <c r="AD14" s="7"/>
       <c r="AE14" s="8" t="s">
         <v>91</v>
       </c>
@@ -3074,24 +2942,12 @@
       <c r="X15" s="7">
         <v>50</v>
       </c>
-      <c r="Y15" s="7">
-        <v>58</v>
-      </c>
-      <c r="Z15" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA15" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB15" s="7">
-        <v>83</v>
-      </c>
-      <c r="AC15" s="7">
-        <v>92</v>
-      </c>
-      <c r="AD15" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="7"/>
       <c r="AE15" s="8" t="s">
         <v>96</v>
       </c>
@@ -3171,24 +3027,12 @@
       <c r="X16" s="7">
         <v>100</v>
       </c>
-      <c r="Y16" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z16" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA16" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB16" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC16" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD16" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
       <c r="AE16" s="8" t="s">
         <v>101</v>
       </c>
@@ -3244,24 +3088,12 @@
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
-      <c r="Y17" s="7">
-        <v>17</v>
-      </c>
-      <c r="Z17" s="7">
-        <v>33</v>
-      </c>
-      <c r="AA17" s="7">
-        <v>50</v>
-      </c>
-      <c r="AB17" s="7">
-        <v>67</v>
-      </c>
-      <c r="AC17" s="7">
-        <v>83</v>
-      </c>
-      <c r="AD17" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7"/>
       <c r="AE17" s="8"/>
       <c r="AF17" s="8"/>
       <c r="AG17" s="9" t="s">
@@ -3317,24 +3149,12 @@
       <c r="V18" s="7"/>
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
-      <c r="Y18" s="7">
-        <v>50</v>
-      </c>
-      <c r="Z18" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA18" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB18" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC18" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD18" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="7"/>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7"/>
       <c r="AE18" s="8"/>
       <c r="AF18" s="8"/>
       <c r="AG18" s="9" t="s">
@@ -3389,21 +3209,11 @@
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
-      <c r="Z19" s="7">
-        <v>50</v>
-      </c>
-      <c r="AA19" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB19" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC19" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD19" s="7">
-        <v>100</v>
-      </c>
+      <c r="Z19" s="7"/>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="7"/>
+      <c r="AC19" s="7"/>
+      <c r="AD19" s="7"/>
       <c r="AE19" s="8"/>
       <c r="AF19" s="8"/>
       <c r="AG19" s="9" t="s">
@@ -3456,15 +3266,9 @@
       <c r="Y20" s="7"/>
       <c r="Z20" s="7"/>
       <c r="AA20" s="7"/>
-      <c r="AB20" s="7">
-        <v>33</v>
-      </c>
-      <c r="AC20" s="7">
-        <v>67</v>
-      </c>
-      <c r="AD20" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB20" s="7"/>
+      <c r="AC20" s="7"/>
+      <c r="AD20" s="7"/>
       <c r="AE20" s="8"/>
       <c r="AF20" s="8"/>
       <c r="AG20" s="9" t="s">
@@ -3516,12 +3320,8 @@
       <c r="Z21" s="7"/>
       <c r="AA21" s="7"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="7">
-        <v>50</v>
-      </c>
-      <c r="AD21" s="7">
-        <v>100</v>
-      </c>
+      <c r="AC21" s="7"/>
+      <c r="AD21" s="7"/>
       <c r="AE21" s="8"/>
       <c r="AF21" s="8"/>
       <c r="AG21" s="9" t="s">
@@ -3572,9 +3372,7 @@
       <c r="AA22" s="7"/>
       <c r="AB22" s="7"/>
       <c r="AC22" s="7"/>
-      <c r="AD22" s="7">
-        <v>100</v>
-      </c>
+      <c r="AD22" s="7"/>
       <c r="AE22" s="8"/>
       <c r="AF22" s="8"/>
       <c r="AG22" s="9" t="s">
@@ -3638,24 +3436,12 @@
       <c r="X23" s="7">
         <v>40</v>
       </c>
-      <c r="Y23" s="7">
-        <v>60</v>
-      </c>
-      <c r="Z23" s="7">
-        <v>80</v>
-      </c>
-      <c r="AA23" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB23" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC23" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD23" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="7"/>
+      <c r="AA23" s="7"/>
+      <c r="AB23" s="7"/>
+      <c r="AC23" s="7"/>
+      <c r="AD23" s="7"/>
       <c r="AE23" s="8" t="s">
         <v>122</v>
       </c>
@@ -3710,15 +3496,9 @@
       <c r="Y24" s="7"/>
       <c r="Z24" s="7"/>
       <c r="AA24" s="7"/>
-      <c r="AB24" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC24" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD24" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB24" s="7"/>
+      <c r="AC24" s="7"/>
+      <c r="AD24" s="7"/>
       <c r="AE24" s="8"/>
       <c r="AF24" s="8"/>
       <c r="AG24" s="9" t="s">
@@ -3770,12 +3550,8 @@
       <c r="Z25" s="7"/>
       <c r="AA25" s="7"/>
       <c r="AB25" s="7"/>
-      <c r="AC25" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD25" s="7">
-        <v>100</v>
-      </c>
+      <c r="AC25" s="7"/>
+      <c r="AD25" s="7"/>
       <c r="AE25" s="8"/>
       <c r="AF25" s="8"/>
       <c r="AG25" s="9" t="s">
@@ -3826,9 +3602,7 @@
       <c r="AA26" s="7"/>
       <c r="AB26" s="7"/>
       <c r="AC26" s="7"/>
-      <c r="AD26" s="7">
-        <v>100</v>
-      </c>
+      <c r="AD26" s="7"/>
       <c r="AE26" s="8"/>
       <c r="AF26" s="8"/>
       <c r="AG26" s="9" t="s">
@@ -3888,24 +3662,12 @@
       <c r="X27" s="7">
         <v>33</v>
       </c>
-      <c r="Y27" s="7">
-        <v>67</v>
-      </c>
-      <c r="Z27" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA27" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB27" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC27" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD27" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y27" s="7"/>
+      <c r="Z27" s="7"/>
+      <c r="AA27" s="7"/>
+      <c r="AB27" s="7"/>
+      <c r="AC27" s="7"/>
+      <c r="AD27" s="7"/>
       <c r="AE27" s="8" t="s">
         <v>130</v>
       </c>
@@ -3964,21 +3726,11 @@
       <c r="W28" s="7"/>
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
-      <c r="Z28" s="7">
-        <v>50</v>
-      </c>
-      <c r="AA28" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB28" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC28" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD28" s="7">
-        <v>100</v>
-      </c>
+      <c r="Z28" s="7"/>
+      <c r="AA28" s="7"/>
+      <c r="AB28" s="7"/>
+      <c r="AC28" s="7"/>
+      <c r="AD28" s="7"/>
       <c r="AE28" s="8"/>
       <c r="AF28" s="8"/>
       <c r="AG28" s="9" t="s">
@@ -4031,15 +3783,9 @@
       <c r="Y29" s="7"/>
       <c r="Z29" s="7"/>
       <c r="AA29" s="7"/>
-      <c r="AB29" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC29" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD29" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB29" s="7"/>
+      <c r="AC29" s="7"/>
+      <c r="AD29" s="7"/>
       <c r="AE29" s="8"/>
       <c r="AF29" s="8"/>
       <c r="AG29" s="9" t="s">
@@ -4091,12 +3837,8 @@
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
       <c r="AB30" s="7"/>
-      <c r="AC30" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD30" s="7">
-        <v>100</v>
-      </c>
+      <c r="AC30" s="7"/>
+      <c r="AD30" s="7"/>
       <c r="AE30" s="8"/>
       <c r="AF30" s="8"/>
       <c r="AG30" s="9" t="s">
@@ -4147,9 +3889,7 @@
       <c r="AA31" s="7"/>
       <c r="AB31" s="7"/>
       <c r="AC31" s="7"/>
-      <c r="AD31" s="7">
-        <v>100</v>
-      </c>
+      <c r="AD31" s="7"/>
       <c r="AE31" s="8"/>
       <c r="AF31" s="8"/>
       <c r="AG31" s="9" t="s">
@@ -4229,24 +3969,12 @@
       <c r="X32" s="7">
         <v>100</v>
       </c>
-      <c r="Y32" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z32" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA32" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB32" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC32" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD32" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y32" s="7"/>
+      <c r="Z32" s="7"/>
+      <c r="AA32" s="7"/>
+      <c r="AB32" s="7"/>
+      <c r="AC32" s="7"/>
+      <c r="AD32" s="7"/>
       <c r="AE32" s="8" t="s">
         <v>142</v>
       </c>
@@ -4328,24 +4056,12 @@
       <c r="X33" s="7">
         <v>100</v>
       </c>
-      <c r="Y33" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z33" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA33" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB33" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC33" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD33" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y33" s="7"/>
+      <c r="Z33" s="7"/>
+      <c r="AA33" s="7"/>
+      <c r="AB33" s="7"/>
+      <c r="AC33" s="7"/>
+      <c r="AD33" s="7"/>
       <c r="AE33" s="8" t="s">
         <v>146</v>
       </c>
@@ -4415,24 +4131,12 @@
       <c r="X34" s="7">
         <v>100</v>
       </c>
-      <c r="Y34" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z34" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA34" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB34" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC34" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD34" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y34" s="7"/>
+      <c r="Z34" s="7"/>
+      <c r="AA34" s="7"/>
+      <c r="AB34" s="7"/>
+      <c r="AC34" s="7"/>
+      <c r="AD34" s="7"/>
       <c r="AE34" s="8" t="s">
         <v>149</v>
       </c>
@@ -4514,24 +4218,12 @@
       <c r="X35" s="7">
         <v>50</v>
       </c>
-      <c r="Y35" s="7">
-        <v>58</v>
-      </c>
-      <c r="Z35" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA35" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB35" s="7">
-        <v>83</v>
-      </c>
-      <c r="AC35" s="7">
-        <v>92</v>
-      </c>
-      <c r="AD35" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y35" s="7"/>
+      <c r="Z35" s="7"/>
+      <c r="AA35" s="7"/>
+      <c r="AB35" s="7"/>
+      <c r="AC35" s="7"/>
+      <c r="AD35" s="7"/>
       <c r="AE35" s="8" t="s">
         <v>153</v>
       </c>
@@ -4587,18 +4279,10 @@
       <c r="X36" s="7"/>
       <c r="Y36" s="7"/>
       <c r="Z36" s="7"/>
-      <c r="AA36" s="7">
-        <v>50</v>
-      </c>
-      <c r="AB36" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC36" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD36" s="7">
-        <v>100</v>
-      </c>
+      <c r="AA36" s="7"/>
+      <c r="AB36" s="7"/>
+      <c r="AC36" s="7"/>
+      <c r="AD36" s="7"/>
       <c r="AE36" s="8"/>
       <c r="AF36" s="8"/>
       <c r="AG36" s="9" t="s">
@@ -4651,15 +4335,9 @@
       <c r="Y37" s="7"/>
       <c r="Z37" s="7"/>
       <c r="AA37" s="7"/>
-      <c r="AB37" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC37" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD37" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB37" s="7"/>
+      <c r="AC37" s="7"/>
+      <c r="AD37" s="7"/>
       <c r="AE37" s="8"/>
       <c r="AF37" s="8"/>
       <c r="AG37" s="9" t="s">
@@ -4727,24 +4405,12 @@
       <c r="X38" s="7">
         <v>43</v>
       </c>
-      <c r="Y38" s="7">
-        <v>57</v>
-      </c>
-      <c r="Z38" s="7">
-        <v>71</v>
-      </c>
-      <c r="AA38" s="7">
-        <v>86</v>
-      </c>
-      <c r="AB38" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC38" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD38" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y38" s="7"/>
+      <c r="Z38" s="7"/>
+      <c r="AA38" s="7"/>
+      <c r="AB38" s="7"/>
+      <c r="AC38" s="7"/>
+      <c r="AD38" s="7"/>
       <c r="AE38" s="8" t="s">
         <v>160</v>
       </c>
@@ -4798,12 +4464,8 @@
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
       <c r="AB39" s="7"/>
-      <c r="AC39" s="7">
-        <v>50</v>
-      </c>
-      <c r="AD39" s="7">
-        <v>100</v>
-      </c>
+      <c r="AC39" s="7"/>
+      <c r="AD39" s="7"/>
       <c r="AE39" s="8"/>
       <c r="AF39" s="8"/>
       <c r="AG39" s="9" t="s">
@@ -4855,12 +4517,8 @@
       <c r="Z40" s="7"/>
       <c r="AA40" s="7"/>
       <c r="AB40" s="7"/>
-      <c r="AC40" s="7">
-        <v>50</v>
-      </c>
-      <c r="AD40" s="7">
-        <v>100</v>
-      </c>
+      <c r="AC40" s="7"/>
+      <c r="AD40" s="7"/>
       <c r="AE40" s="8"/>
       <c r="AF40" s="8"/>
       <c r="AG40" s="9" t="s">
@@ -4936,24 +4594,12 @@
       <c r="X41" s="7">
         <v>100</v>
       </c>
-      <c r="Y41" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z41" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA41" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB41" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC41" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD41" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y41" s="7"/>
+      <c r="Z41" s="7"/>
+      <c r="AA41" s="7"/>
+      <c r="AB41" s="7"/>
+      <c r="AC41" s="7"/>
+      <c r="AD41" s="7"/>
       <c r="AE41" s="8" t="s">
         <v>168</v>
       </c>
@@ -5035,24 +4681,12 @@
       <c r="X42" s="7">
         <v>100</v>
       </c>
-      <c r="Y42" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z42" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA42" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB42" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC42" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD42" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y42" s="7"/>
+      <c r="Z42" s="7"/>
+      <c r="AA42" s="7"/>
+      <c r="AB42" s="7"/>
+      <c r="AC42" s="7"/>
+      <c r="AD42" s="7"/>
       <c r="AE42" s="8" t="s">
         <v>171</v>
       </c>
@@ -5134,24 +4768,12 @@
       <c r="X43" s="7">
         <v>100</v>
       </c>
-      <c r="Y43" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z43" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA43" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB43" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC43" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD43" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y43" s="7"/>
+      <c r="Z43" s="7"/>
+      <c r="AA43" s="7"/>
+      <c r="AB43" s="7"/>
+      <c r="AC43" s="7"/>
+      <c r="AD43" s="7"/>
       <c r="AE43" s="8" t="s">
         <v>174</v>
       </c>
@@ -5229,24 +4851,12 @@
       <c r="X44" s="7">
         <v>45</v>
       </c>
-      <c r="Y44" s="7">
-        <v>55</v>
-      </c>
-      <c r="Z44" s="7">
-        <v>64</v>
-      </c>
-      <c r="AA44" s="7">
-        <v>73</v>
-      </c>
-      <c r="AB44" s="7">
-        <v>82</v>
-      </c>
-      <c r="AC44" s="7">
-        <v>91</v>
-      </c>
-      <c r="AD44" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y44" s="7"/>
+      <c r="Z44" s="7"/>
+      <c r="AA44" s="7"/>
+      <c r="AB44" s="7"/>
+      <c r="AC44" s="7"/>
+      <c r="AD44" s="7"/>
       <c r="AE44" s="8" t="s">
         <v>177</v>
       </c>
@@ -5304,24 +4914,12 @@
       <c r="V45" s="7"/>
       <c r="W45" s="7"/>
       <c r="X45" s="7"/>
-      <c r="Y45" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z45" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA45" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB45" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC45" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD45" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y45" s="7"/>
+      <c r="Z45" s="7"/>
+      <c r="AA45" s="7"/>
+      <c r="AB45" s="7"/>
+      <c r="AC45" s="7"/>
+      <c r="AD45" s="7"/>
       <c r="AE45" s="8"/>
       <c r="AF45" s="8"/>
       <c r="AG45" s="9" t="s">
@@ -5376,21 +4974,11 @@
       <c r="W46" s="7"/>
       <c r="X46" s="7"/>
       <c r="Y46" s="7"/>
-      <c r="Z46" s="7">
-        <v>50</v>
-      </c>
-      <c r="AA46" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB46" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC46" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD46" s="7">
-        <v>100</v>
-      </c>
+      <c r="Z46" s="7"/>
+      <c r="AA46" s="7"/>
+      <c r="AB46" s="7"/>
+      <c r="AC46" s="7"/>
+      <c r="AD46" s="7"/>
       <c r="AE46" s="8"/>
       <c r="AF46" s="8"/>
       <c r="AG46" s="9" t="s">
@@ -5444,18 +5032,10 @@
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="7"/>
-      <c r="AA47" s="7">
-        <v>50</v>
-      </c>
-      <c r="AB47" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC47" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD47" s="7">
-        <v>100</v>
-      </c>
+      <c r="AA47" s="7"/>
+      <c r="AB47" s="7"/>
+      <c r="AC47" s="7"/>
+      <c r="AD47" s="7"/>
       <c r="AE47" s="8"/>
       <c r="AF47" s="8"/>
       <c r="AG47" s="9" t="s">
@@ -5507,12 +5087,8 @@
       <c r="Z48" s="7"/>
       <c r="AA48" s="7"/>
       <c r="AB48" s="7"/>
-      <c r="AC48" s="7">
-        <v>50</v>
-      </c>
-      <c r="AD48" s="7">
-        <v>100</v>
-      </c>
+      <c r="AC48" s="7"/>
+      <c r="AD48" s="7"/>
       <c r="AE48" s="8"/>
       <c r="AF48" s="8"/>
       <c r="AG48" s="9" t="s">
@@ -5592,24 +5168,12 @@
       <c r="X49" s="7">
         <v>100</v>
       </c>
-      <c r="Y49" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z49" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA49" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB49" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC49" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD49" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y49" s="7"/>
+      <c r="Z49" s="7"/>
+      <c r="AA49" s="7"/>
+      <c r="AB49" s="7"/>
+      <c r="AC49" s="7"/>
+      <c r="AD49" s="7"/>
       <c r="AE49" s="8" t="s">
         <v>190</v>
       </c>
@@ -5687,24 +5251,12 @@
       <c r="X50" s="7">
         <v>100</v>
       </c>
-      <c r="Y50" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z50" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA50" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB50" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC50" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD50" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y50" s="7"/>
+      <c r="Z50" s="7"/>
+      <c r="AA50" s="7"/>
+      <c r="AB50" s="7"/>
+      <c r="AC50" s="7"/>
+      <c r="AD50" s="7"/>
       <c r="AE50" s="8" t="s">
         <v>193</v>
       </c>
@@ -5774,24 +5326,12 @@
       <c r="X51" s="7">
         <v>100</v>
       </c>
-      <c r="Y51" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z51" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA51" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB51" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC51" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD51" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y51" s="7"/>
+      <c r="Z51" s="7"/>
+      <c r="AA51" s="7"/>
+      <c r="AB51" s="7"/>
+      <c r="AC51" s="7"/>
+      <c r="AD51" s="7"/>
       <c r="AE51" s="8" t="s">
         <v>196</v>
       </c>
@@ -5857,24 +5397,12 @@
       <c r="X52" s="7">
         <v>100</v>
       </c>
-      <c r="Y52" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z52" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA52" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB52" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC52" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD52" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y52" s="7"/>
+      <c r="Z52" s="7"/>
+      <c r="AA52" s="7"/>
+      <c r="AB52" s="7"/>
+      <c r="AC52" s="7"/>
+      <c r="AD52" s="7"/>
       <c r="AE52" s="8" t="s">
         <v>198</v>
       </c>
@@ -5956,24 +5484,12 @@
       <c r="X53" s="7">
         <v>100</v>
       </c>
-      <c r="Y53" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z53" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA53" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB53" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC53" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD53" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y53" s="7"/>
+      <c r="Z53" s="7"/>
+      <c r="AA53" s="7"/>
+      <c r="AB53" s="7"/>
+      <c r="AC53" s="7"/>
+      <c r="AD53" s="7"/>
       <c r="AE53" s="8" t="s">
         <v>203</v>
       </c>
@@ -6047,24 +5563,12 @@
       <c r="X54" s="7">
         <v>100</v>
       </c>
-      <c r="Y54" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z54" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA54" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB54" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC54" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD54" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y54" s="7"/>
+      <c r="Z54" s="7"/>
+      <c r="AA54" s="7"/>
+      <c r="AB54" s="7"/>
+      <c r="AC54" s="7"/>
+      <c r="AD54" s="7"/>
       <c r="AE54" s="8" t="s">
         <v>206</v>
       </c>
@@ -6134,24 +5638,12 @@
       <c r="X55" s="7">
         <v>43</v>
       </c>
-      <c r="Y55" s="7">
-        <v>57</v>
-      </c>
-      <c r="Z55" s="7">
-        <v>71</v>
-      </c>
-      <c r="AA55" s="7">
-        <v>86</v>
-      </c>
-      <c r="AB55" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC55" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD55" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y55" s="7"/>
+      <c r="Z55" s="7"/>
+      <c r="AA55" s="7"/>
+      <c r="AB55" s="7"/>
+      <c r="AC55" s="7"/>
+      <c r="AD55" s="7"/>
       <c r="AE55" s="8" t="s">
         <v>209</v>
       </c>
@@ -6206,15 +5698,9 @@
       <c r="Y56" s="7"/>
       <c r="Z56" s="7"/>
       <c r="AA56" s="7"/>
-      <c r="AB56" s="7">
-        <v>50</v>
-      </c>
-      <c r="AC56" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD56" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB56" s="7"/>
+      <c r="AC56" s="7"/>
+      <c r="AD56" s="7"/>
       <c r="AE56" s="8"/>
       <c r="AF56" s="8"/>
       <c r="AG56" s="9" t="s">
@@ -6266,12 +5752,8 @@
       <c r="Z57" s="7"/>
       <c r="AA57" s="7"/>
       <c r="AB57" s="7"/>
-      <c r="AC57" s="7">
-        <v>50</v>
-      </c>
-      <c r="AD57" s="7">
-        <v>100</v>
-      </c>
+      <c r="AC57" s="7"/>
+      <c r="AD57" s="7"/>
       <c r="AE57" s="8"/>
       <c r="AF57" s="8"/>
       <c r="AG57" s="9" t="s">
@@ -6322,9 +5804,7 @@
       <c r="AA58" s="7"/>
       <c r="AB58" s="7"/>
       <c r="AC58" s="7"/>
-      <c r="AD58" s="7">
-        <v>100</v>
-      </c>
+      <c r="AD58" s="7"/>
       <c r="AE58" s="8"/>
       <c r="AF58" s="8"/>
       <c r="AG58" s="9" t="s">
@@ -6396,24 +5876,12 @@
       <c r="X59" s="7">
         <v>100</v>
       </c>
-      <c r="Y59" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z59" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA59" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB59" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC59" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD59" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y59" s="7"/>
+      <c r="Z59" s="7"/>
+      <c r="AA59" s="7"/>
+      <c r="AB59" s="7"/>
+      <c r="AC59" s="7"/>
+      <c r="AD59" s="7"/>
       <c r="AE59" s="8" t="s">
         <v>220</v>
       </c>
@@ -6483,24 +5951,12 @@
       <c r="X60" s="7">
         <v>100</v>
       </c>
-      <c r="Y60" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z60" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA60" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB60" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC60" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD60" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y60" s="7"/>
+      <c r="Z60" s="7"/>
+      <c r="AA60" s="7"/>
+      <c r="AB60" s="7"/>
+      <c r="AC60" s="7"/>
+      <c r="AD60" s="7"/>
       <c r="AE60" s="8" t="s">
         <v>224</v>
       </c>
@@ -6566,24 +6022,12 @@
       <c r="X61" s="7">
         <v>100</v>
       </c>
-      <c r="Y61" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z61" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA61" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB61" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC61" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD61" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y61" s="7"/>
+      <c r="Z61" s="7"/>
+      <c r="AA61" s="7"/>
+      <c r="AB61" s="7"/>
+      <c r="AC61" s="7"/>
+      <c r="AD61" s="7"/>
       <c r="AE61" s="8" t="s">
         <v>227</v>
       </c>
@@ -6665,24 +6109,12 @@
       <c r="X62" s="7">
         <v>86</v>
       </c>
-      <c r="Y62" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z62" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA62" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB62" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC62" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD62" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y62" s="7"/>
+      <c r="Z62" s="7"/>
+      <c r="AA62" s="7"/>
+      <c r="AB62" s="7"/>
+      <c r="AC62" s="7"/>
+      <c r="AD62" s="7"/>
       <c r="AE62" s="8" t="s">
         <v>230</v>
       </c>
@@ -6740,24 +6172,12 @@
       <c r="V63" s="7"/>
       <c r="W63" s="7"/>
       <c r="X63" s="7"/>
-      <c r="Y63" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z63" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA63" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB63" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC63" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD63" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y63" s="7"/>
+      <c r="Z63" s="7"/>
+      <c r="AA63" s="7"/>
+      <c r="AB63" s="7"/>
+      <c r="AC63" s="7"/>
+      <c r="AD63" s="7"/>
       <c r="AE63" s="8"/>
       <c r="AF63" s="8"/>
       <c r="AG63" s="9" t="s">
@@ -6837,24 +6257,12 @@
       <c r="X64" s="7">
         <v>100</v>
       </c>
-      <c r="Y64" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z64" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA64" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB64" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC64" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD64" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y64" s="7"/>
+      <c r="Z64" s="7"/>
+      <c r="AA64" s="7"/>
+      <c r="AB64" s="7"/>
+      <c r="AC64" s="7"/>
+      <c r="AD64" s="7"/>
       <c r="AE64" s="8" t="s">
         <v>235</v>
       </c>
@@ -6932,24 +6340,12 @@
       <c r="X65" s="7">
         <v>45</v>
       </c>
-      <c r="Y65" s="7">
-        <v>55</v>
-      </c>
-      <c r="Z65" s="7">
-        <v>64</v>
-      </c>
-      <c r="AA65" s="7">
-        <v>73</v>
-      </c>
-      <c r="AB65" s="7">
-        <v>82</v>
-      </c>
-      <c r="AC65" s="7">
-        <v>91</v>
-      </c>
-      <c r="AD65" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y65" s="7"/>
+      <c r="Z65" s="7"/>
+      <c r="AA65" s="7"/>
+      <c r="AB65" s="7"/>
+      <c r="AC65" s="7"/>
+      <c r="AD65" s="7"/>
       <c r="AE65" s="8" t="s">
         <v>238</v>
       </c>
@@ -7023,24 +6419,12 @@
       <c r="X66" s="7">
         <v>100</v>
       </c>
-      <c r="Y66" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z66" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA66" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB66" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC66" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD66" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y66" s="7"/>
+      <c r="Z66" s="7"/>
+      <c r="AA66" s="7"/>
+      <c r="AB66" s="7"/>
+      <c r="AC66" s="7"/>
+      <c r="AD66" s="7"/>
       <c r="AE66" s="8" t="s">
         <v>241</v>
       </c>
@@ -7110,24 +6494,12 @@
       <c r="X67" s="7">
         <v>100</v>
       </c>
-      <c r="Y67" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z67" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA67" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB67" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC67" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD67" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y67" s="7"/>
+      <c r="Z67" s="7"/>
+      <c r="AA67" s="7"/>
+      <c r="AB67" s="7"/>
+      <c r="AC67" s="7"/>
+      <c r="AD67" s="7"/>
       <c r="AE67" s="8" t="s">
         <v>245</v>
       </c>
@@ -7189,24 +6561,12 @@
       <c r="X68" s="7">
         <v>50</v>
       </c>
-      <c r="Y68" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z68" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA68" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB68" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC68" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD68" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y68" s="7"/>
+      <c r="Z68" s="7"/>
+      <c r="AA68" s="7"/>
+      <c r="AB68" s="7"/>
+      <c r="AC68" s="7"/>
+      <c r="AD68" s="7"/>
       <c r="AE68" s="8" t="s">
         <v>248</v>
       </c>
@@ -7278,24 +6638,12 @@
       <c r="X69" s="7">
         <v>100</v>
       </c>
-      <c r="Y69" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z69" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA69" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB69" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC69" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD69" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y69" s="7"/>
+      <c r="Z69" s="7"/>
+      <c r="AA69" s="7"/>
+      <c r="AB69" s="7"/>
+      <c r="AC69" s="7"/>
+      <c r="AD69" s="7"/>
       <c r="AE69" s="8" t="s">
         <v>252</v>
       </c>
@@ -7355,24 +6703,12 @@
       <c r="V70" s="7"/>
       <c r="W70" s="7"/>
       <c r="X70" s="7"/>
-      <c r="Y70" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z70" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA70" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB70" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC70" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD70" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y70" s="7"/>
+      <c r="Z70" s="7"/>
+      <c r="AA70" s="7"/>
+      <c r="AB70" s="7"/>
+      <c r="AC70" s="7"/>
+      <c r="AD70" s="7"/>
       <c r="AE70" s="8"/>
       <c r="AF70" s="8"/>
       <c r="AG70" s="9" t="s">
@@ -7436,24 +6772,12 @@
       <c r="X71" s="7">
         <v>67</v>
       </c>
-      <c r="Y71" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z71" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA71" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB71" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC71" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD71" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y71" s="7"/>
+      <c r="Z71" s="7"/>
+      <c r="AA71" s="7"/>
+      <c r="AB71" s="7"/>
+      <c r="AC71" s="7"/>
+      <c r="AD71" s="7"/>
       <c r="AE71" s="8" t="s">
         <v>258</v>
       </c>
@@ -7515,24 +6839,12 @@
       <c r="X72" s="7">
         <v>100</v>
       </c>
-      <c r="Y72" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z72" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA72" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB72" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC72" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD72" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y72" s="7"/>
+      <c r="Z72" s="7"/>
+      <c r="AA72" s="7"/>
+      <c r="AB72" s="7"/>
+      <c r="AC72" s="7"/>
+      <c r="AD72" s="7"/>
       <c r="AE72" s="8" t="s">
         <v>262</v>
       </c>
@@ -7594,24 +6906,12 @@
       <c r="X73" s="7">
         <v>50</v>
       </c>
-      <c r="Y73" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z73" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA73" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB73" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC73" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD73" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y73" s="7"/>
+      <c r="Z73" s="7"/>
+      <c r="AA73" s="7"/>
+      <c r="AB73" s="7"/>
+      <c r="AC73" s="7"/>
+      <c r="AD73" s="7"/>
       <c r="AE73" s="8" t="s">
         <v>265</v>
       </c>
@@ -7669,24 +6969,12 @@
       <c r="V74" s="7"/>
       <c r="W74" s="7"/>
       <c r="X74" s="7"/>
-      <c r="Y74" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z74" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA74" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB74" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC74" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD74" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y74" s="7"/>
+      <c r="Z74" s="7"/>
+      <c r="AA74" s="7"/>
+      <c r="AB74" s="7"/>
+      <c r="AC74" s="7"/>
+      <c r="AD74" s="7"/>
       <c r="AE74" s="8"/>
       <c r="AF74" s="8"/>
       <c r="AG74" s="9" t="s">
@@ -7746,24 +7034,12 @@
       <c r="X75" s="7">
         <v>100</v>
       </c>
-      <c r="Y75" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z75" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA75" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB75" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC75" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD75" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y75" s="7"/>
+      <c r="Z75" s="7"/>
+      <c r="AA75" s="7"/>
+      <c r="AB75" s="7"/>
+      <c r="AC75" s="7"/>
+      <c r="AD75" s="7"/>
       <c r="AE75" s="8" t="s">
         <v>271</v>
       </c>
@@ -7827,24 +7103,12 @@
       <c r="X76" s="7">
         <v>33</v>
       </c>
-      <c r="Y76" s="7">
-        <v>67</v>
-      </c>
-      <c r="Z76" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA76" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB76" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC76" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD76" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y76" s="7"/>
+      <c r="Z76" s="7"/>
+      <c r="AA76" s="7"/>
+      <c r="AB76" s="7"/>
+      <c r="AC76" s="7"/>
+      <c r="AD76" s="7"/>
       <c r="AE76" s="8" t="s">
         <v>274</v>
       </c>
@@ -7902,18 +7166,10 @@
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
       <c r="Z77" s="7"/>
-      <c r="AA77" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB77" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC77" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD77" s="7">
-        <v>100</v>
-      </c>
+      <c r="AA77" s="7"/>
+      <c r="AB77" s="7"/>
+      <c r="AC77" s="7"/>
+      <c r="AD77" s="7"/>
       <c r="AE77" s="8"/>
       <c r="AF77" s="8"/>
       <c r="AG77" s="9" t="s">
@@ -7993,24 +7249,12 @@
       <c r="X78" s="7">
         <v>50</v>
       </c>
-      <c r="Y78" s="7">
-        <v>58</v>
-      </c>
-      <c r="Z78" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA78" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB78" s="7">
-        <v>83</v>
-      </c>
-      <c r="AC78" s="7">
-        <v>92</v>
-      </c>
-      <c r="AD78" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y78" s="7"/>
+      <c r="Z78" s="7"/>
+      <c r="AA78" s="7"/>
+      <c r="AB78" s="7"/>
+      <c r="AC78" s="7"/>
+      <c r="AD78" s="7"/>
       <c r="AE78" s="8" t="s">
         <v>282</v>
       </c>
@@ -8072,24 +7316,12 @@
       <c r="X79" s="7">
         <v>25</v>
       </c>
-      <c r="Y79" s="7">
-        <v>50</v>
-      </c>
-      <c r="Z79" s="7">
-        <v>50</v>
-      </c>
-      <c r="AA79" s="7">
-        <v>50</v>
-      </c>
-      <c r="AB79" s="7">
-        <v>50</v>
-      </c>
-      <c r="AC79" s="7">
-        <v>75</v>
-      </c>
-      <c r="AD79" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y79" s="7"/>
+      <c r="Z79" s="7"/>
+      <c r="AA79" s="7"/>
+      <c r="AB79" s="7"/>
+      <c r="AC79" s="7"/>
+      <c r="AD79" s="7"/>
       <c r="AE79" s="8" t="s">
         <v>284</v>
       </c>
@@ -8157,24 +7389,12 @@
       <c r="X80" s="7">
         <v>67</v>
       </c>
-      <c r="Y80" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z80" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA80" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB80" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC80" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD80" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y80" s="7"/>
+      <c r="Z80" s="7"/>
+      <c r="AA80" s="7"/>
+      <c r="AB80" s="7"/>
+      <c r="AC80" s="7"/>
+      <c r="AD80" s="7"/>
       <c r="AE80" s="8" t="s">
         <v>287</v>
       </c>
@@ -8238,24 +7458,12 @@
       <c r="X81" s="7">
         <v>33</v>
       </c>
-      <c r="Y81" s="7">
-        <v>67</v>
-      </c>
-      <c r="Z81" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA81" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB81" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC81" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD81" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y81" s="7"/>
+      <c r="Z81" s="7"/>
+      <c r="AA81" s="7"/>
+      <c r="AB81" s="7"/>
+      <c r="AC81" s="7"/>
+      <c r="AD81" s="7"/>
       <c r="AE81" s="8" t="s">
         <v>291</v>
       </c>
@@ -8317,24 +7525,12 @@
       <c r="X82" s="7">
         <v>33</v>
       </c>
-      <c r="Y82" s="7">
-        <v>67</v>
-      </c>
-      <c r="Z82" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA82" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB82" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC82" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD82" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y82" s="7"/>
+      <c r="Z82" s="7"/>
+      <c r="AA82" s="7"/>
+      <c r="AB82" s="7"/>
+      <c r="AC82" s="7"/>
+      <c r="AD82" s="7"/>
       <c r="AE82" s="8" t="s">
         <v>294</v>
       </c>
@@ -8392,24 +7588,12 @@
       <c r="V83" s="7"/>
       <c r="W83" s="7"/>
       <c r="X83" s="7"/>
-      <c r="Y83" s="7">
-        <v>33</v>
-      </c>
-      <c r="Z83" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA83" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB83" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC83" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD83" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y83" s="7"/>
+      <c r="Z83" s="7"/>
+      <c r="AA83" s="7"/>
+      <c r="AB83" s="7"/>
+      <c r="AC83" s="7"/>
+      <c r="AD83" s="7"/>
       <c r="AE83" s="8"/>
       <c r="AF83" s="8"/>
       <c r="AG83" s="9" t="s">
@@ -8463,18 +7647,10 @@
       <c r="X84" s="7"/>
       <c r="Y84" s="7"/>
       <c r="Z84" s="7"/>
-      <c r="AA84" s="7">
-        <v>50</v>
-      </c>
-      <c r="AB84" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC84" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD84" s="7">
-        <v>100</v>
-      </c>
+      <c r="AA84" s="7"/>
+      <c r="AB84" s="7"/>
+      <c r="AC84" s="7"/>
+      <c r="AD84" s="7"/>
       <c r="AE84" s="8"/>
       <c r="AF84" s="8"/>
       <c r="AG84" s="9" t="s">
@@ -8528,18 +7704,10 @@
       <c r="X85" s="7"/>
       <c r="Y85" s="7"/>
       <c r="Z85" s="7"/>
-      <c r="AA85" s="7">
-        <v>33</v>
-      </c>
-      <c r="AB85" s="7">
-        <v>67</v>
-      </c>
-      <c r="AC85" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD85" s="7">
-        <v>100</v>
-      </c>
+      <c r="AA85" s="7"/>
+      <c r="AB85" s="7"/>
+      <c r="AC85" s="7"/>
+      <c r="AD85" s="7"/>
       <c r="AE85" s="8"/>
       <c r="AF85" s="8"/>
       <c r="AG85" s="9" t="s">
@@ -8594,21 +7762,11 @@
       <c r="W86" s="7"/>
       <c r="X86" s="7"/>
       <c r="Y86" s="7"/>
-      <c r="Z86" s="7">
-        <v>25</v>
-      </c>
-      <c r="AA86" s="7">
-        <v>50</v>
-      </c>
-      <c r="AB86" s="7">
-        <v>75</v>
-      </c>
-      <c r="AC86" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD86" s="7">
-        <v>100</v>
-      </c>
+      <c r="Z86" s="7"/>
+      <c r="AA86" s="7"/>
+      <c r="AB86" s="7"/>
+      <c r="AC86" s="7"/>
+      <c r="AD86" s="7"/>
       <c r="AE86" s="8"/>
       <c r="AF86" s="8"/>
       <c r="AG86" s="9" t="s">
@@ -8663,21 +7821,11 @@
       <c r="W87" s="7"/>
       <c r="X87" s="7"/>
       <c r="Y87" s="7"/>
-      <c r="Z87" s="7">
-        <v>25</v>
-      </c>
-      <c r="AA87" s="7">
-        <v>50</v>
-      </c>
-      <c r="AB87" s="7">
-        <v>75</v>
-      </c>
-      <c r="AC87" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD87" s="7">
-        <v>100</v>
-      </c>
+      <c r="Z87" s="7"/>
+      <c r="AA87" s="7"/>
+      <c r="AB87" s="7"/>
+      <c r="AC87" s="7"/>
+      <c r="AD87" s="7"/>
       <c r="AE87" s="8"/>
       <c r="AF87" s="8"/>
       <c r="AG87" s="9" t="s">
@@ -8757,24 +7905,12 @@
       <c r="X88" s="7">
         <v>50</v>
       </c>
-      <c r="Y88" s="7">
-        <v>58</v>
-      </c>
-      <c r="Z88" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA88" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB88" s="7">
-        <v>83</v>
-      </c>
-      <c r="AC88" s="7">
-        <v>92</v>
-      </c>
-      <c r="AD88" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y88" s="7"/>
+      <c r="Z88" s="7"/>
+      <c r="AA88" s="7"/>
+      <c r="AB88" s="7"/>
+      <c r="AC88" s="7"/>
+      <c r="AD88" s="7"/>
       <c r="AE88" s="8" t="s">
         <v>311</v>
       </c>
@@ -8856,24 +7992,12 @@
       <c r="X89" s="7">
         <v>50</v>
       </c>
-      <c r="Y89" s="7">
-        <v>58</v>
-      </c>
-      <c r="Z89" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA89" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB89" s="7">
-        <v>83</v>
-      </c>
-      <c r="AC89" s="7">
-        <v>92</v>
-      </c>
-      <c r="AD89" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y89" s="7"/>
+      <c r="Z89" s="7"/>
+      <c r="AA89" s="7"/>
+      <c r="AB89" s="7"/>
+      <c r="AC89" s="7"/>
+      <c r="AD89" s="7"/>
       <c r="AE89" s="8" t="s">
         <v>314</v>
       </c>
@@ -8943,24 +8067,12 @@
       <c r="X90" s="7">
         <v>25</v>
       </c>
-      <c r="Y90" s="7">
-        <v>50</v>
-      </c>
-      <c r="Z90" s="7">
-        <v>50</v>
-      </c>
-      <c r="AA90" s="7">
-        <v>50</v>
-      </c>
-      <c r="AB90" s="7">
-        <v>75</v>
-      </c>
-      <c r="AC90" s="7">
-        <v>75</v>
-      </c>
-      <c r="AD90" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y90" s="7"/>
+      <c r="Z90" s="7"/>
+      <c r="AA90" s="7"/>
+      <c r="AB90" s="7"/>
+      <c r="AC90" s="7"/>
+      <c r="AD90" s="7"/>
       <c r="AE90" s="8" t="s">
         <v>317</v>
       </c>
@@ -9042,24 +8154,12 @@
       <c r="X91" s="7">
         <v>50</v>
       </c>
-      <c r="Y91" s="7">
-        <v>58</v>
-      </c>
-      <c r="Z91" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA91" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB91" s="7">
-        <v>83</v>
-      </c>
-      <c r="AC91" s="7">
-        <v>92</v>
-      </c>
-      <c r="AD91" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y91" s="7"/>
+      <c r="Z91" s="7"/>
+      <c r="AA91" s="7"/>
+      <c r="AB91" s="7"/>
+      <c r="AC91" s="7"/>
+      <c r="AD91" s="7"/>
       <c r="AE91" s="8" t="s">
         <v>321</v>
       </c>
@@ -9114,15 +8214,9 @@
       <c r="Y92" s="7"/>
       <c r="Z92" s="7"/>
       <c r="AA92" s="7"/>
-      <c r="AB92" s="7">
-        <v>33</v>
-      </c>
-      <c r="AC92" s="7">
-        <v>67</v>
-      </c>
-      <c r="AD92" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB92" s="7"/>
+      <c r="AC92" s="7"/>
+      <c r="AD92" s="7"/>
       <c r="AE92" s="8"/>
       <c r="AF92" s="8"/>
       <c r="AG92" s="9" t="s">
@@ -9175,15 +8269,9 @@
       <c r="Y93" s="7"/>
       <c r="Z93" s="7"/>
       <c r="AA93" s="7"/>
-      <c r="AB93" s="7">
-        <v>33</v>
-      </c>
-      <c r="AC93" s="7">
-        <v>67</v>
-      </c>
-      <c r="AD93" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB93" s="7"/>
+      <c r="AC93" s="7"/>
+      <c r="AD93" s="7"/>
       <c r="AE93" s="8"/>
       <c r="AF93" s="8"/>
       <c r="AG93" s="9" t="s">
@@ -9236,15 +8324,9 @@
       <c r="Y94" s="7"/>
       <c r="Z94" s="7"/>
       <c r="AA94" s="7"/>
-      <c r="AB94" s="7">
-        <v>33</v>
-      </c>
-      <c r="AC94" s="7">
-        <v>67</v>
-      </c>
-      <c r="AD94" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB94" s="7"/>
+      <c r="AC94" s="7"/>
+      <c r="AD94" s="7"/>
       <c r="AE94" s="8"/>
       <c r="AF94" s="8"/>
       <c r="AG94" s="9" t="s">
@@ -9295,9 +8377,7 @@
       <c r="AA95" s="7"/>
       <c r="AB95" s="7"/>
       <c r="AC95" s="7"/>
-      <c r="AD95" s="7">
-        <v>100</v>
-      </c>
+      <c r="AD95" s="7"/>
       <c r="AE95" s="8"/>
       <c r="AF95" s="8"/>
       <c r="AG95" s="9" t="s">
@@ -9377,24 +8457,12 @@
       <c r="X96" s="7">
         <v>100</v>
       </c>
-      <c r="Y96" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z96" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA96" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB96" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC96" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD96" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y96" s="7"/>
+      <c r="Z96" s="7"/>
+      <c r="AA96" s="7"/>
+      <c r="AB96" s="7"/>
+      <c r="AC96" s="7"/>
+      <c r="AD96" s="7"/>
       <c r="AE96" s="8" t="s">
         <v>335</v>
       </c>
@@ -9468,24 +8536,12 @@
       <c r="X97" s="7">
         <v>100</v>
       </c>
-      <c r="Y97" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z97" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA97" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB97" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC97" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD97" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y97" s="7"/>
+      <c r="Z97" s="7"/>
+      <c r="AA97" s="7"/>
+      <c r="AB97" s="7"/>
+      <c r="AC97" s="7"/>
+      <c r="AD97" s="7"/>
       <c r="AE97" s="8" t="s">
         <v>338</v>
       </c>
@@ -9551,24 +8607,12 @@
       <c r="X98" s="7">
         <v>67</v>
       </c>
-      <c r="Y98" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z98" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA98" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB98" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC98" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD98" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y98" s="7"/>
+      <c r="Z98" s="7"/>
+      <c r="AA98" s="7"/>
+      <c r="AB98" s="7"/>
+      <c r="AC98" s="7"/>
+      <c r="AD98" s="7"/>
       <c r="AE98" s="8" t="s">
         <v>341</v>
       </c>
@@ -9626,24 +8670,12 @@
       <c r="V99" s="7"/>
       <c r="W99" s="7"/>
       <c r="X99" s="7"/>
-      <c r="Y99" s="7">
-        <v>33</v>
-      </c>
-      <c r="Z99" s="7">
-        <v>67</v>
-      </c>
-      <c r="AA99" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB99" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC99" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD99" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y99" s="7"/>
+      <c r="Z99" s="7"/>
+      <c r="AA99" s="7"/>
+      <c r="AB99" s="7"/>
+      <c r="AC99" s="7"/>
+      <c r="AD99" s="7"/>
       <c r="AE99" s="8"/>
       <c r="AF99" s="8"/>
       <c r="AG99" s="9" t="s">
@@ -9696,15 +8728,9 @@
       <c r="Y100" s="7"/>
       <c r="Z100" s="7"/>
       <c r="AA100" s="7"/>
-      <c r="AB100" s="7">
-        <v>33</v>
-      </c>
-      <c r="AC100" s="7">
-        <v>67</v>
-      </c>
-      <c r="AD100" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB100" s="7"/>
+      <c r="AC100" s="7"/>
+      <c r="AD100" s="7"/>
       <c r="AE100" s="8"/>
       <c r="AF100" s="8"/>
       <c r="AG100" s="9" t="s">
@@ -9776,24 +8802,12 @@
       <c r="X101" s="7">
         <v>100</v>
       </c>
-      <c r="Y101" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z101" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA101" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB101" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC101" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD101" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y101" s="7"/>
+      <c r="Z101" s="7"/>
+      <c r="AA101" s="7"/>
+      <c r="AB101" s="7"/>
+      <c r="AC101" s="7"/>
+      <c r="AD101" s="7"/>
       <c r="AE101" s="8" t="s">
         <v>349</v>
       </c>
@@ -9863,24 +8877,12 @@
       <c r="X102" s="7">
         <v>100</v>
       </c>
-      <c r="Y102" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z102" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA102" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB102" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC102" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD102" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y102" s="7"/>
+      <c r="Z102" s="7"/>
+      <c r="AA102" s="7"/>
+      <c r="AB102" s="7"/>
+      <c r="AC102" s="7"/>
+      <c r="AD102" s="7"/>
       <c r="AE102" s="8" t="s">
         <v>352</v>
       </c>
@@ -9950,24 +8952,12 @@
       <c r="X103" s="7">
         <v>33</v>
       </c>
-      <c r="Y103" s="7">
-        <v>44</v>
-      </c>
-      <c r="Z103" s="7">
-        <v>56</v>
-      </c>
-      <c r="AA103" s="7">
-        <v>67</v>
-      </c>
-      <c r="AB103" s="7">
-        <v>78</v>
-      </c>
-      <c r="AC103" s="7">
-        <v>89</v>
-      </c>
-      <c r="AD103" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y103" s="7"/>
+      <c r="Z103" s="7"/>
+      <c r="AA103" s="7"/>
+      <c r="AB103" s="7"/>
+      <c r="AC103" s="7"/>
+      <c r="AD103" s="7"/>
       <c r="AE103" s="8" t="s">
         <v>355</v>
       </c>
@@ -10037,24 +9027,12 @@
       <c r="X104" s="7">
         <v>33</v>
       </c>
-      <c r="Y104" s="7">
-        <v>44</v>
-      </c>
-      <c r="Z104" s="7">
-        <v>56</v>
-      </c>
-      <c r="AA104" s="7">
-        <v>67</v>
-      </c>
-      <c r="AB104" s="7">
-        <v>78</v>
-      </c>
-      <c r="AC104" s="7">
-        <v>89</v>
-      </c>
-      <c r="AD104" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y104" s="7"/>
+      <c r="Z104" s="7"/>
+      <c r="AA104" s="7"/>
+      <c r="AB104" s="7"/>
+      <c r="AC104" s="7"/>
+      <c r="AD104" s="7"/>
       <c r="AE104" s="8" t="s">
         <v>358</v>
       </c>
@@ -10128,24 +9106,12 @@
       <c r="X105" s="7">
         <v>100</v>
       </c>
-      <c r="Y105" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z105" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA105" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB105" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC105" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD105" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y105" s="7"/>
+      <c r="Z105" s="7"/>
+      <c r="AA105" s="7"/>
+      <c r="AB105" s="7"/>
+      <c r="AC105" s="7"/>
+      <c r="AD105" s="7"/>
       <c r="AE105" s="8" t="s">
         <v>362</v>
       </c>
@@ -10219,24 +9185,12 @@
       <c r="X106" s="7">
         <v>100</v>
       </c>
-      <c r="Y106" s="7">
-        <v>100</v>
-      </c>
-      <c r="Z106" s="7">
-        <v>100</v>
-      </c>
-      <c r="AA106" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB106" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC106" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD106" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y106" s="7"/>
+      <c r="Z106" s="7"/>
+      <c r="AA106" s="7"/>
+      <c r="AB106" s="7"/>
+      <c r="AC106" s="7"/>
+      <c r="AD106" s="7"/>
       <c r="AE106" s="8" t="s">
         <v>365</v>
       </c>
@@ -10306,24 +9260,12 @@
       <c r="X107" s="7">
         <v>50</v>
       </c>
-      <c r="Y107" s="7">
-        <v>67</v>
-      </c>
-      <c r="Z107" s="7">
-        <v>83</v>
-      </c>
-      <c r="AA107" s="7">
-        <v>100</v>
-      </c>
-      <c r="AB107" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC107" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD107" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y107" s="7"/>
+      <c r="Z107" s="7"/>
+      <c r="AA107" s="7"/>
+      <c r="AB107" s="7"/>
+      <c r="AC107" s="7"/>
+      <c r="AD107" s="7"/>
       <c r="AE107" s="8" t="s">
         <v>368</v>
       </c>
@@ -10378,15 +9320,9 @@
       <c r="Y108" s="7"/>
       <c r="Z108" s="7"/>
       <c r="AA108" s="7"/>
-      <c r="AB108" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC108" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD108" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB108" s="7"/>
+      <c r="AC108" s="7"/>
+      <c r="AD108" s="7"/>
       <c r="AE108" s="8"/>
       <c r="AF108" s="8"/>
       <c r="AG108" s="9" t="s">
@@ -10438,12 +9374,8 @@
       <c r="Z109" s="7"/>
       <c r="AA109" s="7"/>
       <c r="AB109" s="7"/>
-      <c r="AC109" s="7">
-        <v>50</v>
-      </c>
-      <c r="AD109" s="7">
-        <v>100</v>
-      </c>
+      <c r="AC109" s="7"/>
+      <c r="AD109" s="7"/>
       <c r="AE109" s="8"/>
       <c r="AF109" s="8"/>
       <c r="AG109" s="9" t="s">
@@ -10523,24 +9455,12 @@
       <c r="X110" s="7">
         <v>60</v>
       </c>
-      <c r="Y110" s="7">
-        <v>70</v>
-      </c>
-      <c r="Z110" s="7">
-        <v>80</v>
-      </c>
-      <c r="AA110" s="7">
-        <v>90</v>
-      </c>
-      <c r="AB110" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC110" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD110" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y110" s="7"/>
+      <c r="Z110" s="7"/>
+      <c r="AA110" s="7"/>
+      <c r="AB110" s="7"/>
+      <c r="AC110" s="7"/>
+      <c r="AD110" s="7"/>
       <c r="AE110" s="8" t="s">
         <v>376</v>
       </c>
@@ -10618,24 +9538,12 @@
       <c r="X111" s="7">
         <v>50</v>
       </c>
-      <c r="Y111" s="7">
-        <v>60</v>
-      </c>
-      <c r="Z111" s="7">
-        <v>70</v>
-      </c>
-      <c r="AA111" s="7">
-        <v>80</v>
-      </c>
-      <c r="AB111" s="7">
-        <v>90</v>
-      </c>
-      <c r="AC111" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD111" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y111" s="7"/>
+      <c r="Z111" s="7"/>
+      <c r="AA111" s="7"/>
+      <c r="AB111" s="7"/>
+      <c r="AC111" s="7"/>
+      <c r="AD111" s="7"/>
       <c r="AE111" s="8" t="s">
         <v>379</v>
       </c>
@@ -10715,24 +9623,12 @@
       <c r="X112" s="7">
         <v>50</v>
       </c>
-      <c r="Y112" s="7">
-        <v>60</v>
-      </c>
-      <c r="Z112" s="7">
-        <v>70</v>
-      </c>
-      <c r="AA112" s="7">
-        <v>80</v>
-      </c>
-      <c r="AB112" s="7">
-        <v>90</v>
-      </c>
-      <c r="AC112" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD112" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y112" s="7"/>
+      <c r="Z112" s="7"/>
+      <c r="AA112" s="7"/>
+      <c r="AB112" s="7"/>
+      <c r="AC112" s="7"/>
+      <c r="AD112" s="7"/>
       <c r="AE112" s="8" t="s">
         <v>382</v>
       </c>
@@ -10786,12 +9682,8 @@
       <c r="Z113" s="7"/>
       <c r="AA113" s="7"/>
       <c r="AB113" s="7"/>
-      <c r="AC113" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD113" s="7">
-        <v>100</v>
-      </c>
+      <c r="AC113" s="7"/>
+      <c r="AD113" s="7"/>
       <c r="AE113" s="8"/>
       <c r="AF113" s="8"/>
       <c r="AG113" s="9" t="s">
@@ -10844,15 +9736,9 @@
       <c r="Y114" s="7"/>
       <c r="Z114" s="7"/>
       <c r="AA114" s="7"/>
-      <c r="AB114" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC114" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD114" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB114" s="7"/>
+      <c r="AC114" s="7"/>
+      <c r="AD114" s="7"/>
       <c r="AE114" s="8"/>
       <c r="AF114" s="8"/>
       <c r="AG114" s="9" t="s">
@@ -10905,15 +9791,9 @@
       <c r="Y115" s="7"/>
       <c r="Z115" s="7"/>
       <c r="AA115" s="7"/>
-      <c r="AB115" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC115" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD115" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB115" s="7"/>
+      <c r="AC115" s="7"/>
+      <c r="AD115" s="7"/>
       <c r="AE115" s="8"/>
       <c r="AF115" s="8"/>
       <c r="AG115" s="9" t="s">
@@ -10966,15 +9846,9 @@
       <c r="Y116" s="7"/>
       <c r="Z116" s="7"/>
       <c r="AA116" s="7"/>
-      <c r="AB116" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC116" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD116" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB116" s="7"/>
+      <c r="AC116" s="7"/>
+      <c r="AD116" s="7"/>
       <c r="AE116" s="8"/>
       <c r="AF116" s="8"/>
       <c r="AG116" s="9" t="s">
@@ -11027,15 +9901,9 @@
       <c r="Y117" s="7"/>
       <c r="Z117" s="7"/>
       <c r="AA117" s="7"/>
-      <c r="AB117" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC117" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD117" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB117" s="7"/>
+      <c r="AC117" s="7"/>
+      <c r="AD117" s="7"/>
       <c r="AE117" s="8"/>
       <c r="AF117" s="8"/>
       <c r="AG117" s="9" t="s">
@@ -11088,15 +9956,9 @@
       <c r="Y118" s="7"/>
       <c r="Z118" s="7"/>
       <c r="AA118" s="7"/>
-      <c r="AB118" s="7">
-        <v>50</v>
-      </c>
-      <c r="AC118" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD118" s="7">
-        <v>100</v>
-      </c>
+      <c r="AB118" s="7"/>
+      <c r="AC118" s="7"/>
+      <c r="AD118" s="7"/>
       <c r="AE118" s="8"/>
       <c r="AF118" s="8"/>
       <c r="AG118" s="9" t="s">
@@ -11148,12 +10010,8 @@
       <c r="Z119" s="7"/>
       <c r="AA119" s="7"/>
       <c r="AB119" s="7"/>
-      <c r="AC119" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD119" s="7">
-        <v>100</v>
-      </c>
+      <c r="AC119" s="7"/>
+      <c r="AD119" s="7"/>
       <c r="AE119" s="8"/>
       <c r="AF119" s="8"/>
       <c r="AG119" s="9" t="s">
@@ -11205,12 +10063,8 @@
       <c r="Z120" s="7"/>
       <c r="AA120" s="7"/>
       <c r="AB120" s="7"/>
-      <c r="AC120" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD120" s="7">
-        <v>100</v>
-      </c>
+      <c r="AC120" s="7"/>
+      <c r="AD120" s="7"/>
       <c r="AE120" s="8"/>
       <c r="AF120" s="8"/>
       <c r="AG120" s="9" t="s">
@@ -11261,9 +10115,7 @@
       <c r="AA121" s="7"/>
       <c r="AB121" s="7"/>
       <c r="AC121" s="7"/>
-      <c r="AD121" s="7">
-        <v>100</v>
-      </c>
+      <c r="AD121" s="7"/>
       <c r="AE121" s="8"/>
       <c r="AF121" s="8"/>
       <c r="AG121" s="9" t="s">
@@ -11314,9 +10166,7 @@
       <c r="AA122" s="7"/>
       <c r="AB122" s="7"/>
       <c r="AC122" s="7"/>
-      <c r="AD122" s="7">
-        <v>100</v>
-      </c>
+      <c r="AD122" s="7"/>
       <c r="AE122" s="8"/>
       <c r="AF122" s="8"/>
       <c r="AG122" s="9" t="s">
@@ -11394,24 +10244,12 @@
       <c r="X123" s="7">
         <v>50</v>
       </c>
-      <c r="Y123" s="7">
-        <v>58.3</v>
-      </c>
-      <c r="Z123" s="7">
-        <v>66.7</v>
-      </c>
-      <c r="AA123" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB123" s="7">
-        <v>83.3</v>
-      </c>
-      <c r="AC123" s="7">
-        <v>91.7</v>
-      </c>
-      <c r="AD123" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y123" s="7"/>
+      <c r="Z123" s="7"/>
+      <c r="AA123" s="7"/>
+      <c r="AB123" s="7"/>
+      <c r="AC123" s="7"/>
+      <c r="AD123" s="7"/>
       <c r="AE123" s="8" t="s">
         <v>409</v>
       </c>
@@ -11491,24 +10329,12 @@
       <c r="X124" s="7">
         <v>50</v>
       </c>
-      <c r="Y124" s="7">
-        <v>58.3</v>
-      </c>
-      <c r="Z124" s="7">
-        <v>66.7</v>
-      </c>
-      <c r="AA124" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB124" s="7">
-        <v>83.3</v>
-      </c>
-      <c r="AC124" s="7">
-        <v>91.7</v>
-      </c>
-      <c r="AD124" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y124" s="7"/>
+      <c r="Z124" s="7"/>
+      <c r="AA124" s="7"/>
+      <c r="AB124" s="7"/>
+      <c r="AC124" s="7"/>
+      <c r="AD124" s="7"/>
       <c r="AE124" s="8" t="s">
         <v>414</v>
       </c>
@@ -11588,24 +10414,12 @@
       <c r="X125" s="7">
         <v>50</v>
       </c>
-      <c r="Y125" s="7">
-        <v>58.3</v>
-      </c>
-      <c r="Z125" s="7">
-        <v>66.7</v>
-      </c>
-      <c r="AA125" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB125" s="7">
-        <v>83.3</v>
-      </c>
-      <c r="AC125" s="7">
-        <v>91.7</v>
-      </c>
-      <c r="AD125" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y125" s="7"/>
+      <c r="Z125" s="7"/>
+      <c r="AA125" s="7"/>
+      <c r="AB125" s="7"/>
+      <c r="AC125" s="7"/>
+      <c r="AD125" s="7"/>
       <c r="AE125" s="8" t="s">
         <v>419</v>
       </c>
@@ -11685,24 +10499,12 @@
       <c r="X126" s="7">
         <v>50</v>
       </c>
-      <c r="Y126" s="7">
-        <v>58.3</v>
-      </c>
-      <c r="Z126" s="7">
-        <v>66.7</v>
-      </c>
-      <c r="AA126" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB126" s="7">
-        <v>83.3</v>
-      </c>
-      <c r="AC126" s="7">
-        <v>91.7</v>
-      </c>
-      <c r="AD126" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y126" s="7"/>
+      <c r="Z126" s="7"/>
+      <c r="AA126" s="7"/>
+      <c r="AB126" s="7"/>
+      <c r="AC126" s="7"/>
+      <c r="AD126" s="7"/>
       <c r="AE126" s="8" t="s">
         <v>424</v>
       </c>
@@ -11782,24 +10584,12 @@
       <c r="X127" s="7">
         <v>50</v>
       </c>
-      <c r="Y127" s="7">
-        <v>58.3</v>
-      </c>
-      <c r="Z127" s="7">
-        <v>66.7</v>
-      </c>
-      <c r="AA127" s="7">
-        <v>75</v>
-      </c>
-      <c r="AB127" s="7">
-        <v>83.3</v>
-      </c>
-      <c r="AC127" s="7">
-        <v>91.7</v>
-      </c>
-      <c r="AD127" s="7">
-        <v>100</v>
-      </c>
+      <c r="Y127" s="7"/>
+      <c r="Z127" s="7"/>
+      <c r="AA127" s="7"/>
+      <c r="AB127" s="7"/>
+      <c r="AC127" s="7"/>
+      <c r="AD127" s="7"/>
       <c r="AE127" s="8" t="s">
         <v>429</v>
       </c>

--- a/บันทึกผลการดำเนินงาน_RM_2569.xlsx
+++ b/บันทึกผลการดำเนินงาน_RM_2569.xlsx
@@ -8,33 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devill/1_กฟน./2569/Dashborad_RM/rm-dashboard-2569/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C614761-147F-DE46-BBA3-18EB24F4809D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C5BBDC-F911-284D-BBBF-1593A546BFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="บันทึกผล" sheetId="1" r:id="rId1"/>
     <sheet name="วิธีใช้" sheetId="2" r:id="rId2"/>
+    <sheet name="สรุปรายเดือน_กิจกรรม" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="681">
   <si>
     <t>รหัสกิจกรรม</t>
   </si>
@@ -150,9 +138,6 @@
     <t>ออกแบบและปรับโครงสร้างคณะทำงาน GRC</t>
   </si>
   <si>
-    <t>ดำเนินการ ออกแบบและปรับโครงสร้ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -168,9 +153,6 @@
     <t>วางแผนและปรับโครงสร้าง บทบาท หน้าที่</t>
   </si>
   <si>
-    <t>ดำเนินการ วางแผนและปรับโครงสร้ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>P_1.3.1</t>
   </si>
   <si>
@@ -183,9 +165,6 @@
     <t>ออกแบบและพัฒนา Risk Taxonomy</t>
   </si>
   <si>
-    <t>ดำเนินการ ออกแบบและพัฒนา Risk  (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>P_1.4.1</t>
   </si>
   <si>
@@ -198,9 +177,6 @@
     <t>เก็บข้อมูลและวิเคราะห์แนวโน้ม KRI</t>
   </si>
   <si>
-    <t>ดำเนินการ เก็บข้อมูลและวิเคราะ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>P_1.5.1</t>
   </si>
   <si>
@@ -267,9 +243,6 @@
     <t>รวบรวมนโยบาย/แนวปฏิบัติและออกแบบกระบวนการกำกับดูแล</t>
   </si>
   <si>
-    <t>ดำเนินการ รวบรวมนโยบาย/แนวปฏิบ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>P_1.10.1</t>
   </si>
   <si>
@@ -282,9 +255,6 @@
     <t>จัดทำข้อมูลกระบวนงานทั้งองค์กร</t>
   </si>
   <si>
-    <t>ดำเนินการ จัดทำข้อมูลกระบวนงาน (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>P_1.11.1</t>
   </si>
   <si>
@@ -309,9 +279,6 @@
     <t>รวบรวมข้อมูลเหตุการณ์ (Incident และ Near-miss) มาวิเคราะห์แนวโน้ม</t>
   </si>
   <si>
-    <t>ดำเนินการ รวบรวมข้อมูลเหตุการณ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>P_1.13.1</t>
   </si>
   <si>
@@ -324,9 +291,6 @@
     <t>วางแผนและขยายขอบเขต</t>
   </si>
   <si>
-    <t>ดำเนินการ วางแผนและขยายขอบเขต (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>P_1.14.1</t>
   </si>
   <si>
@@ -339,9 +303,6 @@
     <t>รวบรวมข้อมูลและจัดทำร่างทะเบียนกฎหมาย</t>
   </si>
   <si>
-    <t>ดำเนินการ รวบรวมข้อมูลและจัดทำ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>P_1.14.2</t>
   </si>
   <si>
@@ -402,9 +363,6 @@
     <t>ทบทวนความสอดคล้องของโครงสร้างและบทบาทหน้าที่ด้านการบริหารความเสี่ยง การควบคุมภายใน และกระบวนการอื่นที่เกี่ยวข้อง</t>
   </si>
   <si>
-    <t>ดำเนินการ ทบทวนความสอดคล้องของ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.1.2.2</t>
   </si>
   <si>
@@ -426,9 +384,6 @@
     <t>พิจารณาข้อมูลจาก Feedback Report และแบบประเมินประสิทธิผลของปีก่อน</t>
   </si>
   <si>
-    <t>ดำเนินการ พิจารณาข้อมูลจาก Fee (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>ล่าช้ากว่าแผน ติดขั้นตอนอนุมัติ</t>
   </si>
   <si>
@@ -462,9 +417,6 @@
     <t>งานบริหารความเสี่ยง / แบม</t>
   </si>
   <si>
-    <t>ดำเนินการ ทบทวน Competency และ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>แบม</t>
   </si>
   <si>
@@ -474,18 +426,12 @@
     <t>ทบทวนพฤติกรรมที่พึงประสงค์ด้านการบริหารความเสี่ยงตามกลุ่มของพนักงาน</t>
   </si>
   <si>
-    <t>ดำเนินการ ทบทวนพฤติกรรมที่พึงป (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.1.3</t>
   </si>
   <si>
     <t>ทบทวนหลักสูตร พร้อมให้ ฝอร. แจ้งการอบรม</t>
   </si>
   <si>
-    <t>ดำเนินการ ทบทวนหลักสูตร พร้อมใ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.2.1</t>
   </si>
   <si>
@@ -495,9 +441,6 @@
     <t>ส่งพนักงาน ฝบส. เข้ารับการอบรมตามแผน</t>
   </si>
   <si>
-    <t>ดำเนินการ ส่งพนักงาน ฝบส. เข้า (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.2.2</t>
   </si>
   <si>
@@ -516,9 +459,6 @@
     <t>ดำเนินการตามแผนการอบรม/ให้ความรู้ด้านการบริหารความเสี่ยง แก่ผู้บริหารและพนักงาน</t>
   </si>
   <si>
-    <t>ดำเนินการ ดำเนินการตามแผนการอบ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.2.5</t>
   </si>
   <si>
@@ -540,36 +480,24 @@
     <t>ประสานงาน ฝทม. ในการสื่อสาร/ผลักดันให้เกิดพฤติกรรมที่พึงประสงค์</t>
   </si>
   <si>
-    <t>ดำเนินการ ประสานงาน ฝทม. ในการ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.3.2</t>
   </si>
   <si>
     <t>สื่อสาร/ชี้แจงในงาน GRC Day</t>
   </si>
   <si>
-    <t>ดำเนินการ สื่อสาร/ชี้แจงในงาน  (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.3.3</t>
   </si>
   <si>
     <t>ผู้บริหารเป็นผู้นำต้นแบบและสร้างบรรยากาศ</t>
   </si>
   <si>
-    <t>ดำเนินการ ผู้บริหารเป็นผู้นำต้ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.3.4</t>
   </si>
   <si>
     <t>พัฒนาพฤติกรรม ตามพฤติกรรมพึงประสงค์ด้านการบริหารความเสี่ยง กับผู้บริหาร และพนักงานที่เกี่ยวข้อง ผ่านการสื่อสารในช่องทางที่กำหนด</t>
   </si>
   <si>
-    <t>ดำเนินการ พัฒนาพฤติกรรม ตามพฤต (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.4.1</t>
   </si>
   <si>
@@ -606,33 +534,21 @@
     <t>ทบทวนโครงสร้าง KPI สายงาน เชื่อมโยงผลการบริหารความเสี่ยงใน KPI ผู้บริหารสายงาน ร่วมกับ ฝทม.</t>
   </si>
   <si>
-    <t>ดำเนินการ ทบทวนโครงสร้าง KPI ส (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.5.2</t>
   </si>
   <si>
     <t>กำหนดแนวทางเชื่อมโยงผลการบริหารความเสี่ยงองค์กร/สายงาน/หน่วยงาน</t>
   </si>
   <si>
-    <t>ดำเนินการ กำหนดแนวทางเชื่อมโยง (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.5.3</t>
   </si>
   <si>
     <t>ถ่ายทอดลงสูระดับสายงาน/หน่วยงาน สอดคล้องกับการประเมินผลองค์กร</t>
   </si>
   <si>
-    <t>ดำเนินการ ถ่ายทอดลงสูระดับสายง (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.5.4</t>
   </si>
   <si>
-    <t>ดำเนินการ ประเมินประสิทธิผลและ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.6.1</t>
   </si>
   <si>
@@ -645,27 +561,18 @@
     <t>เจ้นท์ / แบม</t>
   </si>
   <si>
-    <t>ดำเนินการ จัดจ้างที่ปรึกษา (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.6.2</t>
   </si>
   <si>
     <t>ชี้แจงการเข้าร่วมโครงการ</t>
   </si>
   <si>
-    <t>ดำเนินการ ชี้แจงการเข้าร่วมโคร (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.6.3</t>
   </si>
   <si>
     <t>ดำเนินการตามโครงการและให้คำปรึกษาแก่สายงาน</t>
   </si>
   <si>
-    <t>ดำเนินการ ดำเนินการตามโครงการแ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.2.6.4</t>
   </si>
   <si>
@@ -696,9 +603,6 @@
     <t>งานบริหารความเสี่ยง / เป็ด</t>
   </si>
   <si>
-    <t>ดำเนินการ ทบทวนหลักการกำหนด RA (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>เป็ด</t>
   </si>
   <si>
@@ -708,27 +612,18 @@
     <t>พิจารณาเป้าหมายของ SO Goal KPI</t>
   </si>
   <si>
-    <t>ดำเนินการ พิจารณาเป้าหมายของ S (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.1.3</t>
   </si>
   <si>
     <t>กำหนด RA/RT ให้สอดคล้องกับเป้าหมายขององค์กร และเป้าหมายของแผนแม่บท</t>
   </si>
   <si>
-    <t>ดำเนินการ กำหนด RA/RT ให้สอดคล (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.1.4</t>
   </si>
   <si>
     <t>ชี้แจง RA/RT ให้แผนแม่บท และ สื่อสารให้บุคลากรภายในทราบ</t>
   </si>
   <si>
-    <t>ดำเนินการ ชี้แจง RA/RT ให้แผนแ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.1.5</t>
   </si>
   <si>
@@ -741,27 +636,18 @@
     <t>สรุปข้อมูลผลการดำเนินงานด้านการบริหารความเสี่ยงของปีที่ผ่านมา</t>
   </si>
   <si>
-    <t>ดำเนินการ สรุปข้อมูลผลการดำเนิ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.2.2</t>
   </si>
   <si>
     <t>วิเคราะห์ข้อมูล Emerging Risk / ESG Risk</t>
   </si>
   <si>
-    <t>ดำเนินการ วิเคราะห์ข้อมูล Emer (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.2.3</t>
   </si>
   <si>
     <t>นำส่งข้อมูลให้ ฝผก. เพื่อเป็นข้อมูลนำเข้าในการวิเคราะห์สภาพแวดล้อม</t>
   </si>
   <si>
-    <t>ดำเนินการ นำส่งข้อมูลให้ ฝผก.  (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.3.1</t>
   </si>
   <si>
@@ -771,18 +657,12 @@
     <t>วิเคราะห์ Intelligent Risk หรือ วิเคราะห์ความเสี่ยงเพื่อเข้าถึงโอกาสทางธุรกิจ โดยมีการกำหนด Business Model และระบุ Intelligent Risk ที่อาจส่งผลต่อบรรลุเป้าหมายในแต่ละตำแหน่งเชิงยุทธศาสตร์ขององค์กร</t>
   </si>
   <si>
-    <t>ดำเนินการ วิเคราะห์ Intelligen (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.3.2</t>
   </si>
   <si>
     <t>จัดทำข้อมูล Emerging Risk, Intelligent Risk ประกอบเล่มแผนวิสาหกิจการไฟฟ้านครหลวง โดยอาจจัดทำภาคผนวก บทวิเคราะห์ความเสี่ยง แสดงความเชื่อมโยงการบริหารความเสี่ยง (Risk Appetite Intelligent Risk ปัจจัยเสี่ยง SO ความเสี่ยงของเแผนปฏิบัติเชิงยุทธศาสตร์) และการจัดทำแผนยุทธศาสตร์</t>
   </si>
   <si>
-    <t>ดำเนินการ จัดทำข้อมูล Emerging (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.4.1</t>
   </si>
   <si>
@@ -792,9 +672,6 @@
     <t>ระบุและวิเคราะห์ความเสี่ยงที่อาจส่งผลต่อการบรรลุวัตถุประสงค์เชิงยุทธศาสตร์ (SO)</t>
   </si>
   <si>
-    <t>ดำเนินการ ระบุและวิเคราะห์ความ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.4.2</t>
   </si>
   <si>
@@ -810,9 +687,6 @@
     <t>ทบทวนแบบฟอร์มและเกณฑ์การประเมินความเสี่ยง AP และ ประสิทธิผลของการควบคุม และแผนแม่บทที่เกี่ยวข้อง</t>
   </si>
   <si>
-    <t>ดำเนินการ ทบทวนแบบฟอร์มและเกณฑ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.6.1</t>
   </si>
   <si>
@@ -822,18 +696,12 @@
     <t>สื่อสารแบบฟอร์มการประเมินความเสี่ยง และหลักเกณฑ์การประเมินความเพียงพอของการควบคุมภายใน</t>
   </si>
   <si>
-    <t>ดำเนินการ สื่อสารแบบฟอร์มการปร (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.6.2</t>
   </si>
   <si>
     <t>หน่วยงานเจ้าของแผนฯ วิเคราะห์ ระบุ และประเมินความเสี่ยงของแผนปฏิบัติการ พร้อมกำหนดมาตรการจัดการความเสี่ยง ในกรณีที่ความเสี่ยงอยู่ในระดับที่ไม่สามารถยอมรับได้</t>
   </si>
   <si>
-    <t>ดำเนินการ หน่วยงานเจ้าของแผนฯ  (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.6.3</t>
   </si>
   <si>
@@ -849,18 +717,12 @@
     <t>ประสานงานกับ AP Owner ในการทบทวนการประเมินความเสี่ยง</t>
   </si>
   <si>
-    <t>ดำเนินการ ประสานงานกับ AP Owne (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.7.2</t>
   </si>
   <si>
     <t>ติดตามข้อมูลผลการประเมินฯ และให้ข้อเสนอแนะในการกำหนดมาตรการจัดการความเสี่ยง (ถ้ามี)</t>
   </si>
   <si>
-    <t>ดำเนินการ ติดตามข้อมูลผลการประ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.3.7.3</t>
   </si>
   <si>
@@ -882,24 +744,15 @@
     <t>งานบริหารความเสี่ยง</t>
   </si>
   <si>
-    <t>ดำเนินการ ติดตามสถานการณ์ภายใน (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.4.1.2</t>
   </si>
   <si>
-    <t>ดำเนินการ นำข้อมูลความเสี่ยงเข (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.4.1.3</t>
   </si>
   <si>
     <t>ทบทวนเกณฑ์การประเมินความเสี่ยงและการควบคุม</t>
   </si>
   <si>
-    <t>ดำเนินการ ทบทวนเกณฑ์การประเมิน (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.4.2.1</t>
   </si>
   <si>
@@ -909,18 +762,12 @@
     <t>จัดทำข้อมูลการวิเคราะห์ความเสี่ยงระดับองค์กร</t>
   </si>
   <si>
-    <t>ดำเนินการ จัดทำข้อมูลการวิเครา (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.4.2.2</t>
   </si>
   <si>
     <t>วิเคราะห์ Leading / Lagging Indicator ของแต่ละความเสี่ยง</t>
   </si>
   <si>
-    <t>ดำเนินการ วิเคราะห์ Leading /  (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.4.3.1</t>
   </si>
   <si>
@@ -969,27 +816,18 @@
     <t>ติดตามและรายงานผลการบริหารความเสี่ยงและการควบคุมของความเสี่ยงปีปัจจุบัน</t>
   </si>
   <si>
-    <t>ดำเนินการ ติดตามและรายงานผลการ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.4.6.2</t>
   </si>
   <si>
     <t>นำเข้าข้อมูลเข้า Dashboard</t>
   </si>
   <si>
-    <t>ดำเนินการ นำเข้าข้อมูลเข้า Das (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.4.6.3</t>
   </si>
   <si>
     <t>จัดทำวิเคราะห์ผลการดำเนินงานการบริหารความเสี่ยง รายไตรมาส และรายปี</t>
   </si>
   <si>
-    <t>ดำเนินการ จัดทำวิเคราะห์ผลการด (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.4.7.1</t>
   </si>
   <si>
@@ -999,9 +837,6 @@
     <t>ร่วมกับ ฝผก. กำหนดขั้นตอนและจัดทำระบบในการแจ้งเตือนภัยล่วงหน้าสำหรับแผน AP นำร่อง</t>
   </si>
   <si>
-    <t>ดำเนินการ ร่วมกับ ฝผก. กำหนดขั (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.4.8.1</t>
   </si>
   <si>
@@ -1041,27 +876,18 @@
     <t>ทบทวนแบบฟอร์มและขั้นตอนการวิเคราะห์ผลกระทบทางธุรกิจและประเมินความเสี่ยง</t>
   </si>
   <si>
-    <t>ดำเนินการ ทบทวนแบบฟอร์มและขั้น (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.5.1.2</t>
   </si>
   <si>
     <t>จัดการประชุมเชิงปฏิบัติการร่วมกับหน่วยงานเพื่อวิเคราะห์และประเมินฯ และทบทวนกลยุทธ์</t>
   </si>
   <si>
-    <t>ดำเนินการ จัดการประชุมเชิงปฏิบ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.5.1.3</t>
   </si>
   <si>
     <t>รวบรวมข้อมูลผลการวิเคราะห์/ประเมิน นำเสนอผู้บริหาร</t>
   </si>
   <si>
-    <t>ดำเนินการ รวบรวมข้อมูลผลการวิเ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.5.1.4</t>
   </si>
   <si>
@@ -1083,36 +909,24 @@
     <t>แจ้งหน่วยงานกำหนดแผนการฝึกซ้อมประจำปี</t>
   </si>
   <si>
-    <t>ดำเนินการ แจ้งหน่วยงานกำหนดแผน (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.5.2.2</t>
   </si>
   <si>
     <t>รวบรวบแผนการฝึกซ้อมและวิเคราะห์ความจำเป็นในการเข้าร่วมสังเกตการณ์การฝึกซ้อม</t>
   </si>
   <si>
-    <t>ดำเนินการ รวบรวบแผนการฝึกซ้อมแ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.5.2.3</t>
   </si>
   <si>
     <t>เข้าร่วมสังเกตการณ์การฝึกซ้อมตามที่กำหนด</t>
   </si>
   <si>
-    <t>ดำเนินการ เข้าร่วมสังเกตการณ์ก (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.5.2.4</t>
   </si>
   <si>
     <t>สรุปผลการสังเกตการณ์ฝึกซ้อมและรายงานแก่ผู้ที่เกี่ยวข้อง</t>
   </si>
   <si>
-    <t>ดำเนินการ สรุปผลการสังเกตการณ์ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.5.3.1</t>
   </si>
   <si>
@@ -1122,27 +936,18 @@
     <t>รวบรวมและวิเคราะห์ข้อมูลเพื่อกำหนดสถานการณ์ในการฝึกซ้อม</t>
   </si>
   <si>
-    <t>ดำเนินการ รวบรวมและวิเคราะห์ข้ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.5.3.2</t>
   </si>
   <si>
     <t>จัดทำแผนการฝึกซ้อมสถานการณ์ใหญ่นำเสนอผู้ที่เกี่ยวข้อง</t>
   </si>
   <si>
-    <t>ดำเนินการ จัดทำแผนการฝึกซ้อมสถ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.5.3.3</t>
   </si>
   <si>
     <t>ประชุม/ประสานงานกับหน่วยงานที่เกี่ยวข้องเพื่อเตรียมการฝึกซ้อม</t>
   </si>
   <si>
-    <t>ดำเนินการ ประชุม/ประสานงานกับห (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.5.3.4</t>
   </si>
   <si>
@@ -1164,27 +969,18 @@
     <t>รวบรวมข้อมูลบทเรียนจากสถานการณ์จริง/การอบรมต่าง ๆ</t>
   </si>
   <si>
-    <t>ดำเนินการ รวบรวมข้อมูลบทเรียนจ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.5.4.2</t>
   </si>
   <si>
     <t>จัดทำบทวิเคราะห์/ข้อมูลเผยแพร่แก่กลุ่มเป้าหมาย</t>
   </si>
   <si>
-    <t>ดำเนินการ จัดทำบทวิเคราะห์/ข้อ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.5.4.3</t>
   </si>
   <si>
     <t>ดำเนินการสื่อสารตามช่องทางที่กำหนด</t>
   </si>
   <si>
-    <t>ดำเนินการ ดำเนินการสื่อสารตามช (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>M_2.5.4.4</t>
   </si>
   <si>
@@ -1263,9 +1059,6 @@
     <t>ปรับปรุงฐานข้อมูลที่ใช้ในการวิเคราะห์และติดตามการดำเนินงานแบบบูรณาการในกระบวนการทำงานที่สำคัญ (ทั้งกิจกรรม)</t>
   </si>
   <si>
-    <t>ดำเนินการ ปรับปรุงฐานข้อมูลที่ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>P_3.2</t>
   </si>
   <si>
@@ -1278,9 +1071,6 @@
     <t>ใช้งานระบบ GRC เพื่อสนับสนุนการทำงานให้ลดความซับซ้อน ลดระยะเวลา และมีความถูกต้องแม่นยำ (ทั้งกิจกรรม)</t>
   </si>
   <si>
-    <t>ดำเนินการ ใช้งานระบบ GRC เพื่อ (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>P_3.3</t>
   </si>
   <si>
@@ -1293,9 +1083,6 @@
     <t>ทบทวนการทำ Value Creation และ Value Enhancement ที่เชื่อมโยงกับกระบวนการกำหนดตำแหน่งเชิงยุทธศาสตร์ วัตถุประสงค์เชิงยุทธศาสตร์ แผนยุทธศาสตร์องค์กร และแผนแม่บทอื่นๆ ที่เกี่ยวข้องอย่างต่อเนื่อง (ทั้งกิจกรรม)</t>
   </si>
   <si>
-    <t>ดำเนินการ ทบทวนการทำ Value Cre (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>P_3.4</t>
   </si>
   <si>
@@ -1308,9 +1095,6 @@
     <t>กำหนดกระบวนการในการวิเคราะห์ถึงภาพรวมของความเสี่ยง (Portfolio View of Risk) (ทั้งกิจกรรม)</t>
   </si>
   <si>
-    <t>ดำเนินการ กำหนดกระบวนการในการว (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>P_3.5</t>
   </si>
   <si>
@@ -1323,9 +1107,6 @@
     <t>พัฒนา Portfolio View of Risk แสดงการจัดทำแบบจำลองที่เหมาะสม/นำแบบจำลองดังกล่าวไปใช้ในการบริหารความเสี่ยงในภาพรวม (ทั้งกิจกรรม)</t>
   </si>
   <si>
-    <t>ดำเนินการ พัฒนา Portfolio View (ถึง มิ.ย.)</t>
-  </si>
-  <si>
     <t>วิธีกรอกและนำเข้า Dashboard</t>
   </si>
   <si>
@@ -1378,6 +1159,912 @@
   </si>
   <si>
     <t>สถานะงานคำนวณจากผลจริง: 100=เสร็จสิ้น · 1-99=อยู่ระหว่างดำเนินการ · 0/ว่าง=ยังไม่ดำเนินการ</t>
+  </si>
+  <si>
+    <t>รหัส</t>
+  </si>
+  <si>
+    <t>ชื่อกิจกรรม/มาตรการ</t>
+  </si>
+  <si>
+    <t>สรุป ม.ค.</t>
+  </si>
+  <si>
+    <t>สรุป ก.พ.</t>
+  </si>
+  <si>
+    <t>สรุป มี.ค.</t>
+  </si>
+  <si>
+    <t>สรุป เม.ย.</t>
+  </si>
+  <si>
+    <t>สรุป พ.ค.</t>
+  </si>
+  <si>
+    <t>สรุป มิ.ย.</t>
+  </si>
+  <si>
+    <t>สรุป ก.ค.</t>
+  </si>
+  <si>
+    <t>สรุป ส.ค.</t>
+  </si>
+  <si>
+    <t>สรุป ก.ย.</t>
+  </si>
+  <si>
+    <t>สรุป ต.ค.</t>
+  </si>
+  <si>
+    <t>สรุป พ.ย.</t>
+  </si>
+  <si>
+    <t>สรุป ธ.ค.</t>
+  </si>
+  <si>
+    <t>P_1.1</t>
+  </si>
+  <si>
+    <t>การปรับปรุงโครงสร้างการดำเนินงานด้าน GRC เพื่อการดำเนินงานระดับสายงาน</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การปรับปรุงโครงสร้างการดำเนินง ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การปรับปรุงโครงสร้างการดำเนินง ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การปรับปรุงโครงสร้างการดำเนินง ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การปรับปรุงโครงสร้างการดำเนินง ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การปรับปรุงโครงสร้างการดำเนินง ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การปรับปรุงโครงสร้างการดำเนินง ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>P_1.2</t>
+  </si>
+  <si>
+    <t>โครงสร้างหน่วยงานที่ทำหน้าที่รับผิดชอบการกำกับดูแลด้าน IT Risk และ IT Compliance (รวมถึงระบบเทคโนโลยีดิจิทัล และ AI) (2nd line)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ โครงสร้างหน่วยงานที่ทำหน้าที่ร ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ โครงสร้างหน่วยงานที่ทำหน้าที่ร ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ โครงสร้างหน่วยงานที่ทำหน้าที่ร ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ โครงสร้างหน่วยงานที่ทำหน้าที่ร ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ โครงสร้างหน่วยงานที่ทำหน้าที่ร ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ โครงสร้างหน่วยงานที่ทำหน้าที่ร ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>P_1.3</t>
+  </si>
+  <si>
+    <t>การจัดทำ Risk Taxonomy เพื่อความสอดคล้องในการระบุ และจัดประเภทความเสี่ยง</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การจัดทำ Risk Taxonomy เพื่อคว ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การจัดทำ Risk Taxonomy เพื่อคว ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การจัดทำ Risk Taxonomy เพื่อคว ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การจัดทำ Risk Taxonomy เพื่อคว ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การจัดทำ Risk Taxonomy เพื่อคว ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การจัดทำ Risk Taxonomy เพื่อคว ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>P_1.4</t>
+  </si>
+  <si>
+    <t>การวิเคราะห์ตัวชี้วัดความเสี่ยง (KRI) เพื่อวิเคราะห์แนวโน้ม และคาดการณ์เหตุการณ์ความเสี่ยง</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การวิเคราะห์ตัวชี้วัดความเสี่ย ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การวิเคราะห์ตัวชี้วัดความเสี่ย ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การวิเคราะห์ตัวชี้วัดความเสี่ย ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>P_1.5</t>
+  </si>
+  <si>
+    <t>การสร้างวัฒนธรรม GRC ผ่าน GRC Survey และการสนทนากลุ่ม (Focus Group)</t>
+  </si>
+  <si>
+    <t>P_1.6</t>
+  </si>
+  <si>
+    <t>การพัฒนากระบวนการจัดทำหลักสูตรอบรมโดยอ้างอิงความเสี่ยง (Risk-based training) และติดตามผลการอบรม</t>
+  </si>
+  <si>
+    <t>P_1.7</t>
+  </si>
+  <si>
+    <t>การเชื่อมโยงการปฏิบัติงานด้าน GRC กับสิ่งจูงใจ (Incentive) หรือผลการปฏิบัติงาน (Performance)</t>
+  </si>
+  <si>
+    <t>P_1.8</t>
+  </si>
+  <si>
+    <t>การปรับปรุงนโยบายการกำกับการปฏิบัติตามกฎ ระเบียบและจัดทำนโยบาย IT Third Party Risk Management</t>
+  </si>
+  <si>
+    <t>P_1.9</t>
+  </si>
+  <si>
+    <t>การผลักดันให้มีหน่วยงานกลางกำกับและรวบรวมนโยบาย</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การผลักดันให้มีหน่วยงานกลางกำก ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การผลักดันให้มีหน่วยงานกลางกำก ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การผลักดันให้มีหน่วยงานกลางกำก ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การผลักดันให้มีหน่วยงานกลางกำก ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การผลักดันให้มีหน่วยงานกลางกำก ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การผลักดันให้มีหน่วยงานกลางกำก ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>P_1.10</t>
+  </si>
+  <si>
+    <t>การบูรณาการข้อมูลกระบวนงาน</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การบูรณาการข้อมูลกระบวนงาน ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การบูรณาการข้อมูลกระบวนงาน ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การบูรณาการข้อมูลกระบวนงาน ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>P_1.11</t>
+  </si>
+  <si>
+    <t>การปรับแนวทางการประเมิน CSA</t>
+  </si>
+  <si>
+    <t>P_1.12</t>
+  </si>
+  <si>
+    <t>การจัดทำแนวทาง/เอกสารในการรวบรวมข้อมูลเหตุการณ์ (Incident information)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การจัดทำแนวทาง/เอกสารในการรวบร ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การจัดทำแนวทาง/เอกสารในการรวบร ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การจัดทำแนวทาง/เอกสารในการรวบร ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การจัดทำแนวทาง/เอกสารในการรวบร ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การจัดทำแนวทาง/เอกสารในการรวบร ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การจัดทำแนวทาง/เอกสารในการรวบร ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>P_1.13</t>
+  </si>
+  <si>
+    <t>การพัฒนาเครื่องมือติดตามประสิทธิภาพการควบคุมอย่างต่อเนื่อง (Continuous Monitoring)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การพัฒนาเครื่องมือติดตามประสิท ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การพัฒนาเครื่องมือติดตามประสิท ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การพัฒนาเครื่องมือติดตามประสิท ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การพัฒนาเครื่องมือติดตามประสิท ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การพัฒนาเครื่องมือติดตามประสิท ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การพัฒนาเครื่องมือติดตามประสิท ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>P_1.14</t>
+  </si>
+  <si>
+    <t>การพัฒนาทะเบียนกฎหมาย เนื้อหาข้อบังคับที่องค์กรต้องปฏิบัติตาม (Citation) และเชื่อมโยงกับการควบคุมและนโยบาย</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การพัฒนาทะเบียนกฎหมาย เนื้อหาข ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การพัฒนาทะเบียนกฎหมาย เนื้อหาข ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การพัฒนาทะเบียนกฎหมาย เนื้อหาข ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การพัฒนาทะเบียนกฎหมาย เนื้อหาข ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การพัฒนาทะเบียนกฎหมาย เนื้อหาข ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ การพัฒนาทะเบียนกฎหมาย เนื้อหาข ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.1.1</t>
+  </si>
+  <si>
+    <t>2.1.1</t>
+  </si>
+  <si>
+    <t>ทบทวนนโยบาย GRC</t>
+  </si>
+  <si>
+    <t>M_2.1.2</t>
+  </si>
+  <si>
+    <t>2.1.2</t>
+  </si>
+  <si>
+    <t>ทบทวนโครงสร้างและบทบาทหน้าที่ด้านการบริหารความเสี่ยง</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนโครงสร้างและบทบาทหน้าที่ด ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนโครงสร้างและบทบาทหน้าที่ด ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.1.3</t>
+  </si>
+  <si>
+    <t>2.1.3</t>
+  </si>
+  <si>
+    <t>ทบทวนกรอบการดำเนินงานและคู่มือการบริหารความเสี่ยง</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนกรอบการดำเนินงานและคู่มือ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.2.1</t>
+  </si>
+  <si>
+    <t>2.2.1</t>
+  </si>
+  <si>
+    <t>ทบทวน Competency / พฤติกรรมพึงประสงค์ด้านการบริหารความเสี่ยง กับผู้บริหาร และพนักงานที่เกี่ยวข้อง</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวน Competency / พฤติกรรมพึง ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวน Competency / พฤติกรรมพึง ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวน Competency / พฤติกรรมพึง ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวน Competency / พฤติกรรมพึง ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวน Competency / พฤติกรรมพึง ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวน Competency / พฤติกรรมพึง ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.2.2</t>
+  </si>
+  <si>
+    <t>2.2.2</t>
+  </si>
+  <si>
+    <t>อบรมและพัฒนาพนักงานตาม Competency ที่กำหนด</t>
+  </si>
+  <si>
+    <t>ดำเนินการ อบรมและพัฒนาพนักงานตาม Compete ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ อบรมและพัฒนาพนักงานตาม Compete ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ อบรมและพัฒนาพนักงานตาม Compete ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ อบรมและพัฒนาพนักงานตาม Compete ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ อบรมและพัฒนาพนักงานตาม Compete ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ อบรมและพัฒนาพนักงานตาม Compete ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.2.3</t>
+  </si>
+  <si>
+    <t>2.2.3</t>
+  </si>
+  <si>
+    <t>สื่อสารสร้างความตระหนักด้านการบริหารความเสี่ยง</t>
+  </si>
+  <si>
+    <t>ดำเนินการ สื่อสารสร้างความตระหนักด้านการ ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ สื่อสารสร้างความตระหนักด้านการ ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ สื่อสารสร้างความตระหนักด้านการ ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ สื่อสารสร้างความตระหนักด้านการ ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ สื่อสารสร้างความตระหนักด้านการ ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ สื่อสารสร้างความตระหนักด้านการ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.2.4</t>
+  </si>
+  <si>
+    <t>2.2.4</t>
+  </si>
+  <si>
+    <t>M_2.2.5</t>
+  </si>
+  <si>
+    <t>2.2.5</t>
+  </si>
+  <si>
+    <t>ทบทวนการจัดทำการเชื่อมโยง KPI กับผลการดำเนินงานด้านการบริหารความเสี่ยงของแต่ละสายงาน</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนการจัดทำการเชื่อมโยง KPI  ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนการจัดทำการเชื่อมโยง KPI  ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนการจัดทำการเชื่อมโยง KPI  ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนการจัดทำการเชื่อมโยง KPI  ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนการจัดทำการเชื่อมโยง KPI  ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนการจัดทำการเชื่อมโยง KPI  ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.2.6</t>
+  </si>
+  <si>
+    <t>2.2.6</t>
+  </si>
+  <si>
+    <t>ดำเนินการตามโครงการ MEA GRC Award เพื่อบูรณาการการบริหารความเสี่ยงกับผลตอบแทน/แรงจูงใจ</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ดำเนินการตามโครงการ MEA GRC Aw ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ดำเนินการตามโครงการ MEA GRC Aw ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ดำเนินการตามโครงการ MEA GRC Aw ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ดำเนินการตามโครงการ MEA GRC Aw ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ดำเนินการตามโครงการ MEA GRC Aw ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ดำเนินการตามโครงการ MEA GRC Aw ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.3.1</t>
+  </si>
+  <si>
+    <t>2.3.1</t>
+  </si>
+  <si>
+    <t>ทบทวนหลักการกำหนด RA/RT และ RA Statement พร้อมสื่อสารให้แก่ผู้มีส่วนได้ส่วนเสีย</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนหลักการกำหนด RA/RT และ RA ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนหลักการกำหนด RA/RT และ RA ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนหลักการกำหนด RA/RT และ RA ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนหลักการกำหนด RA/RT และ RA ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนหลักการกำหนด RA/RT และ RA ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนหลักการกำหนด RA/RT และ RA ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.3.2</t>
+  </si>
+  <si>
+    <t>2.3.2</t>
+  </si>
+  <si>
+    <t>ระบุ Emerging Risk เป็นข้อมูลนำเข้าในการวิเคราะห์สภาพแวดล้อม</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ระบุ Emerging Risk เป็นข้อมูลน ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ระบุ Emerging Risk เป็นข้อมูลน ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ระบุ Emerging Risk เป็นข้อมูลน ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ระบุ Emerging Risk เป็นข้อมูลน ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ระบุ Emerging Risk เป็นข้อมูลน ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ระบุ Emerging Risk เป็นข้อมูลน ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.3.3</t>
+  </si>
+  <si>
+    <t>2.3.3</t>
+  </si>
+  <si>
+    <t>ระบุ Intelligent Risk ที่อาจส่งผลต่อบรรลุเป้าหมายในแต่ละตำแหน่งเชิงยุทธศาสตร์ขององค์กร</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ระบุ Intelligent Risk ที่อาจส่ ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ระบุ Intelligent Risk ที่อาจส่ ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ระบุ Intelligent Risk ที่อาจส่ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.3.4</t>
+  </si>
+  <si>
+    <t>2.3.4</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ระบุและวิเคราะห์ความเสี่ยงที่อ ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ระบุและวิเคราะห์ความเสี่ยงที่อ ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ระบุและวิเคราะห์ความเสี่ยงที่อ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.3.5</t>
+  </si>
+  <si>
+    <t>2.3.5</t>
+  </si>
+  <si>
+    <t>ทบทวนแบบฟอร์มและเกณฑ์การประเมินความเสี่ยงและ ประสิทธิผลของการควบคุมของแผน AP และแผนแม่บทที่เกี่ยวข้อง</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนแบบฟอร์มและเกณฑ์การประเมิ ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนแบบฟอร์มและเกณฑ์การประเมิ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.3.6</t>
+  </si>
+  <si>
+    <t>2.3.6</t>
+  </si>
+  <si>
+    <t>ดำเนินการ สื่อสารแบบฟอร์มการประเมินความเ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.3.7</t>
+  </si>
+  <si>
+    <t>2.3.7</t>
+  </si>
+  <si>
+    <t>ติดตามการวิเคราะห์ ระบุ และประเมินความเสี่ยงของแผนปฏิบัติการ และแผนแม่บทที่เกี่ยวข้อง พร้อมกำหนดมาตรการจัดการความเสี่ยง</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ติดตามการวิเคราะห์ ระบุ และประ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.4.1</t>
+  </si>
+  <si>
+    <t>2.4.1</t>
+  </si>
+  <si>
+    <t>รวบรวม/วิเคราะห์ข้อมูลความเสี่ยง การควบคุม และนำเข้าใน Risk Inventory พร้อมทบทวนเกณฑ์ประเมินการควบคุม</t>
+  </si>
+  <si>
+    <t>ดำเนินการ รวบรวม/วิเคราะห์ข้อมูลความเสี่ ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ รวบรวม/วิเคราะห์ข้อมูลความเสี่ ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ รวบรวม/วิเคราะห์ข้อมูลความเสี่ ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ รวบรวม/วิเคราะห์ข้อมูลความเสี่ ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ รวบรวม/วิเคราะห์ข้อมูลความเสี่ ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ รวบรวม/วิเคราะห์ข้อมูลความเสี่ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.4.2</t>
+  </si>
+  <si>
+    <t>2.4.2</t>
+  </si>
+  <si>
+    <t>คัดเลือกปัจจัยเสี่ยงระดับองค์กร พร้อมวิเคราะห์ Leading / Lagging Indicator ของแต่ละความเสี่ยง</t>
+  </si>
+  <si>
+    <t>ดำเนินการ คัดเลือกปัจจัยเสี่ยงระดับองค์ก ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.4.3</t>
+  </si>
+  <si>
+    <t>2.4.3</t>
+  </si>
+  <si>
+    <t>จัดให้มีการประเมินความเสี่ยง และสื่อสารความเสี่ยงต่อผู้รับผิดชอบ</t>
+  </si>
+  <si>
+    <t>M_2.4.4</t>
+  </si>
+  <si>
+    <t>2.4.4</t>
+  </si>
+  <si>
+    <t>พิจารณาและคัดเลือกวิธีการจัดการความเสี่ยง พร้อมทั้ง วิเคราะห์และจัดทำ Risk Correlation Map/Portfolio View of Risk</t>
+  </si>
+  <si>
+    <t>M_2.4.5</t>
+  </si>
+  <si>
+    <t>2.4.5</t>
+  </si>
+  <si>
+    <t>จัดทำแผนบริหารความเสี่ยง และทบทวนแผนบริหารความเสี่ยงของปีถัดไป</t>
+  </si>
+  <si>
+    <t>M_2.4.6</t>
+  </si>
+  <si>
+    <t>2.4.6</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ติดตามและรายงานผลการบริหารความ ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ติดตามและรายงานผลการบริหารความ ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ติดตามและรายงานผลการบริหารความ ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ติดตามและรายงานผลการบริหารความ ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ติดตามและรายงานผลการบริหารความ ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ติดตามและรายงานผลการบริหารความ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.4.7</t>
+  </si>
+  <si>
+    <t>2.4.7</t>
+  </si>
+  <si>
+    <t>พัฒนาระบบเทคโนโลยีดิจิทัลเพื่อสนับสนุนกระบวนการบริหารความเสี่ยง และระบบเตือนภัยล่วงหน้า</t>
+  </si>
+  <si>
+    <t>ดำเนินการ พัฒนาระบบเทคโนโลยีดิจิทัลเพื่อ ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ พัฒนาระบบเทคโนโลยีดิจิทัลเพื่อ ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ พัฒนาระบบเทคโนโลยีดิจิทัลเพื่อ ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ พัฒนาระบบเทคโนโลยีดิจิทัลเพื่อ ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ พัฒนาระบบเทคโนโลยีดิจิทัลเพื่อ ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ พัฒนาระบบเทคโนโลยีดิจิทัลเพื่อ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.4.8</t>
+  </si>
+  <si>
+    <t>2.4.8</t>
+  </si>
+  <si>
+    <t>ทบทวน ประเมินประสิทธิผล และปรับปรุงกระบวนการบริหารความเสี่ยง</t>
+  </si>
+  <si>
+    <t>M_2.5.1</t>
+  </si>
+  <si>
+    <t>2.5.1</t>
+  </si>
+  <si>
+    <t>วิเคราะห์ผลกระทบทางธุรกิจ ประเมินความเสี่ยง ทบทวนกลยุทธ์ และ BCP</t>
+  </si>
+  <si>
+    <t>ดำเนินการ วิเคราะห์ผลกระทบทางธุรกิจ ประเ ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ วิเคราะห์ผลกระทบทางธุรกิจ ประเ ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ วิเคราะห์ผลกระทบทางธุรกิจ ประเ ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ วิเคราะห์ผลกระทบทางธุรกิจ ประเ ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ วิเคราะห์ผลกระทบทางธุรกิจ ประเ ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ วิเคราะห์ผลกระทบทางธุรกิจ ประเ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.5.2</t>
+  </si>
+  <si>
+    <t>2.5.2</t>
+  </si>
+  <si>
+    <t>ติดตามและเข้าร่วมฝึกซ้อม BCP ของหน่วยงาน</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ติดตามและเข้าร่วมฝึกซ้อม BCP ข ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ติดตามและเข้าร่วมฝึกซ้อม BCP ข ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ติดตามและเข้าร่วมฝึกซ้อม BCP ข ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ติดตามและเข้าร่วมฝึกซ้อม BCP ข ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.5.3</t>
+  </si>
+  <si>
+    <t>2.5.3</t>
+  </si>
+  <si>
+    <t>ฝึกซ้อมสถานการณ์ใหญ่</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ฝึกซ้อมสถานการณ์ใหญ่ ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ฝึกซ้อมสถานการณ์ใหญ่ ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ฝึกซ้อมสถานการณ์ใหญ่ ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ฝึกซ้อมสถานการณ์ใหญ่ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.5.4</t>
+  </si>
+  <si>
+    <t>2.5.4</t>
+  </si>
+  <si>
+    <t>สร้างความตระหนักและสื่อสารข้อมูลเกี่ยวกับการบริหารความต่อเนื่องทางธุรกิจ</t>
+  </si>
+  <si>
+    <t>ดำเนินการ สร้างความตระหนักและสื่อสารข้อม ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ สร้างความตระหนักและสื่อสารข้อม ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ สร้างความตระหนักและสื่อสารข้อม ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ สร้างความตระหนักและสื่อสารข้อม ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ สร้างความตระหนักและสื่อสารข้อม ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ สร้างความตระหนักและสื่อสารข้อม ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>M_2.5.5</t>
+  </si>
+  <si>
+    <t>2.5.5</t>
+  </si>
+  <si>
+    <t>ตรวจประเมินภายใน/ภายนอก พร้อมทบทวนและปรับปรุงการบริหารความต่อเนื่องทางธุรกิจและความพร้อมใช้ของระบบ</t>
+  </si>
+  <si>
+    <t>ปรับปรุงฐานข้อมูลที่ใช้ในการวิเคราะห์และติดตามการดำเนินงานแบบบูรณาการในกระบวนการทำงานที่สำคัญ</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ปรับปรุงฐานข้อมูลที่ใช้ในการวิ ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ปรับปรุงฐานข้อมูลที่ใช้ในการวิ ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ปรับปรุงฐานข้อมูลที่ใช้ในการวิ ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ปรับปรุงฐานข้อมูลที่ใช้ในการวิ ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ปรับปรุงฐานข้อมูลที่ใช้ในการวิ ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ปรับปรุงฐานข้อมูลที่ใช้ในการวิ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ใช้งานระบบ GRC เพื่อสนับสนุนการทำงานให้ลดความซับซ้อน ลดระยะเวลา และมีความถูกต้องแม่นยำ</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ใช้งานระบบ GRC เพื่อสนับสนุนกา ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ใช้งานระบบ GRC เพื่อสนับสนุนกา ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ใช้งานระบบ GRC เพื่อสนับสนุนกา ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ใช้งานระบบ GRC เพื่อสนับสนุนกา ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ใช้งานระบบ GRC เพื่อสนับสนุนกา ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ใช้งานระบบ GRC เพื่อสนับสนุนกา ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ทบทวนการทำ Value Creation และ Value Enhancement ที่เชื่อมโยงกับกระบวนการกำหนดตำแหน่งเชิงยุทธศาสตร์ วัตถุประสงค์เชิงยุทธศาสตร์ แผนยุทธศาสตร์องค์กร และแผนแม่บทอื่นๆ ที่เกี่ยวข้องอย่างต่อเนื่อง</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนการทำ Value Creation และ  ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนการทำ Value Creation และ  ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนการทำ Value Creation และ  ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนการทำ Value Creation และ  ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนการทำ Value Creation และ  ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ ทบทวนการทำ Value Creation และ  ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>กำหนดกระบวนการในการวิเคราะห์ถึงภาพรวมของความเสี่ยง (Portfolio View of Risk)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ กำหนดกระบวนการในการวิเคราะห์ถึ ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ กำหนดกระบวนการในการวิเคราะห์ถึ ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ กำหนดกระบวนการในการวิเคราะห์ถึ ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ กำหนดกระบวนการในการวิเคราะห์ถึ ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ กำหนดกระบวนการในการวิเคราะห์ถึ ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ กำหนดกระบวนการในการวิเคราะห์ถึ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>พัฒนา Portfolio View of Risk แสดงการจัดทำแบบจำลองที่เหมาะสม/นำแบบจำลองดังกล่าวไปใช้ในการบริหารความเสี่ยงในภาพรวม</t>
+  </si>
+  <si>
+    <t>ดำเนินการ พัฒนา Portfolio View of Risk แ ตามแผนในเดือนม.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ พัฒนา Portfolio View of Risk แ ตามแผนในเดือนก.พ. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ พัฒนา Portfolio View of Risk แ ตามแผนในเดือนมี.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ พัฒนา Portfolio View of Risk แ ตามแผนในเดือนเม.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ พัฒนา Portfolio View of Risk แ ตามแผนในเดือนพ.ค. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
+  </si>
+  <si>
+    <t>ดำเนินการ พัฒนา Portfolio View of Risk แ ตามแผนในเดือนมิ.ย. (สรุปย่อ — แก้เป็นเนื้อหาจริงได้)</t>
   </si>
 </sst>
 </file>
@@ -2024,13 +2711,13 @@
         <v>100</v>
       </c>
       <c r="S2" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T2" s="7">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U2" s="7">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="V2" s="7">
         <v>33</v>
@@ -2047,29 +2734,27 @@
       <c r="AB2" s="7"/>
       <c r="AC2" s="7"/>
       <c r="AD2" s="7"/>
-      <c r="AE2" s="8" t="s">
-        <v>38</v>
-      </c>
+      <c r="AE2" s="8"/>
       <c r="AF2" s="8"/>
       <c r="AG2" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="6">
@@ -2109,13 +2794,13 @@
         <v>100</v>
       </c>
       <c r="S3" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T3" s="7">
         <v>17</v>
       </c>
       <c r="U3" s="7">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="V3" s="7">
         <v>33</v>
@@ -2124,7 +2809,7 @@
         <v>42</v>
       </c>
       <c r="X3" s="7">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
@@ -2132,29 +2817,27 @@
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
       <c r="AD3" s="7"/>
-      <c r="AE3" s="8" t="s">
-        <v>44</v>
-      </c>
+      <c r="AE3" s="8"/>
       <c r="AF3" s="8"/>
       <c r="AG3" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6">
@@ -2194,19 +2877,19 @@
         <v>100</v>
       </c>
       <c r="S4" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T4" s="7">
         <v>17</v>
       </c>
       <c r="U4" s="7">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="V4" s="7">
         <v>33</v>
       </c>
       <c r="W4" s="7">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="X4" s="7">
         <v>50</v>
@@ -2217,29 +2900,27 @@
       <c r="AB4" s="7"/>
       <c r="AC4" s="7"/>
       <c r="AD4" s="7"/>
-      <c r="AE4" s="8" t="s">
-        <v>49</v>
-      </c>
+      <c r="AE4" s="8"/>
       <c r="AF4" s="8"/>
       <c r="AG4" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="6"/>
@@ -2279,7 +2960,7 @@
         <v>33</v>
       </c>
       <c r="W5" s="7">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="X5" s="7">
         <v>100</v>
@@ -2290,29 +2971,27 @@
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
       <c r="AD5" s="7"/>
-      <c r="AE5" s="8" t="s">
-        <v>54</v>
-      </c>
+      <c r="AE5" s="8"/>
       <c r="AF5" s="8"/>
       <c r="AG5" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="6"/>
@@ -2354,24 +3033,24 @@
       <c r="AE6" s="8"/>
       <c r="AF6" s="8"/>
       <c r="AG6" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="6"/>
@@ -2407,24 +3086,24 @@
       <c r="AE7" s="8"/>
       <c r="AF7" s="8"/>
       <c r="AG7" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="6"/>
@@ -2460,24 +3139,24 @@
       <c r="AE8" s="8"/>
       <c r="AF8" s="8"/>
       <c r="AG8" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="6"/>
@@ -2513,24 +3192,24 @@
       <c r="AE9" s="8"/>
       <c r="AF9" s="8"/>
       <c r="AG9" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="6"/>
@@ -2566,24 +3245,24 @@
       <c r="AE10" s="8"/>
       <c r="AF10" s="8"/>
       <c r="AG10" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="6">
@@ -2623,22 +3302,22 @@
         <v>100</v>
       </c>
       <c r="S11" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" s="7">
         <v>17</v>
       </c>
       <c r="U11" s="7">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="V11" s="7">
         <v>33</v>
       </c>
       <c r="W11" s="7">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X11" s="7">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
@@ -2646,29 +3325,27 @@
       <c r="AB11" s="7"/>
       <c r="AC11" s="7"/>
       <c r="AD11" s="7"/>
-      <c r="AE11" s="8" t="s">
-        <v>77</v>
-      </c>
+      <c r="AE11" s="8"/>
       <c r="AF11" s="8"/>
       <c r="AG11" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="6"/>
@@ -2705,10 +3382,10 @@
       <c r="T12" s="7"/>
       <c r="U12" s="7"/>
       <c r="V12" s="7">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="W12" s="7">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="X12" s="7">
         <v>50</v>
@@ -2719,29 +3396,27 @@
       <c r="AB12" s="7"/>
       <c r="AC12" s="7"/>
       <c r="AD12" s="7"/>
-      <c r="AE12" s="8" t="s">
-        <v>82</v>
-      </c>
+      <c r="AE12" s="8"/>
       <c r="AF12" s="8"/>
       <c r="AG12" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="6"/>
@@ -2783,24 +3458,24 @@
       <c r="AE13" s="8"/>
       <c r="AF13" s="8"/>
       <c r="AG13" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="6">
@@ -2840,19 +3515,19 @@
         <v>100</v>
       </c>
       <c r="S14" s="7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T14" s="7">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U14" s="7">
         <v>25</v>
       </c>
       <c r="V14" s="7">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="W14" s="7">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X14" s="7">
         <v>50</v>
@@ -2863,29 +3538,27 @@
       <c r="AB14" s="7"/>
       <c r="AC14" s="7"/>
       <c r="AD14" s="7"/>
-      <c r="AE14" s="8" t="s">
-        <v>91</v>
-      </c>
+      <c r="AE14" s="8"/>
       <c r="AF14" s="8"/>
       <c r="AG14" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="6">
@@ -2931,16 +3604,16 @@
         <v>17</v>
       </c>
       <c r="U15" s="7">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="V15" s="7">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="W15" s="7">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="X15" s="7">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Y15" s="7"/>
       <c r="Z15" s="7"/>
@@ -2948,29 +3621,27 @@
       <c r="AB15" s="7"/>
       <c r="AC15" s="7"/>
       <c r="AD15" s="7"/>
-      <c r="AE15" s="8" t="s">
-        <v>96</v>
-      </c>
+      <c r="AE15" s="8"/>
       <c r="AF15" s="8"/>
       <c r="AG15" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="6">
@@ -3010,19 +3681,19 @@
         <v>100</v>
       </c>
       <c r="S16" s="7">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T16" s="7">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="U16" s="7">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="V16" s="7">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="W16" s="7">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="X16" s="7">
         <v>100</v>
@@ -3033,29 +3704,27 @@
       <c r="AB16" s="7"/>
       <c r="AC16" s="7"/>
       <c r="AD16" s="7"/>
-      <c r="AE16" s="8" t="s">
-        <v>101</v>
-      </c>
+      <c r="AE16" s="8"/>
       <c r="AF16" s="8"/>
       <c r="AG16" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="6"/>
@@ -3097,27 +3766,27 @@
       <c r="AE17" s="8"/>
       <c r="AF17" s="8"/>
       <c r="AG17" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -3158,27 +3827,27 @@
       <c r="AE18" s="8"/>
       <c r="AF18" s="8"/>
       <c r="AG18" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -3217,27 +3886,27 @@
       <c r="AE19" s="8"/>
       <c r="AF19" s="8"/>
       <c r="AG19" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>114</v>
-      </c>
       <c r="F20" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -3272,27 +3941,27 @@
       <c r="AE20" s="8"/>
       <c r="AF20" s="8"/>
       <c r="AG20" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D21" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>116</v>
-      </c>
       <c r="F21" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -3325,27 +3994,27 @@
       <c r="AE21" s="8"/>
       <c r="AF21" s="8"/>
       <c r="AG21" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -3376,27 +4045,27 @@
       <c r="AE22" s="8"/>
       <c r="AF22" s="8"/>
       <c r="AG22" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -3431,7 +4100,7 @@
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
       <c r="W23" s="7">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="X23" s="7">
         <v>40</v>
@@ -3442,32 +4111,30 @@
       <c r="AB23" s="7"/>
       <c r="AC23" s="7"/>
       <c r="AD23" s="7"/>
-      <c r="AE23" s="8" t="s">
-        <v>122</v>
-      </c>
+      <c r="AE23" s="8"/>
       <c r="AF23" s="8"/>
       <c r="AG23" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>114</v>
-      </c>
       <c r="F24" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -3502,27 +4169,27 @@
       <c r="AE24" s="8"/>
       <c r="AF24" s="8"/>
       <c r="AG24" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -3555,27 +4222,27 @@
       <c r="AE25" s="8"/>
       <c r="AF25" s="8"/>
       <c r="AG25" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
@@ -3606,27 +4273,27 @@
       <c r="AE26" s="8"/>
       <c r="AF26" s="8"/>
       <c r="AG26" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
@@ -3660,7 +4327,7 @@
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
@@ -3668,34 +4335,32 @@
       <c r="AB27" s="7"/>
       <c r="AC27" s="7"/>
       <c r="AD27" s="7"/>
-      <c r="AE27" s="8" t="s">
-        <v>130</v>
-      </c>
+      <c r="AE27" s="8"/>
       <c r="AF27" s="8" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="AG27" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
@@ -3734,27 +4399,27 @@
       <c r="AE28" s="8"/>
       <c r="AF28" s="8"/>
       <c r="AG28" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>114</v>
-      </c>
       <c r="F29" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
@@ -3789,27 +4454,27 @@
       <c r="AE29" s="8"/>
       <c r="AF29" s="8"/>
       <c r="AG29" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
@@ -3842,27 +4507,27 @@
       <c r="AE30" s="8"/>
       <c r="AF30" s="8"/>
       <c r="AG30" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
@@ -3893,27 +4558,27 @@
       <c r="AE31" s="8"/>
       <c r="AF31" s="8"/>
       <c r="AG31" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G32" s="6">
         <v>17</v>
@@ -3952,16 +4617,16 @@
         <v>100</v>
       </c>
       <c r="S32" s="7">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T32" s="7">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="U32" s="7">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="V32" s="7">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="W32" s="7">
         <v>83</v>
@@ -3975,32 +4640,30 @@
       <c r="AB32" s="7"/>
       <c r="AC32" s="7"/>
       <c r="AD32" s="7"/>
-      <c r="AE32" s="8" t="s">
-        <v>142</v>
-      </c>
+      <c r="AE32" s="8"/>
       <c r="AF32" s="8"/>
       <c r="AG32" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G33" s="6">
         <v>33</v>
@@ -4039,10 +4702,10 @@
         <v>100</v>
       </c>
       <c r="S33" s="7">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="T33" s="7">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="U33" s="7">
         <v>100</v>
@@ -4062,32 +4725,30 @@
       <c r="AB33" s="7"/>
       <c r="AC33" s="7"/>
       <c r="AD33" s="7"/>
-      <c r="AE33" s="8" t="s">
-        <v>146</v>
-      </c>
+      <c r="AE33" s="8"/>
       <c r="AF33" s="8"/>
       <c r="AG33" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
@@ -4137,32 +4798,30 @@
       <c r="AB34" s="7"/>
       <c r="AC34" s="7"/>
       <c r="AD34" s="7"/>
-      <c r="AE34" s="8" t="s">
-        <v>149</v>
-      </c>
+      <c r="AE34" s="8"/>
       <c r="AF34" s="8"/>
       <c r="AG34" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C35" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>152</v>
-      </c>
       <c r="F35" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G35" s="6">
         <v>8</v>
@@ -4201,16 +4860,16 @@
         <v>100</v>
       </c>
       <c r="S35" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T35" s="7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="U35" s="7">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="V35" s="7">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="W35" s="7">
         <v>42</v>
@@ -4224,32 +4883,30 @@
       <c r="AB35" s="7"/>
       <c r="AC35" s="7"/>
       <c r="AD35" s="7"/>
-      <c r="AE35" s="8" t="s">
-        <v>153</v>
-      </c>
+      <c r="AE35" s="8"/>
       <c r="AF35" s="8"/>
       <c r="AG35" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
@@ -4286,27 +4943,27 @@
       <c r="AE36" s="8"/>
       <c r="AF36" s="8"/>
       <c r="AG36" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
@@ -4341,27 +4998,27 @@
       <c r="AE37" s="8"/>
       <c r="AF37" s="8"/>
       <c r="AG37" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
@@ -4397,10 +5054,10 @@
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
       <c r="V38" s="7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W38" s="7">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="X38" s="7">
         <v>43</v>
@@ -4411,32 +5068,30 @@
       <c r="AB38" s="7"/>
       <c r="AC38" s="7"/>
       <c r="AD38" s="7"/>
-      <c r="AE38" s="8" t="s">
-        <v>160</v>
-      </c>
+      <c r="AE38" s="8"/>
       <c r="AF38" s="8"/>
       <c r="AG38" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
@@ -4469,27 +5124,27 @@
       <c r="AE39" s="8"/>
       <c r="AF39" s="8"/>
       <c r="AG39" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
@@ -4522,27 +5177,27 @@
       <c r="AE40" s="8"/>
       <c r="AF40" s="8"/>
       <c r="AG40" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6">
@@ -4583,16 +5238,16 @@
         <v>33</v>
       </c>
       <c r="U41" s="7">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="V41" s="7">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="W41" s="7">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="X41" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Y41" s="7"/>
       <c r="Z41" s="7"/>
@@ -4600,32 +5255,30 @@
       <c r="AB41" s="7"/>
       <c r="AC41" s="7"/>
       <c r="AD41" s="7"/>
-      <c r="AE41" s="8" t="s">
-        <v>168</v>
-      </c>
+      <c r="AE41" s="8"/>
       <c r="AF41" s="8"/>
       <c r="AG41" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G42" s="6">
         <v>50</v>
@@ -4664,7 +5317,7 @@
         <v>100</v>
       </c>
       <c r="S42" s="7">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="T42" s="7">
         <v>100</v>
@@ -4687,32 +5340,30 @@
       <c r="AB42" s="7"/>
       <c r="AC42" s="7"/>
       <c r="AD42" s="7"/>
-      <c r="AE42" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="AE42" s="8"/>
       <c r="AF42" s="8"/>
       <c r="AG42" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G43" s="6">
         <v>50</v>
@@ -4751,7 +5402,7 @@
         <v>100</v>
       </c>
       <c r="S43" s="7">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T43" s="7">
         <v>100</v>
@@ -4774,32 +5425,30 @@
       <c r="AB43" s="7"/>
       <c r="AC43" s="7"/>
       <c r="AD43" s="7"/>
-      <c r="AE43" s="8" t="s">
-        <v>174</v>
-      </c>
+      <c r="AE43" s="8"/>
       <c r="AF43" s="8"/>
       <c r="AG43" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G44" s="6"/>
       <c r="H44" s="6">
@@ -4837,19 +5486,19 @@
       </c>
       <c r="S44" s="7"/>
       <c r="T44" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U44" s="7">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V44" s="7">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="W44" s="7">
         <v>36</v>
       </c>
       <c r="X44" s="7">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Y44" s="7"/>
       <c r="Z44" s="7"/>
@@ -4857,32 +5506,30 @@
       <c r="AB44" s="7"/>
       <c r="AC44" s="7"/>
       <c r="AD44" s="7"/>
-      <c r="AE44" s="8" t="s">
-        <v>177</v>
-      </c>
+      <c r="AE44" s="8"/>
       <c r="AF44" s="8"/>
       <c r="AG44" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
@@ -4923,27 +5570,27 @@
       <c r="AE45" s="8"/>
       <c r="AF45" s="8"/>
       <c r="AG45" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
@@ -4982,27 +5629,27 @@
       <c r="AE46" s="8"/>
       <c r="AF46" s="8"/>
       <c r="AG46" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
@@ -5039,27 +5686,27 @@
       <c r="AE47" s="8"/>
       <c r="AF47" s="8"/>
       <c r="AG47" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
@@ -5092,27 +5739,27 @@
       <c r="AE48" s="8"/>
       <c r="AF48" s="8"/>
       <c r="AG48" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G49" s="6">
         <v>50</v>
@@ -5151,13 +5798,13 @@
         <v>100</v>
       </c>
       <c r="S49" s="7">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T49" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="U49" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="V49" s="7">
         <v>100</v>
@@ -5174,32 +5821,30 @@
       <c r="AB49" s="7"/>
       <c r="AC49" s="7"/>
       <c r="AD49" s="7"/>
-      <c r="AE49" s="8" t="s">
-        <v>190</v>
-      </c>
+      <c r="AE49" s="8"/>
       <c r="AF49" s="8"/>
       <c r="AG49" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="6">
@@ -5237,16 +5882,16 @@
       </c>
       <c r="S50" s="7"/>
       <c r="T50" s="7">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="U50" s="7">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="V50" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="W50" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X50" s="7">
         <v>100</v>
@@ -5257,32 +5902,30 @@
       <c r="AB50" s="7"/>
       <c r="AC50" s="7"/>
       <c r="AD50" s="7"/>
-      <c r="AE50" s="8" t="s">
-        <v>193</v>
-      </c>
+      <c r="AE50" s="8"/>
       <c r="AF50" s="8"/>
       <c r="AG50" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
@@ -5332,32 +5975,30 @@
       <c r="AB51" s="7"/>
       <c r="AC51" s="7"/>
       <c r="AD51" s="7"/>
-      <c r="AE51" s="8" t="s">
-        <v>196</v>
-      </c>
+      <c r="AE51" s="8"/>
       <c r="AF51" s="8"/>
       <c r="AG51" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
@@ -5392,10 +6033,10 @@
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
       <c r="W52" s="7">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="X52" s="7">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="Y52" s="7"/>
       <c r="Z52" s="7"/>
@@ -5403,32 +6044,30 @@
       <c r="AB52" s="7"/>
       <c r="AC52" s="7"/>
       <c r="AD52" s="7"/>
-      <c r="AE52" s="8" t="s">
-        <v>198</v>
-      </c>
+      <c r="AE52" s="8"/>
       <c r="AF52" s="8"/>
       <c r="AG52" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="G53" s="6">
         <v>33</v>
@@ -5470,7 +6109,7 @@
         <v>33</v>
       </c>
       <c r="T53" s="7">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="U53" s="7">
         <v>100</v>
@@ -5490,32 +6129,30 @@
       <c r="AB53" s="7"/>
       <c r="AC53" s="7"/>
       <c r="AD53" s="7"/>
-      <c r="AE53" s="8" t="s">
-        <v>203</v>
-      </c>
+      <c r="AE53" s="8"/>
       <c r="AF53" s="8"/>
       <c r="AG53" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
@@ -5552,10 +6189,10 @@
       <c r="S54" s="7"/>
       <c r="T54" s="7"/>
       <c r="U54" s="7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="V54" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="W54" s="7">
         <v>100</v>
@@ -5569,32 +6206,30 @@
       <c r="AB54" s="7"/>
       <c r="AC54" s="7"/>
       <c r="AD54" s="7"/>
-      <c r="AE54" s="8" t="s">
-        <v>206</v>
-      </c>
+      <c r="AE54" s="8"/>
       <c r="AF54" s="8"/>
       <c r="AG54" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
@@ -5630,13 +6265,13 @@
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
       <c r="V55" s="7">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="W55" s="7">
         <v>29</v>
       </c>
       <c r="X55" s="7">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="Y55" s="7"/>
       <c r="Z55" s="7"/>
@@ -5644,32 +6279,30 @@
       <c r="AB55" s="7"/>
       <c r="AC55" s="7"/>
       <c r="AD55" s="7"/>
-      <c r="AE55" s="8" t="s">
-        <v>209</v>
-      </c>
+      <c r="AE55" s="8"/>
       <c r="AF55" s="8"/>
       <c r="AG55" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>210</v>
+        <v>183</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
@@ -5704,27 +6337,27 @@
       <c r="AE56" s="8"/>
       <c r="AF56" s="8"/>
       <c r="AG56" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -5757,27 +6390,27 @@
       <c r="AE57" s="8"/>
       <c r="AF57" s="8"/>
       <c r="AG57" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
@@ -5808,27 +6441,27 @@
       <c r="AE58" s="8"/>
       <c r="AF58" s="8"/>
       <c r="AG58" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
@@ -5865,16 +6498,16 @@
       <c r="S59" s="7"/>
       <c r="T59" s="7"/>
       <c r="U59" s="7">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="V59" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="W59" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X59" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Y59" s="7"/>
       <c r="Z59" s="7"/>
@@ -5882,32 +6515,30 @@
       <c r="AB59" s="7"/>
       <c r="AC59" s="7"/>
       <c r="AD59" s="7"/>
-      <c r="AE59" s="8" t="s">
-        <v>220</v>
-      </c>
+      <c r="AE59" s="8"/>
       <c r="AF59" s="8"/>
       <c r="AG59" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
@@ -5946,10 +6577,10 @@
         <v>33</v>
       </c>
       <c r="W60" s="7">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="X60" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Y60" s="7"/>
       <c r="Z60" s="7"/>
@@ -5957,32 +6588,30 @@
       <c r="AB60" s="7"/>
       <c r="AC60" s="7"/>
       <c r="AD60" s="7"/>
-      <c r="AE60" s="8" t="s">
-        <v>224</v>
-      </c>
+      <c r="AE60" s="8"/>
       <c r="AF60" s="8"/>
       <c r="AG60" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
@@ -6020,7 +6649,7 @@
         <v>50</v>
       </c>
       <c r="X61" s="7">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="Y61" s="7"/>
       <c r="Z61" s="7"/>
@@ -6028,32 +6657,30 @@
       <c r="AB61" s="7"/>
       <c r="AC61" s="7"/>
       <c r="AD61" s="7"/>
-      <c r="AE61" s="8" t="s">
-        <v>227</v>
-      </c>
+      <c r="AE61" s="8"/>
       <c r="AF61" s="8"/>
       <c r="AG61" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G62" s="6">
         <v>14</v>
@@ -6095,19 +6722,19 @@
         <v>14</v>
       </c>
       <c r="T62" s="7">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="U62" s="7">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="V62" s="7">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="W62" s="7">
         <v>71</v>
       </c>
       <c r="X62" s="7">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="Y62" s="7"/>
       <c r="Z62" s="7"/>
@@ -6115,32 +6742,30 @@
       <c r="AB62" s="7"/>
       <c r="AC62" s="7"/>
       <c r="AD62" s="7"/>
-      <c r="AE62" s="8" t="s">
-        <v>230</v>
-      </c>
+      <c r="AE62" s="8"/>
       <c r="AF62" s="8"/>
       <c r="AG62" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="63" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
@@ -6181,27 +6806,27 @@
       <c r="AE63" s="8"/>
       <c r="AF63" s="8"/>
       <c r="AG63" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G64" s="6">
         <v>33</v>
@@ -6263,32 +6888,30 @@
       <c r="AB64" s="7"/>
       <c r="AC64" s="7"/>
       <c r="AD64" s="7"/>
-      <c r="AE64" s="8" t="s">
-        <v>235</v>
-      </c>
+      <c r="AE64" s="8"/>
       <c r="AF64" s="8"/>
       <c r="AG64" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G65" s="6"/>
       <c r="H65" s="6">
@@ -6332,13 +6955,13 @@
         <v>18</v>
       </c>
       <c r="V65" s="7">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="W65" s="7">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="X65" s="7">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Y65" s="7"/>
       <c r="Z65" s="7"/>
@@ -6346,32 +6969,30 @@
       <c r="AB65" s="7"/>
       <c r="AC65" s="7"/>
       <c r="AD65" s="7"/>
-      <c r="AE65" s="8" t="s">
-        <v>238</v>
-      </c>
+      <c r="AE65" s="8"/>
       <c r="AF65" s="8"/>
       <c r="AG65" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="66" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G66" s="6"/>
       <c r="H66" s="6"/>
@@ -6408,7 +7029,7 @@
       <c r="S66" s="7"/>
       <c r="T66" s="7"/>
       <c r="U66" s="7">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="V66" s="7">
         <v>100</v>
@@ -6425,32 +7046,30 @@
       <c r="AB66" s="7"/>
       <c r="AC66" s="7"/>
       <c r="AD66" s="7"/>
-      <c r="AE66" s="8" t="s">
-        <v>241</v>
-      </c>
+      <c r="AE66" s="8"/>
       <c r="AF66" s="8"/>
       <c r="AG66" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G67" s="6"/>
       <c r="H67" s="6"/>
@@ -6500,32 +7119,30 @@
       <c r="AB67" s="7"/>
       <c r="AC67" s="7"/>
       <c r="AD67" s="7"/>
-      <c r="AE67" s="8" t="s">
-        <v>245</v>
-      </c>
+      <c r="AE67" s="8"/>
       <c r="AF67" s="8"/>
       <c r="AG67" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:33" ht="112" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G68" s="6"/>
       <c r="H68" s="6"/>
@@ -6559,7 +7176,7 @@
       <c r="V68" s="7"/>
       <c r="W68" s="7"/>
       <c r="X68" s="7">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Y68" s="7"/>
       <c r="Z68" s="7"/>
@@ -6567,34 +7184,32 @@
       <c r="AB68" s="7"/>
       <c r="AC68" s="7"/>
       <c r="AD68" s="7"/>
-      <c r="AE68" s="8" t="s">
-        <v>248</v>
-      </c>
+      <c r="AE68" s="8"/>
       <c r="AF68" s="8" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="AG68" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>250</v>
+        <v>214</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
@@ -6630,13 +7245,13 @@
       <c r="T69" s="7"/>
       <c r="U69" s="7"/>
       <c r="V69" s="7">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="W69" s="7">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="X69" s="7">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="Y69" s="7"/>
       <c r="Z69" s="7"/>
@@ -6644,34 +7259,32 @@
       <c r="AB69" s="7"/>
       <c r="AC69" s="7"/>
       <c r="AD69" s="7"/>
-      <c r="AE69" s="8" t="s">
-        <v>252</v>
-      </c>
+      <c r="AE69" s="8"/>
       <c r="AF69" s="8" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="AG69" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>253</v>
+        <v>216</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>250</v>
+        <v>214</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>254</v>
+        <v>217</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G70" s="6"/>
       <c r="H70" s="6"/>
@@ -6712,27 +7325,27 @@
       <c r="AE70" s="8"/>
       <c r="AF70" s="8"/>
       <c r="AG70" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>255</v>
+        <v>218</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>256</v>
+        <v>219</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>257</v>
+        <v>220</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G71" s="6"/>
       <c r="H71" s="6"/>
@@ -6770,7 +7383,7 @@
         <v>33</v>
       </c>
       <c r="X71" s="7">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Y71" s="7"/>
       <c r="Z71" s="7"/>
@@ -6778,32 +7391,30 @@
       <c r="AB71" s="7"/>
       <c r="AC71" s="7"/>
       <c r="AD71" s="7"/>
-      <c r="AE71" s="8" t="s">
-        <v>258</v>
-      </c>
+      <c r="AE71" s="8"/>
       <c r="AF71" s="8"/>
       <c r="AG71" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>259</v>
+        <v>221</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>260</v>
+        <v>222</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>261</v>
+        <v>223</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G72" s="6"/>
       <c r="H72" s="6"/>
@@ -6845,32 +7456,30 @@
       <c r="AB72" s="7"/>
       <c r="AC72" s="7"/>
       <c r="AD72" s="7"/>
-      <c r="AE72" s="8" t="s">
-        <v>262</v>
-      </c>
+      <c r="AE72" s="8"/>
       <c r="AF72" s="8"/>
       <c r="AG72" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="73" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>260</v>
+        <v>222</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G73" s="6"/>
       <c r="H73" s="6"/>
@@ -6904,7 +7513,7 @@
       <c r="V73" s="7"/>
       <c r="W73" s="7"/>
       <c r="X73" s="7">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Y73" s="7"/>
       <c r="Z73" s="7"/>
@@ -6912,32 +7521,30 @@
       <c r="AB73" s="7"/>
       <c r="AC73" s="7"/>
       <c r="AD73" s="7"/>
-      <c r="AE73" s="8" t="s">
-        <v>265</v>
-      </c>
+      <c r="AE73" s="8"/>
       <c r="AF73" s="8"/>
       <c r="AG73" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="74" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>266</v>
+        <v>226</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>260</v>
+        <v>222</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G74" s="6"/>
       <c r="H74" s="6"/>
@@ -6978,27 +7585,27 @@
       <c r="AE74" s="8"/>
       <c r="AF74" s="8"/>
       <c r="AG74" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>268</v>
+        <v>228</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>269</v>
+        <v>229</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G75" s="6"/>
       <c r="H75" s="6"/>
@@ -7032,7 +7639,7 @@
       <c r="V75" s="7"/>
       <c r="W75" s="7"/>
       <c r="X75" s="7">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="Y75" s="7"/>
       <c r="Z75" s="7"/>
@@ -7040,34 +7647,32 @@
       <c r="AB75" s="7"/>
       <c r="AC75" s="7"/>
       <c r="AD75" s="7"/>
-      <c r="AE75" s="8" t="s">
-        <v>271</v>
-      </c>
+      <c r="AE75" s="8"/>
       <c r="AF75" s="8" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="AG75" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>269</v>
+        <v>229</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>273</v>
+        <v>232</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G76" s="6"/>
       <c r="H76" s="6"/>
@@ -7101,7 +7706,7 @@
       <c r="V76" s="7"/>
       <c r="W76" s="7"/>
       <c r="X76" s="7">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="Y76" s="7"/>
       <c r="Z76" s="7"/>
@@ -7109,34 +7714,32 @@
       <c r="AB76" s="7"/>
       <c r="AC76" s="7"/>
       <c r="AD76" s="7"/>
-      <c r="AE76" s="8" t="s">
-        <v>274</v>
-      </c>
+      <c r="AE76" s="8"/>
       <c r="AF76" s="8" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="AG76" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="77" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>275</v>
+        <v>233</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>269</v>
+        <v>229</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G77" s="6"/>
       <c r="H77" s="6"/>
@@ -7173,27 +7776,27 @@
       <c r="AE77" s="8"/>
       <c r="AF77" s="8"/>
       <c r="AG77" s="9" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="78" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>277</v>
+        <v>235</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>279</v>
+        <v>237</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>280</v>
+        <v>238</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G78" s="6">
         <v>8</v>
@@ -7232,19 +7835,19 @@
         <v>100</v>
       </c>
       <c r="S78" s="7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T78" s="7">
         <v>17</v>
       </c>
       <c r="U78" s="7">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="V78" s="7">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="W78" s="7">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X78" s="7">
         <v>50</v>
@@ -7255,32 +7858,30 @@
       <c r="AB78" s="7"/>
       <c r="AC78" s="7"/>
       <c r="AD78" s="7"/>
-      <c r="AE78" s="8" t="s">
-        <v>282</v>
-      </c>
+      <c r="AE78" s="8"/>
       <c r="AF78" s="8"/>
       <c r="AG78" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>283</v>
+        <v>240</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>279</v>
+        <v>237</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>254</v>
+        <v>217</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G79" s="6"/>
       <c r="H79" s="6"/>
@@ -7314,7 +7915,7 @@
       <c r="V79" s="7"/>
       <c r="W79" s="7"/>
       <c r="X79" s="7">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="Y79" s="7"/>
       <c r="Z79" s="7"/>
@@ -7322,34 +7923,32 @@
       <c r="AB79" s="7"/>
       <c r="AC79" s="7"/>
       <c r="AD79" s="7"/>
-      <c r="AE79" s="8" t="s">
-        <v>284</v>
-      </c>
+      <c r="AE79" s="8"/>
       <c r="AF79" s="8" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="AG79" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="80" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>285</v>
+        <v>241</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>279</v>
+        <v>237</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>286</v>
+        <v>242</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G80" s="6"/>
       <c r="H80" s="6"/>
@@ -7387,7 +7986,7 @@
         <v>33</v>
       </c>
       <c r="X80" s="7">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="Y80" s="7"/>
       <c r="Z80" s="7"/>
@@ -7395,34 +7994,32 @@
       <c r="AB80" s="7"/>
       <c r="AC80" s="7"/>
       <c r="AD80" s="7"/>
-      <c r="AE80" s="8" t="s">
-        <v>287</v>
-      </c>
+      <c r="AE80" s="8"/>
       <c r="AF80" s="8" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="AG80" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>288</v>
+        <v>243</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>289</v>
+        <v>244</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G81" s="6"/>
       <c r="H81" s="6"/>
@@ -7456,7 +8053,7 @@
       <c r="V81" s="7"/>
       <c r="W81" s="7"/>
       <c r="X81" s="7">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Y81" s="7"/>
       <c r="Z81" s="7"/>
@@ -7464,32 +8061,30 @@
       <c r="AB81" s="7"/>
       <c r="AC81" s="7"/>
       <c r="AD81" s="7"/>
-      <c r="AE81" s="8" t="s">
-        <v>291</v>
-      </c>
+      <c r="AE81" s="8"/>
       <c r="AF81" s="8"/>
       <c r="AG81" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>289</v>
+        <v>244</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>293</v>
+        <v>247</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G82" s="6"/>
       <c r="H82" s="6"/>
@@ -7523,7 +8118,7 @@
       <c r="V82" s="7"/>
       <c r="W82" s="7"/>
       <c r="X82" s="7">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="Y82" s="7"/>
       <c r="Z82" s="7"/>
@@ -7531,32 +8126,30 @@
       <c r="AB82" s="7"/>
       <c r="AC82" s="7"/>
       <c r="AD82" s="7"/>
-      <c r="AE82" s="8" t="s">
-        <v>294</v>
-      </c>
+      <c r="AE82" s="8"/>
       <c r="AF82" s="8"/>
       <c r="AG82" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>295</v>
+        <v>248</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>297</v>
+        <v>250</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G83" s="6"/>
       <c r="H83" s="6"/>
@@ -7597,27 +8190,27 @@
       <c r="AE83" s="8"/>
       <c r="AF83" s="8"/>
       <c r="AG83" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="84" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>298</v>
+        <v>251</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G84" s="6"/>
       <c r="H84" s="6"/>
@@ -7654,27 +8247,27 @@
       <c r="AE84" s="8"/>
       <c r="AF84" s="8"/>
       <c r="AG84" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="85" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G85" s="6"/>
       <c r="H85" s="6"/>
@@ -7711,27 +8304,27 @@
       <c r="AE85" s="8"/>
       <c r="AF85" s="8"/>
       <c r="AG85" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
@@ -7770,27 +8363,27 @@
       <c r="AE86" s="8"/>
       <c r="AF86" s="8"/>
       <c r="AG86" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>305</v>
+        <v>258</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>306</v>
+        <v>259</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
@@ -7829,27 +8422,27 @@
       <c r="AE87" s="8"/>
       <c r="AF87" s="8"/>
       <c r="AG87" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="88" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>308</v>
+        <v>261</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>309</v>
+        <v>262</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>310</v>
+        <v>263</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G88" s="6">
         <v>8</v>
@@ -7888,22 +8481,22 @@
         <v>100</v>
       </c>
       <c r="S88" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T88" s="7">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="U88" s="7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="V88" s="7">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="W88" s="7">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="X88" s="7">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y88" s="7"/>
       <c r="Z88" s="7"/>
@@ -7911,32 +8504,30 @@
       <c r="AB88" s="7"/>
       <c r="AC88" s="7"/>
       <c r="AD88" s="7"/>
-      <c r="AE88" s="8" t="s">
-        <v>311</v>
-      </c>
+      <c r="AE88" s="8"/>
       <c r="AF88" s="8"/>
       <c r="AG88" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>312</v>
+        <v>264</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>309</v>
+        <v>262</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>313</v>
+        <v>265</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G89" s="6">
         <v>8</v>
@@ -7975,19 +8566,19 @@
         <v>100</v>
       </c>
       <c r="S89" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T89" s="7">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="U89" s="7">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="V89" s="7">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="W89" s="7">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X89" s="7">
         <v>50</v>
@@ -7998,32 +8589,30 @@
       <c r="AB89" s="7"/>
       <c r="AC89" s="7"/>
       <c r="AD89" s="7"/>
-      <c r="AE89" s="8" t="s">
-        <v>314</v>
-      </c>
+      <c r="AE89" s="8"/>
       <c r="AF89" s="8"/>
       <c r="AG89" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>309</v>
+        <v>262</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G90" s="6"/>
       <c r="H90" s="6"/>
@@ -8073,32 +8662,30 @@
       <c r="AB90" s="7"/>
       <c r="AC90" s="7"/>
       <c r="AD90" s="7"/>
-      <c r="AE90" s="8" t="s">
-        <v>317</v>
-      </c>
+      <c r="AE90" s="8"/>
       <c r="AF90" s="8"/>
       <c r="AG90" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="91" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
-        <v>318</v>
+        <v>268</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G91" s="6">
         <v>8</v>
@@ -8137,22 +8724,22 @@
         <v>100</v>
       </c>
       <c r="S91" s="7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T91" s="7">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="U91" s="7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="V91" s="7">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="W91" s="7">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="X91" s="7">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Y91" s="7"/>
       <c r="Z91" s="7"/>
@@ -8160,32 +8747,30 @@
       <c r="AB91" s="7"/>
       <c r="AC91" s="7"/>
       <c r="AD91" s="7"/>
-      <c r="AE91" s="8" t="s">
-        <v>321</v>
-      </c>
+      <c r="AE91" s="8"/>
       <c r="AF91" s="8"/>
       <c r="AG91" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="92" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>322</v>
+        <v>271</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>323</v>
+        <v>272</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>324</v>
+        <v>273</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G92" s="6"/>
       <c r="H92" s="6"/>
@@ -8220,27 +8805,27 @@
       <c r="AE92" s="8"/>
       <c r="AF92" s="8"/>
       <c r="AG92" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>325</v>
+        <v>274</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>323</v>
+        <v>272</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>326</v>
+        <v>275</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G93" s="6"/>
       <c r="H93" s="6"/>
@@ -8275,27 +8860,27 @@
       <c r="AE93" s="8"/>
       <c r="AF93" s="8"/>
       <c r="AG93" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>323</v>
+        <v>272</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>328</v>
+        <v>277</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G94" s="6"/>
       <c r="H94" s="6"/>
@@ -8330,27 +8915,27 @@
       <c r="AE94" s="8"/>
       <c r="AF94" s="8"/>
       <c r="AG94" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="95" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>329</v>
+        <v>278</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>323</v>
+        <v>272</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>330</v>
+        <v>279</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G95" s="6"/>
       <c r="H95" s="6"/>
@@ -8381,27 +8966,27 @@
       <c r="AE95" s="8"/>
       <c r="AF95" s="8"/>
       <c r="AG95" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="96" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>331</v>
+        <v>280</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>333</v>
+        <v>282</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>334</v>
+        <v>283</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G96" s="6">
         <v>33</v>
@@ -8443,7 +9028,7 @@
         <v>33</v>
       </c>
       <c r="T96" s="7">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="U96" s="7">
         <v>100</v>
@@ -8463,32 +9048,30 @@
       <c r="AB96" s="7"/>
       <c r="AC96" s="7"/>
       <c r="AD96" s="7"/>
-      <c r="AE96" s="8" t="s">
-        <v>335</v>
-      </c>
+      <c r="AE96" s="8"/>
       <c r="AF96" s="8"/>
       <c r="AG96" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>336</v>
+        <v>284</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>333</v>
+        <v>282</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>337</v>
+        <v>285</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G97" s="6"/>
       <c r="H97" s="6"/>
@@ -8525,13 +9108,13 @@
       <c r="S97" s="7"/>
       <c r="T97" s="7"/>
       <c r="U97" s="7">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="V97" s="7">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="W97" s="7">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="X97" s="7">
         <v>100</v>
@@ -8542,32 +9125,30 @@
       <c r="AB97" s="7"/>
       <c r="AC97" s="7"/>
       <c r="AD97" s="7"/>
-      <c r="AE97" s="8" t="s">
-        <v>338</v>
-      </c>
+      <c r="AE97" s="8"/>
       <c r="AF97" s="8"/>
       <c r="AG97" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>333</v>
+        <v>282</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>340</v>
+        <v>287</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G98" s="6"/>
       <c r="H98" s="6"/>
@@ -8602,10 +9183,10 @@
       <c r="U98" s="7"/>
       <c r="V98" s="7"/>
       <c r="W98" s="7">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="X98" s="7">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Y98" s="7"/>
       <c r="Z98" s="7"/>
@@ -8613,32 +9194,30 @@
       <c r="AB98" s="7"/>
       <c r="AC98" s="7"/>
       <c r="AD98" s="7"/>
-      <c r="AE98" s="8" t="s">
-        <v>341</v>
-      </c>
+      <c r="AE98" s="8"/>
       <c r="AF98" s="8"/>
       <c r="AG98" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="99" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>333</v>
+        <v>282</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>343</v>
+        <v>289</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G99" s="6"/>
       <c r="H99" s="6"/>
@@ -8679,27 +9258,27 @@
       <c r="AE99" s="8"/>
       <c r="AF99" s="8"/>
       <c r="AG99" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>344</v>
+        <v>290</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>333</v>
+        <v>282</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>345</v>
+        <v>291</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G100" s="6"/>
       <c r="H100" s="6"/>
@@ -8734,27 +9313,27 @@
       <c r="AE100" s="8"/>
       <c r="AF100" s="8"/>
       <c r="AG100" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>346</v>
+        <v>292</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>347</v>
+        <v>293</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>348</v>
+        <v>294</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G101" s="6"/>
       <c r="H101" s="6"/>
@@ -8808,32 +9387,30 @@
       <c r="AB101" s="7"/>
       <c r="AC101" s="7"/>
       <c r="AD101" s="7"/>
-      <c r="AE101" s="8" t="s">
-        <v>349</v>
-      </c>
+      <c r="AE101" s="8"/>
       <c r="AF101" s="8"/>
       <c r="AG101" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>350</v>
+        <v>295</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>347</v>
+        <v>293</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
@@ -8869,7 +9446,7 @@
       <c r="T102" s="7"/>
       <c r="U102" s="7"/>
       <c r="V102" s="7">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="W102" s="7">
         <v>100</v>
@@ -8883,32 +9460,30 @@
       <c r="AB102" s="7"/>
       <c r="AC102" s="7"/>
       <c r="AD102" s="7"/>
-      <c r="AE102" s="8" t="s">
-        <v>352</v>
-      </c>
+      <c r="AE102" s="8"/>
       <c r="AF102" s="8"/>
       <c r="AG102" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="103" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>353</v>
+        <v>297</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>347</v>
+        <v>293</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>354</v>
+        <v>298</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G103" s="6"/>
       <c r="H103" s="6"/>
@@ -8944,13 +9519,13 @@
       <c r="T103" s="7"/>
       <c r="U103" s="7"/>
       <c r="V103" s="7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W103" s="7">
         <v>22</v>
       </c>
       <c r="X103" s="7">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Y103" s="7"/>
       <c r="Z103" s="7"/>
@@ -8958,32 +9533,30 @@
       <c r="AB103" s="7"/>
       <c r="AC103" s="7"/>
       <c r="AD103" s="7"/>
-      <c r="AE103" s="8" t="s">
-        <v>355</v>
-      </c>
+      <c r="AE103" s="8"/>
       <c r="AF103" s="8"/>
       <c r="AG103" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="104" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>356</v>
+        <v>299</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>347</v>
+        <v>293</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>357</v>
+        <v>300</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G104" s="6"/>
       <c r="H104" s="6"/>
@@ -9019,10 +9592,10 @@
       <c r="T104" s="7"/>
       <c r="U104" s="7"/>
       <c r="V104" s="7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W104" s="7">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="X104" s="7">
         <v>33</v>
@@ -9033,32 +9606,30 @@
       <c r="AB104" s="7"/>
       <c r="AC104" s="7"/>
       <c r="AD104" s="7"/>
-      <c r="AE104" s="8" t="s">
-        <v>358</v>
-      </c>
+      <c r="AE104" s="8"/>
       <c r="AF104" s="8"/>
       <c r="AG104" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="105" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>359</v>
+        <v>301</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>361</v>
+        <v>303</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G105" s="6"/>
       <c r="H105" s="6"/>
@@ -9112,32 +9683,30 @@
       <c r="AB105" s="7"/>
       <c r="AC105" s="7"/>
       <c r="AD105" s="7"/>
-      <c r="AE105" s="8" t="s">
-        <v>362</v>
-      </c>
+      <c r="AE105" s="8"/>
       <c r="AF105" s="8"/>
       <c r="AG105" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="106" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
-        <v>363</v>
+        <v>304</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>364</v>
+        <v>305</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
@@ -9174,10 +9743,10 @@
       <c r="S106" s="7"/>
       <c r="T106" s="7"/>
       <c r="U106" s="7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="V106" s="7">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="W106" s="7">
         <v>100</v>
@@ -9191,32 +9760,30 @@
       <c r="AB106" s="7"/>
       <c r="AC106" s="7"/>
       <c r="AD106" s="7"/>
-      <c r="AE106" s="8" t="s">
-        <v>365</v>
-      </c>
+      <c r="AE106" s="8"/>
       <c r="AF106" s="8"/>
       <c r="AG106" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="107" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>367</v>
+        <v>307</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
@@ -9252,13 +9819,13 @@
       <c r="T107" s="7"/>
       <c r="U107" s="7"/>
       <c r="V107" s="7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="W107" s="7">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="X107" s="7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y107" s="7"/>
       <c r="Z107" s="7"/>
@@ -9266,32 +9833,30 @@
       <c r="AB107" s="7"/>
       <c r="AC107" s="7"/>
       <c r="AD107" s="7"/>
-      <c r="AE107" s="8" t="s">
-        <v>368</v>
-      </c>
+      <c r="AE107" s="8"/>
       <c r="AF107" s="8"/>
       <c r="AG107" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="108" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
-        <v>369</v>
+        <v>308</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>370</v>
+        <v>309</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G108" s="6"/>
       <c r="H108" s="6"/>
@@ -9326,27 +9891,27 @@
       <c r="AE108" s="8"/>
       <c r="AF108" s="8"/>
       <c r="AG108" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="109" spans="1:33" ht="32" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
-        <v>371</v>
+        <v>310</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>372</v>
+        <v>311</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G109" s="6"/>
       <c r="H109" s="6"/>
@@ -9379,27 +9944,27 @@
       <c r="AE109" s="8"/>
       <c r="AF109" s="8"/>
       <c r="AG109" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="110" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
-        <v>373</v>
+        <v>312</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>374</v>
+        <v>313</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>375</v>
+        <v>314</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G110" s="6">
         <v>10</v>
@@ -9447,13 +10012,13 @@
         <v>30</v>
       </c>
       <c r="V110" s="7">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="W110" s="7">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="X110" s="7">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="Y110" s="7"/>
       <c r="Z110" s="7"/>
@@ -9461,32 +10026,30 @@
       <c r="AB110" s="7"/>
       <c r="AC110" s="7"/>
       <c r="AD110" s="7"/>
-      <c r="AE110" s="8" t="s">
-        <v>376</v>
-      </c>
+      <c r="AE110" s="8"/>
       <c r="AF110" s="8"/>
       <c r="AG110" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="111" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>377</v>
+        <v>315</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>374</v>
+        <v>313</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>378</v>
+        <v>316</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G111" s="6"/>
       <c r="H111" s="6">
@@ -9524,19 +10087,19 @@
       </c>
       <c r="S111" s="7"/>
       <c r="T111" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U111" s="7">
         <v>20</v>
       </c>
       <c r="V111" s="7">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="W111" s="7">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="X111" s="7">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="Y111" s="7"/>
       <c r="Z111" s="7"/>
@@ -9544,34 +10107,32 @@
       <c r="AB111" s="7"/>
       <c r="AC111" s="7"/>
       <c r="AD111" s="7"/>
-      <c r="AE111" s="8" t="s">
-        <v>379</v>
-      </c>
+      <c r="AE111" s="8"/>
       <c r="AF111" s="8" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="AG111" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="112" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
-        <v>380</v>
+        <v>317</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>374</v>
+        <v>313</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>381</v>
+        <v>318</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G112" s="6"/>
       <c r="H112" s="6">
@@ -9609,19 +10170,19 @@
       </c>
       <c r="S112" s="7"/>
       <c r="T112" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U112" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="V112" s="7">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="W112" s="7">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="X112" s="7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y112" s="7"/>
       <c r="Z112" s="7"/>
@@ -9629,32 +10190,30 @@
       <c r="AB112" s="7"/>
       <c r="AC112" s="7"/>
       <c r="AD112" s="7"/>
-      <c r="AE112" s="8" t="s">
-        <v>382</v>
-      </c>
+      <c r="AE112" s="8"/>
       <c r="AF112" s="8"/>
       <c r="AG112" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="113" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
-        <v>383</v>
+        <v>319</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>374</v>
+        <v>313</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>384</v>
+        <v>320</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G113" s="6"/>
       <c r="H113" s="6"/>
@@ -9687,27 +10246,27 @@
       <c r="AE113" s="8"/>
       <c r="AF113" s="8"/>
       <c r="AG113" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="114" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
-        <v>385</v>
+        <v>321</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>386</v>
+        <v>322</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>387</v>
+        <v>323</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G114" s="6"/>
       <c r="H114" s="6"/>
@@ -9742,27 +10301,27 @@
       <c r="AE114" s="8"/>
       <c r="AF114" s="8"/>
       <c r="AG114" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="115" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
-        <v>388</v>
+        <v>324</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>386</v>
+        <v>322</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>389</v>
+        <v>325</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
@@ -9797,27 +10356,27 @@
       <c r="AE115" s="8"/>
       <c r="AF115" s="8"/>
       <c r="AG115" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="116" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>390</v>
+        <v>326</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>386</v>
+        <v>322</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>391</v>
+        <v>327</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G116" s="6"/>
       <c r="H116" s="6"/>
@@ -9852,27 +10411,27 @@
       <c r="AE116" s="8"/>
       <c r="AF116" s="8"/>
       <c r="AG116" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="117" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
-        <v>392</v>
+        <v>328</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>386</v>
+        <v>322</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>393</v>
+        <v>329</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G117" s="6"/>
       <c r="H117" s="6"/>
@@ -9907,27 +10466,27 @@
       <c r="AE117" s="8"/>
       <c r="AF117" s="8"/>
       <c r="AG117" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="118" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
-        <v>394</v>
+        <v>330</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>386</v>
+        <v>322</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>395</v>
+        <v>331</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G118" s="6"/>
       <c r="H118" s="6"/>
@@ -9962,27 +10521,27 @@
       <c r="AE118" s="8"/>
       <c r="AF118" s="8"/>
       <c r="AG118" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="119" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
-        <v>396</v>
+        <v>332</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>386</v>
+        <v>322</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>397</v>
+        <v>333</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G119" s="6"/>
       <c r="H119" s="6"/>
@@ -10015,27 +10574,27 @@
       <c r="AE119" s="8"/>
       <c r="AF119" s="8"/>
       <c r="AG119" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="120" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
-        <v>398</v>
+        <v>334</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>386</v>
+        <v>322</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>399</v>
+        <v>335</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G120" s="6"/>
       <c r="H120" s="6"/>
@@ -10068,27 +10627,27 @@
       <c r="AE120" s="8"/>
       <c r="AF120" s="8"/>
       <c r="AG120" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="121" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
-        <v>400</v>
+        <v>336</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>386</v>
+        <v>322</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>401</v>
+        <v>337</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G121" s="6"/>
       <c r="H121" s="6"/>
@@ -10119,27 +10678,27 @@
       <c r="AE121" s="8"/>
       <c r="AF121" s="8"/>
       <c r="AG121" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="122" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
-        <v>402</v>
+        <v>338</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>386</v>
+        <v>322</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>403</v>
+        <v>339</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G122" s="6"/>
       <c r="H122" s="6"/>
@@ -10170,24 +10729,24 @@
       <c r="AE122" s="8"/>
       <c r="AF122" s="8"/>
       <c r="AG122" s="9" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="123" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
-        <v>404</v>
+        <v>340</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>405</v>
+        <v>341</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>406</v>
+        <v>342</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>407</v>
+        <v>343</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>408</v>
+        <v>344</v>
       </c>
       <c r="F123" s="4"/>
       <c r="G123" s="6">
@@ -10227,22 +10786,22 @@
         <v>100</v>
       </c>
       <c r="S123" s="7">
-        <v>8.3000000000000007</v>
+        <v>8</v>
       </c>
       <c r="T123" s="7">
-        <v>16.7</v>
+        <v>21</v>
       </c>
       <c r="U123" s="7">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="V123" s="7">
-        <v>33.299999999999997</v>
+        <v>30</v>
       </c>
       <c r="W123" s="7">
-        <v>41.7</v>
+        <v>47</v>
       </c>
       <c r="X123" s="7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y123" s="7"/>
       <c r="Z123" s="7"/>
@@ -10250,29 +10809,27 @@
       <c r="AB123" s="7"/>
       <c r="AC123" s="7"/>
       <c r="AD123" s="7"/>
-      <c r="AE123" s="8" t="s">
-        <v>409</v>
-      </c>
+      <c r="AE123" s="8"/>
       <c r="AF123" s="8"/>
       <c r="AG123" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="124" spans="1:33" ht="64" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
-        <v>410</v>
+        <v>345</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>405</v>
+        <v>341</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>411</v>
+        <v>346</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>412</v>
+        <v>347</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>413</v>
+        <v>348</v>
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="6">
@@ -10312,22 +10869,22 @@
         <v>100</v>
       </c>
       <c r="S124" s="7">
-        <v>8.3000000000000007</v>
+        <v>8</v>
       </c>
       <c r="T124" s="7">
-        <v>16.7</v>
+        <v>8</v>
       </c>
       <c r="U124" s="7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V124" s="7">
-        <v>33.299999999999997</v>
+        <v>33</v>
       </c>
       <c r="W124" s="7">
-        <v>41.7</v>
+        <v>47</v>
       </c>
       <c r="X124" s="7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y124" s="7"/>
       <c r="Z124" s="7"/>
@@ -10335,29 +10892,27 @@
       <c r="AB124" s="7"/>
       <c r="AC124" s="7"/>
       <c r="AD124" s="7"/>
-      <c r="AE124" s="8" t="s">
-        <v>414</v>
-      </c>
+      <c r="AE124" s="8"/>
       <c r="AF124" s="8"/>
       <c r="AG124" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="125" spans="1:33" ht="128" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
-        <v>415</v>
+        <v>349</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>405</v>
+        <v>341</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>416</v>
+        <v>350</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>417</v>
+        <v>351</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>418</v>
+        <v>352</v>
       </c>
       <c r="F125" s="4"/>
       <c r="G125" s="6">
@@ -10397,22 +10952,22 @@
         <v>100</v>
       </c>
       <c r="S125" s="7">
-        <v>8.3000000000000007</v>
+        <v>13</v>
       </c>
       <c r="T125" s="7">
-        <v>16.7</v>
+        <v>13</v>
       </c>
       <c r="U125" s="7">
         <v>25</v>
       </c>
       <c r="V125" s="7">
-        <v>33.299999999999997</v>
+        <v>33</v>
       </c>
       <c r="W125" s="7">
-        <v>41.7</v>
+        <v>46</v>
       </c>
       <c r="X125" s="7">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Y125" s="7"/>
       <c r="Z125" s="7"/>
@@ -10420,29 +10975,27 @@
       <c r="AB125" s="7"/>
       <c r="AC125" s="7"/>
       <c r="AD125" s="7"/>
-      <c r="AE125" s="8" t="s">
-        <v>419</v>
-      </c>
+      <c r="AE125" s="8"/>
       <c r="AF125" s="8"/>
       <c r="AG125" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="126" spans="1:33" ht="48" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
-        <v>420</v>
+        <v>353</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>405</v>
+        <v>341</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>421</v>
+        <v>354</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>422</v>
+        <v>355</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>423</v>
+        <v>356</v>
       </c>
       <c r="F126" s="4"/>
       <c r="G126" s="6">
@@ -10482,19 +11035,19 @@
         <v>100</v>
       </c>
       <c r="S126" s="7">
-        <v>8.3000000000000007</v>
+        <v>8</v>
       </c>
       <c r="T126" s="7">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="U126" s="7">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="V126" s="7">
-        <v>33.299999999999997</v>
+        <v>27</v>
       </c>
       <c r="W126" s="7">
-        <v>41.7</v>
+        <v>27</v>
       </c>
       <c r="X126" s="7">
         <v>50</v>
@@ -10505,29 +11058,27 @@
       <c r="AB126" s="7"/>
       <c r="AC126" s="7"/>
       <c r="AD126" s="7"/>
-      <c r="AE126" s="8" t="s">
-        <v>424</v>
-      </c>
+      <c r="AE126" s="8"/>
       <c r="AF126" s="8"/>
       <c r="AG126" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="127" spans="1:33" ht="80" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>405</v>
+        <v>341</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>426</v>
+        <v>358</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>427</v>
+        <v>359</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>428</v>
+        <v>360</v>
       </c>
       <c r="F127" s="4"/>
       <c r="G127" s="6">
@@ -10567,22 +11118,22 @@
         <v>100</v>
       </c>
       <c r="S127" s="7">
-        <v>8.3000000000000007</v>
+        <v>8</v>
       </c>
       <c r="T127" s="7">
-        <v>16.7</v>
+        <v>8</v>
       </c>
       <c r="U127" s="7">
         <v>25</v>
       </c>
       <c r="V127" s="7">
-        <v>33.299999999999997</v>
+        <v>33</v>
       </c>
       <c r="W127" s="7">
-        <v>41.7</v>
+        <v>33</v>
       </c>
       <c r="X127" s="7">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Y127" s="7"/>
       <c r="Z127" s="7"/>
@@ -10590,12 +11141,10 @@
       <c r="AB127" s="7"/>
       <c r="AC127" s="7"/>
       <c r="AD127" s="7"/>
-      <c r="AE127" s="8" t="s">
-        <v>429</v>
-      </c>
+      <c r="AE127" s="8"/>
       <c r="AF127" s="8"/>
       <c r="AG127" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -10623,7 +11172,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
-        <v>430</v>
+        <v>361</v>
       </c>
       <c r="B1" s="11"/>
     </row>
@@ -10633,40 +11182,40 @@
     </row>
     <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>431</v>
+        <v>362</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>432</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
-        <v>433</v>
+        <v>364</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>434</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
-        <v>435</v>
+        <v>366</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>436</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="12"/>
       <c r="B6" s="11" t="s">
-        <v>437</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
-        <v>438</v>
+        <v>369</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>439</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -10675,24 +11224,24 @@
     </row>
     <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>440</v>
+        <v>371</v>
       </c>
       <c r="B9" s="11"/>
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>442</v>
+        <v>373</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
-        <v>443</v>
+        <v>374</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>444</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -10701,17 +11250,1676 @@
     </row>
     <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
-        <v>445</v>
+        <v>376</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>446</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="12"/>
       <c r="B14" s="11" t="s">
+        <v>378</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:P49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="16" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+    </row>
+    <row r="3" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+    </row>
+    <row r="4" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+    </row>
+    <row r="5" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+    </row>
+    <row r="6" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+    </row>
+    <row r="7" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+    </row>
+    <row r="8" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+    </row>
+    <row r="9" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+    </row>
+    <row r="10" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+    </row>
+    <row r="11" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+    </row>
+    <row r="13" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>447</v>
       </c>
+      <c r="F13" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+    </row>
+    <row r="14" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+    </row>
+    <row r="15" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+    </row>
+    <row r="16" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+    </row>
+    <row r="17" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+    </row>
+    <row r="18" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+    </row>
+    <row r="19" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+    </row>
+    <row r="20" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+    </row>
+    <row r="21" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+    </row>
+    <row r="22" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+    </row>
+    <row r="23" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+    </row>
+    <row r="24" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+    </row>
+    <row r="25" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+    </row>
+    <row r="26" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+    </row>
+    <row r="27" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+    </row>
+    <row r="28" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+    </row>
+    <row r="29" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
+    </row>
+    <row r="30" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
+    </row>
+    <row r="31" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="8"/>
+    </row>
+    <row r="32" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="8"/>
+    </row>
+    <row r="33" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="8"/>
+    </row>
+    <row r="34" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8"/>
+    </row>
+    <row r="35" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="8"/>
+    </row>
+    <row r="36" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="8"/>
+    </row>
+    <row r="37" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
+      <c r="P37" s="8"/>
+    </row>
+    <row r="38" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
+      <c r="P38" s="8"/>
+    </row>
+    <row r="39" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
+      <c r="P39" s="8"/>
+    </row>
+    <row r="40" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
+      <c r="P40" s="8"/>
+    </row>
+    <row r="41" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8"/>
+    </row>
+    <row r="42" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
+      <c r="P42" s="8"/>
+    </row>
+    <row r="43" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
+      <c r="P43" s="8"/>
+    </row>
+    <row r="44" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
+      <c r="P44" s="8"/>
+    </row>
+    <row r="45" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A45" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
+      <c r="O45" s="8"/>
+      <c r="P45" s="8"/>
+    </row>
+    <row r="46" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="8"/>
+      <c r="P46" s="8"/>
+    </row>
+    <row r="47" spans="1:16" ht="80" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
+      <c r="O47" s="8"/>
+      <c r="P47" s="8"/>
+    </row>
+    <row r="48" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="8"/>
+      <c r="P48" s="8"/>
+    </row>
+    <row r="49" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A49" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="8"/>
+      <c r="O49" s="8"/>
+      <c r="P49" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/บันทึกผลการดำเนินงาน_RM_2569.xlsx
+++ b/บันทึกผลการดำเนินงาน_RM_2569.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devill/1_กฟน./2569/Dashborad_RM/rm-dashboard-2569/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C5BBDC-F911-284D-BBBF-1593A546BFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECB81F4-5C03-CB4F-9C7F-1F20CE3E05F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="บันทึกผล" sheetId="1" r:id="rId1"/>
@@ -2711,13 +2711,13 @@
         <v>100</v>
       </c>
       <c r="S2" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T2" s="7">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U2" s="7">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="V2" s="7">
         <v>33</v>
@@ -2794,13 +2794,13 @@
         <v>100</v>
       </c>
       <c r="S3" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T3" s="7">
         <v>17</v>
       </c>
       <c r="U3" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V3" s="7">
         <v>33</v>
@@ -2809,7 +2809,7 @@
         <v>42</v>
       </c>
       <c r="X3" s="7">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
@@ -2877,19 +2877,19 @@
         <v>100</v>
       </c>
       <c r="S4" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T4" s="7">
         <v>17</v>
       </c>
       <c r="U4" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V4" s="7">
         <v>33</v>
       </c>
       <c r="W4" s="7">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="X4" s="7">
         <v>50</v>
@@ -2960,7 +2960,7 @@
         <v>33</v>
       </c>
       <c r="W5" s="7">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="X5" s="7">
         <v>100</v>
@@ -3302,22 +3302,22 @@
         <v>100</v>
       </c>
       <c r="S11" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" s="7">
         <v>17</v>
       </c>
       <c r="U11" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V11" s="7">
         <v>33</v>
       </c>
       <c r="W11" s="7">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="X11" s="7">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
@@ -3382,10 +3382,10 @@
       <c r="T12" s="7"/>
       <c r="U12" s="7"/>
       <c r="V12" s="7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W12" s="7">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="X12" s="7">
         <v>50</v>
@@ -3515,19 +3515,19 @@
         <v>100</v>
       </c>
       <c r="S14" s="7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T14" s="7">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U14" s="7">
         <v>25</v>
       </c>
       <c r="V14" s="7">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="W14" s="7">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X14" s="7">
         <v>50</v>
@@ -3604,16 +3604,16 @@
         <v>17</v>
       </c>
       <c r="U15" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V15" s="7">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="W15" s="7">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="X15" s="7">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="Y15" s="7"/>
       <c r="Z15" s="7"/>
@@ -3681,19 +3681,19 @@
         <v>100</v>
       </c>
       <c r="S16" s="7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T16" s="7">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="U16" s="7">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="V16" s="7">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="W16" s="7">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="X16" s="7">
         <v>100</v>
@@ -4100,7 +4100,7 @@
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
       <c r="W23" s="7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="X23" s="7">
         <v>40</v>
@@ -4327,7 +4327,7 @@
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
@@ -4617,16 +4617,16 @@
         <v>100</v>
       </c>
       <c r="S32" s="7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T32" s="7">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="U32" s="7">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="V32" s="7">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="W32" s="7">
         <v>83</v>
@@ -4702,10 +4702,10 @@
         <v>100</v>
       </c>
       <c r="S33" s="7">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="T33" s="7">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="U33" s="7">
         <v>100</v>
@@ -4860,16 +4860,16 @@
         <v>100</v>
       </c>
       <c r="S35" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T35" s="7">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="U35" s="7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="V35" s="7">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="W35" s="7">
         <v>42</v>
@@ -5054,10 +5054,10 @@
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
       <c r="V38" s="7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W38" s="7">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="X38" s="7">
         <v>43</v>
@@ -5238,16 +5238,16 @@
         <v>33</v>
       </c>
       <c r="U41" s="7">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="V41" s="7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="W41" s="7">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="X41" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Y41" s="7"/>
       <c r="Z41" s="7"/>
@@ -5317,7 +5317,7 @@
         <v>100</v>
       </c>
       <c r="S42" s="7">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="T42" s="7">
         <v>100</v>
@@ -5402,7 +5402,7 @@
         <v>100</v>
       </c>
       <c r="S43" s="7">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T43" s="7">
         <v>100</v>
@@ -5486,19 +5486,19 @@
       </c>
       <c r="S44" s="7"/>
       <c r="T44" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U44" s="7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V44" s="7">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="W44" s="7">
         <v>36</v>
       </c>
       <c r="X44" s="7">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Y44" s="7"/>
       <c r="Z44" s="7"/>
@@ -5798,13 +5798,13 @@
         <v>100</v>
       </c>
       <c r="S49" s="7">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T49" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="U49" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="V49" s="7">
         <v>100</v>
@@ -5882,16 +5882,16 @@
       </c>
       <c r="S50" s="7"/>
       <c r="T50" s="7">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="U50" s="7">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V50" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="W50" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="X50" s="7">
         <v>100</v>
@@ -6033,10 +6033,10 @@
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
       <c r="W52" s="7">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="X52" s="7">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="Y52" s="7"/>
       <c r="Z52" s="7"/>
@@ -6109,7 +6109,7 @@
         <v>33</v>
       </c>
       <c r="T53" s="7">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="U53" s="7">
         <v>100</v>
@@ -6189,10 +6189,10 @@
       <c r="S54" s="7"/>
       <c r="T54" s="7"/>
       <c r="U54" s="7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="V54" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="W54" s="7">
         <v>100</v>
@@ -6265,13 +6265,13 @@
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
       <c r="V55" s="7">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="W55" s="7">
         <v>29</v>
       </c>
       <c r="X55" s="7">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Y55" s="7"/>
       <c r="Z55" s="7"/>
@@ -6498,16 +6498,16 @@
       <c r="S59" s="7"/>
       <c r="T59" s="7"/>
       <c r="U59" s="7">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="V59" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="W59" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="X59" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Y59" s="7"/>
       <c r="Z59" s="7"/>
@@ -6577,10 +6577,10 @@
         <v>33</v>
       </c>
       <c r="W60" s="7">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="X60" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Y60" s="7"/>
       <c r="Z60" s="7"/>
@@ -6649,7 +6649,7 @@
         <v>50</v>
       </c>
       <c r="X61" s="7">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="Y61" s="7"/>
       <c r="Z61" s="7"/>
@@ -6722,19 +6722,19 @@
         <v>14</v>
       </c>
       <c r="T62" s="7">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="U62" s="7">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="V62" s="7">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="W62" s="7">
         <v>71</v>
       </c>
       <c r="X62" s="7">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Y62" s="7"/>
       <c r="Z62" s="7"/>
@@ -6955,13 +6955,13 @@
         <v>18</v>
       </c>
       <c r="V65" s="7">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="W65" s="7">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X65" s="7">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Y65" s="7"/>
       <c r="Z65" s="7"/>
@@ -7029,7 +7029,7 @@
       <c r="S66" s="7"/>
       <c r="T66" s="7"/>
       <c r="U66" s="7">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="V66" s="7">
         <v>100</v>
@@ -7176,7 +7176,7 @@
       <c r="V68" s="7"/>
       <c r="W68" s="7"/>
       <c r="X68" s="7">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="Y68" s="7"/>
       <c r="Z68" s="7"/>
@@ -7245,13 +7245,13 @@
       <c r="T69" s="7"/>
       <c r="U69" s="7"/>
       <c r="V69" s="7">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="W69" s="7">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="X69" s="7">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="Y69" s="7"/>
       <c r="Z69" s="7"/>
@@ -7383,7 +7383,7 @@
         <v>33</v>
       </c>
       <c r="X71" s="7">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="Y71" s="7"/>
       <c r="Z71" s="7"/>
@@ -7513,7 +7513,7 @@
       <c r="V73" s="7"/>
       <c r="W73" s="7"/>
       <c r="X73" s="7">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="Y73" s="7"/>
       <c r="Z73" s="7"/>
@@ -7639,7 +7639,7 @@
       <c r="V75" s="7"/>
       <c r="W75" s="7"/>
       <c r="X75" s="7">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="Y75" s="7"/>
       <c r="Z75" s="7"/>
@@ -7706,7 +7706,7 @@
       <c r="V76" s="7"/>
       <c r="W76" s="7"/>
       <c r="X76" s="7">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="Y76" s="7"/>
       <c r="Z76" s="7"/>
@@ -7835,19 +7835,19 @@
         <v>100</v>
       </c>
       <c r="S78" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T78" s="7">
         <v>17</v>
       </c>
       <c r="U78" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V78" s="7">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="W78" s="7">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="X78" s="7">
         <v>50</v>
@@ -7915,7 +7915,7 @@
       <c r="V79" s="7"/>
       <c r="W79" s="7"/>
       <c r="X79" s="7">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="Y79" s="7"/>
       <c r="Z79" s="7"/>
@@ -7986,7 +7986,7 @@
         <v>33</v>
       </c>
       <c r="X80" s="7">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="Y80" s="7"/>
       <c r="Z80" s="7"/>
@@ -8053,7 +8053,7 @@
       <c r="V81" s="7"/>
       <c r="W81" s="7"/>
       <c r="X81" s="7">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="Y81" s="7"/>
       <c r="Z81" s="7"/>
@@ -8118,7 +8118,7 @@
       <c r="V82" s="7"/>
       <c r="W82" s="7"/>
       <c r="X82" s="7">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="Y82" s="7"/>
       <c r="Z82" s="7"/>
@@ -8481,22 +8481,22 @@
         <v>100</v>
       </c>
       <c r="S88" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T88" s="7">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="U88" s="7">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="V88" s="7">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="W88" s="7">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="X88" s="7">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Y88" s="7"/>
       <c r="Z88" s="7"/>
@@ -8566,19 +8566,19 @@
         <v>100</v>
       </c>
       <c r="S89" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T89" s="7">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="U89" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V89" s="7">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="W89" s="7">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X89" s="7">
         <v>50</v>
@@ -8724,22 +8724,22 @@
         <v>100</v>
       </c>
       <c r="S91" s="7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T91" s="7">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="U91" s="7">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="V91" s="7">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="W91" s="7">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X91" s="7">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="Y91" s="7"/>
       <c r="Z91" s="7"/>
@@ -9028,7 +9028,7 @@
         <v>33</v>
       </c>
       <c r="T96" s="7">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="U96" s="7">
         <v>100</v>
@@ -9108,13 +9108,13 @@
       <c r="S97" s="7"/>
       <c r="T97" s="7"/>
       <c r="U97" s="7">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="V97" s="7">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="W97" s="7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="X97" s="7">
         <v>100</v>
@@ -9183,10 +9183,10 @@
       <c r="U98" s="7"/>
       <c r="V98" s="7"/>
       <c r="W98" s="7">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="X98" s="7">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="Y98" s="7"/>
       <c r="Z98" s="7"/>
@@ -9446,7 +9446,7 @@
       <c r="T102" s="7"/>
       <c r="U102" s="7"/>
       <c r="V102" s="7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="W102" s="7">
         <v>100</v>
@@ -9519,13 +9519,13 @@
       <c r="T103" s="7"/>
       <c r="U103" s="7"/>
       <c r="V103" s="7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W103" s="7">
         <v>22</v>
       </c>
       <c r="X103" s="7">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Y103" s="7"/>
       <c r="Z103" s="7"/>
@@ -9592,10 +9592,10 @@
       <c r="T104" s="7"/>
       <c r="U104" s="7"/>
       <c r="V104" s="7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W104" s="7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X104" s="7">
         <v>33</v>
@@ -9743,10 +9743,10 @@
       <c r="S106" s="7"/>
       <c r="T106" s="7"/>
       <c r="U106" s="7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="V106" s="7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="W106" s="7">
         <v>100</v>
@@ -9819,13 +9819,13 @@
       <c r="T107" s="7"/>
       <c r="U107" s="7"/>
       <c r="V107" s="7">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="W107" s="7">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="X107" s="7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y107" s="7"/>
       <c r="Z107" s="7"/>
@@ -10012,13 +10012,13 @@
         <v>30</v>
       </c>
       <c r="V110" s="7">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="W110" s="7">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="X110" s="7">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="Y110" s="7"/>
       <c r="Z110" s="7"/>
@@ -10087,19 +10087,19 @@
       </c>
       <c r="S111" s="7"/>
       <c r="T111" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U111" s="7">
         <v>20</v>
       </c>
       <c r="V111" s="7">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="W111" s="7">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="X111" s="7">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="Y111" s="7"/>
       <c r="Z111" s="7"/>
@@ -10170,19 +10170,19 @@
       </c>
       <c r="S112" s="7"/>
       <c r="T112" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U112" s="7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V112" s="7">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="W112" s="7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="X112" s="7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y112" s="7"/>
       <c r="Z112" s="7"/>
@@ -10786,22 +10786,22 @@
         <v>100</v>
       </c>
       <c r="S123" s="7">
-        <v>8</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="T123" s="7">
-        <v>21</v>
+        <v>16.7</v>
       </c>
       <c r="U123" s="7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="V123" s="7">
-        <v>30</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="W123" s="7">
-        <v>47</v>
+        <v>41.7</v>
       </c>
       <c r="X123" s="7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y123" s="7"/>
       <c r="Z123" s="7"/>
@@ -10869,22 +10869,22 @@
         <v>100</v>
       </c>
       <c r="S124" s="7">
-        <v>8</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="T124" s="7">
-        <v>8</v>
+        <v>16.7</v>
       </c>
       <c r="U124" s="7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="V124" s="7">
-        <v>33</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="W124" s="7">
-        <v>47</v>
+        <v>41.7</v>
       </c>
       <c r="X124" s="7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y124" s="7"/>
       <c r="Z124" s="7"/>
@@ -10952,22 +10952,22 @@
         <v>100</v>
       </c>
       <c r="S125" s="7">
-        <v>13</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="T125" s="7">
-        <v>13</v>
+        <v>16.7</v>
       </c>
       <c r="U125" s="7">
         <v>25</v>
       </c>
       <c r="V125" s="7">
-        <v>33</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="W125" s="7">
-        <v>46</v>
+        <v>41.7</v>
       </c>
       <c r="X125" s="7">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Y125" s="7"/>
       <c r="Z125" s="7"/>
@@ -11035,19 +11035,19 @@
         <v>100</v>
       </c>
       <c r="S126" s="7">
-        <v>8</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="T126" s="7">
-        <v>17</v>
+        <v>16.7</v>
       </c>
       <c r="U126" s="7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V126" s="7">
-        <v>27</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="W126" s="7">
-        <v>27</v>
+        <v>41.7</v>
       </c>
       <c r="X126" s="7">
         <v>50</v>
@@ -11118,22 +11118,22 @@
         <v>100</v>
       </c>
       <c r="S127" s="7">
-        <v>8</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="T127" s="7">
-        <v>8</v>
+        <v>16.7</v>
       </c>
       <c r="U127" s="7">
         <v>25</v>
       </c>
       <c r="V127" s="7">
-        <v>33</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="W127" s="7">
-        <v>33</v>
+        <v>41.7</v>
       </c>
       <c r="X127" s="7">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="Y127" s="7"/>
       <c r="Z127" s="7"/>

--- a/บันทึกผลการดำเนินงาน_RM_2569.xlsx
+++ b/บันทึกผลการดำเนินงาน_RM_2569.xlsx
@@ -797,37 +797,37 @@
       </c>
       <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>25</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O2" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R2" s="6" t="n">
         <v>100</v>
@@ -899,37 +899,37 @@
       </c>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>25</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O3" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R3" s="6" t="n">
         <v>100</v>
@@ -1001,37 +1001,37 @@
       </c>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>25</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O4" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R4" s="6" t="n">
         <v>100</v>
@@ -1106,10 +1106,10 @@
       <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
       <c r="J5" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>100</v>
@@ -1276,10 +1276,10 @@
       <c r="N7" s="6" t="inlineStr"/>
       <c r="O7" s="6" t="inlineStr"/>
       <c r="P7" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="R7" s="6" t="n">
         <v>100</v>
@@ -1344,10 +1344,10 @@
       <c r="N8" s="6" t="inlineStr"/>
       <c r="O8" s="6" t="inlineStr"/>
       <c r="P8" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="R8" s="6" t="n">
         <v>100</v>
@@ -1412,10 +1412,10 @@
       <c r="N9" s="6" t="inlineStr"/>
       <c r="O9" s="6" t="inlineStr"/>
       <c r="P9" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="R9" s="6" t="n">
         <v>100</v>
@@ -1471,37 +1471,37 @@
       </c>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>25</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O10" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R10" s="6" t="n">
         <v>100</v>
@@ -1576,19 +1576,19 @@
       <c r="H11" s="6" t="inlineStr"/>
       <c r="I11" s="6" t="inlineStr"/>
       <c r="J11" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="O11" s="6" t="n">
         <v>100</v>
@@ -1669,10 +1669,10 @@
       <c r="K12" s="6" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr"/>
       <c r="M12" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O12" s="6" t="n">
         <v>100</v>
@@ -1737,37 +1737,37 @@
       </c>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>25</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O13" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R13" s="6" t="n">
         <v>100</v>
@@ -1839,37 +1839,37 @@
       </c>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>25</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O14" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R14" s="6" t="n">
         <v>100</v>
@@ -1941,37 +1941,37 @@
       </c>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>25</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O15" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R15" s="6" t="n">
         <v>100</v>
@@ -2301,19 +2301,19 @@
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>50</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>100</v>
@@ -2407,37 +2407,37 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>7.7</v>
+        <v>7.69</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>11.5</v>
+        <v>11.54</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>19.2</v>
+        <v>19.23</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>26.9</v>
+        <v>26.92</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>34.6</v>
+        <v>34.62</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>42.3</v>
+        <v>42.31</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>50</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>61.5</v>
+        <v>61.54</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>76.90000000000001</v>
+        <v>76.92</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>88.5</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="R20" s="6" t="n">
         <v>100</v>
@@ -2513,37 +2513,37 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>11.1</v>
+        <v>11.11</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>44.4</v>
+        <v>44.44</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>55.6</v>
+        <v>55.56</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>61.1</v>
+        <v>61.11</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>72.2</v>
+        <v>72.22</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>77.8</v>
+        <v>77.78</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>88.90000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>94.40000000000001</v>
+        <v>94.44</v>
       </c>
       <c r="R21" s="6" t="n">
         <v>100</v>
@@ -2625,19 +2625,19 @@
       <c r="K22" s="6" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr"/>
       <c r="M22" s="6" t="n">
-        <v>14.3</v>
+        <v>14.29</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>28.6</v>
+        <v>28.57</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>71.40000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>85.7</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="R22" s="6" t="n">
         <v>100</v>
@@ -2803,37 +2803,37 @@
         </is>
       </c>
       <c r="G24" s="6" t="n">
-        <v>5.9</v>
+        <v>5.88</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>11.8</v>
+        <v>11.76</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>23.5</v>
+        <v>23.53</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>35.3</v>
+        <v>35.29</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>41.2</v>
+        <v>41.18</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>47.1</v>
+        <v>47.06</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>52.9</v>
+        <v>52.94</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>58.8</v>
+        <v>58.82</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>64.7</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>76.5</v>
+        <v>76.47</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>88.2</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="R24" s="6" t="n">
         <v>100</v>
@@ -2909,22 +2909,22 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>6.7</v>
+        <v>6.67</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>13.3</v>
+        <v>13.33</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>26.7</v>
+        <v>26.67</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>46.7</v>
+        <v>46.67</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>86.7</v>
+        <v>86.67</v>
       </c>
       <c r="M25" s="6" t="n">
         <v>100</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>6.7</v>
+        <v>6.67</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>20</v>
@@ -3028,28 +3028,28 @@
         <v>40</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>46.7</v>
+        <v>46.67</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>53.3</v>
+        <v>53.33</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>60</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>73.3</v>
+        <v>73.33</v>
       </c>
       <c r="O26" s="6" t="n">
         <v>80</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>86.7</v>
+        <v>86.67</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>93.3</v>
+        <v>93.33</v>
       </c>
       <c r="R26" s="6" t="n">
         <v>100</v>
@@ -3317,10 +3317,10 @@
       <c r="I29" s="6" t="inlineStr"/>
       <c r="J29" s="6" t="inlineStr"/>
       <c r="K29" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="M29" s="6" t="n">
         <v>100</v>
@@ -3579,37 +3579,37 @@
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>5.3</v>
+        <v>5.26</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>10.5</v>
+        <v>10.53</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>15.8</v>
+        <v>15.79</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>21.1</v>
+        <v>21.05</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>31.6</v>
+        <v>31.58</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>47.4</v>
+        <v>47.37</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>63.2</v>
+        <v>63.16</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>68.40000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>73.7</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>78.90000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>89.5</v>
+        <v>89.47</v>
       </c>
       <c r="R32" s="6" t="n">
         <v>100</v>
@@ -3618,10 +3618,10 @@
         <v>2</v>
       </c>
       <c r="T32" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U32" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V32" s="7" t="n">
         <v>15</v>
@@ -3690,10 +3690,10 @@
       <c r="J33" s="6" t="inlineStr"/>
       <c r="K33" s="6" t="inlineStr"/>
       <c r="L33" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>100</v>
@@ -3856,13 +3856,13 @@
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
       <c r="N35" s="6" t="n">
-        <v>14.3</v>
+        <v>14.29</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>42.9</v>
+        <v>42.86</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>71.40000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>100</v>
@@ -4001,37 +4001,37 @@
         </is>
       </c>
       <c r="G37" s="6" t="n">
-        <v>7.1</v>
+        <v>7.14</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>14.3</v>
+        <v>14.29</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>21.4</v>
+        <v>21.43</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>32.1</v>
+        <v>32.14</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>39.3</v>
+        <v>39.29</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>46.4</v>
+        <v>46.43</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>57.1</v>
+        <v>57.14</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>64.3</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>71.40000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>82.09999999999999</v>
+        <v>82.14</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>89.3</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="R37" s="6" t="n">
         <v>100</v>
@@ -4107,37 +4107,37 @@
         </is>
       </c>
       <c r="G38" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>25</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O38" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R38" s="6" t="n">
         <v>100</v>
@@ -4222,13 +4222,13 @@
       <c r="N39" s="6" t="inlineStr"/>
       <c r="O39" s="6" t="inlineStr"/>
       <c r="P39" s="6" t="n">
-        <v>42.9</v>
+        <v>42.86</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>85.7</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>142.9</v>
+        <v>100</v>
       </c>
       <c r="S39" s="7" t="inlineStr"/>
       <c r="T39" s="7" t="inlineStr"/>
@@ -4285,37 +4285,37 @@
         </is>
       </c>
       <c r="G40" s="6" t="n">
-        <v>6.7</v>
+        <v>6.67</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>13.3</v>
+        <v>13.33</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>26.7</v>
+        <v>26.67</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>46.7</v>
+        <v>46.67</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>53.3</v>
+        <v>53.33</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>73.3</v>
+        <v>73.33</v>
       </c>
       <c r="O40" s="6" t="n">
         <v>80</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>86.7</v>
+        <v>86.67</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>93.3</v>
+        <v>93.33</v>
       </c>
       <c r="R40" s="6" t="n">
         <v>100</v>
@@ -4491,31 +4491,31 @@
       <c r="G42" s="6" t="inlineStr"/>
       <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L42" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O42" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R42" s="6" t="n">
         <v>100</v>
@@ -4587,34 +4587,34 @@
         </is>
       </c>
       <c r="G43" s="6" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>12.9</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>22.6</v>
+        <v>22.58</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>32.3</v>
+        <v>32.26</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>41.9</v>
+        <v>41.94</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>51.6</v>
+        <v>51.61</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>61.3</v>
+        <v>61.29</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>71</v>
+        <v>70.97</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>80.59999999999999</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>90.3</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>100</v>
@@ -4761,37 +4761,37 @@
       </c>
       <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>25</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L45" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O45" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q45" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R45" s="6" t="n">
         <v>100</v>
@@ -4863,37 +4863,37 @@
       </c>
       <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>25</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O46" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q46" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R46" s="6" t="n">
         <v>100</v>
@@ -4965,37 +4965,37 @@
       </c>
       <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>25</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L47" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O47" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q47" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R47" s="6" t="n">
         <v>100</v>
@@ -5071,37 +5071,37 @@
       </c>
       <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>25</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O48" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q48" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R48" s="6" t="n">
         <v>100</v>
@@ -5173,37 +5173,37 @@
       </c>
       <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>25</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>33.3</v>
+        <v>33.33</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>41.7</v>
+        <v>41.67</v>
       </c>
       <c r="L49" s="6" t="n">
         <v>50</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>58.3</v>
+        <v>58.33</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>66.7</v>
+        <v>66.67</v>
       </c>
       <c r="O49" s="6" t="n">
         <v>75</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>83.3</v>
+        <v>83.33</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>91.7</v>
+        <v>91.67</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>100</v>

--- a/บันทึกผลการดำเนินงาน_RM_2569.xlsx
+++ b/บันทึกผลการดำเนินงาน_RM_2569.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devill/1_กฟน./2569/Dashborad_RM/rm-dashboard-2569/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBEA026-BEFB-BE4E-B15E-EB470C384679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA1F7A3-1FE1-2445-9800-87AB5E9E54CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="บันทึกผล" sheetId="1" r:id="rId1"/>
-    <sheet name="วิธีใช้" sheetId="2" r:id="rId2"/>
-    <sheet name="สรุปรายเดือน_กิจกรรม" sheetId="3" r:id="rId3"/>
-    <sheet name="รายงานประจำเดือน" sheetId="4" r:id="rId4"/>
-    <sheet name="สรุปเป้าหมายตามแผน" sheetId="5" r:id="rId5"/>
+    <sheet name="วิธีใช้" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="สรุปรายเดือน_กิจกรรม" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="รายงานประจำเดือน" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="สรุปเป้าหมายตามแผน" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1435,7 +1435,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1455,6 +1455,12 @@
       <sz val="13"/>
       <color rgb="FF16275C"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="TH SarabunPSK"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1523,7 +1529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1540,20 +1546,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1567,11 +1561,523 @@
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="35">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="TH SarabunPSK"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1585,43 +2091,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="RMEntry" displayName="RMEntry" ref="A1:AH49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="RMEntry" displayName="RMEntry" ref="A1:AH49" dataDxfId="0">
   <autoFilter ref="A1:AH49" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="34">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="รหัสกิจกรรม"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="แผนหลัก"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="แผนงานย่อย"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="รหัส"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="ชื่อกิจกรรม"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ผู้รับผิดชอบ"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="เป้า ม.ค."/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="เป้า ก.พ."/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="เป้า มี.ค."/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="เป้า เม.ย."/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="เป้า พ.ค."/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="เป้า มิ.ย."/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="เป้า ก.ค."/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="เป้า ส.ค."/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="เป้า ก.ย."/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="เป้า ต.ค."/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="เป้า พ.ย."/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="เป้า ธ.ค."/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="ผล ม.ค."/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="ผล ก.พ."/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="ผล มี.ค."/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="ผล เม.ย."/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="ผล พ.ค."/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="ผล มิ.ย."/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="ผล ก.ค."/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="ผล ส.ค."/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="ผล ก.ย."/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="ผล ต.ค."/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="ผล พ.ย."/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="ผล ธ.ค."/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="รายละเอียดการดำเนินการ (ล่าสุด)"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="ปัญหาอุปสรรค"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="ผู้รายงาน"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="ถ่วงน้ำหนัก(%)"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="รหัสกิจกรรม" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="แผนหลัก" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="แผนงานย่อย" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="รหัส" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="ชื่อกิจกรรม" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ผู้รับผิดชอบ" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="เป้า ม.ค." dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="เป้า ก.พ." dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="เป้า มี.ค." dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="เป้า เม.ย." dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="เป้า พ.ค." dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="เป้า มิ.ย." dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="เป้า ก.ค." dataDxfId="22"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="เป้า ส.ค." dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="เป้า ก.ย." dataDxfId="20"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="เป้า ต.ค." dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="เป้า พ.ย." dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="เป้า ธ.ค." dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="ผล ม.ค." dataDxfId="16"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="ผล ก.พ." dataDxfId="15"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="ผล มี.ค." dataDxfId="14"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="ผล เม.ย." dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="ผล พ.ค." dataDxfId="12"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="ผล มิ.ย." dataDxfId="11"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="ผล ก.ค." dataDxfId="10"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="ผล ส.ค." dataDxfId="9"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="ผล ก.ย." dataDxfId="8"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="ผล ต.ค." dataDxfId="7"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="ผล พ.ย." dataDxfId="6"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="ผล ธ.ค." dataDxfId="5"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="รายละเอียดการดำเนินการ (ล่าสุด)" dataDxfId="4"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="ปัญหาอุปสรรค" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="ผู้รายงาน" dataDxfId="2"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="ถ่วงน้ำหนัก(%)" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1918,14 +2424,14 @@
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" hidden="1" customWidth="1"/>
     <col min="7" max="30" width="7" customWidth="1"/>
-    <col min="31" max="31" width="32" customWidth="1"/>
-    <col min="32" max="32" width="24" customWidth="1"/>
-    <col min="33" max="33" width="13" customWidth="1"/>
-    <col min="34" max="34" width="14" customWidth="1"/>
+    <col min="31" max="31" width="32" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="24" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="13" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="14" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -2032,3425 +2538,3425 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6">
+      <c r="F2" s="11"/>
+      <c r="G2" s="13">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="13">
         <v>16.7</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="13">
         <v>25</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="13">
         <v>41.7</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="13">
         <v>50</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="13">
         <v>58.3</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="13">
         <v>66.7</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="13">
         <v>75</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="13">
         <v>91.7</v>
       </c>
-      <c r="R2" s="6">
-        <v>100</v>
-      </c>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="7"/>
-      <c r="AC2" s="7"/>
-      <c r="AD2" s="7"/>
-      <c r="AE2" s="8" t="s">
+      <c r="R2" s="13">
+        <v>100</v>
+      </c>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="AF2" s="8"/>
-      <c r="AG2" s="9" t="s">
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH2" s="10">
+      <c r="AH2" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="64" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="6">
+      <c r="F3" s="11"/>
+      <c r="G3" s="13">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="13">
         <v>16.7</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="13">
         <v>25</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="13">
         <v>41.7</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="13">
         <v>50</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="13">
         <v>58.3</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="13">
         <v>66.7</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="13">
         <v>75</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q3" s="6">
+      <c r="Q3" s="13">
         <v>91.7</v>
       </c>
-      <c r="R3" s="6">
-        <v>100</v>
-      </c>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
-      <c r="AD3" s="7"/>
-      <c r="AE3" s="8" t="s">
+      <c r="R3" s="13">
+        <v>100</v>
+      </c>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="AF3" s="8"/>
-      <c r="AG3" s="9" t="s">
+      <c r="AF3" s="15"/>
+      <c r="AG3" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH3" s="10">
+      <c r="AH3" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="4" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="6">
+      <c r="F4" s="11"/>
+      <c r="G4" s="13">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="13">
         <v>16.7</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="13">
         <v>25</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="13">
         <v>41.7</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="13">
         <v>50</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="13">
         <v>58.3</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="13">
         <v>66.7</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="13">
         <v>75</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="13">
         <v>91.7</v>
       </c>
-      <c r="R4" s="6">
-        <v>100</v>
-      </c>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7"/>
-      <c r="AB4" s="7"/>
-      <c r="AC4" s="7"/>
-      <c r="AD4" s="7"/>
-      <c r="AE4" s="8" t="s">
+      <c r="R4" s="13">
+        <v>100</v>
+      </c>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="14"/>
+      <c r="Y4" s="14"/>
+      <c r="Z4" s="14"/>
+      <c r="AA4" s="14"/>
+      <c r="AB4" s="14"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="AF4" s="8"/>
-      <c r="AG4" s="9" t="s">
+      <c r="AF4" s="15"/>
+      <c r="AG4" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH4" s="10">
+      <c r="AH4" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6">
+      <c r="F5" s="11"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="13">
         <v>66.7</v>
       </c>
-      <c r="L5" s="6">
-        <v>100</v>
-      </c>
-      <c r="M5" s="6">
-        <v>100</v>
-      </c>
-      <c r="N5" s="6">
-        <v>100</v>
-      </c>
-      <c r="O5" s="6">
-        <v>100</v>
-      </c>
-      <c r="P5" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>100</v>
-      </c>
-      <c r="R5" s="6">
-        <v>100</v>
-      </c>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
-      <c r="AC5" s="7"/>
-      <c r="AD5" s="7"/>
-      <c r="AE5" s="8" t="s">
+      <c r="L5" s="13">
+        <v>100</v>
+      </c>
+      <c r="M5" s="13">
+        <v>100</v>
+      </c>
+      <c r="N5" s="13">
+        <v>100</v>
+      </c>
+      <c r="O5" s="13">
+        <v>100</v>
+      </c>
+      <c r="P5" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>100</v>
+      </c>
+      <c r="R5" s="13">
+        <v>100</v>
+      </c>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="AF5" s="8"/>
-      <c r="AG5" s="9" t="s">
+      <c r="AF5" s="15"/>
+      <c r="AG5" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH5" s="10">
+      <c r="AH5" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6">
+      <c r="F6" s="11"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13">
         <v>20</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="13">
         <v>40</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="13">
         <v>60</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="13">
         <v>80</v>
       </c>
-      <c r="Q6" s="6">
-        <v>100</v>
-      </c>
-      <c r="R6" s="6">
-        <v>100</v>
-      </c>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
-      <c r="AA6" s="7"/>
-      <c r="AB6" s="7"/>
-      <c r="AC6" s="7"/>
-      <c r="AD6" s="7"/>
-      <c r="AE6" s="8"/>
-      <c r="AF6" s="8"/>
-      <c r="AG6" s="9" t="s">
+      <c r="Q6" s="13">
+        <v>100</v>
+      </c>
+      <c r="R6" s="13">
+        <v>100</v>
+      </c>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="15"/>
+      <c r="AF6" s="15"/>
+      <c r="AG6" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH6" s="10">
+      <c r="AH6" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6">
+      <c r="F7" s="11"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="Q7" s="13">
         <v>66.7</v>
       </c>
-      <c r="R7" s="6">
-        <v>100</v>
-      </c>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
-      <c r="AA7" s="7"/>
-      <c r="AB7" s="7"/>
-      <c r="AC7" s="7"/>
-      <c r="AD7" s="7"/>
-      <c r="AE7" s="8"/>
-      <c r="AF7" s="8"/>
-      <c r="AG7" s="9" t="s">
+      <c r="R7" s="13">
+        <v>100</v>
+      </c>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="15"/>
+      <c r="AF7" s="15"/>
+      <c r="AG7" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH7" s="10">
+      <c r="AH7" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6">
+      <c r="F8" s="11"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="Q8" s="6">
+      <c r="Q8" s="13">
         <v>66.7</v>
       </c>
-      <c r="R8" s="6">
-        <v>100</v>
-      </c>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="7"/>
-      <c r="AC8" s="7"/>
-      <c r="AD8" s="7"/>
-      <c r="AE8" s="8"/>
-      <c r="AF8" s="8"/>
-      <c r="AG8" s="9" t="s">
+      <c r="R8" s="13">
+        <v>100</v>
+      </c>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="14"/>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="14"/>
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="15"/>
+      <c r="AF8" s="15"/>
+      <c r="AG8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH8" s="10">
+      <c r="AH8" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6">
+      <c r="F9" s="11"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="Q9" s="13">
         <v>66.7</v>
       </c>
-      <c r="R9" s="6">
-        <v>100</v>
-      </c>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
-      <c r="AC9" s="7"/>
-      <c r="AD9" s="7"/>
-      <c r="AE9" s="8"/>
-      <c r="AF9" s="8"/>
-      <c r="AG9" s="9" t="s">
+      <c r="R9" s="13">
+        <v>100</v>
+      </c>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="15"/>
+      <c r="AF9" s="15"/>
+      <c r="AG9" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH9" s="10">
+      <c r="AH9" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:34" ht="22" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="6">
+      <c r="F10" s="11"/>
+      <c r="G10" s="13">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="13">
         <v>16.7</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="13">
         <v>25</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="13">
         <v>41.7</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="13">
         <v>50</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="13">
         <v>58.3</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="13">
         <v>66.7</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="13">
         <v>75</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="13">
         <v>91.7</v>
       </c>
-      <c r="R10" s="6">
-        <v>100</v>
-      </c>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7"/>
-      <c r="AB10" s="7"/>
-      <c r="AC10" s="7"/>
-      <c r="AD10" s="7"/>
-      <c r="AE10" s="8" t="s">
+      <c r="R10" s="13">
+        <v>100</v>
+      </c>
+      <c r="S10" s="14"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="14"/>
+      <c r="V10" s="14"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="14"/>
+      <c r="Y10" s="14"/>
+      <c r="Z10" s="14"/>
+      <c r="AA10" s="14"/>
+      <c r="AB10" s="14"/>
+      <c r="AC10" s="14"/>
+      <c r="AD10" s="14"/>
+      <c r="AE10" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="AF10" s="8"/>
-      <c r="AG10" s="9" t="s">
+      <c r="AF10" s="15"/>
+      <c r="AG10" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH10" s="10">
+      <c r="AH10" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:34" ht="22" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6">
+      <c r="F11" s="11"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13">
         <v>16.7</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="13">
         <v>50</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="13">
         <v>66.7</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="13">
         <v>83.3</v>
       </c>
-      <c r="O11" s="6">
-        <v>100</v>
-      </c>
-      <c r="P11" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>100</v>
-      </c>
-      <c r="R11" s="6">
-        <v>100</v>
-      </c>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
-      <c r="AB11" s="7"/>
-      <c r="AC11" s="7"/>
-      <c r="AD11" s="7"/>
-      <c r="AE11" s="8" t="s">
+      <c r="O11" s="13">
+        <v>100</v>
+      </c>
+      <c r="P11" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>100</v>
+      </c>
+      <c r="R11" s="13">
+        <v>100</v>
+      </c>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="14"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="14"/>
+      <c r="X11" s="14"/>
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="14"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14"/>
+      <c r="AD11" s="14"/>
+      <c r="AE11" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="AF11" s="8"/>
-      <c r="AG11" s="9" t="s">
+      <c r="AF11" s="15"/>
+      <c r="AG11" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH11" s="10">
+      <c r="AH11" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:34" ht="22" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6">
+      <c r="F12" s="11"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="13">
         <v>66.7</v>
       </c>
-      <c r="O12" s="6">
-        <v>100</v>
-      </c>
-      <c r="P12" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>100</v>
-      </c>
-      <c r="R12" s="6">
-        <v>100</v>
-      </c>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
-      <c r="AB12" s="7"/>
-      <c r="AC12" s="7"/>
-      <c r="AD12" s="7"/>
-      <c r="AE12" s="8"/>
-      <c r="AF12" s="8"/>
-      <c r="AG12" s="9" t="s">
+      <c r="O12" s="13">
+        <v>100</v>
+      </c>
+      <c r="P12" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>100</v>
+      </c>
+      <c r="R12" s="13">
+        <v>100</v>
+      </c>
+      <c r="S12" s="14"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="14"/>
+      <c r="W12" s="14"/>
+      <c r="X12" s="14"/>
+      <c r="Y12" s="14"/>
+      <c r="Z12" s="14"/>
+      <c r="AA12" s="14"/>
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="14"/>
+      <c r="AD12" s="14"/>
+      <c r="AE12" s="15"/>
+      <c r="AF12" s="15"/>
+      <c r="AG12" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH12" s="10">
+      <c r="AH12" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="6">
+      <c r="F13" s="11"/>
+      <c r="G13" s="13">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="13">
         <v>16.7</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="13">
         <v>25</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="13">
         <v>41.7</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="13">
         <v>50</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="13">
         <v>58.3</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="13">
         <v>66.7</v>
       </c>
-      <c r="O13" s="6">
+      <c r="O13" s="13">
         <v>75</v>
       </c>
-      <c r="P13" s="6">
+      <c r="P13" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q13" s="6">
+      <c r="Q13" s="13">
         <v>91.7</v>
       </c>
-      <c r="R13" s="6">
-        <v>100</v>
-      </c>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="7"/>
-      <c r="AB13" s="7"/>
-      <c r="AC13" s="7"/>
-      <c r="AD13" s="7"/>
-      <c r="AE13" s="8" t="s">
+      <c r="R13" s="13">
+        <v>100</v>
+      </c>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="AF13" s="8"/>
-      <c r="AG13" s="9" t="s">
+      <c r="AF13" s="15"/>
+      <c r="AG13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH13" s="10">
+      <c r="AH13" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="6">
+      <c r="F14" s="11"/>
+      <c r="G14" s="13">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="13">
         <v>16.7</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="13">
         <v>25</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="13">
         <v>41.7</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="13">
         <v>50</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="13">
         <v>58.3</v>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="13">
         <v>66.7</v>
       </c>
-      <c r="O14" s="6">
+      <c r="O14" s="13">
         <v>75</v>
       </c>
-      <c r="P14" s="6">
+      <c r="P14" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q14" s="6">
+      <c r="Q14" s="13">
         <v>91.7</v>
       </c>
-      <c r="R14" s="6">
-        <v>100</v>
-      </c>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
-      <c r="AA14" s="7"/>
-      <c r="AB14" s="7"/>
-      <c r="AC14" s="7"/>
-      <c r="AD14" s="7"/>
-      <c r="AE14" s="8" t="s">
+      <c r="R14" s="13">
+        <v>100</v>
+      </c>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
+      <c r="X14" s="14"/>
+      <c r="Y14" s="14"/>
+      <c r="Z14" s="14"/>
+      <c r="AA14" s="14"/>
+      <c r="AB14" s="14"/>
+      <c r="AC14" s="14"/>
+      <c r="AD14" s="14"/>
+      <c r="AE14" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="AF14" s="8"/>
-      <c r="AG14" s="9" t="s">
+      <c r="AF14" s="15"/>
+      <c r="AG14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH14" s="10">
+      <c r="AH14" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="6">
+      <c r="F15" s="11"/>
+      <c r="G15" s="13">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="13">
         <v>16.7</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="13">
         <v>25</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="13">
         <v>41.7</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="13">
         <v>50</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="13">
         <v>58.3</v>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="13">
         <v>66.7</v>
       </c>
-      <c r="O15" s="6">
+      <c r="O15" s="13">
         <v>75</v>
       </c>
-      <c r="P15" s="6">
+      <c r="P15" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q15" s="6">
+      <c r="Q15" s="13">
         <v>91.7</v>
       </c>
-      <c r="R15" s="6">
-        <v>100</v>
-      </c>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="7"/>
-      <c r="AC15" s="7"/>
-      <c r="AD15" s="7"/>
-      <c r="AE15" s="8" t="s">
+      <c r="R15" s="13">
+        <v>100</v>
+      </c>
+      <c r="S15" s="14"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="14"/>
+      <c r="V15" s="14"/>
+      <c r="W15" s="14"/>
+      <c r="X15" s="14"/>
+      <c r="Y15" s="14"/>
+      <c r="Z15" s="14"/>
+      <c r="AA15" s="14"/>
+      <c r="AB15" s="14"/>
+      <c r="AC15" s="14"/>
+      <c r="AD15" s="14"/>
+      <c r="AE15" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="AF15" s="8"/>
-      <c r="AG15" s="9" t="s">
+      <c r="AF15" s="15"/>
+      <c r="AG15" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH15" s="10">
+      <c r="AH15" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6">
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13">
         <v>10</v>
       </c>
-      <c r="N16" s="6">
+      <c r="N16" s="13">
         <v>30</v>
       </c>
-      <c r="O16" s="6">
+      <c r="O16" s="13">
         <v>40</v>
       </c>
-      <c r="P16" s="6">
+      <c r="P16" s="13">
         <v>50</v>
       </c>
-      <c r="Q16" s="6">
+      <c r="Q16" s="13">
         <v>70</v>
       </c>
-      <c r="R16" s="6">
-        <v>100</v>
-      </c>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
-      <c r="AA16" s="7"/>
-      <c r="AB16" s="7"/>
-      <c r="AC16" s="7"/>
-      <c r="AD16" s="7"/>
-      <c r="AE16" s="8"/>
-      <c r="AF16" s="8"/>
-      <c r="AG16" s="9" t="s">
+      <c r="R16" s="13">
+        <v>100</v>
+      </c>
+      <c r="S16" s="14"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="14"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="14"/>
+      <c r="Y16" s="14"/>
+      <c r="Z16" s="14"/>
+      <c r="AA16" s="14"/>
+      <c r="AB16" s="14"/>
+      <c r="AC16" s="14"/>
+      <c r="AD16" s="14"/>
+      <c r="AE16" s="15"/>
+      <c r="AF16" s="15"/>
+      <c r="AG16" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="AH16" s="10">
+      <c r="AH16" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="17" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A17" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6">
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13">
         <v>12.5</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="13">
         <v>25</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="13">
         <v>37.5</v>
       </c>
-      <c r="N17" s="6">
+      <c r="N17" s="13">
         <v>50</v>
       </c>
-      <c r="O17" s="6">
+      <c r="O17" s="13">
         <v>62.5</v>
       </c>
-      <c r="P17" s="6">
+      <c r="P17" s="13">
         <v>75</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="Q17" s="13">
         <v>87.5</v>
       </c>
-      <c r="R17" s="6">
-        <v>100</v>
-      </c>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="7"/>
-      <c r="AA17" s="7"/>
-      <c r="AB17" s="7"/>
-      <c r="AC17" s="7"/>
-      <c r="AD17" s="7"/>
-      <c r="AE17" s="8" t="s">
+      <c r="R17" s="13">
+        <v>100</v>
+      </c>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="14"/>
+      <c r="X17" s="14"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14"/>
+      <c r="AA17" s="14"/>
+      <c r="AB17" s="14"/>
+      <c r="AC17" s="14"/>
+      <c r="AD17" s="14"/>
+      <c r="AE17" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="AF17" s="8"/>
-      <c r="AG17" s="9" t="s">
+      <c r="AF17" s="15"/>
+      <c r="AG17" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="AH17" s="10">
+      <c r="AH17" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="18" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" s="4" t="s">
+      <c r="E18" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6">
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13">
         <v>12.5</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="13">
         <v>25</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N18" s="13">
         <v>50</v>
       </c>
-      <c r="O18" s="6">
+      <c r="O18" s="13">
         <v>62.5</v>
       </c>
-      <c r="P18" s="6">
+      <c r="P18" s="13">
         <v>75</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="Q18" s="13">
         <v>87.5</v>
       </c>
-      <c r="R18" s="6">
-        <v>100</v>
-      </c>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="7"/>
-      <c r="AD18" s="7"/>
-      <c r="AE18" s="8" t="s">
+      <c r="R18" s="13">
+        <v>100</v>
+      </c>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14"/>
+      <c r="AA18" s="14"/>
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="14"/>
+      <c r="AD18" s="14"/>
+      <c r="AE18" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="AF18" s="8"/>
-      <c r="AG18" s="9" t="s">
+      <c r="AF18" s="15"/>
+      <c r="AG18" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="AH18" s="10">
+      <c r="AH18" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="19" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="13">
         <v>16.7</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="13">
         <v>50</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="13">
         <v>66.7</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="13">
         <v>83.3</v>
       </c>
-      <c r="L19" s="6">
-        <v>100</v>
-      </c>
-      <c r="M19" s="6">
-        <v>100</v>
-      </c>
-      <c r="N19" s="6">
-        <v>100</v>
-      </c>
-      <c r="O19" s="6">
-        <v>100</v>
-      </c>
-      <c r="P19" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>100</v>
-      </c>
-      <c r="R19" s="6">
-        <v>100</v>
-      </c>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="7"/>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="7"/>
-      <c r="AC19" s="7"/>
-      <c r="AD19" s="7"/>
-      <c r="AE19" s="8" t="s">
+      <c r="L19" s="13">
+        <v>100</v>
+      </c>
+      <c r="M19" s="13">
+        <v>100</v>
+      </c>
+      <c r="N19" s="13">
+        <v>100</v>
+      </c>
+      <c r="O19" s="13">
+        <v>100</v>
+      </c>
+      <c r="P19" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="13">
+        <v>100</v>
+      </c>
+      <c r="R19" s="13">
+        <v>100</v>
+      </c>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="14"/>
+      <c r="Y19" s="14"/>
+      <c r="Z19" s="14"/>
+      <c r="AA19" s="14"/>
+      <c r="AB19" s="14"/>
+      <c r="AC19" s="14"/>
+      <c r="AD19" s="14"/>
+      <c r="AE19" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="AF19" s="8"/>
-      <c r="AG19" s="9" t="s">
+      <c r="AF19" s="15"/>
+      <c r="AG19" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="AH19" s="10">
+      <c r="AH19" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="20" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="13">
         <v>3.8</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="13">
         <v>7.7</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="13">
         <v>11.5</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="13">
         <v>19.2</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="13">
         <v>26.9</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="13">
         <v>34.6</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="13">
         <v>42.3</v>
       </c>
-      <c r="N20" s="6">
+      <c r="N20" s="13">
         <v>50</v>
       </c>
-      <c r="O20" s="6">
+      <c r="O20" s="13">
         <v>61.5</v>
       </c>
-      <c r="P20" s="6">
+      <c r="P20" s="13">
         <v>76.900000000000006</v>
       </c>
-      <c r="Q20" s="6">
+      <c r="Q20" s="13">
         <v>88.5</v>
       </c>
-      <c r="R20" s="6">
-        <v>100</v>
-      </c>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
-      <c r="Z20" s="7"/>
-      <c r="AA20" s="7"/>
-      <c r="AB20" s="7"/>
-      <c r="AC20" s="7"/>
-      <c r="AD20" s="7"/>
-      <c r="AE20" s="8" t="s">
+      <c r="R20" s="13">
+        <v>100</v>
+      </c>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="14"/>
+      <c r="W20" s="14"/>
+      <c r="X20" s="14"/>
+      <c r="Y20" s="14"/>
+      <c r="Z20" s="14"/>
+      <c r="AA20" s="14"/>
+      <c r="AB20" s="14"/>
+      <c r="AC20" s="14"/>
+      <c r="AD20" s="14"/>
+      <c r="AE20" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="AF20" s="8"/>
-      <c r="AG20" s="9" t="s">
+      <c r="AF20" s="15"/>
+      <c r="AG20" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="AH20" s="10">
+      <c r="AH20" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="21" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="13">
         <v>11.1</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="13">
         <v>44.4</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="13">
         <v>55.6</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="13">
         <v>61.1</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="13">
         <v>66.7</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="13">
         <v>72.2</v>
       </c>
-      <c r="N21" s="6">
+      <c r="N21" s="13">
         <v>77.8</v>
       </c>
-      <c r="O21" s="6">
+      <c r="O21" s="13">
         <v>83.3</v>
       </c>
-      <c r="P21" s="6">
+      <c r="P21" s="13">
         <v>88.9</v>
       </c>
-      <c r="Q21" s="6">
+      <c r="Q21" s="13">
         <v>94.4</v>
       </c>
-      <c r="R21" s="6">
-        <v>100</v>
-      </c>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
-      <c r="Z21" s="7"/>
-      <c r="AA21" s="7"/>
-      <c r="AB21" s="7"/>
-      <c r="AC21" s="7"/>
-      <c r="AD21" s="7"/>
-      <c r="AE21" s="8" t="s">
+      <c r="R21" s="13">
+        <v>100</v>
+      </c>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="14"/>
+      <c r="AA21" s="14"/>
+      <c r="AB21" s="14"/>
+      <c r="AC21" s="14"/>
+      <c r="AD21" s="14"/>
+      <c r="AE21" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="AF21" s="8"/>
-      <c r="AG21" s="9" t="s">
+      <c r="AF21" s="15"/>
+      <c r="AG21" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="AH21" s="10">
+      <c r="AH21" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="22" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6">
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13">
         <v>14.3</v>
       </c>
-      <c r="N22" s="6">
+      <c r="N22" s="13">
         <v>28.6</v>
       </c>
-      <c r="O22" s="6">
+      <c r="O22" s="13">
         <v>57.1</v>
       </c>
-      <c r="P22" s="6">
+      <c r="P22" s="13">
         <v>71.400000000000006</v>
       </c>
-      <c r="Q22" s="6">
+      <c r="Q22" s="13">
         <v>85.7</v>
       </c>
-      <c r="R22" s="6">
-        <v>100</v>
-      </c>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="7"/>
-      <c r="Z22" s="7"/>
-      <c r="AA22" s="7"/>
-      <c r="AB22" s="7"/>
-      <c r="AC22" s="7"/>
-      <c r="AD22" s="7"/>
-      <c r="AE22" s="8"/>
-      <c r="AF22" s="8"/>
-      <c r="AG22" s="9" t="s">
+      <c r="R22" s="13">
+        <v>100</v>
+      </c>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="14"/>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
+      <c r="AA22" s="14"/>
+      <c r="AB22" s="14"/>
+      <c r="AC22" s="14"/>
+      <c r="AD22" s="14"/>
+      <c r="AE22" s="15"/>
+      <c r="AF22" s="15"/>
+      <c r="AG22" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="AH22" s="10">
+      <c r="AH22" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="23" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A23" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="13">
         <v>12.5</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="13">
         <v>37.5</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="13">
         <v>50</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="13">
         <v>75</v>
       </c>
-      <c r="K23" s="6">
-        <v>100</v>
-      </c>
-      <c r="L23" s="6">
-        <v>100</v>
-      </c>
-      <c r="M23" s="6">
-        <v>100</v>
-      </c>
-      <c r="N23" s="6">
-        <v>100</v>
-      </c>
-      <c r="O23" s="6">
-        <v>100</v>
-      </c>
-      <c r="P23" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q23" s="6">
-        <v>100</v>
-      </c>
-      <c r="R23" s="6">
-        <v>100</v>
-      </c>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="7"/>
-      <c r="X23" s="7"/>
-      <c r="Y23" s="7"/>
-      <c r="Z23" s="7"/>
-      <c r="AA23" s="7"/>
-      <c r="AB23" s="7"/>
-      <c r="AC23" s="7"/>
-      <c r="AD23" s="7"/>
-      <c r="AE23" s="8" t="s">
+      <c r="K23" s="13">
+        <v>100</v>
+      </c>
+      <c r="L23" s="13">
+        <v>100</v>
+      </c>
+      <c r="M23" s="13">
+        <v>100</v>
+      </c>
+      <c r="N23" s="13">
+        <v>100</v>
+      </c>
+      <c r="O23" s="13">
+        <v>100</v>
+      </c>
+      <c r="P23" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="13">
+        <v>100</v>
+      </c>
+      <c r="R23" s="13">
+        <v>100</v>
+      </c>
+      <c r="S23" s="14"/>
+      <c r="T23" s="14"/>
+      <c r="U23" s="14"/>
+      <c r="V23" s="14"/>
+      <c r="W23" s="14"/>
+      <c r="X23" s="14"/>
+      <c r="Y23" s="14"/>
+      <c r="Z23" s="14"/>
+      <c r="AA23" s="14"/>
+      <c r="AB23" s="14"/>
+      <c r="AC23" s="14"/>
+      <c r="AD23" s="14"/>
+      <c r="AE23" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="AF23" s="8"/>
-      <c r="AG23" s="9" t="s">
+      <c r="AF23" s="15"/>
+      <c r="AG23" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="AH23" s="10">
+      <c r="AH23" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="24" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="13">
         <v>5.9</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="13">
         <v>11.8</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="13">
         <v>23.5</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J24" s="13">
         <v>35.299999999999997</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="13">
         <v>41.2</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="13">
         <v>47.1</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24" s="13">
         <v>52.9</v>
       </c>
-      <c r="N24" s="6">
+      <c r="N24" s="13">
         <v>58.8</v>
       </c>
-      <c r="O24" s="6">
+      <c r="O24" s="13">
         <v>64.7</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P24" s="13">
         <v>76.5</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="Q24" s="13">
         <v>88.2</v>
       </c>
-      <c r="R24" s="6">
-        <v>100</v>
-      </c>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
-      <c r="U24" s="7"/>
-      <c r="V24" s="7"/>
-      <c r="W24" s="7"/>
-      <c r="X24" s="7"/>
-      <c r="Y24" s="7"/>
-      <c r="Z24" s="7"/>
-      <c r="AA24" s="7"/>
-      <c r="AB24" s="7"/>
-      <c r="AC24" s="7"/>
-      <c r="AD24" s="7"/>
-      <c r="AE24" s="8" t="s">
+      <c r="R24" s="13">
+        <v>100</v>
+      </c>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="14"/>
+      <c r="Z24" s="14"/>
+      <c r="AA24" s="14"/>
+      <c r="AB24" s="14"/>
+      <c r="AC24" s="14"/>
+      <c r="AD24" s="14"/>
+      <c r="AE24" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="AF24" s="8"/>
-      <c r="AG24" s="9" t="s">
+      <c r="AF24" s="15"/>
+      <c r="AG24" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="AH24" s="10">
+      <c r="AH24" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="25" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A25" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="13">
         <v>6.7</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="13">
         <v>13.3</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="13">
         <v>26.7</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="13">
         <v>46.7</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="13">
         <v>66.7</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="13">
         <v>86.7</v>
       </c>
-      <c r="M25" s="6">
-        <v>100</v>
-      </c>
-      <c r="N25" s="6">
-        <v>100</v>
-      </c>
-      <c r="O25" s="6">
-        <v>100</v>
-      </c>
-      <c r="P25" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>100</v>
-      </c>
-      <c r="R25" s="6">
-        <v>100</v>
-      </c>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="7"/>
-      <c r="V25" s="7"/>
-      <c r="W25" s="7"/>
-      <c r="X25" s="7"/>
-      <c r="Y25" s="7"/>
-      <c r="Z25" s="7"/>
-      <c r="AA25" s="7"/>
-      <c r="AB25" s="7"/>
-      <c r="AC25" s="7"/>
-      <c r="AD25" s="7"/>
-      <c r="AE25" s="8" t="s">
+      <c r="M25" s="13">
+        <v>100</v>
+      </c>
+      <c r="N25" s="13">
+        <v>100</v>
+      </c>
+      <c r="O25" s="13">
+        <v>100</v>
+      </c>
+      <c r="P25" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q25" s="13">
+        <v>100</v>
+      </c>
+      <c r="R25" s="13">
+        <v>100</v>
+      </c>
+      <c r="S25" s="14"/>
+      <c r="T25" s="14"/>
+      <c r="U25" s="14"/>
+      <c r="V25" s="14"/>
+      <c r="W25" s="14"/>
+      <c r="X25" s="14"/>
+      <c r="Y25" s="14"/>
+      <c r="Z25" s="14"/>
+      <c r="AA25" s="14"/>
+      <c r="AB25" s="14"/>
+      <c r="AC25" s="14"/>
+      <c r="AD25" s="14"/>
+      <c r="AE25" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="AF25" s="8" t="s">
+      <c r="AF25" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="AG25" s="9" t="s">
+      <c r="AG25" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="AH25" s="10">
+      <c r="AH25" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="26" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A26" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="13">
         <v>6.7</v>
       </c>
-      <c r="H26" s="6">
+      <c r="H26" s="13">
         <v>20</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="13">
         <v>40</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="13">
         <v>46.7</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="13">
         <v>53.3</v>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="13">
         <v>60</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M26" s="13">
         <v>66.7</v>
       </c>
-      <c r="N26" s="6">
+      <c r="N26" s="13">
         <v>73.3</v>
       </c>
-      <c r="O26" s="6">
+      <c r="O26" s="13">
         <v>80</v>
       </c>
-      <c r="P26" s="6">
+      <c r="P26" s="13">
         <v>86.7</v>
       </c>
-      <c r="Q26" s="6">
+      <c r="Q26" s="13">
         <v>93.3</v>
       </c>
-      <c r="R26" s="6">
-        <v>100</v>
-      </c>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="7"/>
-      <c r="X26" s="7"/>
-      <c r="Y26" s="7"/>
-      <c r="Z26" s="7"/>
-      <c r="AA26" s="7"/>
-      <c r="AB26" s="7"/>
-      <c r="AC26" s="7"/>
-      <c r="AD26" s="7"/>
-      <c r="AE26" s="8" t="s">
+      <c r="R26" s="13">
+        <v>100</v>
+      </c>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="X26" s="14"/>
+      <c r="Y26" s="14"/>
+      <c r="Z26" s="14"/>
+      <c r="AA26" s="14"/>
+      <c r="AB26" s="14"/>
+      <c r="AC26" s="14"/>
+      <c r="AD26" s="14"/>
+      <c r="AE26" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="AF26" s="8"/>
-      <c r="AG26" s="9" t="s">
+      <c r="AF26" s="15"/>
+      <c r="AG26" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="AH26" s="10">
+      <c r="AH26" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="27" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A27" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6">
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13">
         <v>25</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="13">
         <v>50</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="13">
         <v>75</v>
       </c>
-      <c r="M27" s="6">
-        <v>100</v>
-      </c>
-      <c r="N27" s="6">
-        <v>100</v>
-      </c>
-      <c r="O27" s="6">
-        <v>100</v>
-      </c>
-      <c r="P27" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q27" s="6">
-        <v>100</v>
-      </c>
-      <c r="R27" s="6">
-        <v>100</v>
-      </c>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="7"/>
-      <c r="V27" s="7"/>
-      <c r="W27" s="7"/>
-      <c r="X27" s="7"/>
-      <c r="Y27" s="7"/>
-      <c r="Z27" s="7"/>
-      <c r="AA27" s="7"/>
-      <c r="AB27" s="7"/>
-      <c r="AC27" s="7"/>
-      <c r="AD27" s="7"/>
-      <c r="AE27" s="8" t="s">
+      <c r="M27" s="13">
+        <v>100</v>
+      </c>
+      <c r="N27" s="13">
+        <v>100</v>
+      </c>
+      <c r="O27" s="13">
+        <v>100</v>
+      </c>
+      <c r="P27" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q27" s="13">
+        <v>100</v>
+      </c>
+      <c r="R27" s="13">
+        <v>100</v>
+      </c>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="X27" s="14"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
+      <c r="AA27" s="14"/>
+      <c r="AB27" s="14"/>
+      <c r="AC27" s="14"/>
+      <c r="AD27" s="14"/>
+      <c r="AE27" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="AF27" s="8"/>
-      <c r="AG27" s="9" t="s">
+      <c r="AF27" s="15"/>
+      <c r="AG27" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="AH27" s="10">
+      <c r="AH27" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="28" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A28" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6">
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13">
         <v>25</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="13">
         <v>50</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="13">
         <v>75</v>
       </c>
-      <c r="M28" s="6">
-        <v>100</v>
-      </c>
-      <c r="N28" s="6">
-        <v>100</v>
-      </c>
-      <c r="O28" s="6">
-        <v>100</v>
-      </c>
-      <c r="P28" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q28" s="6">
-        <v>100</v>
-      </c>
-      <c r="R28" s="6">
-        <v>100</v>
-      </c>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="7"/>
-      <c r="V28" s="7"/>
-      <c r="W28" s="7"/>
-      <c r="X28" s="7"/>
-      <c r="Y28" s="7"/>
-      <c r="Z28" s="7"/>
-      <c r="AA28" s="7"/>
-      <c r="AB28" s="7"/>
-      <c r="AC28" s="7"/>
-      <c r="AD28" s="7"/>
-      <c r="AE28" s="8" t="s">
+      <c r="M28" s="13">
+        <v>100</v>
+      </c>
+      <c r="N28" s="13">
+        <v>100</v>
+      </c>
+      <c r="O28" s="13">
+        <v>100</v>
+      </c>
+      <c r="P28" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q28" s="13">
+        <v>100</v>
+      </c>
+      <c r="R28" s="13">
+        <v>100</v>
+      </c>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="14"/>
+      <c r="AB28" s="14"/>
+      <c r="AC28" s="14"/>
+      <c r="AD28" s="14"/>
+      <c r="AE28" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="AF28" s="8"/>
-      <c r="AG28" s="9" t="s">
+      <c r="AF28" s="15"/>
+      <c r="AG28" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="AH28" s="10">
+      <c r="AH28" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="29" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
+    <row r="29" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+      <c r="A29" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6">
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="13">
         <v>66.7</v>
       </c>
-      <c r="M29" s="6">
-        <v>100</v>
-      </c>
-      <c r="N29" s="6">
-        <v>100</v>
-      </c>
-      <c r="O29" s="6">
-        <v>100</v>
-      </c>
-      <c r="P29" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q29" s="6">
-        <v>100</v>
-      </c>
-      <c r="R29" s="6">
-        <v>100</v>
-      </c>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="7"/>
-      <c r="V29" s="7"/>
-      <c r="W29" s="7"/>
-      <c r="X29" s="7"/>
-      <c r="Y29" s="7"/>
-      <c r="Z29" s="7"/>
-      <c r="AA29" s="7"/>
-      <c r="AB29" s="7"/>
-      <c r="AC29" s="7"/>
-      <c r="AD29" s="7"/>
-      <c r="AE29" s="8" t="s">
+      <c r="M29" s="13">
+        <v>100</v>
+      </c>
+      <c r="N29" s="13">
+        <v>100</v>
+      </c>
+      <c r="O29" s="13">
+        <v>100</v>
+      </c>
+      <c r="P29" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q29" s="13">
+        <v>100</v>
+      </c>
+      <c r="R29" s="13">
+        <v>100</v>
+      </c>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="14"/>
+      <c r="AA29" s="14"/>
+      <c r="AB29" s="14"/>
+      <c r="AC29" s="14"/>
+      <c r="AD29" s="14"/>
+      <c r="AE29" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="AF29" s="8"/>
-      <c r="AG29" s="9" t="s">
+      <c r="AF29" s="15"/>
+      <c r="AG29" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="AH29" s="10">
+      <c r="AH29" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="30" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+      <c r="A30" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6">
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13">
         <v>50</v>
       </c>
-      <c r="M30" s="6">
-        <v>100</v>
-      </c>
-      <c r="N30" s="6">
-        <v>100</v>
-      </c>
-      <c r="O30" s="6">
-        <v>100</v>
-      </c>
-      <c r="P30" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q30" s="6">
-        <v>100</v>
-      </c>
-      <c r="R30" s="6">
-        <v>100</v>
-      </c>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
-      <c r="U30" s="7"/>
-      <c r="V30" s="7"/>
-      <c r="W30" s="7"/>
-      <c r="X30" s="7"/>
-      <c r="Y30" s="7"/>
-      <c r="Z30" s="7"/>
-      <c r="AA30" s="7"/>
-      <c r="AB30" s="7"/>
-      <c r="AC30" s="7"/>
-      <c r="AD30" s="7"/>
-      <c r="AE30" s="8" t="s">
+      <c r="M30" s="13">
+        <v>100</v>
+      </c>
+      <c r="N30" s="13">
+        <v>100</v>
+      </c>
+      <c r="O30" s="13">
+        <v>100</v>
+      </c>
+      <c r="P30" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q30" s="13">
+        <v>100</v>
+      </c>
+      <c r="R30" s="13">
+        <v>100</v>
+      </c>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="14"/>
+      <c r="Z30" s="14"/>
+      <c r="AA30" s="14"/>
+      <c r="AB30" s="14"/>
+      <c r="AC30" s="14"/>
+      <c r="AD30" s="14"/>
+      <c r="AE30" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="AF30" s="8"/>
-      <c r="AG30" s="9" t="s">
+      <c r="AF30" s="15"/>
+      <c r="AG30" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="AH30" s="10">
+      <c r="AH30" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="31" spans="1:34" ht="64" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+      <c r="A31" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6">
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13">
         <v>40</v>
       </c>
-      <c r="M31" s="6">
+      <c r="M31" s="13">
         <v>60</v>
       </c>
-      <c r="N31" s="6">
+      <c r="N31" s="13">
         <v>80</v>
       </c>
-      <c r="O31" s="6">
-        <v>100</v>
-      </c>
-      <c r="P31" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>100</v>
-      </c>
-      <c r="R31" s="6">
-        <v>100</v>
-      </c>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="7"/>
-      <c r="V31" s="7"/>
-      <c r="W31" s="7"/>
-      <c r="X31" s="7"/>
-      <c r="Y31" s="7"/>
-      <c r="Z31" s="7"/>
-      <c r="AA31" s="7"/>
-      <c r="AB31" s="7"/>
-      <c r="AC31" s="7"/>
-      <c r="AD31" s="7"/>
-      <c r="AE31" s="8" t="s">
+      <c r="O31" s="13">
+        <v>100</v>
+      </c>
+      <c r="P31" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q31" s="13">
+        <v>100</v>
+      </c>
+      <c r="R31" s="13">
+        <v>100</v>
+      </c>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="14"/>
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="14"/>
+      <c r="AD31" s="14"/>
+      <c r="AE31" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="AF31" s="8" t="s">
+      <c r="AF31" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="AG31" s="9" t="s">
+      <c r="AG31" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="AH31" s="10">
+      <c r="AH31" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="32" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="13">
         <v>5.3</v>
       </c>
-      <c r="H32" s="6">
+      <c r="H32" s="13">
         <v>10.5</v>
       </c>
-      <c r="I32" s="6">
+      <c r="I32" s="13">
         <v>15.8</v>
       </c>
-      <c r="J32" s="6">
+      <c r="J32" s="13">
         <v>21.1</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="13">
         <v>31.6</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32" s="13">
         <v>47.4</v>
       </c>
-      <c r="M32" s="6">
+      <c r="M32" s="13">
         <v>63.2</v>
       </c>
-      <c r="N32" s="6">
+      <c r="N32" s="13">
         <v>68.400000000000006</v>
       </c>
-      <c r="O32" s="6">
+      <c r="O32" s="13">
         <v>73.7</v>
       </c>
-      <c r="P32" s="6">
+      <c r="P32" s="13">
         <v>78.900000000000006</v>
       </c>
-      <c r="Q32" s="6">
+      <c r="Q32" s="13">
         <v>89.5</v>
       </c>
-      <c r="R32" s="6">
-        <v>100</v>
-      </c>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
-      <c r="U32" s="7"/>
-      <c r="V32" s="7"/>
-      <c r="W32" s="7"/>
-      <c r="X32" s="7"/>
-      <c r="Y32" s="7"/>
-      <c r="Z32" s="7"/>
-      <c r="AA32" s="7"/>
-      <c r="AB32" s="7"/>
-      <c r="AC32" s="7"/>
-      <c r="AD32" s="7"/>
-      <c r="AE32" s="8" t="s">
+      <c r="R32" s="13">
+        <v>100</v>
+      </c>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="14"/>
+      <c r="X32" s="14"/>
+      <c r="Y32" s="14"/>
+      <c r="Z32" s="14"/>
+      <c r="AA32" s="14"/>
+      <c r="AB32" s="14"/>
+      <c r="AC32" s="14"/>
+      <c r="AD32" s="14"/>
+      <c r="AE32" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="AF32" s="8"/>
-      <c r="AG32" s="9" t="s">
+      <c r="AF32" s="15"/>
+      <c r="AG32" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AH32" s="10">
+      <c r="AH32" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="33" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
+    <row r="33" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A33" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6">
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="M33" s="6">
+      <c r="M33" s="13">
         <v>66.7</v>
       </c>
-      <c r="N33" s="6">
-        <v>100</v>
-      </c>
-      <c r="O33" s="6">
-        <v>100</v>
-      </c>
-      <c r="P33" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q33" s="6">
-        <v>100</v>
-      </c>
-      <c r="R33" s="6">
-        <v>100</v>
-      </c>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="7"/>
-      <c r="V33" s="7"/>
-      <c r="W33" s="7"/>
-      <c r="X33" s="7"/>
-      <c r="Y33" s="7"/>
-      <c r="Z33" s="7"/>
-      <c r="AA33" s="7"/>
-      <c r="AB33" s="7"/>
-      <c r="AC33" s="7"/>
-      <c r="AD33" s="7"/>
-      <c r="AE33" s="8" t="s">
+      <c r="N33" s="13">
+        <v>100</v>
+      </c>
+      <c r="O33" s="13">
+        <v>100</v>
+      </c>
+      <c r="P33" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="13">
+        <v>100</v>
+      </c>
+      <c r="R33" s="13">
+        <v>100</v>
+      </c>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="AF33" s="8"/>
-      <c r="AG33" s="9" t="s">
+      <c r="AF33" s="15"/>
+      <c r="AG33" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AH33" s="10">
+      <c r="AH33" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="34" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
+    <row r="34" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A34" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6">
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13">
         <v>20</v>
       </c>
-      <c r="N34" s="6">
+      <c r="N34" s="13">
         <v>40</v>
       </c>
-      <c r="O34" s="6">
+      <c r="O34" s="13">
         <v>80</v>
       </c>
-      <c r="P34" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q34" s="6">
-        <v>100</v>
-      </c>
-      <c r="R34" s="6">
-        <v>100</v>
-      </c>
-      <c r="S34" s="7"/>
-      <c r="T34" s="7"/>
-      <c r="U34" s="7"/>
-      <c r="V34" s="7"/>
-      <c r="W34" s="7"/>
-      <c r="X34" s="7"/>
-      <c r="Y34" s="7"/>
-      <c r="Z34" s="7"/>
-      <c r="AA34" s="7"/>
-      <c r="AB34" s="7"/>
-      <c r="AC34" s="7"/>
-      <c r="AD34" s="7"/>
-      <c r="AE34" s="8"/>
-      <c r="AF34" s="8"/>
-      <c r="AG34" s="9" t="s">
+      <c r="P34" s="13">
+        <v>100</v>
+      </c>
+      <c r="Q34" s="13">
+        <v>100</v>
+      </c>
+      <c r="R34" s="13">
+        <v>100</v>
+      </c>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="14"/>
+      <c r="V34" s="14"/>
+      <c r="W34" s="14"/>
+      <c r="X34" s="14"/>
+      <c r="Y34" s="14"/>
+      <c r="Z34" s="14"/>
+      <c r="AA34" s="14"/>
+      <c r="AB34" s="14"/>
+      <c r="AC34" s="14"/>
+      <c r="AD34" s="14"/>
+      <c r="AE34" s="15"/>
+      <c r="AF34" s="15"/>
+      <c r="AG34" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AH34" s="10">
+      <c r="AH34" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="35" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+      <c r="A35" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6">
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13">
         <v>14.3</v>
       </c>
-      <c r="O35" s="6">
+      <c r="O35" s="13">
         <v>42.9</v>
       </c>
-      <c r="P35" s="6">
+      <c r="P35" s="13">
         <v>71.400000000000006</v>
       </c>
-      <c r="Q35" s="6">
-        <v>100</v>
-      </c>
-      <c r="R35" s="6">
-        <v>100</v>
-      </c>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-      <c r="U35" s="7"/>
-      <c r="V35" s="7"/>
-      <c r="W35" s="7"/>
-      <c r="X35" s="7"/>
-      <c r="Y35" s="7"/>
-      <c r="Z35" s="7"/>
-      <c r="AA35" s="7"/>
-      <c r="AB35" s="7"/>
-      <c r="AC35" s="7"/>
-      <c r="AD35" s="7"/>
-      <c r="AE35" s="8"/>
-      <c r="AF35" s="8"/>
-      <c r="AG35" s="9" t="s">
+      <c r="Q35" s="13">
+        <v>100</v>
+      </c>
+      <c r="R35" s="13">
+        <v>100</v>
+      </c>
+      <c r="S35" s="14"/>
+      <c r="T35" s="14"/>
+      <c r="U35" s="14"/>
+      <c r="V35" s="14"/>
+      <c r="W35" s="14"/>
+      <c r="X35" s="14"/>
+      <c r="Y35" s="14"/>
+      <c r="Z35" s="14"/>
+      <c r="AA35" s="14"/>
+      <c r="AB35" s="14"/>
+      <c r="AC35" s="14"/>
+      <c r="AD35" s="14"/>
+      <c r="AE35" s="15"/>
+      <c r="AF35" s="15"/>
+      <c r="AG35" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AH35" s="10">
+      <c r="AH35" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="36" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A36" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
-      <c r="N36" s="6">
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13">
         <v>25</v>
       </c>
-      <c r="O36" s="6">
+      <c r="O36" s="13">
         <v>50</v>
       </c>
-      <c r="P36" s="6">
+      <c r="P36" s="13">
         <v>75</v>
       </c>
-      <c r="Q36" s="6">
-        <v>100</v>
-      </c>
-      <c r="R36" s="6">
-        <v>100</v>
-      </c>
-      <c r="S36" s="7"/>
-      <c r="T36" s="7"/>
-      <c r="U36" s="7"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="7"/>
-      <c r="X36" s="7"/>
-      <c r="Y36" s="7"/>
-      <c r="Z36" s="7"/>
-      <c r="AA36" s="7"/>
-      <c r="AB36" s="7"/>
-      <c r="AC36" s="7"/>
-      <c r="AD36" s="7"/>
-      <c r="AE36" s="8"/>
-      <c r="AF36" s="8"/>
-      <c r="AG36" s="9" t="s">
+      <c r="Q36" s="13">
+        <v>100</v>
+      </c>
+      <c r="R36" s="13">
+        <v>100</v>
+      </c>
+      <c r="S36" s="14"/>
+      <c r="T36" s="14"/>
+      <c r="U36" s="14"/>
+      <c r="V36" s="14"/>
+      <c r="W36" s="14"/>
+      <c r="X36" s="14"/>
+      <c r="Y36" s="14"/>
+      <c r="Z36" s="14"/>
+      <c r="AA36" s="14"/>
+      <c r="AB36" s="14"/>
+      <c r="AC36" s="14"/>
+      <c r="AD36" s="14"/>
+      <c r="AE36" s="15"/>
+      <c r="AF36" s="15"/>
+      <c r="AG36" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AH36" s="10">
+      <c r="AH36" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="37" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A37" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37" s="13">
         <v>7.1</v>
       </c>
-      <c r="H37" s="6">
+      <c r="H37" s="13">
         <v>14.3</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I37" s="13">
         <v>21.4</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37" s="13">
         <v>32.1</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="13">
         <v>39.299999999999997</v>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="13">
         <v>46.4</v>
       </c>
-      <c r="M37" s="6">
+      <c r="M37" s="13">
         <v>57.1</v>
       </c>
-      <c r="N37" s="6">
+      <c r="N37" s="13">
         <v>64.3</v>
       </c>
-      <c r="O37" s="6">
+      <c r="O37" s="13">
         <v>71.400000000000006</v>
       </c>
-      <c r="P37" s="6">
+      <c r="P37" s="13">
         <v>82.1</v>
       </c>
-      <c r="Q37" s="6">
+      <c r="Q37" s="13">
         <v>89.3</v>
       </c>
-      <c r="R37" s="6">
-        <v>100</v>
-      </c>
-      <c r="S37" s="7"/>
-      <c r="T37" s="7"/>
-      <c r="U37" s="7"/>
-      <c r="V37" s="7"/>
-      <c r="W37" s="7"/>
-      <c r="X37" s="7"/>
-      <c r="Y37" s="7"/>
-      <c r="Z37" s="7"/>
-      <c r="AA37" s="7"/>
-      <c r="AB37" s="7"/>
-      <c r="AC37" s="7"/>
-      <c r="AD37" s="7"/>
-      <c r="AE37" s="8" t="s">
+      <c r="R37" s="13">
+        <v>100</v>
+      </c>
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="14"/>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="14"/>
+      <c r="Y37" s="14"/>
+      <c r="Z37" s="14"/>
+      <c r="AA37" s="14"/>
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="14"/>
+      <c r="AD37" s="14"/>
+      <c r="AE37" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="AF37" s="8"/>
-      <c r="AG37" s="9" t="s">
+      <c r="AF37" s="15"/>
+      <c r="AG37" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AH37" s="10">
+      <c r="AH37" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="38" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
+    <row r="38" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A38" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G38" s="6">
+      <c r="G38" s="13">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H38" s="6">
+      <c r="H38" s="13">
         <v>16.7</v>
       </c>
-      <c r="I38" s="6">
+      <c r="I38" s="13">
         <v>25</v>
       </c>
-      <c r="J38" s="6">
+      <c r="J38" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="13">
         <v>41.7</v>
       </c>
-      <c r="L38" s="6">
+      <c r="L38" s="13">
         <v>50</v>
       </c>
-      <c r="M38" s="6">
+      <c r="M38" s="13">
         <v>58.3</v>
       </c>
-      <c r="N38" s="6">
+      <c r="N38" s="13">
         <v>66.7</v>
       </c>
-      <c r="O38" s="6">
+      <c r="O38" s="13">
         <v>75</v>
       </c>
-      <c r="P38" s="6">
+      <c r="P38" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q38" s="6">
+      <c r="Q38" s="13">
         <v>91.7</v>
       </c>
-      <c r="R38" s="6">
-        <v>100</v>
-      </c>
-      <c r="S38" s="7"/>
-      <c r="T38" s="7"/>
-      <c r="U38" s="7"/>
-      <c r="V38" s="7"/>
-      <c r="W38" s="7"/>
-      <c r="X38" s="7"/>
-      <c r="Y38" s="7"/>
-      <c r="Z38" s="7"/>
-      <c r="AA38" s="7"/>
-      <c r="AB38" s="7"/>
-      <c r="AC38" s="7"/>
-      <c r="AD38" s="7"/>
-      <c r="AE38" s="8" t="s">
+      <c r="R38" s="13">
+        <v>100</v>
+      </c>
+      <c r="S38" s="14"/>
+      <c r="T38" s="14"/>
+      <c r="U38" s="14"/>
+      <c r="V38" s="14"/>
+      <c r="W38" s="14"/>
+      <c r="X38" s="14"/>
+      <c r="Y38" s="14"/>
+      <c r="Z38" s="14"/>
+      <c r="AA38" s="14"/>
+      <c r="AB38" s="14"/>
+      <c r="AC38" s="14"/>
+      <c r="AD38" s="14"/>
+      <c r="AE38" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="AF38" s="8"/>
-      <c r="AG38" s="9" t="s">
+      <c r="AF38" s="15"/>
+      <c r="AG38" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AH38" s="10">
+      <c r="AH38" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="39" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
+    <row r="39" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A39" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6">
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13">
         <v>42.9</v>
       </c>
-      <c r="Q39" s="6">
+      <c r="Q39" s="13">
         <v>85.7</v>
       </c>
-      <c r="R39" s="6">
+      <c r="R39" s="13">
         <v>142.9</v>
       </c>
-      <c r="S39" s="7"/>
-      <c r="T39" s="7"/>
-      <c r="U39" s="7"/>
-      <c r="V39" s="7"/>
-      <c r="W39" s="7"/>
-      <c r="X39" s="7"/>
-      <c r="Y39" s="7"/>
-      <c r="Z39" s="7"/>
-      <c r="AA39" s="7"/>
-      <c r="AB39" s="7"/>
-      <c r="AC39" s="7"/>
-      <c r="AD39" s="7"/>
-      <c r="AE39" s="8"/>
-      <c r="AF39" s="8"/>
-      <c r="AG39" s="9" t="s">
+      <c r="S39" s="14"/>
+      <c r="T39" s="14"/>
+      <c r="U39" s="14"/>
+      <c r="V39" s="14"/>
+      <c r="W39" s="14"/>
+      <c r="X39" s="14"/>
+      <c r="Y39" s="14"/>
+      <c r="Z39" s="14"/>
+      <c r="AA39" s="14"/>
+      <c r="AB39" s="14"/>
+      <c r="AC39" s="14"/>
+      <c r="AD39" s="14"/>
+      <c r="AE39" s="15"/>
+      <c r="AF39" s="15"/>
+      <c r="AG39" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AH39" s="10">
+      <c r="AH39" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="40" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
+    <row r="40" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A40" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G40" s="6">
+      <c r="G40" s="13">
         <v>6.7</v>
       </c>
-      <c r="H40" s="6">
+      <c r="H40" s="13">
         <v>13.3</v>
       </c>
-      <c r="I40" s="6">
+      <c r="I40" s="13">
         <v>26.7</v>
       </c>
-      <c r="J40" s="6">
+      <c r="J40" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="13">
         <v>46.7</v>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="13">
         <v>53.3</v>
       </c>
-      <c r="M40" s="6">
+      <c r="M40" s="13">
         <v>66.7</v>
       </c>
-      <c r="N40" s="6">
+      <c r="N40" s="13">
         <v>73.3</v>
       </c>
-      <c r="O40" s="6">
+      <c r="O40" s="13">
         <v>80</v>
       </c>
-      <c r="P40" s="6">
+      <c r="P40" s="13">
         <v>86.7</v>
       </c>
-      <c r="Q40" s="6">
+      <c r="Q40" s="13">
         <v>93.3</v>
       </c>
-      <c r="R40" s="6">
-        <v>100</v>
-      </c>
-      <c r="S40" s="7"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="7"/>
-      <c r="V40" s="7"/>
-      <c r="W40" s="7"/>
-      <c r="X40" s="7"/>
-      <c r="Y40" s="7"/>
-      <c r="Z40" s="7"/>
-      <c r="AA40" s="7"/>
-      <c r="AB40" s="7"/>
-      <c r="AC40" s="7"/>
-      <c r="AD40" s="7"/>
-      <c r="AE40" s="8" t="s">
+      <c r="R40" s="13">
+        <v>100</v>
+      </c>
+      <c r="S40" s="14"/>
+      <c r="T40" s="14"/>
+      <c r="U40" s="14"/>
+      <c r="V40" s="14"/>
+      <c r="W40" s="14"/>
+      <c r="X40" s="14"/>
+      <c r="Y40" s="14"/>
+      <c r="Z40" s="14"/>
+      <c r="AA40" s="14"/>
+      <c r="AB40" s="14"/>
+      <c r="AC40" s="14"/>
+      <c r="AD40" s="14"/>
+      <c r="AE40" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="AF40" s="8"/>
-      <c r="AG40" s="9" t="s">
+      <c r="AF40" s="15"/>
+      <c r="AG40" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AH40" s="10">
+      <c r="AH40" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="41" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
+    <row r="41" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A41" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13">
         <v>5</v>
       </c>
-      <c r="J41" s="6">
+      <c r="J41" s="13">
         <v>20</v>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="13">
         <v>30</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="13">
         <v>40</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41" s="13">
         <v>50</v>
       </c>
-      <c r="N41" s="6">
+      <c r="N41" s="13">
         <v>60</v>
       </c>
-      <c r="O41" s="6">
+      <c r="O41" s="13">
         <v>70</v>
       </c>
-      <c r="P41" s="6">
+      <c r="P41" s="13">
         <v>80</v>
       </c>
-      <c r="Q41" s="6">
+      <c r="Q41" s="13">
         <v>90</v>
       </c>
-      <c r="R41" s="6">
-        <v>100</v>
-      </c>
-      <c r="S41" s="7"/>
-      <c r="T41" s="7"/>
-      <c r="U41" s="7"/>
-      <c r="V41" s="7"/>
-      <c r="W41" s="7"/>
-      <c r="X41" s="7"/>
-      <c r="Y41" s="7"/>
-      <c r="Z41" s="7"/>
-      <c r="AA41" s="7"/>
-      <c r="AB41" s="7"/>
-      <c r="AC41" s="7"/>
-      <c r="AD41" s="7"/>
-      <c r="AE41" s="8" t="s">
+      <c r="R41" s="13">
+        <v>100</v>
+      </c>
+      <c r="S41" s="14"/>
+      <c r="T41" s="14"/>
+      <c r="U41" s="14"/>
+      <c r="V41" s="14"/>
+      <c r="W41" s="14"/>
+      <c r="X41" s="14"/>
+      <c r="Y41" s="14"/>
+      <c r="Z41" s="14"/>
+      <c r="AA41" s="14"/>
+      <c r="AB41" s="14"/>
+      <c r="AC41" s="14"/>
+      <c r="AD41" s="14"/>
+      <c r="AE41" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="AF41" s="8"/>
-      <c r="AG41" s="9" t="s">
+      <c r="AF41" s="15"/>
+      <c r="AG41" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AH41" s="10">
+      <c r="AH41" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="42" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
+    <row r="42" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A42" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13">
         <v>16.7</v>
       </c>
-      <c r="J42" s="6">
+      <c r="J42" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K42" s="6">
+      <c r="K42" s="13">
         <v>41.7</v>
       </c>
-      <c r="L42" s="6">
+      <c r="L42" s="13">
         <v>50</v>
       </c>
-      <c r="M42" s="6">
+      <c r="M42" s="13">
         <v>58.3</v>
       </c>
-      <c r="N42" s="6">
+      <c r="N42" s="13">
         <v>66.7</v>
       </c>
-      <c r="O42" s="6">
+      <c r="O42" s="13">
         <v>75</v>
       </c>
-      <c r="P42" s="6">
+      <c r="P42" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q42" s="6">
+      <c r="Q42" s="13">
         <v>91.7</v>
       </c>
-      <c r="R42" s="6">
-        <v>100</v>
-      </c>
-      <c r="S42" s="7"/>
-      <c r="T42" s="7"/>
-      <c r="U42" s="7"/>
-      <c r="V42" s="7"/>
-      <c r="W42" s="7"/>
-      <c r="X42" s="7"/>
-      <c r="Y42" s="7"/>
-      <c r="Z42" s="7"/>
-      <c r="AA42" s="7"/>
-      <c r="AB42" s="7"/>
-      <c r="AC42" s="7"/>
-      <c r="AD42" s="7"/>
-      <c r="AE42" s="8" t="s">
+      <c r="R42" s="13">
+        <v>100</v>
+      </c>
+      <c r="S42" s="14"/>
+      <c r="T42" s="14"/>
+      <c r="U42" s="14"/>
+      <c r="V42" s="14"/>
+      <c r="W42" s="14"/>
+      <c r="X42" s="14"/>
+      <c r="Y42" s="14"/>
+      <c r="Z42" s="14"/>
+      <c r="AA42" s="14"/>
+      <c r="AB42" s="14"/>
+      <c r="AC42" s="14"/>
+      <c r="AD42" s="14"/>
+      <c r="AE42" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="AF42" s="8"/>
-      <c r="AG42" s="9" t="s">
+      <c r="AF42" s="15"/>
+      <c r="AG42" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AH42" s="10">
+      <c r="AH42" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="43" spans="1:34" ht="32" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
+    <row r="43" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A43" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G43" s="13">
         <v>3.2</v>
       </c>
-      <c r="H43" s="6">
+      <c r="H43" s="13">
         <v>12.9</v>
       </c>
-      <c r="I43" s="6">
+      <c r="I43" s="13">
         <v>22.6</v>
       </c>
-      <c r="J43" s="6">
+      <c r="J43" s="13">
         <v>32.299999999999997</v>
       </c>
-      <c r="K43" s="6">
+      <c r="K43" s="13">
         <v>41.9</v>
       </c>
-      <c r="L43" s="6">
+      <c r="L43" s="13">
         <v>51.6</v>
       </c>
-      <c r="M43" s="6">
+      <c r="M43" s="13">
         <v>61.3</v>
       </c>
-      <c r="N43" s="6">
+      <c r="N43" s="13">
         <v>71</v>
       </c>
-      <c r="O43" s="6">
+      <c r="O43" s="13">
         <v>80.599999999999994</v>
       </c>
-      <c r="P43" s="6">
+      <c r="P43" s="13">
         <v>90.3</v>
       </c>
-      <c r="Q43" s="6">
-        <v>100</v>
-      </c>
-      <c r="R43" s="6">
-        <v>100</v>
-      </c>
-      <c r="S43" s="7"/>
-      <c r="T43" s="7"/>
-      <c r="U43" s="7"/>
-      <c r="V43" s="7"/>
-      <c r="W43" s="7"/>
-      <c r="X43" s="7"/>
-      <c r="Y43" s="7"/>
-      <c r="Z43" s="7"/>
-      <c r="AA43" s="7"/>
-      <c r="AB43" s="7"/>
-      <c r="AC43" s="7"/>
-      <c r="AD43" s="7"/>
-      <c r="AE43" s="8" t="s">
+      <c r="Q43" s="13">
+        <v>100</v>
+      </c>
+      <c r="R43" s="13">
+        <v>100</v>
+      </c>
+      <c r="S43" s="14"/>
+      <c r="T43" s="14"/>
+      <c r="U43" s="14"/>
+      <c r="V43" s="14"/>
+      <c r="W43" s="14"/>
+      <c r="X43" s="14"/>
+      <c r="Y43" s="14"/>
+      <c r="Z43" s="14"/>
+      <c r="AA43" s="14"/>
+      <c r="AB43" s="14"/>
+      <c r="AC43" s="14"/>
+      <c r="AD43" s="14"/>
+      <c r="AE43" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="AF43" s="8"/>
-      <c r="AG43" s="9" t="s">
+      <c r="AF43" s="15"/>
+      <c r="AG43" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AH43" s="10">
+      <c r="AH43" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="44" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
+    <row r="44" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+      <c r="A44" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="6"/>
-      <c r="P44" s="6">
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13"/>
+      <c r="P44" s="13">
         <v>50</v>
       </c>
-      <c r="Q44" s="6">
+      <c r="Q44" s="13">
         <v>80</v>
       </c>
-      <c r="R44" s="6">
-        <v>100</v>
-      </c>
-      <c r="S44" s="7"/>
-      <c r="T44" s="7"/>
-      <c r="U44" s="7"/>
-      <c r="V44" s="7"/>
-      <c r="W44" s="7"/>
-      <c r="X44" s="7"/>
-      <c r="Y44" s="7"/>
-      <c r="Z44" s="7"/>
-      <c r="AA44" s="7"/>
-      <c r="AB44" s="7"/>
-      <c r="AC44" s="7"/>
-      <c r="AD44" s="7"/>
-      <c r="AE44" s="8"/>
-      <c r="AF44" s="8"/>
-      <c r="AG44" s="9" t="s">
+      <c r="R44" s="13">
+        <v>100</v>
+      </c>
+      <c r="S44" s="14"/>
+      <c r="T44" s="14"/>
+      <c r="U44" s="14"/>
+      <c r="V44" s="14"/>
+      <c r="W44" s="14"/>
+      <c r="X44" s="14"/>
+      <c r="Y44" s="14"/>
+      <c r="Z44" s="14"/>
+      <c r="AA44" s="14"/>
+      <c r="AB44" s="14"/>
+      <c r="AC44" s="14"/>
+      <c r="AD44" s="14"/>
+      <c r="AE44" s="15"/>
+      <c r="AF44" s="15"/>
+      <c r="AG44" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AH44" s="10">
+      <c r="AH44" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="45" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
+    <row r="45" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A45" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="6">
+      <c r="F45" s="11"/>
+      <c r="G45" s="13">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45" s="13">
         <v>16.7</v>
       </c>
-      <c r="I45" s="6">
+      <c r="I45" s="13">
         <v>25</v>
       </c>
-      <c r="J45" s="6">
+      <c r="J45" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K45" s="6">
+      <c r="K45" s="13">
         <v>41.7</v>
       </c>
-      <c r="L45" s="6">
+      <c r="L45" s="13">
         <v>50</v>
       </c>
-      <c r="M45" s="6">
+      <c r="M45" s="13">
         <v>58.3</v>
       </c>
-      <c r="N45" s="6">
+      <c r="N45" s="13">
         <v>66.7</v>
       </c>
-      <c r="O45" s="6">
+      <c r="O45" s="13">
         <v>75</v>
       </c>
-      <c r="P45" s="6">
+      <c r="P45" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q45" s="6">
+      <c r="Q45" s="13">
         <v>91.7</v>
       </c>
-      <c r="R45" s="6">
-        <v>100</v>
-      </c>
-      <c r="S45" s="7"/>
-      <c r="T45" s="7"/>
-      <c r="U45" s="7"/>
-      <c r="V45" s="7"/>
-      <c r="W45" s="7"/>
-      <c r="X45" s="7"/>
-      <c r="Y45" s="7"/>
-      <c r="Z45" s="7"/>
-      <c r="AA45" s="7"/>
-      <c r="AB45" s="7"/>
-      <c r="AC45" s="7"/>
-      <c r="AD45" s="7"/>
-      <c r="AE45" s="8" t="s">
+      <c r="R45" s="13">
+        <v>100</v>
+      </c>
+      <c r="S45" s="14"/>
+      <c r="T45" s="14"/>
+      <c r="U45" s="14"/>
+      <c r="V45" s="14"/>
+      <c r="W45" s="14"/>
+      <c r="X45" s="14"/>
+      <c r="Y45" s="14"/>
+      <c r="Z45" s="14"/>
+      <c r="AA45" s="14"/>
+      <c r="AB45" s="14"/>
+      <c r="AC45" s="14"/>
+      <c r="AD45" s="14"/>
+      <c r="AE45" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="AF45" s="8"/>
-      <c r="AG45" s="9" t="s">
+      <c r="AF45" s="15"/>
+      <c r="AG45" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH45" s="10">
+      <c r="AH45" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="46" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
+    <row r="46" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A46" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="6">
+      <c r="F46" s="11"/>
+      <c r="G46" s="13">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H46" s="6">
+      <c r="H46" s="13">
         <v>16.7</v>
       </c>
-      <c r="I46" s="6">
+      <c r="I46" s="13">
         <v>25</v>
       </c>
-      <c r="J46" s="6">
+      <c r="J46" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K46" s="6">
+      <c r="K46" s="13">
         <v>41.7</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="13">
         <v>50</v>
       </c>
-      <c r="M46" s="6">
+      <c r="M46" s="13">
         <v>58.3</v>
       </c>
-      <c r="N46" s="6">
+      <c r="N46" s="13">
         <v>66.7</v>
       </c>
-      <c r="O46" s="6">
+      <c r="O46" s="13">
         <v>75</v>
       </c>
-      <c r="P46" s="6">
+      <c r="P46" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q46" s="6">
+      <c r="Q46" s="13">
         <v>91.7</v>
       </c>
-      <c r="R46" s="6">
-        <v>100</v>
-      </c>
-      <c r="S46" s="7"/>
-      <c r="T46" s="7"/>
-      <c r="U46" s="7"/>
-      <c r="V46" s="7"/>
-      <c r="W46" s="7"/>
-      <c r="X46" s="7"/>
-      <c r="Y46" s="7"/>
-      <c r="Z46" s="7"/>
-      <c r="AA46" s="7"/>
-      <c r="AB46" s="7"/>
-      <c r="AC46" s="7"/>
-      <c r="AD46" s="7"/>
-      <c r="AE46" s="8" t="s">
+      <c r="R46" s="13">
+        <v>100</v>
+      </c>
+      <c r="S46" s="14"/>
+      <c r="T46" s="14"/>
+      <c r="U46" s="14"/>
+      <c r="V46" s="14"/>
+      <c r="W46" s="14"/>
+      <c r="X46" s="14"/>
+      <c r="Y46" s="14"/>
+      <c r="Z46" s="14"/>
+      <c r="AA46" s="14"/>
+      <c r="AB46" s="14"/>
+      <c r="AC46" s="14"/>
+      <c r="AD46" s="14"/>
+      <c r="AE46" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="AF46" s="8"/>
-      <c r="AG46" s="9" t="s">
+      <c r="AF46" s="15"/>
+      <c r="AG46" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH46" s="10">
+      <c r="AH46" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="47" spans="1:34" ht="80" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
+    <row r="47" spans="1:34" ht="110" x14ac:dyDescent="0.2">
+      <c r="A47" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="6">
+      <c r="F47" s="11"/>
+      <c r="G47" s="13">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47" s="13">
         <v>16.7</v>
       </c>
-      <c r="I47" s="6">
+      <c r="I47" s="13">
         <v>25</v>
       </c>
-      <c r="J47" s="6">
+      <c r="J47" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47" s="13">
         <v>41.7</v>
       </c>
-      <c r="L47" s="6">
+      <c r="L47" s="13">
         <v>50</v>
       </c>
-      <c r="M47" s="6">
+      <c r="M47" s="13">
         <v>58.3</v>
       </c>
-      <c r="N47" s="6">
+      <c r="N47" s="13">
         <v>66.7</v>
       </c>
-      <c r="O47" s="6">
+      <c r="O47" s="13">
         <v>75</v>
       </c>
-      <c r="P47" s="6">
+      <c r="P47" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q47" s="6">
+      <c r="Q47" s="13">
         <v>91.7</v>
       </c>
-      <c r="R47" s="6">
-        <v>100</v>
-      </c>
-      <c r="S47" s="7"/>
-      <c r="T47" s="7"/>
-      <c r="U47" s="7"/>
-      <c r="V47" s="7"/>
-      <c r="W47" s="7"/>
-      <c r="X47" s="7"/>
-      <c r="Y47" s="7"/>
-      <c r="Z47" s="7"/>
-      <c r="AA47" s="7"/>
-      <c r="AB47" s="7"/>
-      <c r="AC47" s="7"/>
-      <c r="AD47" s="7"/>
-      <c r="AE47" s="8" t="s">
+      <c r="R47" s="13">
+        <v>100</v>
+      </c>
+      <c r="S47" s="14"/>
+      <c r="T47" s="14"/>
+      <c r="U47" s="14"/>
+      <c r="V47" s="14"/>
+      <c r="W47" s="14"/>
+      <c r="X47" s="14"/>
+      <c r="Y47" s="14"/>
+      <c r="Z47" s="14"/>
+      <c r="AA47" s="14"/>
+      <c r="AB47" s="14"/>
+      <c r="AC47" s="14"/>
+      <c r="AD47" s="14"/>
+      <c r="AE47" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="AF47" s="8" t="s">
+      <c r="AF47" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="AG47" s="9" t="s">
+      <c r="AG47" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH47" s="10">
+      <c r="AH47" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="48" spans="1:34" ht="48" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
+    <row r="48" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+      <c r="A48" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="F48" s="4"/>
-      <c r="G48" s="6">
+      <c r="F48" s="11"/>
+      <c r="G48" s="13">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H48" s="6">
+      <c r="H48" s="13">
         <v>16.7</v>
       </c>
-      <c r="I48" s="6">
+      <c r="I48" s="13">
         <v>25</v>
       </c>
-      <c r="J48" s="6">
+      <c r="J48" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="13">
         <v>41.7</v>
       </c>
-      <c r="L48" s="6">
+      <c r="L48" s="13">
         <v>50</v>
       </c>
-      <c r="M48" s="6">
+      <c r="M48" s="13">
         <v>58.3</v>
       </c>
-      <c r="N48" s="6">
+      <c r="N48" s="13">
         <v>66.7</v>
       </c>
-      <c r="O48" s="6">
+      <c r="O48" s="13">
         <v>75</v>
       </c>
-      <c r="P48" s="6">
+      <c r="P48" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q48" s="6">
+      <c r="Q48" s="13">
         <v>91.7</v>
       </c>
-      <c r="R48" s="6">
-        <v>100</v>
-      </c>
-      <c r="S48" s="7"/>
-      <c r="T48" s="7"/>
-      <c r="U48" s="7"/>
-      <c r="V48" s="7"/>
-      <c r="W48" s="7"/>
-      <c r="X48" s="7"/>
-      <c r="Y48" s="7"/>
-      <c r="Z48" s="7"/>
-      <c r="AA48" s="7"/>
-      <c r="AB48" s="7"/>
-      <c r="AC48" s="7"/>
-      <c r="AD48" s="7"/>
-      <c r="AE48" s="8" t="s">
+      <c r="R48" s="13">
+        <v>100</v>
+      </c>
+      <c r="S48" s="14"/>
+      <c r="T48" s="14"/>
+      <c r="U48" s="14"/>
+      <c r="V48" s="14"/>
+      <c r="W48" s="14"/>
+      <c r="X48" s="14"/>
+      <c r="Y48" s="14"/>
+      <c r="Z48" s="14"/>
+      <c r="AA48" s="14"/>
+      <c r="AB48" s="14"/>
+      <c r="AC48" s="14"/>
+      <c r="AD48" s="14"/>
+      <c r="AE48" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="AF48" s="8"/>
-      <c r="AG48" s="9" t="s">
+      <c r="AF48" s="15"/>
+      <c r="AG48" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH48" s="10">
+      <c r="AH48" s="17">
         <v>2.08</v>
       </c>
     </row>
-    <row r="49" spans="1:34" ht="64" x14ac:dyDescent="0.2">
-      <c r="A49" s="4" t="s">
+    <row r="49" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+      <c r="A49" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="6">
+      <c r="F49" s="11"/>
+      <c r="G49" s="13">
         <v>8.3000000000000007</v>
       </c>
-      <c r="H49" s="6">
+      <c r="H49" s="13">
         <v>16.7</v>
       </c>
-      <c r="I49" s="6">
+      <c r="I49" s="13">
         <v>25</v>
       </c>
-      <c r="J49" s="6">
+      <c r="J49" s="13">
         <v>33.299999999999997</v>
       </c>
-      <c r="K49" s="6">
+      <c r="K49" s="13">
         <v>41.7</v>
       </c>
-      <c r="L49" s="6">
+      <c r="L49" s="13">
         <v>50</v>
       </c>
-      <c r="M49" s="6">
+      <c r="M49" s="13">
         <v>58.3</v>
       </c>
-      <c r="N49" s="6">
+      <c r="N49" s="13">
         <v>66.7</v>
       </c>
-      <c r="O49" s="6">
+      <c r="O49" s="13">
         <v>75</v>
       </c>
-      <c r="P49" s="6">
+      <c r="P49" s="13">
         <v>83.3</v>
       </c>
-      <c r="Q49" s="6">
+      <c r="Q49" s="13">
         <v>91.7</v>
       </c>
-      <c r="R49" s="6">
-        <v>100</v>
-      </c>
-      <c r="S49" s="7"/>
-      <c r="T49" s="7"/>
-      <c r="U49" s="7"/>
-      <c r="V49" s="7"/>
-      <c r="W49" s="7"/>
-      <c r="X49" s="7"/>
-      <c r="Y49" s="7"/>
-      <c r="Z49" s="7"/>
-      <c r="AA49" s="7"/>
-      <c r="AB49" s="7"/>
-      <c r="AC49" s="7"/>
-      <c r="AD49" s="7"/>
-      <c r="AE49" s="8" t="s">
+      <c r="R49" s="13">
+        <v>100</v>
+      </c>
+      <c r="S49" s="14"/>
+      <c r="T49" s="14"/>
+      <c r="U49" s="14"/>
+      <c r="V49" s="14"/>
+      <c r="W49" s="14"/>
+      <c r="X49" s="14"/>
+      <c r="Y49" s="14"/>
+      <c r="Z49" s="14"/>
+      <c r="AA49" s="14"/>
+      <c r="AB49" s="14"/>
+      <c r="AC49" s="14"/>
+      <c r="AD49" s="14"/>
+      <c r="AE49" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="AF49" s="8"/>
-      <c r="AG49" s="9" t="s">
+      <c r="AF49" s="15"/>
+      <c r="AG49" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH49" s="10">
+      <c r="AH49" s="17">
         <v>2.08</v>
       </c>
     </row>
@@ -5478,106 +5984,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B1" s="12"/>
+      <c r="B1" s="8"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="13"/>
-      <c r="B2" s="12"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="8"/>
     </row>
     <row r="3" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="8" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="8" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="8" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="8" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="8" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="13"/>
-      <c r="B8" s="12"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="8"/>
     </row>
     <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B9" s="12"/>
+      <c r="B9" s="8"/>
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="8" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="8" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="12"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="8"/>
     </row>
     <row r="13" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="8" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A14" s="13"/>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="9"/>
+      <c r="B14" s="8" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="12" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="8" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="13"/>
-      <c r="B16" s="12" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="8" t="s">
         <v>251</v>
       </c>
     </row>
@@ -5661,30 +6167,30 @@
       <c r="D2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
     </row>
     <row r="3" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
@@ -5699,30 +6205,30 @@
       <c r="D3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
     </row>
     <row r="4" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
@@ -5737,30 +6243,30 @@
       <c r="D4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
     </row>
     <row r="5" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
@@ -5775,24 +6281,24 @@
       <c r="D5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8" t="s">
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
     </row>
     <row r="6" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
@@ -5807,18 +6313,18 @@
       <c r="D6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
     </row>
     <row r="7" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
@@ -5833,18 +6339,18 @@
       <c r="D7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
     </row>
     <row r="8" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
@@ -5859,18 +6365,18 @@
       <c r="D8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
     </row>
     <row r="9" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
@@ -5885,18 +6391,18 @@
       <c r="D9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
     </row>
     <row r="10" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -5911,30 +6417,30 @@
       <c r="D10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
     </row>
     <row r="11" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
@@ -5949,24 +6455,24 @@
       <c r="D11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8" t="s">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
     </row>
     <row r="12" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
@@ -5981,18 +6487,18 @@
       <c r="D12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
     </row>
     <row r="13" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
@@ -6007,30 +6513,30 @@
       <c r="D13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
     </row>
     <row r="14" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
@@ -6045,30 +6551,30 @@
       <c r="D14" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
     </row>
     <row r="15" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
@@ -6083,30 +6589,30 @@
       <c r="D15" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
@@ -6121,18 +6627,18 @@
       <c r="D16" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
     </row>
     <row r="17" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
@@ -6147,22 +6653,22 @@
       <c r="D17" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="s">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
     </row>
     <row r="18" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
@@ -6177,20 +6683,20 @@
       <c r="D18" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8" t="s">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
     </row>
     <row r="19" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
@@ -6205,30 +6711,30 @@
       <c r="D19" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
     </row>
     <row r="20" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
@@ -6243,30 +6749,30 @@
       <c r="D20" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="I20" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
     </row>
     <row r="21" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
@@ -6281,30 +6787,30 @@
       <c r="D21" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
     </row>
     <row r="22" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
@@ -6319,18 +6825,18 @@
       <c r="D22" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
     </row>
     <row r="23" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
@@ -6345,30 +6851,30 @@
       <c r="D23" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="J23" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
     </row>
     <row r="24" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
@@ -6383,30 +6889,30 @@
       <c r="D24" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
     </row>
     <row r="25" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
@@ -6421,30 +6927,30 @@
       <c r="D25" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="J25" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
     </row>
     <row r="26" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
@@ -6459,30 +6965,30 @@
       <c r="D26" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="I26" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="J26" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
     </row>
     <row r="27" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
@@ -6497,24 +7003,24 @@
       <c r="D27" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8" t="s">
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="J27" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
     </row>
     <row r="28" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
@@ -6529,24 +7035,24 @@
       <c r="D28" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8" t="s">
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="I28" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="J28" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
     </row>
     <row r="29" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
@@ -6561,22 +7067,22 @@
       <c r="D29" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8" t="s">
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="J29" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
     </row>
     <row r="30" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
@@ -6591,20 +7097,20 @@
       <c r="D30" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8" t="s">
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
     </row>
     <row r="31" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
@@ -6619,20 +7125,20 @@
       <c r="D31" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8" t="s">
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
     </row>
     <row r="32" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
@@ -6647,30 +7153,30 @@
       <c r="D32" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I32" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="J32" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-      <c r="P32" s="8"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
     </row>
     <row r="33" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
@@ -6685,20 +7191,20 @@
       <c r="D33" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8" t="s">
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
     </row>
     <row r="34" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
@@ -6713,18 +7219,18 @@
       <c r="D34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-      <c r="P34" s="8"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
     </row>
     <row r="35" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
@@ -6739,18 +7245,18 @@
       <c r="D35" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8"/>
-      <c r="P35" s="8"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
     </row>
     <row r="36" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
@@ -6765,18 +7271,18 @@
       <c r="D36" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="8"/>
-      <c r="P36" s="8"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
     </row>
     <row r="37" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
@@ -6791,30 +7297,30 @@
       <c r="D37" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F37" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="G37" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="I37" s="8" t="s">
+      <c r="I37" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="J37" s="8" t="s">
+      <c r="J37" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-      <c r="P37" s="8"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
     </row>
     <row r="38" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
@@ -6829,30 +7335,30 @@
       <c r="D38" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="F38" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="I38" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="J38" s="8" t="s">
+      <c r="J38" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="8"/>
-      <c r="P38" s="8"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
     </row>
     <row r="39" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
@@ -6867,18 +7373,18 @@
       <c r="D39" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="8"/>
-      <c r="P39" s="8"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="6"/>
     </row>
     <row r="40" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
@@ -6893,30 +7399,30 @@
       <c r="D40" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="G40" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="I40" s="8" t="s">
+      <c r="I40" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="J40" s="8" t="s">
+      <c r="J40" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="K40" s="8"/>
-      <c r="L40" s="8"/>
-      <c r="M40" s="8"/>
-      <c r="N40" s="8"/>
-      <c r="O40" s="8"/>
-      <c r="P40" s="8"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
     </row>
     <row r="41" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
@@ -6931,26 +7437,26 @@
       <c r="D41" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8" t="s">
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="I41" s="8" t="s">
+      <c r="I41" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="J41" s="8" t="s">
+      <c r="J41" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8"/>
-      <c r="O41" s="8"/>
-      <c r="P41" s="8"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
     </row>
     <row r="42" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
@@ -6965,26 +7471,26 @@
       <c r="D42" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8" t="s">
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="H42" s="8" t="s">
+      <c r="H42" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="I42" s="8" t="s">
+      <c r="I42" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="J42" s="8" t="s">
+      <c r="J42" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
-      <c r="O42" s="8"/>
-      <c r="P42" s="8"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
     </row>
     <row r="43" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
@@ -6999,30 +7505,30 @@
       <c r="D43" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="G43" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="I43" s="8" t="s">
+      <c r="I43" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="J43" s="8" t="s">
+      <c r="J43" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="8"/>
-      <c r="N43" s="8"/>
-      <c r="O43" s="8"/>
-      <c r="P43" s="8"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="6"/>
     </row>
     <row r="44" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
@@ -7037,18 +7543,18 @@
       <c r="D44" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
-      <c r="L44" s="8"/>
-      <c r="M44" s="8"/>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
-      <c r="P44" s="8"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
     </row>
     <row r="45" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
@@ -7063,30 +7569,30 @@
       <c r="D45" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="F45" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="G45" s="8" t="s">
+      <c r="G45" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="H45" s="8" t="s">
+      <c r="H45" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="I45" s="8" t="s">
+      <c r="I45" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="J45" s="8" t="s">
+      <c r="J45" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8"/>
-      <c r="O45" s="8"/>
-      <c r="P45" s="8"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
+      <c r="P45" s="6"/>
     </row>
     <row r="46" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
@@ -7101,30 +7607,30 @@
       <c r="D46" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G46" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="H46" s="8" t="s">
+      <c r="H46" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="I46" s="8" t="s">
+      <c r="I46" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="J46" s="8" t="s">
+      <c r="J46" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="K46" s="8"/>
-      <c r="L46" s="8"/>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8"/>
-      <c r="O46" s="8"/>
-      <c r="P46" s="8"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
+      <c r="P46" s="6"/>
     </row>
     <row r="47" spans="1:16" ht="80" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
@@ -7139,30 +7645,30 @@
       <c r="D47" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="G47" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="H47" s="8" t="s">
+      <c r="H47" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="I47" s="8" t="s">
+      <c r="I47" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="J47" s="8" t="s">
+      <c r="J47" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8"/>
-      <c r="N47" s="8"/>
-      <c r="O47" s="8"/>
-      <c r="P47" s="8"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="P47" s="6"/>
     </row>
     <row r="48" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
@@ -7177,30 +7683,30 @@
       <c r="D48" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="F48" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="G48" s="8" t="s">
+      <c r="G48" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="H48" s="8" t="s">
+      <c r="H48" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="I48" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="J48" s="8" t="s">
+      <c r="J48" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="8"/>
-      <c r="N48" s="8"/>
-      <c r="O48" s="8"/>
-      <c r="P48" s="8"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="6"/>
     </row>
     <row r="49" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
@@ -7215,30 +7721,30 @@
       <c r="D49" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="F49" s="8" t="s">
+      <c r="F49" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="G49" s="8" t="s">
+      <c r="G49" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="H49" s="8" t="s">
+      <c r="H49" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="I49" s="8" t="s">
+      <c r="I49" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="J49" s="8" t="s">
+      <c r="J49" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="8"/>
-      <c r="N49" s="8"/>
-      <c r="O49" s="8"/>
-      <c r="P49" s="8"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
+      <c r="P49" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7266,7 +7772,7 @@
       <c r="A2" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>440</v>
       </c>
     </row>
@@ -7274,7 +7780,7 @@
       <c r="A3" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>442</v>
       </c>
     </row>
@@ -7282,7 +7788,7 @@
       <c r="A4" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>444</v>
       </c>
     </row>
@@ -7290,7 +7796,7 @@
       <c r="A5" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>446</v>
       </c>
     </row>
@@ -7298,7 +7804,7 @@
       <c r="A6" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>448</v>
       </c>
     </row>
@@ -7306,7 +7812,7 @@
       <c r="A7" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>450</v>
       </c>
     </row>
@@ -7314,37 +7820,37 @@
       <c r="A8" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="B8" s="8"/>
+      <c r="B8" s="6"/>
     </row>
     <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="B9" s="8"/>
+      <c r="B9" s="6"/>
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="B10" s="8"/>
+      <c r="B10" s="6"/>
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="B11" s="8"/>
+      <c r="B11" s="6"/>
     </row>
     <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="B12" s="8"/>
+      <c r="B12" s="6"/>
     </row>
     <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="B13" s="8"/>
+      <c r="B13" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7411,51 +7917,51 @@
       <c r="B2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!G$2:G$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>8.300000000000006</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!H$2:H$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>16.700000000000003</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!I$2:I$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>25.000000000000007</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!J$2:J$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>33.300000000000011</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!K$2:K$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>41.700000000000024</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!L$2:L$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>50.000000000000014</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!M$2:M$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>58.300000000000004</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!N$2:N$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>66.700000000000045</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!O$2:O$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>75.000000000000028</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!P$2:P$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>83.300000000000054</v>
       </c>
-      <c r="M2" s="14">
+      <c r="M2" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!Q$2:Q$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>91.700000000000031</v>
       </c>
-      <c r="N2" s="14">
+      <c r="N2" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!R$2:R$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B2)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>100.00000000000003</v>
       </c>
@@ -7467,51 +7973,51 @@
       <c r="B3" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!G$2:G$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>8.3000000000000096</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!H$2:H$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>16.700000000000006</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!I$2:I$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>25.000000000000014</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!J$2:J$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>33.299999999999997</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!K$2:K$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>41.700000000000031</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!L$2:L$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>50.000000000000028</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!M$2:M$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>58.300000000000047</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!N$2:N$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>66.700000000000031</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!O$2:O$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>75.000000000000043</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!P$2:P$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>83.300000000000097</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!Q$2:Q$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>91.700000000000031</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!R$2:R$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B3)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>100.00000000000006</v>
       </c>
@@ -7523,51 +8029,51 @@
       <c r="B4" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!G$2:G$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>8.3000000000000025</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!H$2:H$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>16.699999999999996</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!I$2:I$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>25</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!J$2:J$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>33.299999999999997</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!K$2:K$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>41.699999999999996</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!L$2:L$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>50</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!M$2:M$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>58.29999999999999</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!N$2:N$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>66.7</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!O$2:O$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>75</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!P$2:P$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>83.3</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!Q$2:Q$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>91.7</v>
       </c>
-      <c r="N4" s="14">
+      <c r="N4" s="10">
         <f>IFERROR(SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!R$2:R$49))/SUMPRODUCT((บันทึกผล!$B$2:$B$49=$B4)*บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>100</v>
       </c>
@@ -7579,51 +8085,51 @@
       <c r="B5" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="10">
         <f>IFERROR(SUMPRODUCT(บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!G$2:G$49))/SUMPRODUCT(บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>8.3000000000000096</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="10">
         <f>IFERROR(SUMPRODUCT(บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!H$2:H$49))/SUMPRODUCT(บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>16.700000000000028</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="10">
         <f>IFERROR(SUMPRODUCT(บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!I$2:I$49))/SUMPRODUCT(บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>25.000000000000018</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="10">
         <f>IFERROR(SUMPRODUCT(บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!J$2:J$49))/SUMPRODUCT(บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>33.300000000000033</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="10">
         <f>IFERROR(SUMPRODUCT(บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!K$2:K$49))/SUMPRODUCT(บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>41.700000000000017</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="10">
         <f>IFERROR(SUMPRODUCT(บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!L$2:L$49))/SUMPRODUCT(บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>50.000000000000036</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="10">
         <f>IFERROR(SUMPRODUCT(บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!M$2:M$49))/SUMPRODUCT(บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>58.300000000000068</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="10">
         <f>IFERROR(SUMPRODUCT(บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!N$2:N$49))/SUMPRODUCT(บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>66.700000000000017</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="10">
         <f>IFERROR(SUMPRODUCT(บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!O$2:O$49))/SUMPRODUCT(บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>75.000000000000057</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="10">
         <f>IFERROR(SUMPRODUCT(บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!P$2:P$49))/SUMPRODUCT(บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>83.300000000000097</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="10">
         <f>IFERROR(SUMPRODUCT(บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!Q$2:Q$49))/SUMPRODUCT(บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>91.700000000000074</v>
       </c>
-      <c r="N5" s="14">
+      <c r="N5" s="10">
         <f>IFERROR(SUMPRODUCT(บันทึกผล!$AH$2:$AH$49*N(บันทึกผล!R$2:R$49))/SUMPRODUCT(บันทึกผล!$AH$2:$AH$49),"")</f>
         <v>100.00000000000007</v>
       </c>

--- a/บันทึกผลการดำเนินงาน_RM_2569.xlsx
+++ b/บันทึกผลการดำเนินงาน_RM_2569.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devill/1_กฟน./2569/Dashborad_RM/rm-dashboard-2569/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2507517\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA1F7A3-1FE1-2445-9800-87AB5E9E54CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F16EB43-7F9F-442F-8B3D-24B1DDA7A9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="บันทึกผล" sheetId="1" r:id="rId1"/>
@@ -2091,43 +2091,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="RMEntry" displayName="RMEntry" ref="A1:AH49" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="RMEntry" displayName="RMEntry" ref="A1:AH49" dataDxfId="34">
   <autoFilter ref="A1:AH49" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="34">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="รหัสกิจกรรม" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="แผนหลัก" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="แผนงานย่อย" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="รหัส" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="ชื่อกิจกรรม" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ผู้รับผิดชอบ" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="เป้า ม.ค." dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="เป้า ก.พ." dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="เป้า มี.ค." dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="เป้า เม.ย." dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="เป้า พ.ค." dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="เป้า มิ.ย." dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="เป้า ก.ค." dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="เป้า ส.ค." dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="เป้า ก.ย." dataDxfId="20"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="เป้า ต.ค." dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="เป้า พ.ย." dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="เป้า ธ.ค." dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="ผล ม.ค." dataDxfId="16"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="ผล ก.พ." dataDxfId="15"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="ผล มี.ค." dataDxfId="14"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="ผล เม.ย." dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="ผล พ.ค." dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="ผล มิ.ย." dataDxfId="11"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="ผล ก.ค." dataDxfId="10"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="ผล ส.ค." dataDxfId="9"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="ผล ก.ย." dataDxfId="8"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="ผล ต.ค." dataDxfId="7"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="ผล พ.ย." dataDxfId="6"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="ผล ธ.ค." dataDxfId="5"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="รายละเอียดการดำเนินการ (ล่าสุด)" dataDxfId="4"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="ปัญหาอุปสรรค" dataDxfId="3"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="ผู้รายงาน" dataDxfId="2"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="ถ่วงน้ำหนัก(%)" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="รหัสกิจกรรม" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="แผนหลัก" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="แผนงานย่อย" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="รหัส" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="ชื่อกิจกรรม" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ผู้รับผิดชอบ" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="เป้า ม.ค." dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="เป้า ก.พ." dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="เป้า มี.ค." dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="เป้า เม.ย." dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="เป้า พ.ค." dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="เป้า มิ.ย." dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="เป้า ก.ค." dataDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="เป้า ส.ค." dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="เป้า ก.ย." dataDxfId="19"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="เป้า ต.ค." dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="เป้า พ.ย." dataDxfId="17"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="เป้า ธ.ค." dataDxfId="16"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="ผล ม.ค." dataDxfId="15"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="ผล ก.พ." dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="ผล มี.ค." dataDxfId="13"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="ผล เม.ย." dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="ผล พ.ค." dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="ผล มิ.ย." dataDxfId="10"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="ผล ก.ค." dataDxfId="9"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="ผล ส.ค." dataDxfId="8"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="ผล ก.ย." dataDxfId="7"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="ผล ต.ค." dataDxfId="6"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="ผล พ.ย." dataDxfId="5"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="ผล ธ.ค." dataDxfId="4"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="รายละเอียดการดำเนินการ (ล่าสุด)" dataDxfId="3"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="ปัญหาอุปสรรค" dataDxfId="2"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="ผู้รายงาน" dataDxfId="1"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="ถ่วงน้ำหนัก(%)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2419,7 +2419,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
@@ -2434,7 +2434,7 @@
     <col min="34" max="34" width="14" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>34</v>
       </c>
@@ -2591,13 +2591,27 @@
       <c r="R2" s="13">
         <v>100</v>
       </c>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14"/>
+      <c r="S2" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T2" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="U2" s="14">
+        <v>25</v>
+      </c>
+      <c r="V2" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W2" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X2" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y2" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z2" s="14"/>
       <c r="AA2" s="14"/>
       <c r="AB2" s="14"/>
@@ -2614,7 +2628,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>40</v>
       </c>
@@ -2667,13 +2681,27 @@
       <c r="R3" s="13">
         <v>100</v>
       </c>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
+      <c r="S3" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T3" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="U3" s="14">
+        <v>25</v>
+      </c>
+      <c r="V3" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W3" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X3" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y3" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z3" s="14"/>
       <c r="AA3" s="14"/>
       <c r="AB3" s="14"/>
@@ -2690,7 +2718,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="4" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>44</v>
       </c>
@@ -2743,13 +2771,27 @@
       <c r="R4" s="13">
         <v>100</v>
       </c>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="14"/>
+      <c r="S4" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T4" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="U4" s="14">
+        <v>25</v>
+      </c>
+      <c r="V4" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W4" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X4" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y4" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z4" s="14"/>
       <c r="AA4" s="14"/>
       <c r="AB4" s="14"/>
@@ -2766,7 +2808,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
         <v>48</v>
       </c>
@@ -2816,10 +2858,18 @@
       <c r="S5" s="14"/>
       <c r="T5" s="14"/>
       <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14"/>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="14"/>
+      <c r="V5" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W5" s="14">
+        <v>66.7</v>
+      </c>
+      <c r="X5" s="14">
+        <v>100</v>
+      </c>
+      <c r="Y5" s="14">
+        <v>100</v>
+      </c>
       <c r="Z5" s="14"/>
       <c r="AA5" s="14"/>
       <c r="AB5" s="14"/>
@@ -2836,7 +2886,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
         <v>52</v>
       </c>
@@ -2883,7 +2933,9 @@
       <c r="V6" s="14"/>
       <c r="W6" s="14"/>
       <c r="X6" s="14"/>
-      <c r="Y6" s="14"/>
+      <c r="Y6" s="14">
+        <v>20</v>
+      </c>
       <c r="Z6" s="14"/>
       <c r="AA6" s="14"/>
       <c r="AB6" s="14"/>
@@ -2898,7 +2950,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>55</v>
       </c>
@@ -2954,7 +3006,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>58</v>
       </c>
@@ -3010,7 +3062,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>61</v>
       </c>
@@ -3066,7 +3118,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>64</v>
       </c>
@@ -3119,13 +3171,27 @@
       <c r="R10" s="13">
         <v>100</v>
       </c>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="14"/>
-      <c r="X10" s="14"/>
-      <c r="Y10" s="14"/>
+      <c r="S10" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T10" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="U10" s="14">
+        <v>25</v>
+      </c>
+      <c r="V10" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W10" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X10" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y10" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z10" s="14"/>
       <c r="AA10" s="14"/>
       <c r="AB10" s="14"/>
@@ -3142,7 +3208,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>68</v>
       </c>
@@ -3192,10 +3258,18 @@
       <c r="S11" s="14"/>
       <c r="T11" s="14"/>
       <c r="U11" s="14"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14"/>
+      <c r="V11" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="W11" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="X11" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y11" s="14">
+        <v>66.7</v>
+      </c>
       <c r="Z11" s="14"/>
       <c r="AA11" s="14"/>
       <c r="AB11" s="14"/>
@@ -3212,7 +3286,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>72</v>
       </c>
@@ -3259,7 +3333,9 @@
       <c r="V12" s="14"/>
       <c r="W12" s="14"/>
       <c r="X12" s="14"/>
-      <c r="Y12" s="14"/>
+      <c r="Y12" s="14">
+        <v>33.299999999999997</v>
+      </c>
       <c r="Z12" s="14"/>
       <c r="AA12" s="14"/>
       <c r="AB12" s="14"/>
@@ -3274,7 +3350,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>75</v>
       </c>
@@ -3327,13 +3403,27 @@
       <c r="R13" s="13">
         <v>100</v>
       </c>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14"/>
+      <c r="S13" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T13" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="U13" s="14">
+        <v>25</v>
+      </c>
+      <c r="V13" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W13" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X13" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y13" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z13" s="14"/>
       <c r="AA13" s="14"/>
       <c r="AB13" s="14"/>
@@ -3350,7 +3440,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>79</v>
       </c>
@@ -3403,13 +3493,27 @@
       <c r="R14" s="13">
         <v>100</v>
       </c>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14"/>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="14"/>
+      <c r="S14" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T14" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="U14" s="14">
+        <v>25</v>
+      </c>
+      <c r="V14" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W14" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X14" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y14" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z14" s="14"/>
       <c r="AA14" s="14"/>
       <c r="AB14" s="14"/>
@@ -3426,7 +3530,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>83</v>
       </c>
@@ -3479,13 +3583,27 @@
       <c r="R15" s="13">
         <v>100</v>
       </c>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14"/>
+      <c r="S15" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T15" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="U15" s="14">
+        <v>25</v>
+      </c>
+      <c r="V15" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W15" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X15" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y15" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z15" s="14"/>
       <c r="AA15" s="14"/>
       <c r="AB15" s="14"/>
@@ -3502,7 +3620,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>87</v>
       </c>
@@ -3551,7 +3669,9 @@
       <c r="V16" s="14"/>
       <c r="W16" s="14"/>
       <c r="X16" s="14"/>
-      <c r="Y16" s="14"/>
+      <c r="Y16" s="14">
+        <v>10</v>
+      </c>
       <c r="Z16" s="14"/>
       <c r="AA16" s="14"/>
       <c r="AB16" s="14"/>
@@ -3566,7 +3686,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="17" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>94</v>
       </c>
@@ -3617,9 +3737,15 @@
       <c r="T17" s="14"/>
       <c r="U17" s="14"/>
       <c r="V17" s="14"/>
-      <c r="W17" s="14"/>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="14"/>
+      <c r="W17" s="14">
+        <v>12.5</v>
+      </c>
+      <c r="X17" s="14">
+        <v>25</v>
+      </c>
+      <c r="Y17" s="14">
+        <v>37.5</v>
+      </c>
       <c r="Z17" s="14"/>
       <c r="AA17" s="14"/>
       <c r="AB17" s="14"/>
@@ -3636,7 +3762,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="18" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
         <v>98</v>
       </c>
@@ -3686,8 +3812,12 @@
       <c r="U18" s="14"/>
       <c r="V18" s="14"/>
       <c r="W18" s="14"/>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="14"/>
+      <c r="X18" s="14">
+        <v>12.5</v>
+      </c>
+      <c r="Y18" s="14">
+        <v>25</v>
+      </c>
       <c r="Z18" s="14"/>
       <c r="AA18" s="14"/>
       <c r="AB18" s="14"/>
@@ -3704,7 +3834,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="19" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
         <v>102</v>
       </c>
@@ -3759,13 +3889,27 @@
       <c r="R19" s="13">
         <v>100</v>
       </c>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="14"/>
+      <c r="S19" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="T19" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="U19" s="14">
+        <v>50</v>
+      </c>
+      <c r="V19" s="14">
+        <v>66.7</v>
+      </c>
+      <c r="W19" s="14">
+        <v>83.3</v>
+      </c>
+      <c r="X19" s="14">
+        <v>100</v>
+      </c>
+      <c r="Y19" s="14">
+        <v>100</v>
+      </c>
       <c r="Z19" s="14"/>
       <c r="AA19" s="14"/>
       <c r="AB19" s="14"/>
@@ -3782,7 +3926,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="20" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
         <v>109</v>
       </c>
@@ -3837,13 +3981,27 @@
       <c r="R20" s="13">
         <v>100</v>
       </c>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
+      <c r="S20" s="14">
+        <v>3.8</v>
+      </c>
+      <c r="T20" s="14">
+        <v>7.7</v>
+      </c>
+      <c r="U20" s="14">
+        <v>11.5</v>
+      </c>
+      <c r="V20" s="14">
+        <v>19.2</v>
+      </c>
+      <c r="W20" s="14">
+        <v>26.9</v>
+      </c>
+      <c r="X20" s="14">
+        <v>34.6</v>
+      </c>
+      <c r="Y20" s="14">
+        <v>42.3</v>
+      </c>
       <c r="Z20" s="14"/>
       <c r="AA20" s="14"/>
       <c r="AB20" s="14"/>
@@ -3860,7 +4018,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="21" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>113</v>
       </c>
@@ -3915,13 +4073,27 @@
       <c r="R21" s="13">
         <v>100</v>
       </c>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
+      <c r="S21" s="14">
+        <v>11.1</v>
+      </c>
+      <c r="T21" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="U21" s="14">
+        <v>44.4</v>
+      </c>
+      <c r="V21" s="14">
+        <v>55.6</v>
+      </c>
+      <c r="W21" s="14">
+        <v>61.1</v>
+      </c>
+      <c r="X21" s="14">
+        <v>66.7</v>
+      </c>
+      <c r="Y21" s="14">
+        <v>72.2</v>
+      </c>
       <c r="Z21" s="14"/>
       <c r="AA21" s="14"/>
       <c r="AB21" s="14"/>
@@ -3938,7 +4110,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="22" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
         <v>117</v>
       </c>
@@ -3987,7 +4159,9 @@
       <c r="V22" s="14"/>
       <c r="W22" s="14"/>
       <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
+      <c r="Y22" s="14">
+        <v>14.3</v>
+      </c>
       <c r="Z22" s="14"/>
       <c r="AA22" s="14"/>
       <c r="AB22" s="14"/>
@@ -4002,7 +4176,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="23" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
         <v>120</v>
       </c>
@@ -4057,13 +4231,27 @@
       <c r="R23" s="13">
         <v>100</v>
       </c>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="14"/>
+      <c r="S23" s="14">
+        <v>12.5</v>
+      </c>
+      <c r="T23" s="14">
+        <v>37.5</v>
+      </c>
+      <c r="U23" s="14">
+        <v>50</v>
+      </c>
+      <c r="V23" s="14">
+        <v>75</v>
+      </c>
+      <c r="W23" s="14">
+        <v>100</v>
+      </c>
+      <c r="X23" s="14">
+        <v>100</v>
+      </c>
+      <c r="Y23" s="14">
+        <v>100</v>
+      </c>
       <c r="Z23" s="14"/>
       <c r="AA23" s="14"/>
       <c r="AB23" s="14"/>
@@ -4080,7 +4268,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="24" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
         <v>124</v>
       </c>
@@ -4135,13 +4323,27 @@
       <c r="R24" s="13">
         <v>100</v>
       </c>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14"/>
+      <c r="S24" s="14">
+        <v>5.9</v>
+      </c>
+      <c r="T24" s="14">
+        <v>11.8</v>
+      </c>
+      <c r="U24" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="V24" s="14">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="W24" s="14">
+        <v>41.2</v>
+      </c>
+      <c r="X24" s="14">
+        <v>47.1</v>
+      </c>
+      <c r="Y24" s="14">
+        <v>52.9</v>
+      </c>
       <c r="Z24" s="14"/>
       <c r="AA24" s="14"/>
       <c r="AB24" s="14"/>
@@ -4158,7 +4360,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="25" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>129</v>
       </c>
@@ -4213,13 +4415,27 @@
       <c r="R25" s="13">
         <v>100</v>
       </c>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-      <c r="X25" s="14"/>
-      <c r="Y25" s="14"/>
+      <c r="S25" s="14">
+        <v>6.7</v>
+      </c>
+      <c r="T25" s="14">
+        <v>13.3</v>
+      </c>
+      <c r="U25" s="14">
+        <v>26.7</v>
+      </c>
+      <c r="V25" s="14">
+        <v>46.7</v>
+      </c>
+      <c r="W25" s="14">
+        <v>66.7</v>
+      </c>
+      <c r="X25" s="14">
+        <v>86.7</v>
+      </c>
+      <c r="Y25" s="14">
+        <v>100</v>
+      </c>
       <c r="Z25" s="14"/>
       <c r="AA25" s="14"/>
       <c r="AB25" s="14"/>
@@ -4238,7 +4454,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="26" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
         <v>137</v>
       </c>
@@ -4293,13 +4509,27 @@
       <c r="R26" s="13">
         <v>100</v>
       </c>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
-      <c r="X26" s="14"/>
-      <c r="Y26" s="14"/>
+      <c r="S26" s="14">
+        <v>6.7</v>
+      </c>
+      <c r="T26" s="14">
+        <v>20</v>
+      </c>
+      <c r="U26" s="14">
+        <v>40</v>
+      </c>
+      <c r="V26" s="14">
+        <v>46.7</v>
+      </c>
+      <c r="W26" s="14">
+        <v>53.3</v>
+      </c>
+      <c r="X26" s="14">
+        <v>60</v>
+      </c>
+      <c r="Y26" s="14">
+        <v>66.7</v>
+      </c>
       <c r="Z26" s="14"/>
       <c r="AA26" s="14"/>
       <c r="AB26" s="14"/>
@@ -4316,7 +4546,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="27" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
         <v>141</v>
       </c>
@@ -4368,10 +4598,18 @@
       <c r="S27" s="14"/>
       <c r="T27" s="14"/>
       <c r="U27" s="14"/>
-      <c r="V27" s="14"/>
-      <c r="W27" s="14"/>
-      <c r="X27" s="14"/>
-      <c r="Y27" s="14"/>
+      <c r="V27" s="14">
+        <v>25</v>
+      </c>
+      <c r="W27" s="14">
+        <v>50</v>
+      </c>
+      <c r="X27" s="14">
+        <v>75</v>
+      </c>
+      <c r="Y27" s="14">
+        <v>100</v>
+      </c>
       <c r="Z27" s="14"/>
       <c r="AA27" s="14"/>
       <c r="AB27" s="14"/>
@@ -4388,7 +4626,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="28" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
         <v>145</v>
       </c>
@@ -4440,10 +4678,18 @@
       <c r="S28" s="14"/>
       <c r="T28" s="14"/>
       <c r="U28" s="14"/>
-      <c r="V28" s="14"/>
-      <c r="W28" s="14"/>
-      <c r="X28" s="14"/>
-      <c r="Y28" s="14"/>
+      <c r="V28" s="14">
+        <v>25</v>
+      </c>
+      <c r="W28" s="14">
+        <v>50</v>
+      </c>
+      <c r="X28" s="14">
+        <v>75</v>
+      </c>
+      <c r="Y28" s="14">
+        <v>100</v>
+      </c>
       <c r="Z28" s="14"/>
       <c r="AA28" s="14"/>
       <c r="AB28" s="14"/>
@@ -4460,7 +4706,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="29" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
         <v>149</v>
       </c>
@@ -4511,9 +4757,15 @@
       <c r="T29" s="14"/>
       <c r="U29" s="14"/>
       <c r="V29" s="14"/>
-      <c r="W29" s="14"/>
-      <c r="X29" s="14"/>
-      <c r="Y29" s="14"/>
+      <c r="W29" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="X29" s="14">
+        <v>66.7</v>
+      </c>
+      <c r="Y29" s="14">
+        <v>100</v>
+      </c>
       <c r="Z29" s="14"/>
       <c r="AA29" s="14"/>
       <c r="AB29" s="14"/>
@@ -4530,7 +4782,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="30" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
         <v>153</v>
       </c>
@@ -4580,8 +4832,12 @@
       <c r="U30" s="14"/>
       <c r="V30" s="14"/>
       <c r="W30" s="14"/>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="14"/>
+      <c r="X30" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y30" s="14">
+        <v>100</v>
+      </c>
       <c r="Z30" s="14"/>
       <c r="AA30" s="14"/>
       <c r="AB30" s="14"/>
@@ -4598,7 +4854,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="31" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
         <v>157</v>
       </c>
@@ -4648,8 +4904,12 @@
       <c r="U31" s="14"/>
       <c r="V31" s="14"/>
       <c r="W31" s="14"/>
-      <c r="X31" s="14"/>
-      <c r="Y31" s="14"/>
+      <c r="X31" s="14">
+        <v>40</v>
+      </c>
+      <c r="Y31" s="14">
+        <v>60</v>
+      </c>
       <c r="Z31" s="14"/>
       <c r="AA31" s="14"/>
       <c r="AB31" s="14"/>
@@ -4668,7 +4928,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="32" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
         <v>161</v>
       </c>
@@ -4723,13 +4983,27 @@
       <c r="R32" s="13">
         <v>100</v>
       </c>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
-      <c r="V32" s="14"/>
-      <c r="W32" s="14"/>
-      <c r="X32" s="14"/>
-      <c r="Y32" s="14"/>
+      <c r="S32" s="14">
+        <v>5.3</v>
+      </c>
+      <c r="T32" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="U32" s="14">
+        <v>15.8</v>
+      </c>
+      <c r="V32" s="14">
+        <v>21.1</v>
+      </c>
+      <c r="W32" s="14">
+        <v>31.6</v>
+      </c>
+      <c r="X32" s="14">
+        <v>47.4</v>
+      </c>
+      <c r="Y32" s="14">
+        <v>63.2</v>
+      </c>
       <c r="Z32" s="14"/>
       <c r="AA32" s="14"/>
       <c r="AB32" s="14"/>
@@ -4746,7 +5020,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="33" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
         <v>167</v>
       </c>
@@ -4796,8 +5070,12 @@
       <c r="U33" s="14"/>
       <c r="V33" s="14"/>
       <c r="W33" s="14"/>
-      <c r="X33" s="14"/>
-      <c r="Y33" s="14"/>
+      <c r="X33" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="Y33" s="14">
+        <v>66.7</v>
+      </c>
       <c r="Z33" s="14"/>
       <c r="AA33" s="14"/>
       <c r="AB33" s="14"/>
@@ -4814,7 +5092,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="34" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
         <v>171</v>
       </c>
@@ -4863,7 +5141,9 @@
       <c r="V34" s="14"/>
       <c r="W34" s="14"/>
       <c r="X34" s="14"/>
-      <c r="Y34" s="14"/>
+      <c r="Y34" s="14">
+        <v>20</v>
+      </c>
       <c r="Z34" s="14"/>
       <c r="AA34" s="14"/>
       <c r="AB34" s="14"/>
@@ -4878,7 +5158,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="35" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
         <v>174</v>
       </c>
@@ -4940,7 +5220,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="36" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
         <v>177</v>
       </c>
@@ -5002,7 +5282,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="37" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
         <v>180</v>
       </c>
@@ -5057,13 +5337,27 @@
       <c r="R37" s="13">
         <v>100</v>
       </c>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14"/>
+      <c r="S37" s="14">
+        <v>7.1</v>
+      </c>
+      <c r="T37" s="14">
+        <v>14.3</v>
+      </c>
+      <c r="U37" s="14">
+        <v>21.4</v>
+      </c>
+      <c r="V37" s="14">
+        <v>32.1</v>
+      </c>
+      <c r="W37" s="14">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="X37" s="14">
+        <v>46.4</v>
+      </c>
+      <c r="Y37" s="14">
+        <v>57.1</v>
+      </c>
       <c r="Z37" s="14"/>
       <c r="AA37" s="14"/>
       <c r="AB37" s="14"/>
@@ -5080,7 +5374,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="38" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
         <v>184</v>
       </c>
@@ -5135,13 +5429,27 @@
       <c r="R38" s="13">
         <v>100</v>
       </c>
-      <c r="S38" s="14"/>
-      <c r="T38" s="14"/>
-      <c r="U38" s="14"/>
-      <c r="V38" s="14"/>
-      <c r="W38" s="14"/>
-      <c r="X38" s="14"/>
-      <c r="Y38" s="14"/>
+      <c r="S38" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T38" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="U38" s="14">
+        <v>25</v>
+      </c>
+      <c r="V38" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W38" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X38" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y38" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z38" s="14"/>
       <c r="AA38" s="14"/>
       <c r="AB38" s="14"/>
@@ -5158,7 +5466,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="39" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
         <v>188</v>
       </c>
@@ -5216,7 +5524,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="40" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A40" s="11" t="s">
         <v>191</v>
       </c>
@@ -5271,13 +5579,27 @@
       <c r="R40" s="13">
         <v>100</v>
       </c>
-      <c r="S40" s="14"/>
-      <c r="T40" s="14"/>
-      <c r="U40" s="14"/>
-      <c r="V40" s="14"/>
-      <c r="W40" s="14"/>
-      <c r="X40" s="14"/>
-      <c r="Y40" s="14"/>
+      <c r="S40" s="14">
+        <v>6.7</v>
+      </c>
+      <c r="T40" s="14">
+        <v>13.3</v>
+      </c>
+      <c r="U40" s="14">
+        <v>26.7</v>
+      </c>
+      <c r="V40" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W40" s="14">
+        <v>46.7</v>
+      </c>
+      <c r="X40" s="14">
+        <v>53.3</v>
+      </c>
+      <c r="Y40" s="14">
+        <v>66.7</v>
+      </c>
       <c r="Z40" s="14"/>
       <c r="AA40" s="14"/>
       <c r="AB40" s="14"/>
@@ -5294,7 +5616,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="41" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A41" s="11" t="s">
         <v>196</v>
       </c>
@@ -5347,11 +5669,21 @@
       </c>
       <c r="S41" s="14"/>
       <c r="T41" s="14"/>
-      <c r="U41" s="14"/>
-      <c r="V41" s="14"/>
-      <c r="W41" s="14"/>
-      <c r="X41" s="14"/>
-      <c r="Y41" s="14"/>
+      <c r="U41" s="14">
+        <v>5</v>
+      </c>
+      <c r="V41" s="14">
+        <v>20</v>
+      </c>
+      <c r="W41" s="14">
+        <v>30</v>
+      </c>
+      <c r="X41" s="14">
+        <v>40</v>
+      </c>
+      <c r="Y41" s="14">
+        <v>50</v>
+      </c>
       <c r="Z41" s="14"/>
       <c r="AA41" s="14"/>
       <c r="AB41" s="14"/>
@@ -5368,7 +5700,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="42" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A42" s="11" t="s">
         <v>200</v>
       </c>
@@ -5421,11 +5753,21 @@
       </c>
       <c r="S42" s="14"/>
       <c r="T42" s="14"/>
-      <c r="U42" s="14"/>
-      <c r="V42" s="14"/>
-      <c r="W42" s="14"/>
-      <c r="X42" s="14"/>
-      <c r="Y42" s="14"/>
+      <c r="U42" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="V42" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W42" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X42" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y42" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z42" s="14"/>
       <c r="AA42" s="14"/>
       <c r="AB42" s="14"/>
@@ -5442,7 +5784,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="43" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
         <v>204</v>
       </c>
@@ -5497,13 +5839,27 @@
       <c r="R43" s="13">
         <v>100</v>
       </c>
-      <c r="S43" s="14"/>
-      <c r="T43" s="14"/>
-      <c r="U43" s="14"/>
-      <c r="V43" s="14"/>
-      <c r="W43" s="14"/>
-      <c r="X43" s="14"/>
-      <c r="Y43" s="14"/>
+      <c r="S43" s="14">
+        <v>3.2</v>
+      </c>
+      <c r="T43" s="14">
+        <v>12.9</v>
+      </c>
+      <c r="U43" s="14">
+        <v>22.6</v>
+      </c>
+      <c r="V43" s="14">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="W43" s="14">
+        <v>41.9</v>
+      </c>
+      <c r="X43" s="14">
+        <v>51.6</v>
+      </c>
+      <c r="Y43" s="14">
+        <v>61.3</v>
+      </c>
       <c r="Z43" s="14"/>
       <c r="AA43" s="14"/>
       <c r="AB43" s="14"/>
@@ -5520,7 +5876,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="44" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A44" s="11" t="s">
         <v>208</v>
       </c>
@@ -5578,7 +5934,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="45" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A45" s="11" t="s">
         <v>211</v>
       </c>
@@ -5631,13 +5987,27 @@
       <c r="R45" s="13">
         <v>100</v>
       </c>
-      <c r="S45" s="14"/>
-      <c r="T45" s="14"/>
-      <c r="U45" s="14"/>
-      <c r="V45" s="14"/>
-      <c r="W45" s="14"/>
-      <c r="X45" s="14"/>
-      <c r="Y45" s="14"/>
+      <c r="S45" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T45" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="U45" s="14">
+        <v>25</v>
+      </c>
+      <c r="V45" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W45" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X45" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y45" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z45" s="14"/>
       <c r="AA45" s="14"/>
       <c r="AB45" s="14"/>
@@ -5654,7 +6024,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="46" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A46" s="11" t="s">
         <v>216</v>
       </c>
@@ -5707,13 +6077,27 @@
       <c r="R46" s="13">
         <v>100</v>
       </c>
-      <c r="S46" s="14"/>
-      <c r="T46" s="14"/>
-      <c r="U46" s="14"/>
-      <c r="V46" s="14"/>
-      <c r="W46" s="14"/>
-      <c r="X46" s="14"/>
-      <c r="Y46" s="14"/>
+      <c r="S46" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T46" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="U46" s="14">
+        <v>25</v>
+      </c>
+      <c r="V46" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W46" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X46" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y46" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z46" s="14"/>
       <c r="AA46" s="14"/>
       <c r="AB46" s="14"/>
@@ -5730,7 +6114,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="47" spans="1:34" ht="110" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:34" ht="90" x14ac:dyDescent="0.35">
       <c r="A47" s="11" t="s">
         <v>220</v>
       </c>
@@ -5783,13 +6167,27 @@
       <c r="R47" s="13">
         <v>100</v>
       </c>
-      <c r="S47" s="14"/>
-      <c r="T47" s="14"/>
-      <c r="U47" s="14"/>
-      <c r="V47" s="14"/>
-      <c r="W47" s="14"/>
-      <c r="X47" s="14"/>
-      <c r="Y47" s="14"/>
+      <c r="S47" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T47" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="U47" s="14">
+        <v>25</v>
+      </c>
+      <c r="V47" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W47" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X47" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y47" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z47" s="14"/>
       <c r="AA47" s="14"/>
       <c r="AB47" s="14"/>
@@ -5808,7 +6206,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="48" spans="1:34" ht="44" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:34" ht="36" x14ac:dyDescent="0.35">
       <c r="A48" s="11" t="s">
         <v>224</v>
       </c>
@@ -5861,13 +6259,27 @@
       <c r="R48" s="13">
         <v>100</v>
       </c>
-      <c r="S48" s="14"/>
-      <c r="T48" s="14"/>
-      <c r="U48" s="14"/>
-      <c r="V48" s="14"/>
-      <c r="W48" s="14"/>
-      <c r="X48" s="14"/>
-      <c r="Y48" s="14"/>
+      <c r="S48" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T48" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="U48" s="14">
+        <v>25</v>
+      </c>
+      <c r="V48" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W48" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X48" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y48" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z48" s="14"/>
       <c r="AA48" s="14"/>
       <c r="AB48" s="14"/>
@@ -5884,7 +6296,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="49" spans="1:34" ht="66" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:34" ht="54" x14ac:dyDescent="0.35">
       <c r="A49" s="11" t="s">
         <v>228</v>
       </c>
@@ -5937,13 +6349,27 @@
       <c r="R49" s="13">
         <v>100</v>
       </c>
-      <c r="S49" s="14"/>
-      <c r="T49" s="14"/>
-      <c r="U49" s="14"/>
-      <c r="V49" s="14"/>
-      <c r="W49" s="14"/>
-      <c r="X49" s="14"/>
-      <c r="Y49" s="14"/>
+      <c r="S49" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T49" s="14">
+        <v>16.7</v>
+      </c>
+      <c r="U49" s="14">
+        <v>25</v>
+      </c>
+      <c r="V49" s="14">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="W49" s="14">
+        <v>41.7</v>
+      </c>
+      <c r="X49" s="14">
+        <v>50</v>
+      </c>
+      <c r="Y49" s="14">
+        <v>58.3</v>
+      </c>
       <c r="Z49" s="14"/>
       <c r="AA49" s="14"/>
       <c r="AB49" s="14"/>
@@ -5977,23 +6403,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="92" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>232</v>
       </c>
       <c r="B1" s="8"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="9"/>
       <c r="B2" s="8"/>
     </row>
-    <row r="3" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>233</v>
       </c>
@@ -6001,7 +6427,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>235</v>
       </c>
@@ -6009,7 +6435,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>237</v>
       </c>
@@ -6017,13 +6443,13 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="9"/>
       <c r="B6" s="8" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>240</v>
       </c>
@@ -6031,17 +6457,17 @@
         <v>241</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="9"/>
       <c r="B8" s="8"/>
     </row>
-    <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>242</v>
       </c>
       <c r="B9" s="8"/>
     </row>
-    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>243</v>
       </c>
@@ -6049,7 +6475,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>245</v>
       </c>
@@ -6057,11 +6483,11 @@
         <v>246</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="9"/>
       <c r="B12" s="8"/>
     </row>
-    <row r="13" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>247</v>
       </c>
@@ -6069,19 +6495,19 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="9"/>
       <c r="B14" s="8" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="9"/>
       <c r="B15" s="8" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
       <c r="B16" s="8" t="s">
         <v>251</v>
@@ -6095,7 +6521,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -6104,7 +6530,7 @@
     <col min="5" max="16" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6154,7 +6580,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>34</v>
       </c>
@@ -6192,7 +6618,7 @@
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
     </row>
-    <row r="3" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>40</v>
       </c>
@@ -6230,7 +6656,7 @@
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
     </row>
-    <row r="4" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>44</v>
       </c>
@@ -6268,7 +6694,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
     </row>
-    <row r="5" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>48</v>
       </c>
@@ -6300,7 +6726,7 @@
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>52</v>
       </c>
@@ -6326,7 +6752,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>55</v>
       </c>
@@ -6352,7 +6778,7 @@
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
     </row>
-    <row r="8" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>58</v>
       </c>
@@ -6378,7 +6804,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>61</v>
       </c>
@@ -6404,7 +6830,7 @@
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>64</v>
       </c>
@@ -6442,7 +6868,7 @@
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>68</v>
       </c>
@@ -6474,7 +6900,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>72</v>
       </c>
@@ -6500,7 +6926,7 @@
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>75</v>
       </c>
@@ -6538,7 +6964,7 @@
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>79</v>
       </c>
@@ -6576,7 +7002,7 @@
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>83</v>
       </c>
@@ -6614,7 +7040,7 @@
       <c r="O15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>87</v>
       </c>
@@ -6640,7 +7066,7 @@
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>94</v>
       </c>
@@ -6670,7 +7096,7 @@
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>98</v>
       </c>
@@ -6698,7 +7124,7 @@
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>102</v>
       </c>
@@ -6736,7 +7162,7 @@
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>109</v>
       </c>
@@ -6774,7 +7200,7 @@
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>113</v>
       </c>
@@ -6812,7 +7238,7 @@
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>117</v>
       </c>
@@ -6838,7 +7264,7 @@
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
     </row>
-    <row r="23" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>120</v>
       </c>
@@ -6876,7 +7302,7 @@
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
     </row>
-    <row r="24" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>124</v>
       </c>
@@ -6914,7 +7340,7 @@
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
     </row>
-    <row r="25" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>129</v>
       </c>
@@ -6952,7 +7378,7 @@
       <c r="O25" s="6"/>
       <c r="P25" s="6"/>
     </row>
-    <row r="26" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>137</v>
       </c>
@@ -6990,7 +7416,7 @@
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
     </row>
-    <row r="27" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>141</v>
       </c>
@@ -7022,7 +7448,7 @@
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>145</v>
       </c>
@@ -7054,7 +7480,7 @@
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>149</v>
       </c>
@@ -7084,7 +7510,7 @@
       <c r="O29" s="6"/>
       <c r="P29" s="6"/>
     </row>
-    <row r="30" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>153</v>
       </c>
@@ -7112,7 +7538,7 @@
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
     </row>
-    <row r="31" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>157</v>
       </c>
@@ -7140,7 +7566,7 @@
       <c r="O31" s="6"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>161</v>
       </c>
@@ -7178,7 +7604,7 @@
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
     </row>
-    <row r="33" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>167</v>
       </c>
@@ -7206,7 +7632,7 @@
       <c r="O33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>171</v>
       </c>
@@ -7232,7 +7658,7 @@
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
     </row>
-    <row r="35" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>174</v>
       </c>
@@ -7258,7 +7684,7 @@
       <c r="O35" s="6"/>
       <c r="P35" s="6"/>
     </row>
-    <row r="36" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>177</v>
       </c>
@@ -7284,7 +7710,7 @@
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
     </row>
-    <row r="37" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>180</v>
       </c>
@@ -7322,7 +7748,7 @@
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
     </row>
-    <row r="38" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>184</v>
       </c>
@@ -7360,7 +7786,7 @@
       <c r="O38" s="6"/>
       <c r="P38" s="6"/>
     </row>
-    <row r="39" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>188</v>
       </c>
@@ -7386,7 +7812,7 @@
       <c r="O39" s="6"/>
       <c r="P39" s="6"/>
     </row>
-    <row r="40" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>191</v>
       </c>
@@ -7424,7 +7850,7 @@
       <c r="O40" s="6"/>
       <c r="P40" s="6"/>
     </row>
-    <row r="41" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>196</v>
       </c>
@@ -7458,7 +7884,7 @@
       <c r="O41" s="6"/>
       <c r="P41" s="6"/>
     </row>
-    <row r="42" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>200</v>
       </c>
@@ -7492,7 +7918,7 @@
       <c r="O42" s="6"/>
       <c r="P42" s="6"/>
     </row>
-    <row r="43" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>204</v>
       </c>
@@ -7530,7 +7956,7 @@
       <c r="O43" s="6"/>
       <c r="P43" s="6"/>
     </row>
-    <row r="44" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>208</v>
       </c>
@@ -7556,7 +7982,7 @@
       <c r="O44" s="6"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>211</v>
       </c>
@@ -7594,7 +8020,7 @@
       <c r="O45" s="6"/>
       <c r="P45" s="6"/>
     </row>
-    <row r="46" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>216</v>
       </c>
@@ -7632,7 +8058,7 @@
       <c r="O46" s="6"/>
       <c r="P46" s="6"/>
     </row>
-    <row r="47" spans="1:16" ht="80" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>220</v>
       </c>
@@ -7670,7 +8096,7 @@
       <c r="O47" s="6"/>
       <c r="P47" s="6"/>
     </row>
-    <row r="48" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>224</v>
       </c>
@@ -7708,7 +8134,7 @@
       <c r="O48" s="6"/>
       <c r="P48" s="6"/>
     </row>
-    <row r="49" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>228</v>
       </c>
@@ -7754,13 +8180,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>437</v>
       </c>
@@ -7768,7 +8194,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>439</v>
       </c>
@@ -7776,7 +8202,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>441</v>
       </c>
@@ -7784,7 +8210,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>443</v>
       </c>
@@ -7792,7 +8218,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>445</v>
       </c>
@@ -7800,7 +8226,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>447</v>
       </c>
@@ -7808,7 +8234,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>449</v>
       </c>
@@ -7816,37 +8242,37 @@
         <v>450</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>451</v>
       </c>
       <c r="B8" s="6"/>
     </row>
-    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>452</v>
       </c>
       <c r="B9" s="6"/>
     </row>
-    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>453</v>
       </c>
       <c r="B10" s="6"/>
     </row>
-    <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>454</v>
       </c>
       <c r="B11" s="6"/>
     </row>
-    <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>455</v>
       </c>
       <c r="B12" s="6"/>
     </row>
-    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>456</v>
       </c>
@@ -7860,13 +8286,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="14" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -7910,7 +8336,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="48" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>458</v>
       </c>
@@ -7966,7 +8392,7 @@
         <v>100.00000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>459</v>
       </c>
@@ -8022,7 +8448,7 @@
         <v>100.00000000000006</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>460</v>
       </c>
@@ -8078,7 +8504,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>461</v>
       </c>
